--- a/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
@@ -1085,7 +1085,11 @@
           <t>SP-CAM</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>Cam sensor signal</t>
@@ -2265,7 +2269,11 @@
           <t>SP-GND-ECU</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>ECU power ground</t>
@@ -2855,7 +2863,11 @@
           <t>SP-GND-ECU</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>ECU power ground</t>
@@ -3231,7 +3243,11 @@
           <t>SP-TACH</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>Engine speed (tacho)</t>
@@ -4092,7 +4108,11 @@
           <t>SP-AC-SG</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>Ambient sensor return</t>
@@ -4294,7 +4314,11 @@
           <t>POWER-NEG-BAR</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>A/C coolant-OK ground</t>
@@ -4496,7 +4520,11 @@
           <t>SP-AC-PSW</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>A/C pressure sw out</t>
@@ -4601,7 +4629,11 @@
           <t>SP-AC-PSW</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>A/C pressure sw out</t>
@@ -6895,7 +6927,11 @@
           <t>SP-SW12</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
           <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse</t>
@@ -6988,7 +7024,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>screen</t>
+          <t>Screen</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6996,7 +7032,11 @@
           <t>SP-SHIELD-A-APS</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr">
         <is>
           <t>Pedal 1 cable shield</t>
@@ -7089,7 +7129,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>screen</t>
+          <t>Screen</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -7097,7 +7137,11 @@
           <t>SP-SHIELD-A-APS</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr">
         <is>
           <t>Pedal 2 cable shield</t>
@@ -7190,7 +7234,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>screen</t>
+          <t>Screen</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -7198,7 +7242,11 @@
           <t>SP-SHIELD-A-WSF</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr">
         <is>
           <t>FR wheel spd shield</t>
@@ -7299,7 +7347,11 @@
           <t>SP-A5</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse (+ IG2 wake diode)</t>
@@ -7396,7 +7448,11 @@
           <t>SP-SHIELD-A</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr">
         <is>
           <t>Flex fuel shield</t>
@@ -7493,7 +7549,11 @@
           <t>SP-SHIELD-A</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr">
         <is>
           <t>Throttle shield</t>
@@ -7590,7 +7650,11 @@
           <t>SP-SHIELD-B</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
           <t>ETB motor shield</t>
@@ -7683,7 +7747,11 @@
           <t>SP-SHIELD-A</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr">
         <is>
           <t>Turbo speed shield</t>
@@ -7780,7 +7848,11 @@
           <t>SP-SHIELD-A</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr">
         <is>
           <t>Cam sensor shield</t>
@@ -7970,7 +8042,11 @@
           <t>SP-SHIELD-B</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr">
         <is>
           <t>Gearbox speed shield</t>
@@ -8164,7 +8240,11 @@
           <t>SP-SHIELD-B</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr">
         <is>
           <t>Knock sensor shield</t>
@@ -8257,7 +8337,11 @@
           <t>SP-SHIELD-A</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr">
         <is>
           <t>Crank sensor shield</t>
@@ -8358,7 +8442,11 @@
           <t>SP-REV</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr">
         <is>
           <t>Reverse sw +12 V out</t>
@@ -8455,7 +8543,11 @@
           <t>POWER-NEG-BAR</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr">
         <is>
           <t>CAN-Lambda ground</t>
@@ -8653,7 +8745,11 @@
           <t>SP-FUEL-LVL</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr">
         <is>
           <t>Fuel level signal</t>
@@ -9283,7 +9379,11 @@
           <t>SP-SHIELD-A-WSF</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr">
         <is>
           <t>WS-F screen drain</t>
@@ -9804,7 +9904,11 @@
           <t>SP-SHIELD-B-WSR</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F94" t="inlineStr">
         <is>
           <t>WS-R screen drain</t>
@@ -11281,13 +11385,21 @@
           <t>POWER-NEG-BAR</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
       <c r="D109" t="inlineStr">
         <is>
           <t>SP-CSB-GND</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr">
         <is>
           <t>CSB3 + opto ground</t>
@@ -11388,7 +11500,11 @@
           <t>SP-CAM</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr">
         <is>
           <t>Cam pull-up 1.8k</t>
@@ -11766,7 +11882,11 @@
           <t>SP-8V</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr"/>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D114" t="inlineStr">
         <is>
           <t>ECU-A</t>
@@ -11863,7 +11983,11 @@
           <t>SP-8V</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D115" t="inlineStr">
         <is>
           <t>R-CAM-PULLUP</t>
@@ -11956,7 +12080,11 @@
           <t>SP-8V</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D116" t="inlineStr">
         <is>
           <t>DRB102-CABIN</t>
@@ -12053,7 +12181,11 @@
           <t>SP-A5</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D117" t="inlineStr">
         <is>
           <t>ECU-A</t>
@@ -12154,7 +12286,11 @@
           <t>SP-AC-SG</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D118" t="inlineStr">
         <is>
           <t>A32</t>
@@ -12255,7 +12391,11 @@
           <t>SP-ACC12</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr"/>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D119" t="inlineStr">
         <is>
           <t>K-ACC</t>
@@ -12356,7 +12496,11 @@
           <t>SP-CAM</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr">
         <is>
           <t>DRB102-CABIN</t>
@@ -12453,7 +12597,11 @@
           <t>SP-CAN-SH-BH</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D121" t="inlineStr">
         <is>
           <t>DRB102-CABIN</t>
@@ -12554,7 +12702,11 @@
           <t>SP-CANH</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D122" t="inlineStr">
         <is>
           <t>DRB102-CABIN</t>
@@ -12659,7 +12811,11 @@
           <t>SP-CANL</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D123" t="inlineStr">
         <is>
           <t>DRB102-CABIN</t>
@@ -12764,7 +12920,11 @@
           <t>SP-FUEL-LVL</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr"/>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D124" t="inlineStr">
         <is>
           <t>R-FUELLVL</t>
@@ -12853,7 +13013,11 @@
           <t>SP-FUEL-LVL</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr"/>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D125" t="inlineStr">
         <is>
           <t>ECU-B</t>
@@ -12946,13 +13110,21 @@
           <t>SP-GND-ECU</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D126" t="inlineStr">
         <is>
           <t>POWER-NEG-BAR</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
       <c r="F126" t="inlineStr">
         <is>
           <t>ECU power ground</t>
@@ -13043,7 +13215,11 @@
           <t>SP-GND-ECU</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D127" t="inlineStr">
         <is>
           <t>ECU-B</t>
@@ -13144,7 +13320,11 @@
           <t>SP-GND-ECU</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr"/>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D128" t="inlineStr">
         <is>
           <t>ECU-B</t>
@@ -13245,7 +13425,11 @@
           <t>SP-REV</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr"/>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D129" t="inlineStr">
         <is>
           <t>IG2</t>
@@ -13346,7 +13530,11 @@
           <t>SP-REV</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr"/>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D130" t="inlineStr">
         <is>
           <t>OPTO-8</t>
@@ -13443,7 +13631,11 @@
           <t>SP-SHIELD-A</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr"/>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D131" t="inlineStr">
         <is>
           <t>ECU-A</t>
@@ -13544,13 +13736,21 @@
           <t>SP-SHIELD-A-APS</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr"/>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D132" t="inlineStr">
         <is>
           <t>SP-SHIELD-A</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F132" t="inlineStr">
         <is>
           <t>Shield drain</t>
@@ -13637,13 +13837,21 @@
           <t>SP-SHIELD-A-WSF</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D133" t="inlineStr">
         <is>
           <t>SP-SHIELD-A</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F133" t="inlineStr">
         <is>
           <t>Shield drain</t>
@@ -13730,7 +13938,11 @@
           <t>SP-SHIELD-B</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D134" t="inlineStr">
         <is>
           <t>ECU-B</t>
@@ -13823,13 +14035,21 @@
           <t>SP-SHIELD-B-WSR</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D135" t="inlineStr">
         <is>
           <t>SP-SHIELD-B</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F135" t="inlineStr">
         <is>
           <t>Shield drain B</t>
@@ -13916,13 +14136,21 @@
           <t>SP-SW12</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D136" t="inlineStr">
         <is>
           <t>SP-A5</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="F136" t="inlineStr">
         <is>
           <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse (+ IG2 wake diode)</t>
@@ -14013,7 +14241,11 @@
           <t>SP-SW12</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D137" t="inlineStr">
         <is>
           <t>DRB102-CABIN</t>
@@ -14114,7 +14346,11 @@
           <t>SP-SW12</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D138" t="inlineStr">
         <is>
           <t>DRB102-CABIN</t>
@@ -14215,7 +14451,11 @@
           <t>SP-TACH</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D139" t="inlineStr">
         <is>
           <t>A18</t>
@@ -14320,7 +14560,11 @@
           <t>SP-TACH</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Splice</t>
+        </is>
+      </c>
       <c r="D140" t="inlineStr">
         <is>
           <t>R-LOCK</t>
@@ -18608,7 +18852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -18652,12 +18896,19 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Contact PN 'solder splice' / 'solder onto the factory lead' = no contact; TBD = not confirmed by a maker document.</t>
+          <t>Pin 'Splice' / 'Terminal' / 'Screen' = an end with no cavity (a solder splice, a ring or spade lug, a cable screen).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>Contact PN 'solder splice' / 'solder onto the factory lead' = no contact; TBD = not confirmed by a maker document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Wires: 139   Connectors / ends: 59   Splices: 20   Spare cavities: 61</t>
         </is>

--- a/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
@@ -11827,12 +11827,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>K-ACC</t>
+          <t>LOGIC</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>BUS2-8</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>w_fb_k_acc_30_cp</t>
+          <t>w_acc_fuse</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">

--- a/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wires'!$A$1:$Z$140</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Connectors'!$A$1:$I$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Splices'!$A$1:$G$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spare Cavities'!$A$1:$D$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spare Cavities'!$A$1:$D$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -16284,7 +16284,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>3-1447221-3</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -16730,7 +16730,7 @@
         <v>64</v>
       </c>
       <c r="H9" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -19529,7 +19529,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -19551,7 +19551,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -19573,7 +19573,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -19595,7 +19595,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -19617,7 +19617,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -19639,12 +19639,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0413-214-1205</t>
+          <t>114017</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -19661,7 +19661,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -19683,7 +19683,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -19705,7 +19705,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -19727,7 +19727,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -19771,7 +19771,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -19793,7 +19793,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -19815,12 +19815,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>114017</t>
+          <t>114019-ZZ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>114019-ZZ</t>
+          <t>114018-ZZ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -19859,7 +19859,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -19881,12 +19881,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>114018-ZZ</t>
+          <t>114017</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -19903,12 +19903,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>114017</t>
+          <t>114018-ZZ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -19925,7 +19925,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -19947,12 +19947,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>114018-ZZ</t>
+          <t>114019-ZZ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -19969,12 +19969,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>114019-ZZ</t>
+          <t>114017</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>82</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -20013,7 +20013,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -20035,7 +20035,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -20057,7 +20057,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -20079,7 +20079,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -20101,7 +20101,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -20123,7 +20123,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>91</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -20145,7 +20145,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>92</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -20167,7 +20167,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -20189,7 +20189,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>94</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -20211,12 +20211,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>97</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>114017</t>
+          <t>0413-214-1205</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -20233,7 +20233,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>98</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -20277,7 +20277,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -20299,7 +20299,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>101</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -20321,7 +20321,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -20338,34 +20338,34 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DRB102-CABIN</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>0413-214-1205</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
+          <t>spare, not used</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -20387,7 +20387,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -20409,7 +20409,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -20431,7 +20431,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -20475,7 +20475,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -20497,7 +20497,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -20519,7 +20519,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -20541,7 +20541,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -20558,29 +20558,29 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>IX-WS-F-S</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>114017</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>spare, not used</t>
+          <t>spare, sealing plug</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>IX-WS-F-S</t>
+          <t>IX-WS-R-S</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -20599,30 +20599,8 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>IX-WS-R-S</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>114017</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D62"/>
+  <autoFilter ref="A1:D61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20712,7 +20690,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Wires: 139   Connectors / ends: 59   Splices: 20   Spare cavities: 61</t>
+          <t>Wires: 139   Connectors / ends: 59   Splices: 20   Spare cavities: 60</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
@@ -14,10 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wires'!$A$1:$Z$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wires'!$A$1:$Z$141</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Connectors'!$A$1:$I$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Splices'!$A$1:$G$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spare Cavities'!$A$1:$D$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spare Cavities'!$A$1:$D$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z140"/>
+  <dimension ref="A1:Z141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7908,7 +7908,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>w_rail_sp_sw12_c</t>
+          <t>w_cop_gnd_ac</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7918,69 +7918,65 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>POWER-NEG-BAR</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>SP-SW12 &gt; SP-A5</t>
-        </is>
-      </c>
+          <t>Lug</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse</t>
+          <t>Coil ground to the POWER box NEG bar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Blue-White-Yellow-Yellow</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>500</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>M22759/16-18-2</t>
+          <t>M22759/16-14-0</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>0460-202-1631</t>
+          <t>0460-220-1231</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>solder splice SP-SW12</t>
+          <t>320575</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -7990,12 +7986,12 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>via SP-SW12 &gt; SP-A5</t>
+          <t>POWER box NEG bar M8 stud (glove box)</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>SW12</t>
+          <t>COPG</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -8005,30 +8001,30 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>SP-SW12</t>
+          <t>COPG</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_rail_sp_sw12_e at DRB102-ENGINE 30, to splice SP-SW12-ENG</t>
+          <t>ST185-AB-engine w_cop_gnd_e_ae at DRB102-ENGINE 4, to splice SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>trunk ECU-A to bulkhead (RH firewall)</t>
+          <t>bulkhead to the glove-box POWER box</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>+12 V boost + flex | +12 V boost + flex</t>
+          <t>(firewall bulkhead, RH) | M8 ring lug on the POWER box battery-negative bar (Dan 2026-10-29: coil ground, cleanest return) | est length; runs with the coil +12 V (w_cop_pwr_ac, LOGIC COP 15 A) from the glove box to bulkhead pin 1 / 4; 14 AWG like that feed</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>w_shc_flex</t>
+          <t>w_rail_sp_sw12_c</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -8038,7 +8034,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8048,12 +8044,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-SW12 &gt; SP-A5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -8063,22 +8059,22 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Flex fuel shield</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Yellow-Yellow-Yellow</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -8088,7 +8084,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>M22759/16-18-2</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -8100,7 +8096,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-A</t>
+          <t>solder splice SP-SW12</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -8110,12 +8106,12 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-A</t>
+          <t>via SP-SW12 &gt; SP-A5</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>SW12</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -8125,12 +8121,12 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-SW12</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_flex_sh at DRB102-ENGINE 32, to NC, floats NC</t>
+          <t>ST185-AB-engine w_rail_sp_sw12_e at DRB102-ENGINE 30, to splice SP-SW12-ENG</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
@@ -8139,12 +8135,16 @@
         </is>
       </c>
       <c r="Y68" t="inlineStr"/>
-      <c r="Z68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>+12 V boost + flex | +12 V boost + flex</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>w_shc_etbs</t>
+          <t>w_shc_flex</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Throttle shield</t>
+          <t>Flex fuel shield</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Blue-Blue-White</t>
+          <t>Yellow-Yellow-Yellow</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>ETBS</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_etbs_sh at DRB102-ENGINE 47, to NC, floats NC</t>
+          <t>ST185-AB-engine cab_flex_sh at DRB102-ENGINE 32, to NC, floats NC</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
@@ -8260,7 +8260,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>w_shc_etbm</t>
+          <t>w_shc_etbs</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -8270,22 +8270,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>ETB motor shield</t>
+          <t>Throttle shield</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Blue-Yellow-White</t>
+          <t>Blue-Blue-White</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-B</t>
+          <t>solder splice SP-SHIELD-A</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -8342,12 +8342,12 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-B</t>
+          <t>via SP-SHIELD-A</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>ETBM</t>
+          <t>ETBS</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8357,22 +8357,26 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_etbm_ae_sh at DRB102-ENGINE 50, to NC, floats NC</t>
-        </is>
-      </c>
-      <c r="X70" t="inlineStr"/>
+          <t>ST185-AB-engine cab_etbs_sh at DRB102-ENGINE 47, to NC, floats NC</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>trunk ECU-A to bulkhead (RH firewall)</t>
+        </is>
+      </c>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>w_shc_turbo</t>
+          <t>w_shc_etbm</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8382,22 +8386,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-SHIELD-B</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -8407,7 +8411,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Turbo speed shield</t>
+          <t>ETB motor shield</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8417,7 +8421,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Yellow-Blue-White</t>
+          <t>Blue-Yellow-White</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -8444,7 +8448,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-A</t>
+          <t>solder splice SP-SHIELD-B</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -8454,12 +8458,12 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-A</t>
+          <t>via SP-SHIELD-B</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>TURBO</t>
+          <t>ETBM</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8469,26 +8473,22 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-SHIELD-B</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_turbo_sh at DRB102-ENGINE 57, to NC, floats NC</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>trunk ECU-A to bulkhead (RH firewall)</t>
-        </is>
-      </c>
+          <t>ST185-AB-engine cab_etbm_ae_sh at DRB102-ENGINE 50, to NC, floats NC</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>w_rail_sp_8v_c</t>
+          <t>w_shc_turbo</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8508,12 +8508,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SP-8V</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -8523,17 +8523,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>+8 V to cam sensor</t>
+          <t>Turbo speed shield</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>White-Blue-White</t>
+          <t>Yellow-Blue-White</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>solder splice SP-8V</t>
+          <t>solder splice SP-SHIELD-A</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>via SP-8V</t>
+          <t>via SP-SHIELD-A</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>8V</t>
+          <t>TURBO</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8585,12 +8585,12 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>SP-8V</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_rail_sp_8v_e at DRB102-ENGINE 63, to CAM 1</t>
+          <t>ST185-AB-engine cab_turbo_sh at DRB102-ENGINE 57, to NC, floats NC</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
@@ -8604,7 +8604,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>w_cam_sig_c</t>
+          <t>w_rail_sp_8v_c</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SP-CAM</t>
+          <t>SP-8V</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -8639,17 +8639,17 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Cam sensor signal</t>
+          <t>+8 V to cam sensor</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Blue-Blue-Yellow</t>
+          <t>White-Blue-White</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-20-3</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -8676,7 +8676,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>solder splice SP-CAM</t>
+          <t>solder splice SP-8V</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -8686,12 +8686,12 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>via SP-CAM</t>
+          <t>via SP-8V</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>CAM</t>
+          <t>8V</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8701,12 +8701,12 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>SP-CAM</t>
+          <t>SP-8V</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_cam_c2 at DRB102-ENGINE 64, to CAM 2</t>
+          <t>ST185-AB-engine w_rail_sp_8v_e at DRB102-ENGINE 63, to CAM 1</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
@@ -8720,7 +8720,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>w_shc_cam</t>
+          <t>w_cam_sig_c</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-CAM</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Cam sensor shield</t>
+          <t>Cam sensor signal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-A</t>
+          <t>solder splice SP-CAM</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-A</t>
+          <t>via SP-CAM</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
@@ -8817,12 +8817,12 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-CAM</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_cam_sh at DRB102-ENGINE 66, to NC, floats NC</t>
+          <t>ST185-AB-engine cab_cam_c2 at DRB102-ENGINE 64, to CAM 2</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
@@ -8836,7 +8836,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>w_rail_sw12_b_c_ac</t>
+          <t>w_shc_cam</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -8856,12 +8856,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SP-SW12 &gt; SP-A5</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -8871,17 +8871,17 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse</t>
+          <t>Cam sensor shield</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Blue-Blue-Yellow</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>M22759/16-20-2</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -8908,7 +8908,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>solder splice SP-SW12</t>
+          <t>solder splice SP-SHIELD-A</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>via SP-SW12 &gt; SP-A5</t>
+          <t>via SP-SHIELD-A</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>SW12</t>
+          <t>CAM</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8933,30 +8933,26 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>SP-SW12</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_vss_12v at DRB102-ENGINE 67, to VSS 1</t>
+          <t>ST185-AB-engine cab_cam_sh at DRB102-ENGINE 66, to NC, floats NC</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>to ECU-B plug (beside ECU-A)</t>
+          <t>trunk ECU-A to bulkhead (RH firewall)</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr"/>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>+12 V gearbox speed | (firewall bulkhead, RH); sensor +12V | owner TBD: a half has no length estimate (drawn today as w_rail_sw12_b_c_ac on ECU-cabin, ? mm; w_rail_sw12_b_c on ECU-cabin, 520 mm)</t>
-        </is>
-      </c>
+      <c r="Z75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>w_vss_sig_c</t>
+          <t>w_rail_sw12_b_c_ac</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8966,38 +8962,42 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>67</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>SP-SW12 &gt; SP-A5</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Gearbox speed signal</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Yellow-White-Yellow</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-20-2</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>solder splice SP-SW12</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -9034,12 +9034,12 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>via SP-SW12 &gt; SP-A5</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>VSS</t>
+          <t>SW12</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -9049,22 +9049,30 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>VSS</t>
+          <t>SP-SW12</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_vss_sig_e at DRB102-ENGINE 68, to VSS 3</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr"/>
+          <t>ST185-AB-engine w_vss_12v at DRB102-ENGINE 67, to VSS 1</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>to ECU-B plug (beside ECU-A)</t>
+        </is>
+      </c>
       <c r="Y76" t="inlineStr"/>
-      <c r="Z76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>+12 V gearbox speed | (firewall bulkhead, RH); sensor +12V | owner TBD: a half has no length estimate (drawn today as w_rail_sw12_b_c_ac on ECU-cabin, ? mm; w_rail_sw12_b_c on ECU-cabin, 520 mm)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>w_shc_vss</t>
+          <t>w_vss_sig_c</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -9074,7 +9082,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9084,27 +9092,23 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>SP-SHIELD-B</t>
-        </is>
-      </c>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Gearbox speed shield</t>
+          <t>Gearbox speed signal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9119,12 +9123,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>540</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -9136,7 +9140,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-B</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -9146,7 +9150,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-B</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -9161,12 +9165,12 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B</t>
+          <t>VSS</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_vss_sh at DRB102-ENGINE 69, to NC, floats NC</t>
+          <t>ST185-AB-engine w_vss_sig_e at DRB102-ENGINE 68, to VSS 3</t>
         </is>
       </c>
       <c r="X77" t="inlineStr"/>
@@ -9176,7 +9180,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>w12_c</t>
+          <t>w_shc_vss</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -9186,38 +9190,42 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-B</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>SP-SHIELD-B</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Knock sensor (-)</t>
+          <t>Gearbox speed shield</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Blue-Blue-Blue-White</t>
+          <t>Yellow-White-Yellow</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -9227,12 +9235,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -9244,7 +9252,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>solder splice SP-SHIELD-B</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -9254,12 +9262,12 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>DT06-12 plug (ECU splice point)</t>
+          <t>via SP-SHIELD-B</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>KNOCK</t>
+          <t>VSS</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -9269,26 +9277,22 @@
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-B</t>
+          <t>SP-SHIELD-B</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_knock1_c2 at DRB102-ENGINE 72, to KNOCK-1 2</t>
-        </is>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>trunk ECU to bulkhead (RH firewall)</t>
-        </is>
-      </c>
+          <t>ST185-AB-engine cab_vss_sh at DRB102-ENGINE 69, to NC, floats NC</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>w_shc_knock1</t>
+          <t>w12_c</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -9298,37 +9302,33 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>BUS-GNDOUT-B</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>SP-SHIELD-B</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Knock sensor shield</t>
+          <t>Knock sensor (-)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>430</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>M22759/16-20-6</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -9360,7 +9360,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-B</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-B</t>
+          <t>DT06-12 plug (ECU splice point)</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -9385,22 +9385,26 @@
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B</t>
+          <t>BUS-GNDOUT-B</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_knock1_sh at DRB102-ENGINE 73, to NC, floats NC</t>
-        </is>
-      </c>
-      <c r="X79" t="inlineStr"/>
+          <t>ST185-AB-engine cab_knock1_c2 at DRB102-ENGINE 72, to KNOCK-1 2</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>trunk ECU to bulkhead (RH firewall)</t>
+        </is>
+      </c>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>w_shc_crank</t>
+          <t>w_shc_knock1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9410,22 +9414,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-SHIELD-B</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -9435,7 +9439,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Crank sensor shield</t>
+          <t>Knock sensor shield</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -9445,7 +9449,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Blue-Blue-White-Blue</t>
+          <t>Blue-Blue-Blue-White</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -9472,7 +9476,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-A</t>
+          <t>solder splice SP-SHIELD-B</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -9482,12 +9486,12 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-A</t>
+          <t>via SP-SHIELD-B</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>CRANKC</t>
+          <t>KNOCK</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9497,30 +9501,22 @@
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-SHIELD-B</t>
         </is>
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_crank_sh at DRB102-ENGINE 76, to NC, floats NC</t>
-        </is>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>trunk ECU-A to bulkhead (RH firewall)</t>
-        </is>
-      </c>
+          <t>ST185-AB-engine cab_knock1_sh at DRB102-ENGINE 73, to NC, floats NC</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr"/>
       <c r="Y80" t="inlineStr"/>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>build (R30): this drain is the one crimped into A7</t>
-        </is>
-      </c>
+      <c r="Z80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>wc_h_bh_bc</t>
+          <t>w_shc_crank</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9530,42 +9526,42 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ECU-C</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SP-CANH</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>leg core</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>CAN H to CAN-Lambda</t>
+          <t>Crank sensor shield</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Blue-Blue-White-Blue</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -9575,24 +9571,16 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>(cable core)</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>CAB-CANBH-BC</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
           <t>TBD</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>0460-202-1631</t>
@@ -9600,7 +9588,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>solder splice SP-CANH</t>
+          <t>solder splice SP-SHIELD-A</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -9610,12 +9598,12 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>via SP-CANH</t>
+          <t>via SP-SHIELD-A</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>CRANKC</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9625,26 +9613,30 @@
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>SP-CANH</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>ST185-AB-engine wc_h_lam_be at DRB102-ENGINE 79, to splice SP-CANH-LAM; SP-CANH also joins ST185-CAN</t>
-        </is>
-      </c>
-      <c r="X81" t="inlineStr"/>
+          <t>ST185-AB-engine cab_crank_sh at DRB102-ENGINE 76, to NC, floats NC</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>trunk ECU-A to bulkhead (RH firewall)</t>
+        </is>
+      </c>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as wc_h_bh on CAN, ? mm; wc_h_bh_bc on ECU-cabin, 120 mm)</t>
+          <t>build (R30): this drain is the one crimped into A7</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>wc_l_bh_bc</t>
+          <t>wc_h_bh_bc</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9654,7 +9646,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -9664,12 +9656,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SP-CANL</t>
+          <t>SP-CANH</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -9679,12 +9671,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>CAN L to CAN-Lambda</t>
+          <t>CAN H to CAN-Lambda</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9724,7 +9716,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>solder splice SP-CANL</t>
+          <t>solder splice SP-CANH</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -9734,7 +9726,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>via SP-CANL</t>
+          <t>via SP-CANH</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
@@ -9749,26 +9741,26 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>SP-CANL</t>
+          <t>SP-CANH</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>ST185-AB-engine wc_l_lam_be at DRB102-ENGINE 80, to splice SP-CANL-LAM; SP-CANL also joins ST185-CAN</t>
+          <t>ST185-AB-engine wc_h_lam_be at DRB102-ENGINE 79, to splice SP-CANH-LAM; SP-CANH also joins ST185-CAN</t>
         </is>
       </c>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as wc_l_bh on CAN, ? mm; wc_l_bh_bc on ECU-cabin, 120 mm)</t>
+          <t>owner TBD: a half has no length estimate (drawn today as wc_h_bh on CAN, ? mm; wc_h_bh_bc on ECU-cabin, 120 mm)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>cab_canbh_bc_sh</t>
+          <t>wc_l_bh_bc</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9778,7 +9770,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -9788,12 +9780,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SP-CAN-SH-BH &gt; SP-CAN-SH-CLU</t>
+          <t>SP-CANL</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -9803,12 +9795,12 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>CAN-Lambda shield</t>
+          <t>CAN L to CAN-Lambda</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9816,7 +9808,11 @@
           <t>Yellow</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>120</t>
@@ -9844,7 +9840,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>solder splice SP-CAN-SH-BH</t>
+          <t>solder splice SP-CANL</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -9854,7 +9850,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>via SP-CAN-SH-BH &gt; SP-CAN-SH-CLU</t>
+          <t>via SP-CANL</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
@@ -9869,26 +9865,26 @@
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>SP-CAN-SH-BH</t>
+          <t>SP-CANL</t>
         </is>
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_lamcan_be_sh at DRB102-ENGINE 81, to NC, floats NC; SP-CAN-SH-BH also joins ST185-CAN; SP-CAN-SH-CLU also joins ST185-CAN</t>
+          <t>ST185-AB-engine wc_l_lam_be at DRB102-ENGINE 80, to splice SP-CANL-LAM; SP-CANL also joins ST185-CAN</t>
         </is>
       </c>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as cab_can_bh_sh on CAN, ? mm; cab_canbh_bc_sh on ECU-cabin, 120 mm)</t>
+          <t>owner TBD: a half has no length estimate (drawn today as wc_l_bh on CAN, ? mm; wc_l_bh_bc on ECU-cabin, 120 mm)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>w_lamg_ac</t>
+          <t>cab_canbh_bc_sh</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9898,65 +9894,73 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>POWER-NEG-BAR</t>
+          <t>ECU-C</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Lug</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>SP-CAN-SH-BH &gt; SP-CAN-SH-CLU</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg core</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>CAN-Lambda ground</t>
+          <t>CAN-Lambda shield</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Shield</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Blue-White-White</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>120</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>M22759/16-14-0</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>CAB-CANBH-BC</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>0460-220-1231</t>
+          <t>0460-202-1631</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>320575</t>
+          <t>solder splice SP-CAN-SH-BH</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -9966,12 +9970,12 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>POWER box NEG bar M8 stud (glove box)</t>
+          <t>via SP-CAN-SH-BH &gt; SP-CAN-SH-CLU</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>LAM</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9981,50 +9985,46 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>LAM</t>
+          <t>SP-CAN-SH-BH</t>
         </is>
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_lamg_be14 at DRB102-ENGINE 96, to splice SP-LAMG-B</t>
-        </is>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>bulkhead to the glove-box POWER box</t>
-        </is>
-      </c>
+          <t>ST185-AB-engine cab_lamcan_be_sh at DRB102-ENGINE 81, to NC, floats NC; SP-CAN-SH-BH also joins ST185-CAN; SP-CAN-SH-CLU also joins ST185-CAN</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>(firewall bulkhead, RH) | M8 ring lug on the POWER box battery-negative bar (R213: a CAN node never on chassis or the ECU ground) | est length; runs with the CAN-Lambda +12 V (w_lam12_cp, LOGIC LAM) from the glove box to bulkhead pin 95 / 96 (R217)</t>
+          <t>owner TBD: a half has no length estimate (drawn today as cab_can_bh_sh on CAN, ? mm; cab_canbh_bc_sh on ECU-cabin, 120 mm)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>w_rev_feed_c</t>
+          <t>w_lamg_ac</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>IG2</t>
+          <t>DRB102-CABIN</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>DRB102-CABIN</t>
+          <t>POWER-NEG-BAR</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>Lug</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -10035,59 +10035,59 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Back-up sw +12 V in</t>
+          <t>CAN-Lambda ground</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue-White-White</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>500</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>M22759/16-16-2</t>
+          <t>M22759/16-14-0</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>crimp butt splice into the factory cowl-</t>
+          <t>0460-220-1231</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>0460-202-1631</t>
+          <t>320575</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>OEM IG2 pin 4 (under the ECU, cowl side) - factory back-up SW feed</t>
+          <t>DRB102 receptacle (RH firewall)</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>DRB102 receptacle (RH firewall)</t>
+          <t>POWER box NEG bar M8 stud (glove box)</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>REV</t>
+          <t>LAM</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -10097,30 +10097,30 @@
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>REV</t>
+          <t>LAM</t>
         </is>
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_rev_feed_e at DRB102-ENGINE 77, to REV-SW 2</t>
-        </is>
-      </c>
-      <c r="X85" t="inlineStr"/>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>OEM IG2 pin 4 (under the ECU, cowl side) - R-L, GAUGE 15 A back-up SW feed; OEM colour R-L; EWD 1992 p.132 / 1990 p.82; crimp butt splice into the factory cowl-side lead at IG2 (cabin, under the ECU; the engine wire is removed)</t>
-        </is>
-      </c>
+          <t>ST185-AB-engine w_lamg_be14 at DRB102-ENGINE 96, to splice SP-LAMG-B</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>bulkhead to the glove-box POWER box</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>Circuit 11: factory feed kept. New engine-harness switch in splices to the IG2-4 pigtail.</t>
+          <t>(firewall bulkhead, RH) | M8 ring lug on the POWER box battery-negative bar (R213: a CAN node never on chassis or the ECU ground) | est length; runs with the CAN-Lambda +12 V (w_lam12_cp, LOGIC LAM) from the glove box to bulkhead pin 95 / 96 (R217)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>w_rev_lamps</t>
+          <t>w_rev_feed_c</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10140,27 +10140,23 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>SP-REV</t>
-        </is>
-      </c>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Back-up lamp +12 V</t>
+          <t>Back-up sw +12 V in</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10175,12 +10171,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>840</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>M22759/16-16-4</t>
+          <t>M22759/16-16-2</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -10192,17 +10188,17 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>solder splice SP-REV</t>
+          <t>0460-202-1631</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>OEM IG2 pin 13 (under the ECU, cowl side) - factory back-up lamp output</t>
+          <t>OEM IG2 pin 4 (under the ECU, cowl side) - factory back-up SW feed</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>via SP-REV</t>
+          <t>DRB102 receptacle (RH firewall)</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
@@ -10217,55 +10213,55 @@
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>SP-REV</t>
+          <t>REV</t>
         </is>
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_sw7_e at DRB102-ENGINE 78, to REV-SW 1</t>
+          <t>ST185-AB-engine w_rev_feed_e at DRB102-ENGINE 77, to REV-SW 2</t>
         </is>
       </c>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>OEM IG2 pin 13 (under the ECU, cowl side) - R-B, back-up lamp output; OEM colour R-B; EWD 1992 p.132; crimp butt splice into the factory cowl-side lead at IG2</t>
+          <t>OEM IG2 pin 4 (under the ECU, cowl side) - R-L, GAUGE 15 A back-up SW feed; OEM colour R-L; EWD 1992 p.132 / 1990 p.82; crimp butt splice into the factory cowl-side lead at IG2 (cabin, under the ECU; the engine wire is removed)</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>Circuit 11: new switch out splices to the IG2-13 pigtail; rear lamps stay on the factory harness.</t>
+          <t>Circuit 11: factory feed kept. New engine-harness switch in splices to the IG2-4 pigtail.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>w_fl_sig</t>
+          <t>w_rev_lamps</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>IX-FUEL-P</t>
+          <t>IG2</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>DRB102-CABIN</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SP-FUEL-LVL</t>
+          <t>SP-REV</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -10275,22 +10271,22 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Fuel level signal</t>
+          <t>Back-up lamp +12 V</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
           <t>White</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>Blue-Yellow-Blue</t>
-        </is>
-      </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -10300,34 +10296,34 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-16-4</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>0460-202-1631</t>
+          <t>crimp butt splice into the factory cowl-</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>solder splice SP-FUEL-LVL</t>
+          <t>solder splice SP-REV</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>IX-FUEL inline to fuel sender lead (trunk end)</t>
+          <t>OEM IG2 pin 13 (under the ECU, cowl side) - factory back-up lamp output</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>via SP-FUEL-LVL</t>
+          <t>via SP-REV</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>FLVL</t>
+          <t>REV</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -10337,18 +10333,30 @@
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>SP-FUEL-LVL</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr"/>
+          <t>SP-REV</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>ST185-AB-engine w_sw7_e at DRB102-ENGINE 78, to REV-SW 1</t>
+        </is>
+      </c>
       <c r="X87" t="inlineStr"/>
-      <c r="Y87" t="inlineStr"/>
-      <c r="Z87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>OEM IG2 pin 13 (under the ECU, cowl side) - R-B, back-up lamp output; OEM colour R-B; EWD 1992 p.132; crimp butt splice into the factory cowl-side lead at IG2</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>Circuit 11: new switch out splices to the IG2-13 pigtail; rear lamps stay on the factory harness.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>w45</t>
+          <t>w_fl_sig</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10358,38 +10366,42 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-B</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr"/>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>SP-FUEL-LVL</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Fuel level ground</t>
+          <t>Fuel level signal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Yellow-Yellow</t>
+          <t>Blue-Yellow-Blue</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -10404,7 +10416,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
@@ -10416,7 +10428,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>solder splice SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -10426,12 +10438,12 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>DT06-12 plug (ECU splice point)</t>
+          <t>via SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>SGND</t>
+          <t>FLVL</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -10441,7 +10453,7 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-B</t>
+          <t>SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="W88" t="inlineStr"/>
@@ -10452,48 +10464,48 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>cab_fspur_5v</t>
+          <t>w45</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>IX-WS-F-S</t>
+          <t>IX-FUEL-P</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>BUS-5V</t>
+          <t>BUS-GNDOUT-B</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>VRC-F +5V</t>
+          <t>Fuel level ground</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Blue-Blue</t>
+          <t>Yellow-Yellow</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -10508,22 +10520,14 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>(cable core)</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>CAB-FSPUR</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>55A1831-20-2/4/6-9</t>
-        </is>
-      </c>
+          <t>M22759/16-20-6</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>0460-202-1631</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
@@ -10533,7 +10537,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>to front VR conditioner</t>
+          <t>IX-FUEL inline to fuel sender lead (trunk end)</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -10543,7 +10547,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>5V</t>
+          <t>SGND</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -10553,22 +10557,18 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>BUS-5V</t>
+          <t>BUS-GNDOUT-B</t>
         </is>
       </c>
       <c r="W89" t="inlineStr"/>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>dash branch (front WS inline)</t>
-        </is>
-      </c>
+      <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>cab_fspur_gnd</t>
+          <t>cab_fspur_5v</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10578,17 +10578,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-A</t>
+          <t>BUS-5V</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -10599,17 +10599,17 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>VRC-F GND</t>
+          <t>VRC-F +5V</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Yellow-Yellow</t>
+          <t>Blue-Blue</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -10659,7 +10659,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>SGND</t>
+          <t>5V</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10669,7 +10669,7 @@
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-A</t>
+          <t>BUS-5V</t>
         </is>
       </c>
       <c r="W90" t="inlineStr"/>
@@ -10684,7 +10684,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>cab_fspur_l</t>
+          <t>cab_fspur_gnd</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10694,17 +10694,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>BUS-GNDOUT-A</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
@@ -10715,17 +10715,17 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>FL conditioned out</t>
+          <t>VRC-F GND</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>White-Blue-Yellow</t>
+          <t>Yellow-Yellow</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -10770,12 +10770,12 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>DT06-12 plug (ECU splice point)</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>WSSF</t>
+          <t>SGND</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>WSSF</t>
+          <t>BUS-GNDOUT-A</t>
         </is>
       </c>
       <c r="W91" t="inlineStr"/>
@@ -10800,7 +10800,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>cab_fspur_r_ac</t>
+          <t>cab_fspur_l</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10810,17 +10810,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
@@ -10831,12 +10831,12 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>FR conditioned out</t>
+          <t>FL conditioned out</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>330</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -10861,12 +10861,12 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>CAB-FSPUR-FR-AC</t>
+          <t>CAB-FSPUR</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>55A1811-20-9-9CS2275</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
@@ -10911,16 +10911,12 @@
         </is>
       </c>
       <c r="Y92" t="inlineStr"/>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>ECU-B plug pin B21 (Link G4X, centre dash); wheel speed | owner proposed: longer half (drawn today as cab_fspur_r_ac on ECU-cabin, 350 mm; cab_fspur_r on ECU-cabin, 530 mm)</t>
-        </is>
-      </c>
+      <c r="Z92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>cab_fspur_sh</t>
+          <t>cab_fspur_r_ac</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10930,37 +10926,33 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
-        </is>
-      </c>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>leg core</t>
+          <t>core</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>WS-F screen drain</t>
+          <t>FR conditioned out</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -10968,10 +10960,14 @@
           <t>White-Blue-Yellow</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>350</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -10981,12 +10977,12 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>CAB-FSPUR</t>
+          <t>CAB-FSPUR-FR-AC</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>55A1811-20-9-9CS2275</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -10996,7 +10992,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-A-WSF</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -11006,7 +11002,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
@@ -11021,7 +11017,7 @@
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-WSF</t>
+          <t>WSSF</t>
         </is>
       </c>
       <c r="W93" t="inlineStr"/>
@@ -11031,60 +11027,64 @@
         </is>
       </c>
       <c r="Y93" t="inlineStr"/>
-      <c r="Z93" t="inlineStr"/>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>ECU-B plug pin B21 (Link G4X, centre dash); wheel speed | owner proposed: longer half (drawn today as cab_fspur_r_ac on ECU-cabin, 350 mm; cab_fspur_r on ECU-cabin, 530 mm)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>cab_rspur_5v</t>
+          <t>cab_fspur_sh</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>IX-WS-R-S</t>
+          <t>IX-WS-F-S</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>BUS-5V</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
+        </is>
+      </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>leg core</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>VRC-R +5V</t>
+          <t>WS-F screen drain</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Shield</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Blue-Blue</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>White-Blue-Yellow</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -11097,12 +11097,12 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>CAB-RSPUR</t>
+          <t>CAB-FSPUR</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>55A1841-20-2/4/5/6-9</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11112,22 +11112,22 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>solder splice SP-SHIELD-A-WSF</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>IX-WS-R inline to rear VRC (dash above ECU)</t>
+          <t>to front VR conditioner</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>DT06-12 plug (ECU splice point)</t>
+          <t>via SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>5V</t>
+          <t>WSSF</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -11137,18 +11137,22 @@
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>BUS-5V</t>
+          <t>SP-SHIELD-A-WSF</t>
         </is>
       </c>
       <c r="W94" t="inlineStr"/>
-      <c r="X94" t="inlineStr"/>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>dash branch (front WS inline)</t>
+        </is>
+      </c>
       <c r="Y94" t="inlineStr"/>
       <c r="Z94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>cab_rspur_gnd</t>
+          <t>cab_rspur_5v</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -11158,17 +11162,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-B</t>
+          <t>BUS-5V</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
@@ -11179,17 +11183,17 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>VRC-R GND</t>
+          <t>VRC-R +5V</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Yellow-Yellow</t>
+          <t>Blue-Blue</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -11239,7 +11243,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>SGND</t>
+          <t>5V</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -11249,7 +11253,7 @@
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-B</t>
+          <t>BUS-5V</t>
         </is>
       </c>
       <c r="W95" t="inlineStr"/>
@@ -11260,7 +11264,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>cab_rspur_l</t>
+          <t>cab_rspur_gnd</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -11270,17 +11274,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>BUS-GNDOUT-B</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>ECU-B</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -11291,17 +11295,17 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Rear left wheel spd</t>
+          <t>VRC-R GND</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Blue-Blue-Yellow-Yellow</t>
+          <t>Yellow-Yellow</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -11311,7 +11315,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -11336,7 +11340,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -11346,12 +11350,12 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>DT06-12 plug (ECU splice point)</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>WSSR</t>
+          <t>SGND</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -11361,7 +11365,7 @@
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>WSSR</t>
+          <t>BUS-GNDOUT-B</t>
         </is>
       </c>
       <c r="W96" t="inlineStr"/>
@@ -11372,7 +11376,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>cab_rspur_r</t>
+          <t>cab_rspur_l</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -11382,7 +11386,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11392,7 +11396,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -11403,12 +11407,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Rear right wheel spd</t>
+          <t>Rear left wheel spd</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11484,7 +11488,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>cab_rspur_sh</t>
+          <t>cab_rspur_r</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -11494,7 +11498,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -11504,27 +11508,23 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>SP-SHIELD-B-WSR &gt; SP-SHIELD-B</t>
-        </is>
-      </c>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>leg core</t>
+          <t>core</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>WS-R screen drain</t>
+          <t>Rear right wheel spd</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11532,10 +11532,14 @@
           <t>Blue-Blue-Yellow-Yellow</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>530</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -11560,7 +11564,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-B-WSR</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -11570,7 +11574,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-B-WSR &gt; SP-SHIELD-B</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
@@ -11585,7 +11589,7 @@
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B-WSR</t>
+          <t>WSSR</t>
         </is>
       </c>
       <c r="W98" t="inlineStr"/>
@@ -11596,86 +11600,98 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>w_ig2_in</t>
+          <t>cab_rspur_sh</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>JB1-1H</t>
+          <t>IX-WS-R-S</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>D-IG2-WAKE</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr"/>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>SP-SHIELD-B-WSR &gt; SP-SHIELD-B</t>
+        </is>
+      </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg core</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>IG2 wake feed</t>
+          <t>WS-R screen drain</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Shield</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Blue-Yellow-Yellow-White</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Blue-Blue-Yellow-Yellow</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>CAB-RSPUR</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>55A1841-20-2/4/5/6-9</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>solder onto the factory lead</t>
-        </is>
-      </c>
-      <c r="Q99" t="inlineStr"/>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>solder splice SP-SHIELD-B-WSR</t>
+        </is>
+      </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O</t>
+          <t>IX-WS-R inline to rear VRC (dash above ECU)</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>IG2 wake diode (1N5822)</t>
+          <t>via SP-SHIELD-B-WSR &gt; SP-SHIELD-B</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>IG2WAKE</t>
+          <t>WSSR</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -11685,26 +11701,18 @@
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>IG2WAKE</t>
+          <t>SP-SHIELD-B-WSR</t>
         </is>
       </c>
       <c r="W99" t="inlineStr"/>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>IG2 tap branch (LH kick panel)</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O - IGN fuse out (EWD 1993 p.62); same lead as the ECU-B B28 sense tap, own splice; OEM colour B-O; EWD 1993 TIS EWD p.62 (Power Source); solder splice onto the factory lead</t>
-        </is>
-      </c>
+      <c r="X99" t="inlineStr"/>
+      <c r="Y99" t="inlineStr"/>
       <c r="Z99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>w_ign</t>
+          <t>w_ig2_in</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -11719,12 +11727,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>D-IG2-WAKE</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
@@ -11735,7 +11743,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Ignition sw sense</t>
+          <t>IG2 wake feed</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -11745,7 +11753,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Blue-Yellow-White-Blue</t>
+          <t>Blue-Yellow-Yellow-White</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -11755,7 +11763,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>900</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -11770,11 +11778,7 @@
           <t>solder onto the factory lead</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>3-1447221-4</t>
-        </is>
-      </c>
+      <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr">
         <is>
           <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O</t>
@@ -11782,12 +11786,12 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>IG2 wake diode (1N5822)</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>IGNSW</t>
+          <t>IG2WAKE</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -11797,14 +11801,18 @@
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>IGNSW</t>
+          <t>IG2WAKE</t>
         </is>
       </c>
       <c r="W100" t="inlineStr"/>
-      <c r="X100" t="inlineStr"/>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>IG2 tap branch (LH kick panel)</t>
+        </is>
+      </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O - IGN fuse out (EWD 1993 p.62); OEM colour B-O; EWD 1993 TIS EWD p.62 (Power Source); solder splice onto the factory lead</t>
+          <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O - IGN fuse out (EWD 1993 p.62); same lead as the ECU-B B28 sense tap, own splice; OEM colour B-O; EWD 1993 TIS EWD p.62 (Power Source); solder splice onto the factory lead</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr"/>
@@ -11812,94 +11820,90 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>w_acc86</t>
+          <t>w_ign</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>K-ACC</t>
+          <t>JB1-1H</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LOGIC</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>BUS2-8</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>SP-ACC12</t>
-        </is>
-      </c>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>A/C clutch relay coil+</t>
+          <t>Ignition sw sense</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Yellow-Blue</t>
+          <t>Blue-Yellow-White-Blue</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>M22759/16-18-2</t>
+          <t>M22759/16-20-4</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>280919-2</t>
+          <t>solder onto the factory lead</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>solder splice SP-ACC12</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>B2-M5 A/C clutch relay (k_acc) - amp A15 pin 8 sinks coil- (85); coil+ (86) fused +12 V from B2-BUS2-8</t>
+          <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>via SP-ACC12</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>IGNSW</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -11909,71 +11913,67 @@
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>SP-ACC12</t>
-        </is>
-      </c>
-      <c r="W101" t="inlineStr">
-        <is>
-          <t>SP-ACC12 also joins ST185-CabinPower</t>
-        </is>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A/C amp branch (behind dash)</t>
-        </is>
-      </c>
-      <c r="Y101" t="inlineStr"/>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>LOGIC box (glove box) relay M15 A/C clutch, pin 86 | B15: coil 86 is fused +12 V. Pressure switch stays on amp pin 13 only.</t>
-        </is>
-      </c>
+          <t>IGNSW</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr"/>
+      <c r="X101" t="inlineStr"/>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O - IGN fuse out (EWD 1993 p.62); OEM colour B-O; EWD 1993 TIS EWD p.62 (Power Source); solder splice onto the factory lead</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>w76</t>
+          <t>w_acc86</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>K-EFI</t>
+          <t>K-ACC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>86</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>LOGIC</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr"/>
+          <t>BUS2-8</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>SP-ACC12</t>
+        </is>
+      </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>EFI relay coil (-)</t>
+          <t>A/C clutch relay coil+</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Blue-Yellow</t>
+          <t>Yellow-Blue</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -11983,73 +11983,77 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>M22759/16-18-2</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>42281-1</t>
+          <t>280919-2</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>3-1447221-3</t>
+          <t>solder splice SP-ACC12</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>B1-R2 EFI Main Relay (seated in the POWER box R2) - ACTIVE-LOW - ECU sinks coil- (85); coil+ (86) permanent 12 V (LOGIC EFI86 5 A)</t>
+          <t>B2-M5 A/C clutch relay (k_acc) - amp A15 pin 8 sinks coil- (85); coil+ (86) fused +12 V from B2-BUS2-8</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>via SP-ACC12</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>EFI</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>ST185-CabinPower</t>
+          <t>ST185-AB-cabin</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>EFI</t>
-        </is>
-      </c>
-      <c r="W102" t="inlineStr"/>
+          <t>SP-ACC12</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>SP-ACC12 also joins ST185-CabinPower</t>
+        </is>
+      </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>glove-box branch (POWER / LOGIC boxes)</t>
+          <t>A/C amp branch (behind dash)</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>POWER box (glove box) relay R2 EFI main, pin 85 | owner proposed: longer half (drawn today as w76 on ECU-cabin, 370 mm; w76_cp on CabinPower, 400 mm)</t>
+          <t>LOGIC box (glove box) relay M15 A/C clutch, pin 86 | B15: coil 86 is fused +12 V. Pressure switch stays on amp pin 13 only.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>w_eps_rly</t>
+          <t>w76</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>K-EPS</t>
+          <t>K-EFI</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -12059,12 +12063,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>DRB102-CABIN</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
@@ -12075,7 +12079,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>EHPS relay coil (-)</t>
+          <t>EFI relay coil (-)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -12085,7 +12089,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Blue-Blue-Blue</t>
+          <t>Blue-Yellow</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -12095,7 +12099,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>370</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -12107,65 +12111,61 @@
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>282110-1</t>
+          <t>42281-1</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>0460-202-1631</t>
+          <t>3-1447221-3</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>B4 EPS pump relay (HCR150, glove box, beside the POWER box) - coil- (85) switched to ground by the MR-S pump pin B5 (R22); coil+ (86) switched 12 V - HCR 150 coil is a 2-pole plug (TE terminals 1/2, not marked 85/86), resistor-suppressed so polarity-free</t>
+          <t>B1-R2 EFI Main Relay (seated in the POWER box R2) - ACTIVE-LOW - ECU sinks coil- (85); coil+ (86) permanent 12 V (LOGIC EFI86 5 A)</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>DRB102 receptacle (RH firewall)</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>EPS</t>
+          <t>EFI</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin</t>
+          <t>ST185-CabinPower</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>EPS</t>
-        </is>
-      </c>
-      <c r="W103" t="inlineStr">
-        <is>
-          <t>ST185-EngineRoom-C w_eps_rly_e at DRB102-ENGINE 85, to MRS-B 5</t>
-        </is>
-      </c>
+          <t>EFI</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr"/>
       <c r="X103" t="inlineStr">
         <is>
-          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
+          <t>glove-box branch (POWER / LOGIC boxes)</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr"/>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>EHPS pump relay (glove box), pin 85 | owner proposed: longer half (drawn today as w_eps_rly on ECU-cabin, 530 mm; w_eps_rly_cp on CabinPower, 400 mm)</t>
+          <t>POWER box (glove box) relay R2 EFI main, pin 85 | owner proposed: longer half (drawn today as w76 on ECU-cabin, 370 mm; w76_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>w81</t>
+          <t>w_eps_rly</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>K-ETB</t>
+          <t>K-EPS</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>DRB102-CABIN</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -12191,7 +12191,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>ETB relay coil (-)</t>
+          <t>EHPS relay coil (-)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -12201,78 +12201,82 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>White-White</t>
+          <t>Blue-Blue-Blue</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>530</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-18-9</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>280919-2</t>
+          <t>282110-1</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>0460-202-1631</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>B2-M4 ETB Power Relay (seated in the LOGIC box M4) - ACTIVE-LOW - ECU sinks coil- (85); coil+ (86) switched 12 V</t>
+          <t>B4 EPS pump relay (HCR150, glove box, beside the POWER box) - coil- (85) switched to ground by the MR-S pump pin B5 (R22); coil+ (86) switched 12 V - HCR 150 coil is a 2-pole plug (TE terminals 1/2, not marked 85/86), resistor-suppressed so polarity-free</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>DRB102 receptacle (RH firewall)</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>ETB</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>ST185-CabinPower</t>
+          <t>ST185-AB-cabin</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>ETB</t>
-        </is>
-      </c>
-      <c r="W104" t="inlineStr"/>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>ST185-EngineRoom-C w_eps_rly_e at DRB102-ENGINE 85, to MRS-B 5</t>
+        </is>
+      </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>glove-box branch (POWER / LOGIC boxes)</t>
+          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr"/>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) relay M14 ETB power, pin 85 | owner proposed: longer half (drawn today as w81 on ECU-cabin, 380 mm; w81_cp on CabinPower, 400 mm)</t>
+          <t>EHPS pump relay (glove box), pin 85 | owner proposed: longer half (drawn today as w_eps_rly on ECU-cabin, 530 mm; w_eps_rly_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>w82_ac</t>
+          <t>w81</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -12282,17 +12286,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
@@ -12303,12 +12307,12 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>ETB motor +12 V</t>
+          <t>ETB relay coil (-)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -12318,29 +12322,29 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>380</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>M22759/16-18-2</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>42281-1</t>
+          <t>280919-2</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>3-1447221-3</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -12350,7 +12354,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
@@ -12369,38 +12373,42 @@
         </is>
       </c>
       <c r="W105" t="inlineStr"/>
-      <c r="X105" t="inlineStr"/>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>glove-box branch (POWER / LOGIC boxes)</t>
+        </is>
+      </c>
       <c r="Y105" t="inlineStr"/>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w82_ac on CabinPower, 400 mm; w82 on ECU-cabin, 340 mm)</t>
+          <t>LOGIC box (glove box) relay M14 ETB power, pin 85 | owner proposed: longer half (drawn today as w81 on ECU-cabin, 380 mm; w81_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>w_fan85</t>
+          <t>w82_ac</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>K-FAN</t>
+          <t>K-ETB</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
@@ -12411,17 +12419,17 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Rad fan relay (-)</t>
+          <t>ETB motor +12 V</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Yellow-White</t>
+          <t>White-White</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -12431,12 +12439,12 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>400</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>M22759/16-18-2</t>
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
@@ -12453,51 +12461,47 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>B1-R4 Radiator fan relay (seated in the POWER box R4)</t>
+          <t>B2-M4 ETB Power Relay (seated in the LOGIC box M4) - ACTIVE-LOW - ECU sinks coil- (85); coil+ (86) switched 12 V</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>ETB</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin</t>
+          <t>ST185-CabinPower</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>ETB</t>
         </is>
       </c>
       <c r="W106" t="inlineStr"/>
-      <c r="X106" t="inlineStr">
-        <is>
-          <t>glove-box branch (POWER / LOGIC boxes)</t>
-        </is>
-      </c>
+      <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr"/>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>POWER box (glove box) relay R4 radiator fan, pin 85 | owner proposed: longer half (drawn today as w_fan85 on ECU-cabin, 410 mm; w_fan85_cp on CabinPower, 400 mm)</t>
+          <t>owner proposed: longer half (drawn today as w82_ac on CabinPower, 400 mm; w82 on ECU-cabin, 340 mm)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>w_fan285</t>
+          <t>w_fan85</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>K-FAN2</t>
+          <t>K-FAN</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -12507,12 +12511,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
@@ -12523,7 +12527,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Cond fan relay (-)</t>
+          <t>Rad fan relay (-)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -12533,7 +12537,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>White-Blue</t>
+          <t>Yellow-White</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -12543,7 +12547,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>410</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -12565,17 +12569,17 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>B1-R5 Condenser fan relay (seated in the POWER box R5)</t>
+          <t>B1-R4 Radiator fan relay (seated in the POWER box R4)</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>FAN2</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -12585,27 +12589,31 @@
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>FAN2</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="W107" t="inlineStr"/>
-      <c r="X107" t="inlineStr"/>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>glove-box branch (POWER / LOGIC boxes)</t>
+        </is>
+      </c>
       <c r="Y107" t="inlineStr"/>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_fan285_cp on CabinPower, 400 mm; w_fan285 on ECU-cabin, 480 mm)</t>
+          <t>POWER box (glove box) relay R4 radiator fan, pin 85 | owner proposed: longer half (drawn today as w_fan85 on ECU-cabin, 410 mm; w_fan85_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>w_fp85</t>
+          <t>w_fan285</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>K-FP</t>
+          <t>K-FAN2</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -12615,12 +12623,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
@@ -12631,7 +12639,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Fuel pump relay (-)</t>
+          <t>Cond fan relay (-)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -12641,7 +12649,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>White-White-Blue</t>
+          <t>White-Blue</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -12651,7 +12659,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>480</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -12663,7 +12671,7 @@
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>282110-1</t>
+          <t>42281-1</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
@@ -12673,17 +12681,17 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>B3-K1 Fuel Pump Relay, TE HCR150 (seated in the battery relay block K1) - ACTIVE-LOW - ECU sinks coil- (85); coil+ (86) switched 12 V - HCR 150 coil is a 2-pole Superseal plug (TE terminals 1/2, not marked 85/86), resistor-suppressed so polarity-free</t>
+          <t>B1-R5 Condenser fan relay (seated in the POWER box R5)</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>FP</t>
+          <t>FAN2</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -12693,46 +12701,42 @@
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>FP</t>
+          <t>FAN2</t>
         </is>
       </c>
       <c r="W108" t="inlineStr"/>
-      <c r="X108" t="inlineStr">
-        <is>
-          <t>glove-box branch (POWER / LOGIC boxes)</t>
-        </is>
-      </c>
+      <c r="X108" t="inlineStr"/>
       <c r="Y108" t="inlineStr"/>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>Battery relay block (trunk) relay K1 fuel pump, pin 85 | owner proposed: longer half (drawn today as w_fp85 on ECU-cabin, 390 mm; w_fp85_h on HeavyDC, 150 mm)</t>
+          <t>owner proposed: longer half (drawn today as w_fan285_cp on CabinPower, 400 mm; w_fan285 on ECU-cabin, 480 mm)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>w_lam12_cp</t>
+          <t>w_fp85</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LOGIC</t>
+          <t>K-FP</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BUS2-1</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>DRB102-CABIN</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
@@ -12743,88 +12747,88 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC LAM 7.5 A fuse</t>
+          <t>Fuel pump relay (-)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Blue-White-White</t>
+          <t>White-White-Blue</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>390</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>M22759/16-14-2</t>
+          <t>M22759/16-18-9</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>1-968851-1</t>
+          <t>282110-1</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>0460-220-1231</t>
+          <t>3-1447221-3</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>B2 LOGIC box - custom fuse + relay box, glove box inboard (cad/fusebox rev 5, DECISIONS R75): Bus 1 (permanent) and Bus 2 (switched, k_efi 30) mini fuse strips, micro relays M1-M10</t>
+          <t>B3-K1 Fuel Pump Relay, TE HCR150 (seated in the battery relay block K1) - ACTIVE-LOW - ECU sinks coil- (85); coil+ (86) switched 12 V - HCR 150 coil is a 2-pole Superseal plug (TE terminals 1/2, not marked 85/86), resistor-suppressed so polarity-free</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>DRB102 receptacle (RH firewall)</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>LAM</t>
+          <t>FP</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>ST185-CabinPower</t>
+          <t>ST185-AB-cabin</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>LAM</t>
-        </is>
-      </c>
-      <c r="W109" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine w_lam12_be14 at DRB102-ENGINE 95, to splice SP-LAM12-B</t>
-        </is>
-      </c>
-      <c r="X109" t="inlineStr"/>
+          <t>FP</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr"/>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>glove-box branch (POWER / LOGIC boxes)</t>
+        </is>
+      </c>
       <c r="Y109" t="inlineStr"/>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>CAN-Lambda +12 V | CAN-Lambda +12 V | owner proposed: longer half (drawn today as w_lam12_cp on CabinPower, 250 mm; w_lam12_bc on ECU-cabin, 120 mm)</t>
+          <t>Battery relay block (trunk) relay K1 fuel pump, pin 85 | owner proposed: longer half (drawn today as w_fp85 on ECU-cabin, 390 mm; w_fp85_h on HeavyDC, 150 mm)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>w_fb_mrs_en</t>
+          <t>w_lam12_cp</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -12834,7 +12838,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BUS2-12</t>
+          <t>BUS2-1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -12844,7 +12848,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
@@ -12855,7 +12859,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC MRS 7.5 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC LAM 7.5 A fuse</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -12865,34 +12869,34 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Blue-White</t>
+          <t>Blue-White-White</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>250</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>M22759/16-20-2</t>
+          <t>M22759/16-14-2</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>1-968849-1</t>
+          <t>1-968851-1</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>0460-202-1631</t>
+          <t>0460-220-1231</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -12907,40 +12911,36 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>EPSEN</t>
+          <t>LAM</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin</t>
+          <t>ST185-CabinPower</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>EPSEN</t>
+          <t>LAM</t>
         </is>
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>ST185-EngineRoom-C w_hv_mrs_en_e at DRB102-ENGINE 83, to MRS-C 1</t>
-        </is>
-      </c>
-      <c r="X110" t="inlineStr">
-        <is>
-          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
-        </is>
-      </c>
+          <t>ST185-AB-engine w_lam12_be14 at DRB102-ENGINE 95, to splice SP-LAM12-B</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr"/>
       <c r="Y110" t="inlineStr"/>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) fuse MRS 7.5A Fuse fed from EPS enable relay k_eps_en pin 87 (ignition-switched). | EHPS enable +12 V | fuse fed from EPS enable relay k_eps_en pin 87 (ignition-switched); owner proposed: longer half (drawn today as w_fb_mrs_en on ECU-cabin, 530 mm; w_fb_mrs_en_cp on CabinPower, 250 mm)</t>
+          <t>CAN-Lambda +12 V | CAN-Lambda +12 V | owner proposed: longer half (drawn today as w_lam12_cp on CabinPower, 250 mm; w_lam12_bc on ECU-cabin, 120 mm)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>w_start</t>
+          <t>w_fb_mrs_en</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -12950,17 +12950,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BUS2-13</t>
+          <t>BUS2-12</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>DRB102-CABIN</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>83</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
@@ -12971,17 +12971,17 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Start request</t>
+          <t>EFI relay k_efi -&gt; LOGIC MRS 7.5 A fuse</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Blue-Yellow-Yellow</t>
+          <t>Blue-White</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>530</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>M22759/16-20-2</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -13008,7 +13008,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>0460-202-1631</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>DRB102 receptacle (RH firewall)</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>B30</t>
+          <t>EPSEN</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
@@ -13033,22 +13033,30 @@
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>B30</t>
-        </is>
-      </c>
-      <c r="W111" t="inlineStr"/>
-      <c r="X111" t="inlineStr"/>
+          <t>EPSEN</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>ST185-EngineRoom-C w_hv_mrs_en_e at DRB102-ENGINE 83, to MRS-C 1</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
+        </is>
+      </c>
       <c r="Y111" t="inlineStr"/>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_start_cp on CabinPower, 530 mm; w_start on ECU-cabin, 1230 mm)</t>
+          <t>LOGIC box (glove box) fuse MRS 7.5A Fuse fed from EPS enable relay k_eps_en pin 87 (ignition-switched). | EHPS enable +12 V | fuse fed from EPS enable relay k_eps_en pin 87 (ignition-switched); owner proposed: longer half (drawn today as w_fb_mrs_en on ECU-cabin, 530 mm; w_fb_mrs_en_cp on CabinPower, 250 mm)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>w_cop_pwr_ac</t>
+          <t>w_start</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -13058,17 +13066,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>BUS2-3</t>
+          <t>BUS2-13</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>DRB102-CABIN</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
@@ -13079,44 +13087,44 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC COP 15 A fuse</t>
+          <t>Start request</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Blue-White-Yellow</t>
+          <t>Blue-Yellow-Yellow</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>M22759/16-14-2</t>
+          <t>M22759/16-20-4</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>1-968851-1</t>
+          <t>1-968849-1</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>0460-220-1231</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -13126,45 +13134,37 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>DRB102 receptacle (RH firewall)</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>B30</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>ST185-CabinPower</t>
+          <t>ST185-AB-cabin</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>COP</t>
-        </is>
-      </c>
-      <c r="W112" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine w_cop_pwr_e_ae at DRB102-ENGINE 1, to splice SP-COP-ENG</t>
-        </is>
-      </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
-        </is>
-      </c>
+          <t>B30</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr"/>
+      <c r="X112" t="inlineStr"/>
       <c r="Y112" t="inlineStr"/>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) fuse COP 15A | Coil +12 V feed | owner proposed: longer half (drawn today as w_cop_pwr_ac on ECU-cabin, 180 mm; w_cop_pwr_c_ac on CabinPower, 250 mm)</t>
+          <t>owner proposed: longer half (drawn today as w_start_cp on CabinPower, 530 mm; w_start on ECU-cabin, 1230 mm)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>w_inj_pwr_ac</t>
+          <t>w_cop_pwr_ac</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>BUS2-4</t>
+          <t>BUS2-3</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
@@ -13195,7 +13195,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC INJ 15 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC COP 15 A fuse</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -13205,7 +13205,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Blue-White-Blue</t>
+          <t>Blue-White-Yellow</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -13247,7 +13247,7 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>INJ</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
@@ -13257,12 +13257,12 @@
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>INJ</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_inj_pwr_e_ae at DRB102-ENGINE 2, to splice SP-INJ-ENG</t>
+          <t>ST185-AB-engine w_cop_pwr_e_ae at DRB102-ENGINE 1, to splice SP-COP-ENG</t>
         </is>
       </c>
       <c r="X113" t="inlineStr">
@@ -13273,24 +13273,24 @@
       <c r="Y113" t="inlineStr"/>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) fuse INJ 15A | Injector +12 V feed | owner proposed: longer half (drawn today as w_inj_pwr_ac on ECU-cabin, 180 mm; w_inj_pwr_c_ac on CabinPower, 250 mm)</t>
+          <t>LOGIC box (glove box) fuse COP 15A | Coil +12 V feed | owner proposed: longer half (drawn today as w_cop_pwr_ac on ECU-cabin, 180 mm; w_cop_pwr_c_ac on CabinPower, 250 mm)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>w_sw7_c</t>
+          <t>w_inj_pwr_ac</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>OPTO-8</t>
+          <t>LOGIC</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>IN2</t>
+          <t>BUS2-4</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13300,128 +13300,128 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>SP-REV</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Reverse to opto in 2</t>
+          <t>EFI relay k_efi -&gt; LOGIC INJ 15 A fuse</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue-White-Blue</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>M22759/16-16-4</t>
+          <t>M22759/16-14-2</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>screw terminal (on the board)</t>
+          <t>1-968851-1</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>solder splice SP-REV</t>
+          <t>0460-220-1231</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>Optocoupler board, 8 channel (Dan's, generic EL814) - inline at the CSB3</t>
+          <t>B2 LOGIC box - custom fuse + relay box, glove box inboard (cad/fusebox rev 5, DECISIONS R75): Bus 1 (permanent) and Bus 2 (switched, k_efi 30) mini fuse strips, micro relays M1-M10</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>via SP-REV</t>
+          <t>DRB102 receptacle (RH firewall)</t>
         </is>
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>REV</t>
+          <t>INJ</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin</t>
+          <t>ST185-CabinPower</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>SP-REV</t>
+          <t>INJ</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_sw7_e at DRB102-ENGINE 78, to REV-SW 1</t>
-        </is>
-      </c>
-      <c r="X114" t="inlineStr"/>
+          <t>ST185-AB-engine w_inj_pwr_e_ae at DRB102-ENGINE 2, to splice SP-INJ-ENG</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
+        </is>
+      </c>
       <c r="Y114" t="inlineStr"/>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as w_sw7_c on ECU-cabin, ? mm; w_sw7_c_csb on CSB3, 180 mm)</t>
+          <t>LOGIC box (glove box) fuse INJ 15A | Injector +12 V feed | owner proposed: longer half (drawn today as w_inj_pwr_ac on ECU-cabin, 180 mm; w_inj_pwr_c_ac on CabinPower, 250 mm)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>w_cam_pullup_8v</t>
+          <t>w_sw7_c</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>R-CAM-PULLUP</t>
+          <t>OPTO-8</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>IN2</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>DRB102-CABIN</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>SP-8V</t>
+          <t>SP-REV</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -13431,22 +13431,22 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>+8 V to cam pull-up</t>
+          <t>Reverse to opto in 2</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Blue-Blue-Yellow</t>
+          <t>White</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -13456,30 +13456,34 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>M22759/16-16-4</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>screw terminal (on the board)</t>
+        </is>
+      </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>solder splice SP-8V</t>
+          <t>solder splice SP-REV</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>Cam pull-up 1.8 k to +8 V</t>
+          <t>Optocoupler board, 8 channel (Dan's, generic EL814) - inline at the CSB3</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>via SP-8V</t>
+          <t>via SP-REV</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>CAM</t>
+          <t>REV</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
@@ -13489,22 +13493,26 @@
       </c>
       <c r="V115" t="inlineStr">
         <is>
-          <t>SP-8V</t>
-        </is>
-      </c>
-      <c r="W115" t="inlineStr"/>
-      <c r="X115" t="inlineStr">
-        <is>
-          <t>at ECU-A plug</t>
-        </is>
-      </c>
+          <t>SP-REV</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>ST185-AB-engine w_sw7_e at DRB102-ENGINE 78, to REV-SW 1</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr"/>
       <c r="Y115" t="inlineStr"/>
-      <c r="Z115" t="inlineStr"/>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>owner TBD: a half has no length estimate (drawn today as w_sw7_c on ECU-cabin, ? mm; w_sw7_c_csb on CSB3, 180 mm)</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>w_cam_pullup_sig</t>
+          <t>w_cam_pullup_8v</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -13514,7 +13522,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -13524,12 +13532,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>SP-CAM</t>
+          <t>SP-8V</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -13539,12 +13547,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Cam pull-up 1.8k</t>
+          <t>+8 V to cam pull-up</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -13564,7 +13572,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-20-3</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -13572,7 +13580,7 @@
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>solder splice SP-CAM</t>
+          <t>solder splice SP-8V</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -13582,7 +13590,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>via SP-CAM</t>
+          <t>via SP-8V</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
@@ -13597,7 +13605,7 @@
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>SP-CAM</t>
+          <t>SP-8V</t>
         </is>
       </c>
       <c r="W116" t="inlineStr"/>
@@ -13612,32 +13620,32 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>w43</t>
+          <t>w_cam_pullup_sig</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>R-FUELLVL</t>
+          <t>R-CAM-PULLUP</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>SP-FUEL-LVL</t>
+          <t>SP-CAM</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -13647,7 +13655,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Fuel lvl pull-up</t>
+          <t>Cam pull-up 1.8k</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -13657,7 +13665,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Blue-Yellow-Blue</t>
+          <t>Blue-Blue-Yellow</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -13680,22 +13688,22 @@
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>solder splice SP-FUEL-LVL</t>
+          <t>solder splice SP-CAM</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>470R fuel level pull-up to +5V</t>
+          <t>Cam pull-up 1.8 k to +8 V</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>via SP-FUEL-LVL</t>
+          <t>via SP-CAM</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>FLVL</t>
+          <t>CAM</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
@@ -13705,18 +13713,22 @@
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>SP-FUEL-LVL</t>
+          <t>SP-CAM</t>
         </is>
       </c>
       <c r="W117" t="inlineStr"/>
-      <c r="X117" t="inlineStr"/>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>at ECU-A plug</t>
+        </is>
+      </c>
       <c r="Y117" t="inlineStr"/>
       <c r="Z117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>w44</t>
+          <t>w43</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -13726,33 +13738,37 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>BUS-5V-2</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr"/>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>SP-FUEL-LVL</t>
+        </is>
+      </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>+5 V fuel lvl pullup</t>
+          <t>Fuel lvl pull-up</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -13772,7 +13788,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -13780,7 +13796,7 @@
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>solder splice SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -13790,7 +13806,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>DT06-8 plug (ECU splice point)</t>
+          <t>via SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="T118" t="inlineStr">
@@ -13805,7 +13821,7 @@
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>BUS-5V-2</t>
+          <t>SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="W118" t="inlineStr"/>
@@ -13816,52 +13832,48 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>w_tach_r</t>
+          <t>w44</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>R-LOCK</t>
+          <t>R-FUELLVL</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>BUS-5V-2</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>SP-TACH</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Tacho to lock-sensor 4.7k</t>
+          <t>+5 V fuel lvl pullup</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Yellow-Blue-Yellow</t>
+          <t>Blue-Yellow-Blue</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -13876,7 +13888,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-20-3</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -13884,22 +13896,22 @@
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>solder splice SP-TACH</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>Lock-sensor tap 4.7 k from tacho</t>
+          <t>470R fuel level pull-up to +5V</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>via SP-TACH</t>
+          <t>DT06-8 plug (ECU splice point)</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>TACH</t>
+          <t>FLVL</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
@@ -13909,26 +13921,18 @@
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>SP-TACH</t>
+          <t>BUS-5V-2</t>
         </is>
       </c>
       <c r="W119" t="inlineStr"/>
-      <c r="X119" t="inlineStr">
-        <is>
-          <t>A/C amp branch (behind dash)</t>
-        </is>
-      </c>
+      <c r="X119" t="inlineStr"/>
       <c r="Y119" t="inlineStr"/>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>OPEN-ITEMS History 2026-10-21 N61: first bench try is tach -&gt; 4.7 kohm -&gt; A15-9. Dan 2026-10-26: lock-sensor input needs a modified tachometer signal; apply that workaround.</t>
-        </is>
-      </c>
+      <c r="Z119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>w_lock_9</t>
+          <t>w_tach_r</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -13938,28 +13942,32 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>A18</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>SP-TACH</t>
+        </is>
+      </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Lock-sensor input (modified tacho)</t>
+          <t>Tacho to lock-sensor 4.7k</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -13992,7 +14000,7 @@
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>solder onto the factory lead</t>
+          <t>solder splice SP-TACH</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -14002,7 +14010,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>OEM A/C amplifier A18 (1993 book: A15)</t>
+          <t>via SP-TACH</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
@@ -14017,7 +14025,7 @@
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>TACH</t>
+          <t>SP-TACH</t>
         </is>
       </c>
       <c r="W120" t="inlineStr"/>
@@ -14026,41 +14034,37 @@
           <t>A/C amp branch (behind dash)</t>
         </is>
       </c>
-      <c r="Y120" t="inlineStr">
-        <is>
-          <t>A/C amplifier A18 (1993: A15) pin 9, behind the glove box; OEM colour W-L; EWD 1993 p.210-211; solder onto the factory lead</t>
-        </is>
-      </c>
+      <c r="Y120" t="inlineStr"/>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>A15 pin 9 lock-sensor (factory W-L / IH1-4). Engine-side lock sensor unused. | Factory lock sensor is A15 pins 9-14 (W-L / W-R, Mitchell ~115 ohm). Workaround: modified tacho through 4.7k to pin 9 (N61 2026-10-21). IH1-4/5 engine wires unused (Engine Wire gone).</t>
+          <t>OPEN-ITEMS History 2026-10-21 N61: first bench try is tach -&gt; 4.7 kohm -&gt; A15-9. Dan 2026-10-26: lock-sensor input needs a modified tachometer signal; apply that workaround.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>w_start_in_cp</t>
+          <t>w_lock_9</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>RB4</t>
+          <t>R-LOCK</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LOGIC</t>
+          <t>A18</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>BUS2-13 IN</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
@@ -14071,17 +14075,17 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Start sw ST1 feed</t>
+          <t>Lock-sensor input (modified tacho)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Blue-Yellow-Yellow</t>
+          <t>Yellow-Blue-Yellow</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -14091,184 +14095,180 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr">
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr">
         <is>
           <t>solder onto the factory lead</t>
         </is>
       </c>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>1-968849-1</t>
-        </is>
-      </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>OEM ST1 lead B-W at old R/B No.4 pin 1, RH kick panel</t>
+          <t>Lock-sensor tap 4.7 k from tacho</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>B2 LOGIC box - custom fuse + relay box, glove box inboard (cad/fusebox rev 5, DECISIONS R75): Bus 1 (permanent) and Bus 2 (switched, k_efi 30) mini fuse strips, micro relays M1-M10</t>
+          <t>OEM A/C amplifier A18 (1993 book: A15)</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>B30</t>
+          <t>TACH</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>ST185-CabinPower</t>
+          <t>ST185-AB-cabin</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>B30</t>
+          <t>TACH</t>
         </is>
       </c>
       <c r="W121" t="inlineStr"/>
-      <c r="X121" t="inlineStr"/>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>A/C amp branch (behind dash)</t>
+        </is>
+      </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>OEM ST1 lead B-W at old R/B No.4 pin 1, RH kick panel - start (EWD 1993 p.66); OEM colour B-W; EWD 1993 TIS EWD p.66 (Starting and Ignition, All-Trac); solder splice onto the factory lead</t>
+          <t>A/C amplifier A18 (1993: A15) pin 9, behind the glove box; OEM colour W-L; EWD 1993 p.210-211; solder onto the factory lead</t>
         </is>
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_start_in on ECU-cabin, 350 mm; w_start_in_cp on CabinPower, 530 mm)</t>
+          <t>A15 pin 9 lock-sensor (factory W-L / IH1-4). Engine-side lock sensor unused. | Factory lock sensor is A15 pins 9-14 (W-L / W-R, Mitchell ~115 ohm). Workaround: modified tacho through 4.7k to pin 9 (N61 2026-10-21). IH1-4/5 engine wires unused (Engine Wire gone).</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>cab_aps1_sh</t>
+          <t>w_start_in_cp</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>NC, floats</t>
+          <t>RB4</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>LOGIC</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
-        </is>
-      </c>
+          <t>BUS2-13 IN</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>drain</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Pedal 1 cable shield</t>
+          <t>Start sw ST1 feed</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Yellow-White-White</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr"/>
+          <t>Blue-Yellow-Yellow</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>530</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>(cable core)</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr">
-        <is>
-          <t>CAB-APS1</t>
-        </is>
-      </c>
-      <c r="O122" t="inlineStr">
-        <is>
-          <t>55A1831-20-2/4/6-9</t>
-        </is>
-      </c>
-      <c r="P122" t="inlineStr"/>
+          <t>M22759/16-20-4</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>solder onto the factory lead</t>
+        </is>
+      </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-A-APS</t>
+          <t>1-968849-1</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>cab_aps1 screen (floats at the device end)</t>
+          <t>OEM ST1 lead B-W at old R/B No.4 pin 1, RH kick panel</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
+          <t>B2 LOGIC box - custom fuse + relay box, glove box inboard (cad/fusebox rev 5, DECISIONS R75): Bus 1 (permanent) and Bus 2 (switched, k_efi 30) mini fuse strips, micro relays M1-M10</t>
         </is>
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>B30</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin</t>
+          <t>ST185-CabinPower</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-APS</t>
+          <t>B30</t>
         </is>
       </c>
       <c r="W122" t="inlineStr"/>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>at ECU-A plug</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr"/>
+      <c r="X122" t="inlineStr"/>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>OEM ST1 lead B-W at old R/B No.4 pin 1, RH kick panel - start (EWD 1993 p.66); OEM colour B-W; EWD 1993 TIS EWD p.66 (Starting and Ignition, All-Trac); solder splice onto the factory lead</t>
+        </is>
+      </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>Screen floats at this end: cut back and seal under heat-shrink | screen floats at the far end; pedal branch length estimated from OEM body dimensions + 10 % (990 mm ECU-A</t>
+          <t>owner proposed: longer half (drawn today as w_start_in on ECU-cabin, 350 mm; w_start_in_cp on CabinPower, 530 mm)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>cab_aps_sh</t>
+          <t>cab_aps1_sh</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -14303,7 +14303,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Pedal 2 cable shield</t>
+          <t>Pedal 1 cable shield</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -14329,7 +14329,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>CAB-APS2</t>
+          <t>CAB-APS1</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -14345,7 +14345,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>cab_aps2 screen (floats at the device end)</t>
+          <t>cab_aps1 screen (floats at the device end)</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
@@ -14384,7 +14384,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>cab_fspur_fr_sh_ac</t>
+          <t>cab_aps_sh</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
+          <t>SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -14419,7 +14419,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>FR wheel spd shield</t>
+          <t>Pedal 2 cable shield</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -14429,7 +14429,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>White-Blue-Yellow</t>
+          <t>Yellow-White-White</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -14445,33 +14445,33 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>CAB-FSPUR-FR-AC</t>
+          <t>CAB-APS2</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>55A1811-20-9-9CS2275</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-A-WSF</t>
+          <t>solder splice SP-SHIELD-A-APS</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>cab_fspur_fr_ac screen (floats at the device end)</t>
+          <t>cab_aps2 screen (floats at the device end)</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
+          <t>via SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>WSSF</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
@@ -14481,36 +14481,36 @@
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-WSF</t>
+          <t>SP-SHIELD-A-APS</t>
         </is>
       </c>
       <c r="W124" t="inlineStr"/>
       <c r="X124" t="inlineStr">
         <is>
-          <t>dash branch (front WS inline)</t>
+          <t>at ECU-A plug</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr"/>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>Screen floats at this end: cut back and seal under heat-shrink | tied at the A end only; the far (B) end floats, dressed back at the ECU-B plug (no A-B shield bridge)</t>
+          <t>Screen floats at this end: cut back and seal under heat-shrink | screen floats at the far end; pedal branch length estimated from OEM body dimensions + 10 % (990 mm ECU-A</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>w19</t>
+          <t>cab_fspur_fr_sh_ac</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>legs of SP-8V</t>
+          <t>NC, floats</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -14520,39 +14520,35 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>SP-8V</t>
+          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>trunk</t>
+          <t>drain</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>+8 V sensor supply</t>
+          <t>FR wheel spd shield</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Shield</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>White-Blue-White</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>White-Blue-Yellow</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -14560,34 +14556,38 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr">
-        <is>
-          <t>solder splice</t>
-        </is>
-      </c>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>CAB-FSPUR-FR-AC</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>55A1811-20-9-9CS2275</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>solder splice SP-SHIELD-A-WSF</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>ECU splice point - SP-8V: +8 V cam sensor supply (ECU A6)</t>
+          <t>cab_fspur_fr_ac screen (floats at the device end)</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>via SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>8V</t>
+          <t>WSSF</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
@@ -14597,27 +14597,31 @@
       </c>
       <c r="V125" t="inlineStr">
         <is>
-          <t>SP-8V</t>
+          <t>SP-SHIELD-A-WSF</t>
         </is>
       </c>
       <c r="W125" t="inlineStr"/>
       <c r="X125" t="inlineStr">
         <is>
-          <t>at ECU-A plug</t>
+          <t>dash branch (front WS inline)</t>
         </is>
       </c>
       <c r="Y125" t="inlineStr"/>
-      <c r="Z125" t="inlineStr"/>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>Screen floats at this end: cut back and seal under heat-shrink | tied at the A end only; the far (B) end floats, dressed back at the ECU-B plug (no A-B shield bridge)</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>w_a5_pin</t>
+          <t>w19</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>legs of SP-A5</t>
+          <t>legs of SP-8V</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -14632,12 +14636,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SP-A5</t>
+          <t>SP-8V</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -14647,22 +14651,22 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse (+ IG2 wake diode)</t>
+          <t>+8 V sensor supply</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White-Blue-White</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -14672,7 +14676,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>M22759/16-18-2</t>
+          <t>M22759/16-20-3</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -14684,12 +14688,12 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>3-1447221-3</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>ECU splice point - SP-A5: ECU main feed (SW12 + IG2 diode)</t>
+          <t>ECU splice point - SP-8V: +8 V cam sensor supply (ECU A6)</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
@@ -14699,7 +14703,7 @@
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>SW12</t>
+          <t>8V</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
@@ -14709,7 +14713,7 @@
       </c>
       <c r="V126" t="inlineStr">
         <is>
-          <t>SP-A5</t>
+          <t>SP-8V</t>
         </is>
       </c>
       <c r="W126" t="inlineStr"/>
@@ -14719,21 +14723,17 @@
         </is>
       </c>
       <c r="Y126" t="inlineStr"/>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>ECU main +12 V | ECU main +12 V</t>
-        </is>
-      </c>
+      <c r="Z126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>w_ac_psw_in</t>
+          <t>w_a5_pin</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>legs of SP-AC-PSW</t>
+          <t>legs of SP-A5</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -14743,17 +14743,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>SP-AC-PSW</t>
+          <t>SP-A5</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -14763,22 +14763,22 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>A/C pressure sw out</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse (+ IG2 wake diode)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Yellow-Blue</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -14788,7 +14788,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>M22759/16-18-2</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -14800,22 +14800,22 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t xml:space="preserve">new-wire run terminated at the switch's </t>
+          <t>3-1447221-3</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>At A/C amp - SP-AC-PSW: A/C pressure switch output</t>
+          <t>ECU splice point - SP-A5: ECU main feed (SW12 + IG2 diode)</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>OEM A5, factory Y-R lead</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>SW12</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
@@ -14825,35 +14825,31 @@
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>SP-AC-PSW</t>
+          <t>SP-A5</t>
         </is>
       </c>
       <c r="W127" t="inlineStr"/>
       <c r="X127" t="inlineStr">
         <is>
-          <t>A/C amp branch (behind dash)</t>
-        </is>
-      </c>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>A/C pressure switch A5, engine bay; exact spot TBD (no locator figure in the repo); OEM colour Y-R (factory wiring; new wire here); EWD 1990 ST185 EWD p.152 (docs/electrical/ewd-snips/1990-st185-autoac-pressure-clutch-p152.png); 1990 ST185 EWD p.152 (A5 pin 4 Y-R); new-wire run terminated at the switch's own mating plug (no factory engine-bay wire reused, Section 39, 2026-10-04); plug part number not yet chosen</t>
-        </is>
-      </c>
+          <t>at ECU-A plug</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr"/>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>Runs on in ST185-EngineRoom-C to A/C pressure switch A5 pin 4 (engine bay): new wire to the switch's own mating plug, plug part TBD. EWD 1990 p.152. | owner TBD: a half has no length estimate (drawn today as w_ac_psw_in on ECU-cabin, ? mm; w_ac_psw on EngineRoom-C, 100 mm)</t>
+          <t>ECU main +12 V | ECU main +12 V</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>w_amb_sg</t>
+          <t>w_ac_psw_in</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>legs of SP-AC-SG</t>
+          <t>legs of SP-AC-PSW</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -14863,17 +14859,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>A32</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SP-AC-SG</t>
+          <t>SP-AC-PSW</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -14883,7 +14879,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>A/C sensor common</t>
+          <t>A/C pressure sw out</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -14893,7 +14889,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Blue-Yellow</t>
+          <t>Yellow-Blue</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -14903,7 +14899,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -14920,22 +14916,22 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>solder onto the factory lead</t>
+          <t xml:space="preserve">new-wire run terminated at the switch's </t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>SP-AC-SG - cabin A/C sensor common (replaces E10; A32-15, A24-3, A21, A18-2 stay factory)</t>
+          <t>At A/C amp - SP-AC-PSW: A/C pressure switch output</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>OEM auto A/C amplifier A32 pin 15 SG</t>
+          <t>OEM A5, factory Y-R lead</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>AMB</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="U128" t="inlineStr">
@@ -14945,31 +14941,35 @@
       </c>
       <c r="V128" t="inlineStr">
         <is>
-          <t>SP-AC-SG</t>
+          <t>SP-AC-PSW</t>
         </is>
       </c>
       <c r="W128" t="inlineStr"/>
-      <c r="X128" t="inlineStr"/>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>A/C amp branch (behind dash)</t>
+        </is>
+      </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>Auto A/C amplifier A32 pin 15 SG, behind the glove box; OEM colour V-W; EWD 1993 p.211-212; solder onto the factory lead</t>
+          <t>A/C pressure switch A5, engine bay; exact spot TBD (no locator figure in the repo); OEM colour Y-R (factory wiring; new wire here); EWD 1990 ST185 EWD p.152 (docs/electrical/ewd-snips/1990-st185-autoac-pressure-clutch-p152.png); 1990 ST185 EWD p.152 (A5 pin 4 Y-R); new-wire run terminated at the switch's own mating plug (no factory engine-bay wire reused, Section 39, 2026-10-04); plug part number not yet chosen</t>
         </is>
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>Cabin landing of SP-AC-SG on the amp sensor common.</t>
+          <t>Runs on in ST185-EngineRoom-C to A/C pressure switch A5 pin 4 (engine bay): new wire to the switch's own mating plug, plug part TBD. EWD 1990 p.152. | owner TBD: a half has no length estimate (drawn today as w_ac_psw_in on ECU-cabin, ? mm; w_ac_psw on EngineRoom-C, 100 mm)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>w_trig2_pin</t>
+          <t>w_amb_sg</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>legs of SP-CAM</t>
+          <t>legs of SP-AC-SG</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -14979,17 +14979,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>A32</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>SP-CAM</t>
+          <t>SP-AC-SG</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -14999,17 +14999,17 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Cam sensor signal</t>
+          <t>A/C sensor common</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Blue-Blue-Yellow</t>
+          <t>Blue-Yellow</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -15019,12 +15019,12 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>200</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-20-4</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
@@ -15036,22 +15036,22 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>solder onto the factory lead</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>At the ECU plugs - SP-CAM: cam signal + 1.8k pull-up to +8V</t>
+          <t>SP-AC-SG - cabin A/C sensor common (replaces E10; A32-15, A24-3, A21, A18-2 stay factory)</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>OEM auto A/C amplifier A32 pin 15 SG</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>CAM</t>
+          <t>AMB</t>
         </is>
       </c>
       <c r="U129" t="inlineStr">
@@ -15061,27 +15061,31 @@
       </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>SP-CAM</t>
+          <t>SP-AC-SG</t>
         </is>
       </c>
       <c r="W129" t="inlineStr"/>
-      <c r="X129" t="inlineStr">
-        <is>
-          <t>at ECU-A plug</t>
-        </is>
-      </c>
-      <c r="Y129" t="inlineStr"/>
-      <c r="Z129" t="inlineStr"/>
+      <c r="X129" t="inlineStr"/>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>Auto A/C amplifier A32 pin 15 SG, behind the glove box; OEM colour V-W; EWD 1993 p.211-212; solder onto the factory lead</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>Cabin landing of SP-AC-SG on the amp sensor common.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>w_csbg_ac</t>
+          <t>w_trig2_pin</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>legs of SP-CSB-GND</t>
+          <t>legs of SP-CAM</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -15091,17 +15095,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>POWER-NEG-BAR</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Lug</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>SP-CSB-GND</t>
+          <t>SP-CAM</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -15111,17 +15115,17 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>CSB3 + opto ground</t>
+          <t>Cam sensor signal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Yellow-Blue-Blue</t>
+          <t>Blue-Blue-Yellow</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -15131,12 +15135,12 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>M22759/16-20-0</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
@@ -15148,22 +15152,22 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>CSB3 ground splice - CSB3 pin 2, opto board COM and stalk ground</t>
+          <t>At the ECU plugs - SP-CAM: cam signal + 1.8k pull-up to +8V</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>POWER box NEG bar M8 stud (glove box)</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>CAM</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
@@ -15173,35 +15177,27 @@
       </c>
       <c r="V130" t="inlineStr">
         <is>
-          <t>SP-CSB-GND</t>
-        </is>
-      </c>
-      <c r="W130" t="inlineStr">
-        <is>
-          <t>SP-CSB-GND also joins ST185-CSB3</t>
-        </is>
-      </c>
+          <t>SP-CAM</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr"/>
       <c r="X130" t="inlineStr">
         <is>
-          <t>glove-box POWER box to the CSB3 branch</t>
+          <t>at ECU-A plug</t>
         </is>
       </c>
       <c r="Y130" t="inlineStr"/>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>M8 ring lug on the POWER box battery-negative bar (R213: CSB3, opto board and cruise ladder never on chassis or the ECU ground) | (CSB3 loom, under centre cluster) | est length; runs with the CSB3 +12 V (w_csb12, LOGIC CSB 5A) (R217)</t>
-        </is>
-      </c>
+      <c r="Z130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>w_fl_sig_pin</t>
+          <t>w_csbg_ac</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>legs of SP-FUEL-LVL</t>
+          <t>legs of SP-CSB-GND</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -15211,17 +15207,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>POWER-NEG-BAR</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Lug</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>SP-FUEL-LVL</t>
+          <t>SP-CSB-GND</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -15231,17 +15227,17 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Fuel level signal</t>
+          <t>CSB3 + opto ground</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Blue-Yellow-Blue</t>
+          <t>Yellow-Blue-Blue</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -15251,12 +15247,12 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>900</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-20-0</t>
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
@@ -15268,22 +15264,22 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>SP-FUEL-LVL - fuel sender signal + 470R pull-up to ECU-B B24</t>
+          <t>CSB3 ground splice - CSB3 pin 2, opto board COM and stalk ground</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>POWER box NEG bar M8 stud (glove box)</t>
         </is>
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>FLVL</t>
+          <t>CSB</t>
         </is>
       </c>
       <c r="U131" t="inlineStr">
@@ -15293,23 +15289,35 @@
       </c>
       <c r="V131" t="inlineStr">
         <is>
-          <t>SP-FUEL-LVL</t>
-        </is>
-      </c>
-      <c r="W131" t="inlineStr"/>
-      <c r="X131" t="inlineStr"/>
+          <t>SP-CSB-GND</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>SP-CSB-GND also joins ST185-CSB3</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>glove-box POWER box to the CSB3 branch</t>
+        </is>
+      </c>
       <c r="Y131" t="inlineStr"/>
-      <c r="Z131" t="inlineStr"/>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>M8 ring lug on the POWER box battery-negative bar (R213: CSB3, opto board and cruise ladder never on chassis or the ECU ground) | (CSB3 loom, under centre cluster) | est length; runs with the CSB3 +12 V (w_csb12, LOGIC CSB 5A) (R217)</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>w66</t>
+          <t>w_fl_sig_pin</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>legs of SP-GND-ECU</t>
+          <t>legs of SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -15319,17 +15327,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>POWER-NEG-BAR</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Lug</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>SP-GND-ECU</t>
+          <t>SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -15339,32 +15347,32 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>ECU power ground</t>
+          <t>Fuel level signal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Yellow-Yellow-White</t>
+          <t>Blue-Yellow-Blue</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>M22759/16-10-0</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -15376,22 +15384,22 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>ECU splice point - SP-GND-ECU: ECU power ground (A25 A34 B25 B34) to the NEG bar</t>
+          <t>SP-FUEL-LVL - fuel sender signal + 470R pull-up to ECU-B B24</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>POWER box NEG bar M8 stud (glove box)</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>GND</t>
+          <t>FLVL</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
@@ -15401,31 +15409,23 @@
       </c>
       <c r="V132" t="inlineStr">
         <is>
-          <t>SP-GND-ECU</t>
+          <t>SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="W132" t="inlineStr"/>
-      <c r="X132" t="inlineStr">
-        <is>
-          <t>ECU to the glove-box POWER box</t>
-        </is>
-      </c>
+      <c r="X132" t="inlineStr"/>
       <c r="Y132" t="inlineStr"/>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>M8 ring lug on the POWER box battery-negative bar (R216): the ECU grounds only, nothing else | est length; the ONE ECU ground return (DECISIONS R216)</t>
-        </is>
-      </c>
+      <c r="Z132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>w_rev_sw_c</t>
+          <t>w66</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>legs of SP-REV</t>
+          <t>legs of SP-GND-ECU</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -15435,17 +15435,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>DRB102-CABIN</t>
+          <t>POWER-NEG-BAR</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>Lug</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>SP-REV</t>
+          <t>SP-GND-ECU</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -15455,32 +15455,32 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Reverse sw +12 V out</t>
+          <t>ECU power ground</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Yellow-Yellow-White</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>900</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>M22759/16-16-4</t>
+          <t>M22759/16-10-0</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -15492,22 +15492,22 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>0460-202-1631</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>SP-REV - reverse switch out to CSB3 opto IN2 and IG2-13 lamps</t>
+          <t>ECU splice point - SP-GND-ECU: ECU power ground (A25 A34 B25 B34) to the NEG bar</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>DRB102 receptacle (RH firewall)</t>
+          <t>POWER box NEG bar M8 stud (glove box)</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>REV</t>
+          <t>GND</t>
         </is>
       </c>
       <c r="U133" t="inlineStr">
@@ -15517,31 +15517,31 @@
       </c>
       <c r="V133" t="inlineStr">
         <is>
-          <t>SP-REV</t>
-        </is>
-      </c>
-      <c r="W133" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine w_sw7_e at DRB102-ENGINE 78, to REV-SW 1</t>
-        </is>
-      </c>
-      <c r="X133" t="inlineStr"/>
+          <t>SP-GND-ECU</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr"/>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>ECU to the glove-box POWER box</t>
+        </is>
+      </c>
       <c r="Y133" t="inlineStr"/>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>Circuit 11: switch out tapped to opto IN2; lamps stay on the factory IG2-13 run.</t>
+          <t>M8 ring lug on the POWER box battery-negative bar (R216): the ECU grounds only, nothing else | est length; the ONE ECU ground return (DECISIONS R216)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>w_drain_ecu_a</t>
+          <t>w_rev_sw_c</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-A</t>
+          <t>legs of SP-REV</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -15551,17 +15551,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>DRB102-CABIN</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-REV</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -15571,22 +15571,22 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Shield drain</t>
+          <t>Reverse sw +12 V out</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Yellow-White-Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -15596,7 +15596,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>M22759/16-16-4</t>
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
@@ -15608,22 +15608,22 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>0460-202-1631</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>6 mm behind the ECU-A plug - SP-SHIELD-A: drains to A7</t>
+          <t>SP-REV - reverse switch out to CSB3 opto IN2 and IG2-13 lamps</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>DRB102 receptacle (RH firewall)</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>SHLD</t>
+          <t>REV</t>
         </is>
       </c>
       <c r="U134" t="inlineStr">
@@ -15633,31 +15633,31 @@
       </c>
       <c r="V134" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
-        </is>
-      </c>
-      <c r="W134" t="inlineStr"/>
-      <c r="X134" t="inlineStr">
-        <is>
-          <t>at ECU-A plug</t>
-        </is>
-      </c>
+          <t>SP-REV</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>ST185-AB-engine w_sw7_e at DRB102-ENGINE 78, to REV-SW 1</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr"/>
       <c r="Y134" t="inlineStr"/>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>build (R30): the crank drain is the one crimped into A7; the other drains are soldered onto it 6 mm behind the plug</t>
+          <t>Circuit 11: switch out tapped to opto IN2; lamps stay on the factory IG2-13 run.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>w_shd_a_aps</t>
+          <t>w_drain_ecu_a</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-A-APS</t>
+          <t>legs of SP-SHIELD-A</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -15667,22 +15667,22 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-A</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>trunk</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -15724,17 +15724,17 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>solder splice</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>At the pedal branch - SP-SHIELD-A-APS: pedal drains</t>
+          <t>6 mm behind the ECU-A plug - SP-SHIELD-A: drains to A7</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>6 mm behind the ECU-A plug - SP-SHIELD-A: drains to A7</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="T135" t="inlineStr">
@@ -15749,27 +15749,31 @@
       </c>
       <c r="V135" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-APS / SP-SHIELD-A</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="W135" t="inlineStr"/>
-      <c r="X135" t="inlineStr"/>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>at ECU-A plug</t>
+        </is>
+      </c>
       <c r="Y135" t="inlineStr"/>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>branch-point join (R207): the device drain meets the loom shield trunk where its signal wires join the main loom, then runs to the ECU splice</t>
+          <t>build (R30): the crank drain is the one crimped into A7; the other drains are soldered onto it 6 mm behind the plug</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>w_shd_a_wsf</t>
+          <t>w_shd_a_aps</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-A-WSF</t>
+          <t>legs of SP-SHIELD-A-APS</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -15789,7 +15793,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
+          <t>SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -15841,7 +15845,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>At the front WS inline - SP-SHIELD-A-WSF: front wheel-speed drains</t>
+          <t>At the pedal branch - SP-SHIELD-A-APS: pedal drains</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
@@ -15861,7 +15865,7 @@
       </c>
       <c r="V136" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-WSF / SP-SHIELD-A</t>
+          <t>SP-SHIELD-A-APS / SP-SHIELD-A</t>
         </is>
       </c>
       <c r="W136" t="inlineStr"/>
@@ -15876,12 +15880,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>w_drain_ecu_b</t>
+          <t>w_shd_a_wsf</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-B</t>
+          <t>legs of SP-SHIELD-A-WSF</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -15891,27 +15895,27 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>legs of SP-SHIELD-A</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B</t>
+          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>trunk</t>
+          <t>link</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Shield drain B</t>
+          <t>Shield drain</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -15948,17 +15952,17 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>solder splice</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>6 mm behind the ECU-B plug - SP-SHIELD-B: drains to B17</t>
+          <t>At the front WS inline - SP-SHIELD-A-WSF: front wheel-speed drains</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>6 mm behind the ECU-A plug - SP-SHIELD-A: drains to A7</t>
         </is>
       </c>
       <c r="T137" t="inlineStr">
@@ -15973,23 +15977,27 @@
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B</t>
+          <t>SP-SHIELD-A-WSF / SP-SHIELD-A</t>
         </is>
       </c>
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr"/>
       <c r="Y137" t="inlineStr"/>
-      <c r="Z137" t="inlineStr"/>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>branch-point join (R207): the device drain meets the loom shield trunk where its signal wires join the main loom, then runs to the ECU splice</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>w_shd_b_wsr</t>
+          <t>w_drain_ecu_b</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-B-WSR</t>
+          <t>legs of SP-SHIELD-B</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -15999,22 +16007,22 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-B</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B-WSR &gt; SP-SHIELD-B</t>
+          <t>SP-SHIELD-B</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>trunk</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -16056,17 +16064,17 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>solder splice</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>At the rear WS inline - SP-SHIELD-B-WSR: rear wheel-speed drains</t>
+          <t>6 mm behind the ECU-B plug - SP-SHIELD-B: drains to B17</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>6 mm behind the ECU-B plug - SP-SHIELD-B: drains to B17</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="T138" t="inlineStr">
@@ -16081,27 +16089,23 @@
       </c>
       <c r="V138" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B-WSR / SP-SHIELD-B</t>
+          <t>SP-SHIELD-B</t>
         </is>
       </c>
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr"/>
       <c r="Y138" t="inlineStr"/>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>branch-point join (R207): the device drain meets the loom shield trunk where its signal wires join the main loom, then runs to the ECU splice</t>
-        </is>
-      </c>
+      <c r="Z138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>w78</t>
+          <t>w_shd_b_wsr</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>legs of SP-SW12</t>
+          <t>legs of SP-SHIELD-B-WSR</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -16111,7 +16115,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>legs of SP-A5</t>
+          <t>legs of SP-SHIELD-B</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -16121,7 +16125,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>SP-SW12 &gt; SP-A5</t>
+          <t>SP-SHIELD-B-WSR &gt; SP-SHIELD-B</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -16131,22 +16135,22 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse (+ IG2 wake diode)</t>
+          <t>Shield drain B</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Yellow-White-Blue</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -16156,7 +16160,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>M22759/16-18-2</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
@@ -16173,17 +16177,17 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>ECU splice point - SP-SW12: switched +12 V (LOGIC SW12)</t>
+          <t>At the rear WS inline - SP-SHIELD-B-WSR: rear wheel-speed drains</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>ECU splice point - SP-A5: ECU main feed (SW12 + IG2 diode)</t>
+          <t>6 mm behind the ECU-B plug - SP-SHIELD-B: drains to B17</t>
         </is>
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>SW12</t>
+          <t>SHLD</t>
         </is>
       </c>
       <c r="U139" t="inlineStr">
@@ -16193,31 +16197,27 @@
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>SP-SW12 / SP-A5</t>
+          <t>SP-SHIELD-B-WSR / SP-SHIELD-B</t>
         </is>
       </c>
       <c r="W139" t="inlineStr"/>
-      <c r="X139" t="inlineStr">
-        <is>
-          <t>at ECU-A plug</t>
-        </is>
-      </c>
+      <c r="X139" t="inlineStr"/>
       <c r="Y139" t="inlineStr"/>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>ECU main +12 V | ECU main +12 V</t>
+          <t>branch-point join (R207): the device drain meets the loom shield trunk where its signal wires join the main loom, then runs to the ECU splice</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>w_tach</t>
+          <t>w78</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>legs of SP-TACH</t>
+          <t>legs of SP-SW12</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -16227,52 +16227,52 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>legs of SP-A5</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SP-TACH</t>
+          <t>SP-SW12 &gt; SP-A5</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>trunk</t>
+          <t>link</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Engine speed (tacho)</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse (+ IG2 wake diode)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Yellow-Blue-Yellow</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-18-2</t>
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
@@ -16284,22 +16284,22 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>solder splice</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>SP-TACH - Ign 8 tacho to A15 pin 18 and 4.7k lock-sensor tap</t>
+          <t>ECU splice point - SP-SW12: switched +12 V (LOGIC SW12)</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>ECU splice point - SP-A5: ECU main feed (SW12 + IG2 diode)</t>
         </is>
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>TACH</t>
+          <t>SW12</t>
         </is>
       </c>
       <c r="U140" t="inlineStr">
@@ -16309,24 +16309,140 @@
       </c>
       <c r="V140" t="inlineStr">
         <is>
-          <t>SP-TACH</t>
+          <t>SP-SW12 / SP-A5</t>
         </is>
       </c>
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr">
         <is>
-          <t>A/C amp branch (behind dash)</t>
+          <t>at ECU-A plug</t>
         </is>
       </c>
       <c r="Y140" t="inlineStr"/>
       <c r="Z140" t="inlineStr">
         <is>
+          <t>ECU main +12 V | ECU main +12 V</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>w_tach</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>legs of SP-TACH</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>ECU-B</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>SP-TACH</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>trunk</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Engine speed (tacho)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Yellow-Blue-Yellow</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>M22759/16-20-9</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>solder splice</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>3-1447221-4</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>SP-TACH - Ign 8 tacho to A15 pin 18 and 4.7k lock-sensor tap</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>TACH</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>ST185-AB-cabin</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>SP-TACH</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr"/>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>A/C amp branch (behind dash)</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr"/>
+      <c r="Z141" t="inlineStr">
+        <is>
           <t>Ign 8 (ECU-B 10) tacho. Split at SP-TACH: pin 18 plus 4.7k to pin 9 (OPEN-ITEMS History 2026-10-21 N61).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z140"/>
+  <autoFilter ref="A1:Z141"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16727,10 +16843,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -17632,7 +17748,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -19248,7 +19364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -19529,7 +19645,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -19551,7 +19667,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -19573,7 +19689,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -19595,7 +19711,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -19617,12 +19733,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0413-214-1205</t>
+          <t>114017</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -19639,7 +19755,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -19661,7 +19777,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -19683,7 +19799,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -19705,7 +19821,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -19727,7 +19843,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -19749,7 +19865,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -19771,7 +19887,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -19793,12 +19909,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>114017</t>
+          <t>114019-ZZ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -19815,12 +19931,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>114019-ZZ</t>
+          <t>114018-ZZ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -19837,7 +19953,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -19859,12 +19975,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>114018-ZZ</t>
+          <t>114017</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -19881,12 +19997,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>114017</t>
+          <t>114018-ZZ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -19903,7 +20019,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -19925,12 +20041,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>114018-ZZ</t>
+          <t>114019-ZZ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -19947,12 +20063,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>114019-ZZ</t>
+          <t>114017</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -19969,7 +20085,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>82</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -19991,7 +20107,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -20013,7 +20129,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -20035,7 +20151,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -20057,7 +20173,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -20079,7 +20195,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -20101,7 +20217,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>91</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -20123,7 +20239,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>92</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -20145,7 +20261,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -20167,7 +20283,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>94</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -20189,12 +20305,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>97</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>114017</t>
+          <t>0413-214-1205</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -20211,7 +20327,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>98</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -20233,7 +20349,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -20255,7 +20371,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -20277,7 +20393,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>101</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -20299,7 +20415,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -20316,34 +20432,34 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DRB102-CABIN</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>0413-214-1205</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
+          <t>spare, not used</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -20365,7 +20481,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -20387,7 +20503,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -20409,7 +20525,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -20431,7 +20547,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -20453,7 +20569,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -20475,7 +20591,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -20497,7 +20613,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -20519,7 +20635,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -20536,29 +20652,29 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>IX-WS-F-S</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>114017</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>spare, not used</t>
+          <t>spare, sealing plug</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IX-WS-F-S</t>
+          <t>IX-WS-R-S</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -20577,30 +20693,8 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>IX-WS-R-S</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>114017</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D61"/>
+  <autoFilter ref="A1:D60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20690,7 +20784,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Wires: 139   Connectors / ends: 59   Splices: 20   Spare cavities: 60</t>
+          <t>Wires: 140   Connectors / ends: 59   Splices: 20   Spare cavities: 59</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wires" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Splices" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Wires" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Splices" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Key" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wires'!$A$1:$Z$140</definedName>

--- a/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
@@ -12651,7 +12651,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -12699,13 +12699,13 @@
       <c r="W108" t="inlineStr"/>
       <c r="X108" t="inlineStr">
         <is>
-          <t>glove-box branch (POWER / LOGIC boxes)</t>
+          <t>glove-box branch (POWER / LOGIC boxes) / cabin run to the trunk relay block (Routes 1 / 11)</t>
         </is>
       </c>
       <c r="Y108" t="inlineStr"/>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>Battery relay block (trunk) relay K1 fuel pump, pin 85 | owner proposed: longer half (drawn today as w_fp85 on ECU-cabin, 390 mm; w_fp85_h on HeavyDC, 150 mm)</t>
+          <t>Battery relay block (trunk) relay K1 fuel pump, pin 85 | est length: ECU-A to the glove-box boxes (390 mm) plus the cabin run to K-FP in the trunk relay block, alongside w_k_fp_86_cp (2500 mm); row 157</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
@@ -2602,7 +2602,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>ST185-EngineRoom-C w_mrs_e at DRB102-ENGINE 84, to MRS-B 2</t>
+          <t>ST185-AB-engine w_mrs_e at DRB102-ENGINE 84, to MRS-B 2</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -12258,7 +12258,7 @@
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>ST185-EngineRoom-C w_eps_rly_e at DRB102-ENGINE 85, to MRS-B 5</t>
+          <t>ST185-AB-engine w_eps_rly_e at DRB102-ENGINE 85, to MRS-B 5</t>
         </is>
       </c>
       <c r="X104" t="inlineStr">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>ST185-EngineRoom-C w_hv_mrs_en_e at DRB102-ENGINE 83, to MRS-C 1</t>
+          <t>ST185-AB-engine w_hv_mrs_en_e at DRB102-ENGINE 83, to MRS-C 1</t>
         </is>
       </c>
       <c r="X111" t="inlineStr">

--- a/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
@@ -9706,7 +9706,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>55A1821-20-9/5-9</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>55A1821-20-9/5-9</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>55A1821-20-9/5-9</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">

--- a/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Wires" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Splices" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Key" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wires" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Splices" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wires'!$A$1:$Z$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wires'!$A$1:$Z$141</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Connectors'!$A$1:$I$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Splices'!$A$1:$G$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spare Cavities'!$A$1:$D$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spare Cavities'!$A$1:$D$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z140"/>
+  <dimension ref="A1:Z141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>ST185-EngineRoom-C w_mrs_e at DRB102-ENGINE 84, to MRS-B 2</t>
+          <t>ST185-AB-engine w_mrs_e at DRB102-ENGINE 84, to MRS-B 2</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -7908,7 +7908,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>w_rail_sp_sw12_c</t>
+          <t>w_cop_gnd_ac</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7918,69 +7918,65 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>POWER-NEG-BAR</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>SP-SW12 &gt; SP-A5</t>
-        </is>
-      </c>
+          <t>Lug</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse</t>
+          <t>Coil ground to the POWER box NEG bar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Blue-White-Yellow-Yellow</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>500</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>M22759/16-18-2</t>
+          <t>M22759/16-14-0</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>0460-202-1631</t>
+          <t>0460-220-1231</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>solder splice SP-SW12</t>
+          <t>320575</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -7990,12 +7986,12 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>via SP-SW12 &gt; SP-A5</t>
+          <t>POWER box NEG bar M8 stud (glove box)</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>SW12</t>
+          <t>COPG</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -8005,30 +8001,30 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>SP-SW12</t>
+          <t>COPG</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_rail_sp_sw12_e at DRB102-ENGINE 30, to splice SP-SW12-ENG</t>
+          <t>ST185-AB-engine w_cop_gnd_e_ae at DRB102-ENGINE 4, to splice SP-CHASSIS-ENG</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>trunk ECU-A to bulkhead (RH firewall)</t>
+          <t>bulkhead to the glove-box POWER box</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>+12 V boost + flex | +12 V boost + flex</t>
+          <t>(firewall bulkhead, RH) | M8 ring lug on the POWER box battery-negative bar (Dan 2026-10-29: coil ground, cleanest return) | est length; runs with the coil +12 V (w_cop_pwr_ac, LOGIC COP 15 A) from the glove box to bulkhead pin 1 / 4; 14 AWG like that feed</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>w_shc_flex</t>
+          <t>w_rail_sp_sw12_c</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -8038,7 +8034,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8048,12 +8044,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-SW12 &gt; SP-A5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -8063,22 +8059,22 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Flex fuel shield</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Yellow-Yellow-Yellow</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -8088,7 +8084,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>M22759/16-18-2</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -8100,7 +8096,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-A</t>
+          <t>solder splice SP-SW12</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -8110,12 +8106,12 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-A</t>
+          <t>via SP-SW12 &gt; SP-A5</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>SW12</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -8125,12 +8121,12 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-SW12</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_flex_sh at DRB102-ENGINE 32, to NC, floats NC</t>
+          <t>ST185-AB-engine w_rail_sp_sw12_e at DRB102-ENGINE 30, to splice SP-SW12-ENG</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
@@ -8139,12 +8135,16 @@
         </is>
       </c>
       <c r="Y68" t="inlineStr"/>
-      <c r="Z68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>+12 V boost + flex | +12 V boost + flex</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>w_shc_etbs</t>
+          <t>w_shc_flex</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Throttle shield</t>
+          <t>Flex fuel shield</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Blue-Blue-White</t>
+          <t>Yellow-Yellow-Yellow</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>ETBS</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_etbs_sh at DRB102-ENGINE 47, to NC, floats NC</t>
+          <t>ST185-AB-engine cab_flex_sh at DRB102-ENGINE 32, to NC, floats NC</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
@@ -8260,7 +8260,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>w_shc_etbm</t>
+          <t>w_shc_etbs</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -8270,22 +8270,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>ETB motor shield</t>
+          <t>Throttle shield</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Blue-Yellow-White</t>
+          <t>Blue-Blue-White</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-B</t>
+          <t>solder splice SP-SHIELD-A</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -8342,12 +8342,12 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-B</t>
+          <t>via SP-SHIELD-A</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>ETBM</t>
+          <t>ETBS</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8357,22 +8357,26 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_etbm_ae_sh at DRB102-ENGINE 50, to NC, floats NC</t>
-        </is>
-      </c>
-      <c r="X70" t="inlineStr"/>
+          <t>ST185-AB-engine cab_etbs_sh at DRB102-ENGINE 47, to NC, floats NC</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>trunk ECU-A to bulkhead (RH firewall)</t>
+        </is>
+      </c>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>w_shc_turbo</t>
+          <t>w_shc_etbm</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8382,22 +8386,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-SHIELD-B</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -8407,7 +8411,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Turbo speed shield</t>
+          <t>ETB motor shield</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8417,7 +8421,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Yellow-Blue-White</t>
+          <t>Blue-Yellow-White</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -8444,7 +8448,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-A</t>
+          <t>solder splice SP-SHIELD-B</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -8454,12 +8458,12 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-A</t>
+          <t>via SP-SHIELD-B</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>TURBO</t>
+          <t>ETBM</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8469,26 +8473,22 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-SHIELD-B</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_turbo_sh at DRB102-ENGINE 57, to NC, floats NC</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>trunk ECU-A to bulkhead (RH firewall)</t>
-        </is>
-      </c>
+          <t>ST185-AB-engine cab_etbm_ae_sh at DRB102-ENGINE 50, to NC, floats NC</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>w_rail_sp_8v_c</t>
+          <t>w_shc_turbo</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8508,12 +8508,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SP-8V</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -8523,17 +8523,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>+8 V to cam sensor</t>
+          <t>Turbo speed shield</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>White-Blue-White</t>
+          <t>Yellow-Blue-White</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>solder splice SP-8V</t>
+          <t>solder splice SP-SHIELD-A</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>via SP-8V</t>
+          <t>via SP-SHIELD-A</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>8V</t>
+          <t>TURBO</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8585,12 +8585,12 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>SP-8V</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_rail_sp_8v_e at DRB102-ENGINE 63, to CAM 1</t>
+          <t>ST185-AB-engine cab_turbo_sh at DRB102-ENGINE 57, to NC, floats NC</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
@@ -8604,7 +8604,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>w_cam_sig_c</t>
+          <t>w_rail_sp_8v_c</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SP-CAM</t>
+          <t>SP-8V</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -8639,17 +8639,17 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Cam sensor signal</t>
+          <t>+8 V to cam sensor</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Blue-Blue-Yellow</t>
+          <t>White-Blue-White</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-20-3</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -8676,7 +8676,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>solder splice SP-CAM</t>
+          <t>solder splice SP-8V</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -8686,12 +8686,12 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>via SP-CAM</t>
+          <t>via SP-8V</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>CAM</t>
+          <t>8V</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8701,12 +8701,12 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>SP-CAM</t>
+          <t>SP-8V</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_cam_c2 at DRB102-ENGINE 64, to CAM 2</t>
+          <t>ST185-AB-engine w_rail_sp_8v_e at DRB102-ENGINE 63, to CAM 1</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
@@ -8720,7 +8720,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>w_shc_cam</t>
+          <t>w_cam_sig_c</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-CAM</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Cam sensor shield</t>
+          <t>Cam sensor signal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-A</t>
+          <t>solder splice SP-CAM</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-A</t>
+          <t>via SP-CAM</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
@@ -8817,12 +8817,12 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-CAM</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_cam_sh at DRB102-ENGINE 66, to NC, floats NC</t>
+          <t>ST185-AB-engine cab_cam_c2 at DRB102-ENGINE 64, to CAM 2</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
@@ -8836,7 +8836,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>w_rail_sw12_b_c_ac</t>
+          <t>w_shc_cam</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -8856,12 +8856,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SP-SW12 &gt; SP-A5</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -8871,17 +8871,17 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse</t>
+          <t>Cam sensor shield</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Blue-Blue-Yellow</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>M22759/16-20-2</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -8908,7 +8908,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>solder splice SP-SW12</t>
+          <t>solder splice SP-SHIELD-A</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>via SP-SW12 &gt; SP-A5</t>
+          <t>via SP-SHIELD-A</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>SW12</t>
+          <t>CAM</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8933,30 +8933,26 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>SP-SW12</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_vss_12v at DRB102-ENGINE 67, to VSS 1</t>
+          <t>ST185-AB-engine cab_cam_sh at DRB102-ENGINE 66, to NC, floats NC</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>to ECU-B plug (beside ECU-A)</t>
+          <t>trunk ECU-A to bulkhead (RH firewall)</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr"/>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>+12 V gearbox speed | (firewall bulkhead, RH); sensor +12V | owner TBD: a half has no length estimate (drawn today as w_rail_sw12_b_c_ac on ECU-cabin, ? mm; w_rail_sw12_b_c on ECU-cabin, 520 mm)</t>
-        </is>
-      </c>
+      <c r="Z75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>w_vss_sig_c</t>
+          <t>w_rail_sw12_b_c_ac</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8966,38 +8962,42 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>67</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>SP-SW12 &gt; SP-A5</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Gearbox speed signal</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Yellow-White-Yellow</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-20-2</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>solder splice SP-SW12</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -9034,12 +9034,12 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>via SP-SW12 &gt; SP-A5</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>VSS</t>
+          <t>SW12</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -9049,22 +9049,30 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>VSS</t>
+          <t>SP-SW12</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_vss_sig_e at DRB102-ENGINE 68, to VSS 3</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr"/>
+          <t>ST185-AB-engine w_vss_12v at DRB102-ENGINE 67, to VSS 1</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>to ECU-B plug (beside ECU-A)</t>
+        </is>
+      </c>
       <c r="Y76" t="inlineStr"/>
-      <c r="Z76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>+12 V gearbox speed | (firewall bulkhead, RH); sensor +12V | owner TBD: a half has no length estimate (drawn today as w_rail_sw12_b_c_ac on ECU-cabin, ? mm; w_rail_sw12_b_c on ECU-cabin, 520 mm)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>w_shc_vss</t>
+          <t>w_vss_sig_c</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -9074,7 +9082,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9084,27 +9092,23 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>SP-SHIELD-B</t>
-        </is>
-      </c>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Gearbox speed shield</t>
+          <t>Gearbox speed signal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9119,12 +9123,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>540</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -9136,7 +9140,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-B</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -9146,7 +9150,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-B</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -9161,12 +9165,12 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B</t>
+          <t>VSS</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_vss_sh at DRB102-ENGINE 69, to NC, floats NC</t>
+          <t>ST185-AB-engine w_vss_sig_e at DRB102-ENGINE 68, to VSS 3</t>
         </is>
       </c>
       <c r="X77" t="inlineStr"/>
@@ -9176,7 +9180,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>w12_c</t>
+          <t>w_shc_vss</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -9186,38 +9190,42 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-B</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>SP-SHIELD-B</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Knock sensor (-)</t>
+          <t>Gearbox speed shield</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Blue-Blue-Blue-White</t>
+          <t>Yellow-White-Yellow</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -9227,12 +9235,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -9244,7 +9252,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>solder splice SP-SHIELD-B</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -9254,12 +9262,12 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>DT06-12 plug (ECU splice point)</t>
+          <t>via SP-SHIELD-B</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>KNOCK</t>
+          <t>VSS</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -9269,26 +9277,22 @@
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-B</t>
+          <t>SP-SHIELD-B</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_knock1_c2 at DRB102-ENGINE 72, to KNOCK-1 2</t>
-        </is>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>trunk ECU to bulkhead (RH firewall)</t>
-        </is>
-      </c>
+          <t>ST185-AB-engine cab_vss_sh at DRB102-ENGINE 69, to NC, floats NC</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>w_shc_knock1</t>
+          <t>w12_c</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -9298,37 +9302,33 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>BUS-GNDOUT-B</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>SP-SHIELD-B</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Knock sensor shield</t>
+          <t>Knock sensor (-)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>430</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>M22759/16-20-6</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -9360,7 +9360,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-B</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-B</t>
+          <t>DT06-12 plug (ECU splice point)</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -9385,22 +9385,26 @@
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B</t>
+          <t>BUS-GNDOUT-B</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_knock1_sh at DRB102-ENGINE 73, to NC, floats NC</t>
-        </is>
-      </c>
-      <c r="X79" t="inlineStr"/>
+          <t>ST185-AB-engine cab_knock1_c2 at DRB102-ENGINE 72, to KNOCK-1 2</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>trunk ECU to bulkhead (RH firewall)</t>
+        </is>
+      </c>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>w_shc_crank</t>
+          <t>w_shc_knock1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9410,22 +9414,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-SHIELD-B</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -9435,7 +9439,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Crank sensor shield</t>
+          <t>Knock sensor shield</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -9445,7 +9449,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Blue-Blue-White-Blue</t>
+          <t>Blue-Blue-Blue-White</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -9472,7 +9476,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-A</t>
+          <t>solder splice SP-SHIELD-B</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -9482,12 +9486,12 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-A</t>
+          <t>via SP-SHIELD-B</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>CRANKC</t>
+          <t>KNOCK</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9497,30 +9501,22 @@
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-SHIELD-B</t>
         </is>
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_crank_sh at DRB102-ENGINE 76, to NC, floats NC</t>
-        </is>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>trunk ECU-A to bulkhead (RH firewall)</t>
-        </is>
-      </c>
+          <t>ST185-AB-engine cab_knock1_sh at DRB102-ENGINE 73, to NC, floats NC</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr"/>
       <c r="Y80" t="inlineStr"/>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>build (R30): this drain is the one crimped into A7</t>
-        </is>
-      </c>
+      <c r="Z80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>wc_h_bh_bc</t>
+          <t>w_shc_crank</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9530,42 +9526,42 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ECU-C</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SP-CANH</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>leg core</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>CAN H to CAN-Lambda</t>
+          <t>Crank sensor shield</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Blue-Blue-White-Blue</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -9575,24 +9571,16 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>(cable core)</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>CAB-CANBH-BC</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
           <t>TBD</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>0460-202-1631</t>
@@ -9600,7 +9588,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>solder splice SP-CANH</t>
+          <t>solder splice SP-SHIELD-A</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -9610,12 +9598,12 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>via SP-CANH</t>
+          <t>via SP-SHIELD-A</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>CRANKC</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9625,26 +9613,30 @@
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>SP-CANH</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>ST185-AB-engine wc_h_lam_be at DRB102-ENGINE 79, to splice SP-CANH-LAM; SP-CANH also joins ST185-CAN</t>
-        </is>
-      </c>
-      <c r="X81" t="inlineStr"/>
+          <t>ST185-AB-engine cab_crank_sh at DRB102-ENGINE 76, to NC, floats NC</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>trunk ECU-A to bulkhead (RH firewall)</t>
+        </is>
+      </c>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as wc_h_bh on CAN, ? mm; wc_h_bh_bc on ECU-cabin, 120 mm)</t>
+          <t>build (R30): this drain is the one crimped into A7</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>wc_l_bh_bc</t>
+          <t>wc_h_bh_bc</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9654,7 +9646,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -9664,12 +9656,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SP-CANL</t>
+          <t>SP-CANH</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -9679,12 +9671,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>CAN L to CAN-Lambda</t>
+          <t>CAN H to CAN-Lambda</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9714,7 +9706,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>55A1821-20-9/5-9</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9724,7 +9716,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>solder splice SP-CANL</t>
+          <t>solder splice SP-CANH</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -9734,7 +9726,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>via SP-CANL</t>
+          <t>via SP-CANH</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
@@ -9749,26 +9741,26 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>SP-CANL</t>
+          <t>SP-CANH</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>ST185-AB-engine wc_l_lam_be at DRB102-ENGINE 80, to splice SP-CANL-LAM; SP-CANL also joins ST185-CAN</t>
+          <t>ST185-AB-engine wc_h_lam_be at DRB102-ENGINE 79, to splice SP-CANH-LAM; SP-CANH also joins ST185-CAN</t>
         </is>
       </c>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as wc_l_bh on CAN, ? mm; wc_l_bh_bc on ECU-cabin, 120 mm)</t>
+          <t>owner TBD: a half has no length estimate (drawn today as wc_h_bh on CAN, ? mm; wc_h_bh_bc on ECU-cabin, 120 mm)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>cab_canbh_bc_sh</t>
+          <t>wc_l_bh_bc</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9778,7 +9770,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -9788,12 +9780,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SP-CAN-SH-BH &gt; SP-CAN-SH-CLU</t>
+          <t>SP-CANL</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -9803,12 +9795,12 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>CAN-Lambda shield</t>
+          <t>CAN L to CAN-Lambda</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9816,7 +9808,11 @@
           <t>Yellow</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>120</t>
@@ -9834,7 +9830,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>55A1821-20-9/5-9</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9844,7 +9840,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>solder splice SP-CAN-SH-BH</t>
+          <t>solder splice SP-CANL</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -9854,7 +9850,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>via SP-CAN-SH-BH &gt; SP-CAN-SH-CLU</t>
+          <t>via SP-CANL</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
@@ -9869,26 +9865,26 @@
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>SP-CAN-SH-BH</t>
+          <t>SP-CANL</t>
         </is>
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_lamcan_be_sh at DRB102-ENGINE 81, to NC, floats NC; SP-CAN-SH-BH also joins ST185-CAN; SP-CAN-SH-CLU also joins ST185-CAN</t>
+          <t>ST185-AB-engine wc_l_lam_be at DRB102-ENGINE 80, to splice SP-CANL-LAM; SP-CANL also joins ST185-CAN</t>
         </is>
       </c>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as cab_can_bh_sh on CAN, ? mm; cab_canbh_bc_sh on ECU-cabin, 120 mm)</t>
+          <t>owner TBD: a half has no length estimate (drawn today as wc_l_bh on CAN, ? mm; wc_l_bh_bc on ECU-cabin, 120 mm)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>w_lamg_ac</t>
+          <t>cab_canbh_bc_sh</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9898,65 +9894,73 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>POWER-NEG-BAR</t>
+          <t>ECU-C</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Lug</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>SP-CAN-SH-BH &gt; SP-CAN-SH-CLU</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg core</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>CAN-Lambda ground</t>
+          <t>CAN-Lambda shield</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Shield</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Blue-White-White</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>120</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>M22759/16-14-0</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>CAB-CANBH-BC</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>55A1821-20-9/5-9</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>0460-220-1231</t>
+          <t>0460-202-1631</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>320575</t>
+          <t>solder splice SP-CAN-SH-BH</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -9966,12 +9970,12 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>POWER box NEG bar M8 stud (glove box)</t>
+          <t>via SP-CAN-SH-BH &gt; SP-CAN-SH-CLU</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>LAM</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9981,50 +9985,46 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>LAM</t>
+          <t>SP-CAN-SH-BH</t>
         </is>
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_lamg_be14 at DRB102-ENGINE 96, to splice SP-LAMG-B</t>
-        </is>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>bulkhead to the glove-box POWER box</t>
-        </is>
-      </c>
+          <t>ST185-AB-engine cab_lamcan_be_sh at DRB102-ENGINE 81, to NC, floats NC; SP-CAN-SH-BH also joins ST185-CAN; SP-CAN-SH-CLU also joins ST185-CAN</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>(firewall bulkhead, RH) | M8 ring lug on the POWER box battery-negative bar (R213: a CAN node never on chassis or the ECU ground) | est length; runs with the CAN-Lambda +12 V (w_lam12_cp, LOGIC LAM) from the glove box to bulkhead pin 95 / 96 (R217)</t>
+          <t>owner TBD: a half has no length estimate (drawn today as cab_can_bh_sh on CAN, ? mm; cab_canbh_bc_sh on ECU-cabin, 120 mm)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>w_rev_feed_c</t>
+          <t>w_lamg_ac</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>IG2</t>
+          <t>DRB102-CABIN</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>DRB102-CABIN</t>
+          <t>POWER-NEG-BAR</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>Lug</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -10035,59 +10035,59 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Back-up sw +12 V in</t>
+          <t>CAN-Lambda ground</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue-White-White</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>500</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>M22759/16-16-2</t>
+          <t>M22759/16-14-0</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>crimp butt splice into the factory cowl-</t>
+          <t>0460-220-1231</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>0460-202-1631</t>
+          <t>320575</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>OEM IG2 pin 4 (under the ECU, cowl side) - factory back-up SW feed</t>
+          <t>DRB102 receptacle (RH firewall)</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>DRB102 receptacle (RH firewall)</t>
+          <t>POWER box NEG bar M8 stud (glove box)</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>REV</t>
+          <t>LAM</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -10097,30 +10097,30 @@
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>REV</t>
+          <t>LAM</t>
         </is>
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_rev_feed_e at DRB102-ENGINE 77, to REV-SW 2</t>
-        </is>
-      </c>
-      <c r="X85" t="inlineStr"/>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>OEM IG2 pin 4 (under the ECU, cowl side) - R-L, GAUGE 15 A back-up SW feed; OEM colour R-L; EWD 1992 p.132 / 1990 p.82; crimp butt splice into the factory cowl-side lead at IG2 (cabin, under the ECU; the engine wire is removed)</t>
-        </is>
-      </c>
+          <t>ST185-AB-engine w_lamg_be14 at DRB102-ENGINE 96, to splice SP-LAMG-B</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>bulkhead to the glove-box POWER box</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>Circuit 11: factory feed kept. New engine-harness switch in splices to the IG2-4 pigtail.</t>
+          <t>(firewall bulkhead, RH) | M8 ring lug on the POWER box battery-negative bar (R213: a CAN node never on chassis or the ECU ground) | est length; runs with the CAN-Lambda +12 V (w_lam12_cp, LOGIC LAM) from the glove box to bulkhead pin 95 / 96 (R217)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>w_rev_lamps</t>
+          <t>w_rev_feed_c</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10140,27 +10140,23 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>SP-REV</t>
-        </is>
-      </c>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Back-up lamp +12 V</t>
+          <t>Back-up sw +12 V in</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10175,12 +10171,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>840</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>M22759/16-16-4</t>
+          <t>M22759/16-16-2</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -10192,17 +10188,17 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>solder splice SP-REV</t>
+          <t>0460-202-1631</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>OEM IG2 pin 13 (under the ECU, cowl side) - factory back-up lamp output</t>
+          <t>OEM IG2 pin 4 (under the ECU, cowl side) - factory back-up SW feed</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>via SP-REV</t>
+          <t>DRB102 receptacle (RH firewall)</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
@@ -10217,55 +10213,55 @@
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>SP-REV</t>
+          <t>REV</t>
         </is>
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_sw7_e at DRB102-ENGINE 78, to REV-SW 1</t>
+          <t>ST185-AB-engine w_rev_feed_e at DRB102-ENGINE 77, to REV-SW 2</t>
         </is>
       </c>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>OEM IG2 pin 13 (under the ECU, cowl side) - R-B, back-up lamp output; OEM colour R-B; EWD 1992 p.132; crimp butt splice into the factory cowl-side lead at IG2</t>
+          <t>OEM IG2 pin 4 (under the ECU, cowl side) - R-L, GAUGE 15 A back-up SW feed; OEM colour R-L; EWD 1992 p.132 / 1990 p.82; crimp butt splice into the factory cowl-side lead at IG2 (cabin, under the ECU; the engine wire is removed)</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>Circuit 11: new switch out splices to the IG2-13 pigtail; rear lamps stay on the factory harness.</t>
+          <t>Circuit 11: factory feed kept. New engine-harness switch in splices to the IG2-4 pigtail.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>w_fl_sig</t>
+          <t>w_rev_lamps</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>IX-FUEL-P</t>
+          <t>IG2</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>DRB102-CABIN</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SP-FUEL-LVL</t>
+          <t>SP-REV</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -10275,22 +10271,22 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Fuel level signal</t>
+          <t>Back-up lamp +12 V</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
           <t>White</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>Blue-Yellow-Blue</t>
-        </is>
-      </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -10300,34 +10296,34 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-16-4</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>0460-202-1631</t>
+          <t>crimp butt splice into the factory cowl-</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>solder splice SP-FUEL-LVL</t>
+          <t>solder splice SP-REV</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>IX-FUEL inline to fuel sender lead (trunk end)</t>
+          <t>OEM IG2 pin 13 (under the ECU, cowl side) - factory back-up lamp output</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>via SP-FUEL-LVL</t>
+          <t>via SP-REV</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>FLVL</t>
+          <t>REV</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -10337,18 +10333,30 @@
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>SP-FUEL-LVL</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr"/>
+          <t>SP-REV</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>ST185-AB-engine w_sw7_e at DRB102-ENGINE 78, to REV-SW 1</t>
+        </is>
+      </c>
       <c r="X87" t="inlineStr"/>
-      <c r="Y87" t="inlineStr"/>
-      <c r="Z87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>OEM IG2 pin 13 (under the ECU, cowl side) - R-B, back-up lamp output; OEM colour R-B; EWD 1992 p.132; crimp butt splice into the factory cowl-side lead at IG2</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>Circuit 11: new switch out splices to the IG2-13 pigtail; rear lamps stay on the factory harness.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>w45</t>
+          <t>w_fl_sig</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10358,38 +10366,42 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-B</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr"/>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>SP-FUEL-LVL</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Fuel level ground</t>
+          <t>Fuel level signal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Yellow-Yellow</t>
+          <t>Blue-Yellow-Blue</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -10404,7 +10416,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
@@ -10416,7 +10428,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>solder splice SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -10426,12 +10438,12 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>DT06-12 plug (ECU splice point)</t>
+          <t>via SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>SGND</t>
+          <t>FLVL</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -10441,7 +10453,7 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-B</t>
+          <t>SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="W88" t="inlineStr"/>
@@ -10452,48 +10464,48 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>cab_fspur_5v</t>
+          <t>w45</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>IX-WS-F-S</t>
+          <t>IX-FUEL-P</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>BUS-5V</t>
+          <t>BUS-GNDOUT-B</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>VRC-F +5V</t>
+          <t>Fuel level ground</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Blue-Blue</t>
+          <t>Yellow-Yellow</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -10508,22 +10520,14 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>(cable core)</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>CAB-FSPUR</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>55A1831-20-2/4/6-9</t>
-        </is>
-      </c>
+          <t>M22759/16-20-6</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
+          <t>0460-202-1631</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
@@ -10533,7 +10537,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>to front VR conditioner</t>
+          <t>IX-FUEL inline to fuel sender lead (trunk end)</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -10543,7 +10547,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>5V</t>
+          <t>SGND</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -10553,22 +10557,18 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>BUS-5V</t>
+          <t>BUS-GNDOUT-B</t>
         </is>
       </c>
       <c r="W89" t="inlineStr"/>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>dash branch (front WS inline)</t>
-        </is>
-      </c>
+      <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>cab_fspur_gnd</t>
+          <t>cab_fspur_5v</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10578,17 +10578,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-A</t>
+          <t>BUS-5V</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -10599,17 +10599,17 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>VRC-F GND</t>
+          <t>VRC-F +5V</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Yellow-Yellow</t>
+          <t>Blue-Blue</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -10659,7 +10659,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>SGND</t>
+          <t>5V</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10669,7 +10669,7 @@
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-A</t>
+          <t>BUS-5V</t>
         </is>
       </c>
       <c r="W90" t="inlineStr"/>
@@ -10684,7 +10684,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>cab_fspur_l</t>
+          <t>cab_fspur_gnd</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10694,17 +10694,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>BUS-GNDOUT-A</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
@@ -10715,17 +10715,17 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>FL conditioned out</t>
+          <t>VRC-F GND</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>White-Blue-Yellow</t>
+          <t>Yellow-Yellow</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -10770,12 +10770,12 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>DT06-12 plug (ECU splice point)</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>WSSF</t>
+          <t>SGND</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>WSSF</t>
+          <t>BUS-GNDOUT-A</t>
         </is>
       </c>
       <c r="W91" t="inlineStr"/>
@@ -10800,7 +10800,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>cab_fspur_r_ac</t>
+          <t>cab_fspur_l</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10810,17 +10810,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
@@ -10831,12 +10831,12 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>FR conditioned out</t>
+          <t>FL conditioned out</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>330</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -10861,12 +10861,12 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>CAB-FSPUR-FR-AC</t>
+          <t>CAB-FSPUR</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>55A1811-20-9-9CS2275</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
@@ -10911,16 +10911,12 @@
         </is>
       </c>
       <c r="Y92" t="inlineStr"/>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>ECU-B plug pin B21 (Link G4X, centre dash); wheel speed | owner proposed: longer half (drawn today as cab_fspur_r_ac on ECU-cabin, 350 mm; cab_fspur_r on ECU-cabin, 530 mm)</t>
-        </is>
-      </c>
+      <c r="Z92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>cab_fspur_sh</t>
+          <t>cab_fspur_r_ac</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10930,37 +10926,33 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
-        </is>
-      </c>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>leg core</t>
+          <t>core</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>WS-F screen drain</t>
+          <t>FR conditioned out</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -10968,10 +10960,14 @@
           <t>White-Blue-Yellow</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>350</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -10981,12 +10977,12 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>CAB-FSPUR</t>
+          <t>CAB-FSPUR-FR-AC</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>55A1811-20-9-9CS2275</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -10996,7 +10992,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-A-WSF</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -11006,7 +11002,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
@@ -11021,7 +11017,7 @@
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-WSF</t>
+          <t>WSSF</t>
         </is>
       </c>
       <c r="W93" t="inlineStr"/>
@@ -11031,60 +11027,64 @@
         </is>
       </c>
       <c r="Y93" t="inlineStr"/>
-      <c r="Z93" t="inlineStr"/>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>ECU-B plug pin B21 (Link G4X, centre dash); wheel speed | owner proposed: longer half (drawn today as cab_fspur_r_ac on ECU-cabin, 350 mm; cab_fspur_r on ECU-cabin, 530 mm)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>cab_rspur_5v</t>
+          <t>cab_fspur_sh</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>IX-WS-R-S</t>
+          <t>IX-WS-F-S</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>BUS-5V</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
+        </is>
+      </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>leg core</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>VRC-R +5V</t>
+          <t>WS-F screen drain</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Shield</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Blue-Blue</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>White-Blue-Yellow</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -11097,12 +11097,12 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>CAB-RSPUR</t>
+          <t>CAB-FSPUR</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>55A1841-20-2/4/5/6-9</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11112,22 +11112,22 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>solder splice SP-SHIELD-A-WSF</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>IX-WS-R inline to rear VRC (dash above ECU)</t>
+          <t>to front VR conditioner</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>DT06-12 plug (ECU splice point)</t>
+          <t>via SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>5V</t>
+          <t>WSSF</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -11137,18 +11137,22 @@
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>BUS-5V</t>
+          <t>SP-SHIELD-A-WSF</t>
         </is>
       </c>
       <c r="W94" t="inlineStr"/>
-      <c r="X94" t="inlineStr"/>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>dash branch (front WS inline)</t>
+        </is>
+      </c>
       <c r="Y94" t="inlineStr"/>
       <c r="Z94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>cab_rspur_gnd</t>
+          <t>cab_rspur_5v</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -11158,17 +11162,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-B</t>
+          <t>BUS-5V</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
@@ -11179,17 +11183,17 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>VRC-R GND</t>
+          <t>VRC-R +5V</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Yellow-Yellow</t>
+          <t>Blue-Blue</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -11239,7 +11243,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>SGND</t>
+          <t>5V</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -11249,7 +11253,7 @@
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-B</t>
+          <t>BUS-5V</t>
         </is>
       </c>
       <c r="W95" t="inlineStr"/>
@@ -11260,7 +11264,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>cab_rspur_l</t>
+          <t>cab_rspur_gnd</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -11270,17 +11274,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>BUS-GNDOUT-B</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>ECU-B</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -11291,17 +11295,17 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Rear left wheel spd</t>
+          <t>VRC-R GND</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Blue-Blue-Yellow-Yellow</t>
+          <t>Yellow-Yellow</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -11311,7 +11315,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -11336,7 +11340,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -11346,12 +11350,12 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>DT06-12 plug (ECU splice point)</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>WSSR</t>
+          <t>SGND</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -11361,7 +11365,7 @@
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>WSSR</t>
+          <t>BUS-GNDOUT-B</t>
         </is>
       </c>
       <c r="W96" t="inlineStr"/>
@@ -11372,7 +11376,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>cab_rspur_r</t>
+          <t>cab_rspur_l</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -11382,7 +11386,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11392,7 +11396,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -11403,12 +11407,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Rear right wheel spd</t>
+          <t>Rear left wheel spd</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11484,7 +11488,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>cab_rspur_sh</t>
+          <t>cab_rspur_r</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -11494,7 +11498,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -11504,27 +11508,23 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>SP-SHIELD-B-WSR &gt; SP-SHIELD-B</t>
-        </is>
-      </c>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>leg core</t>
+          <t>core</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>WS-R screen drain</t>
+          <t>Rear right wheel spd</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11532,10 +11532,14 @@
           <t>Blue-Blue-Yellow-Yellow</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>530</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -11560,7 +11564,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-B-WSR</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -11570,7 +11574,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-B-WSR &gt; SP-SHIELD-B</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
@@ -11585,7 +11589,7 @@
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B-WSR</t>
+          <t>WSSR</t>
         </is>
       </c>
       <c r="W98" t="inlineStr"/>
@@ -11596,86 +11600,98 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>w_ig2_in</t>
+          <t>cab_rspur_sh</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>JB1-1H</t>
+          <t>IX-WS-R-S</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>D-IG2-WAKE</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr"/>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>SP-SHIELD-B-WSR &gt; SP-SHIELD-B</t>
+        </is>
+      </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg core</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>IG2 wake feed</t>
+          <t>WS-R screen drain</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Shield</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Blue-Yellow-Yellow-White</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Blue-Blue-Yellow-Yellow</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>CAB-RSPUR</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>55A1841-20-2/4/5/6-9</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>solder onto the factory lead</t>
-        </is>
-      </c>
-      <c r="Q99" t="inlineStr"/>
+          <t>0462-201-1631</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>solder splice SP-SHIELD-B-WSR</t>
+        </is>
+      </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O</t>
+          <t>IX-WS-R inline to rear VRC (dash above ECU)</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>IG2 wake diode (1N5822)</t>
+          <t>via SP-SHIELD-B-WSR &gt; SP-SHIELD-B</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>IG2WAKE</t>
+          <t>WSSR</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -11685,26 +11701,18 @@
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>IG2WAKE</t>
+          <t>SP-SHIELD-B-WSR</t>
         </is>
       </c>
       <c r="W99" t="inlineStr"/>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>IG2 tap branch (LH kick panel)</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O - IGN fuse out (EWD 1993 p.62); same lead as the ECU-B B28 sense tap, own splice; OEM colour B-O; EWD 1993 TIS EWD p.62 (Power Source); solder splice onto the factory lead</t>
-        </is>
-      </c>
+      <c r="X99" t="inlineStr"/>
+      <c r="Y99" t="inlineStr"/>
       <c r="Z99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>w_ign</t>
+          <t>w_ig2_in</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -11719,12 +11727,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>D-IG2-WAKE</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
@@ -11735,7 +11743,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Ignition sw sense</t>
+          <t>IG2 wake feed</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -11745,7 +11753,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Blue-Yellow-White-Blue</t>
+          <t>Blue-Yellow-Yellow-White</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -11755,7 +11763,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>900</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -11770,11 +11778,7 @@
           <t>solder onto the factory lead</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>3-1447221-4</t>
-        </is>
-      </c>
+      <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr">
         <is>
           <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O</t>
@@ -11782,12 +11786,12 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>IG2 wake diode (1N5822)</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>IGNSW</t>
+          <t>IG2WAKE</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -11797,14 +11801,18 @@
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>IGNSW</t>
+          <t>IG2WAKE</t>
         </is>
       </c>
       <c r="W100" t="inlineStr"/>
-      <c r="X100" t="inlineStr"/>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>IG2 tap branch (LH kick panel)</t>
+        </is>
+      </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O - IGN fuse out (EWD 1993 p.62); OEM colour B-O; EWD 1993 TIS EWD p.62 (Power Source); solder splice onto the factory lead</t>
+          <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O - IGN fuse out (EWD 1993 p.62); same lead as the ECU-B B28 sense tap, own splice; OEM colour B-O; EWD 1993 TIS EWD p.62 (Power Source); solder splice onto the factory lead</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr"/>
@@ -11812,94 +11820,90 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>w_acc86</t>
+          <t>w_ign</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>K-ACC</t>
+          <t>JB1-1H</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LOGIC</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>BUS2-8</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>SP-ACC12</t>
-        </is>
-      </c>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>A/C clutch relay coil+</t>
+          <t>Ignition sw sense</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Yellow-Blue</t>
+          <t>Blue-Yellow-White-Blue</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>M22759/16-18-2</t>
+          <t>M22759/16-20-4</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>280919-2</t>
+          <t>solder onto the factory lead</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>solder splice SP-ACC12</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>B2-M5 A/C clutch relay (k_acc) - amp A15 pin 8 sinks coil- (85); coil+ (86) fused +12 V from B2-BUS2-8</t>
+          <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>via SP-ACC12</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>IGNSW</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -11909,71 +11913,67 @@
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>SP-ACC12</t>
-        </is>
-      </c>
-      <c r="W101" t="inlineStr">
-        <is>
-          <t>SP-ACC12 also joins ST185-CabinPower</t>
-        </is>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A/C amp branch (behind dash)</t>
-        </is>
-      </c>
-      <c r="Y101" t="inlineStr"/>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>LOGIC box (glove box) relay M15 A/C clutch, pin 86 | B15: coil 86 is fused +12 V. Pressure switch stays on amp pin 13 only.</t>
-        </is>
-      </c>
+          <t>IGNSW</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr"/>
+      <c r="X101" t="inlineStr"/>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O - IGN fuse out (EWD 1993 p.62); OEM colour B-O; EWD 1993 TIS EWD p.62 (Power Source); solder splice onto the factory lead</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>w76</t>
+          <t>w_acc86</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>K-EFI</t>
+          <t>K-ACC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>86</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>LOGIC</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr"/>
+          <t>BUS2-8</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>SP-ACC12</t>
+        </is>
+      </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>EFI relay coil (-)</t>
+          <t>A/C clutch relay coil+</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Blue-Yellow</t>
+          <t>Yellow-Blue</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -11983,73 +11983,77 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>M22759/16-18-2</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>42281-1</t>
+          <t>280919-2</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>3-1447221-3</t>
+          <t>solder splice SP-ACC12</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>B1-R2 EFI Main Relay (seated in the POWER box R2) - ACTIVE-LOW - ECU sinks coil- (85); coil+ (86) permanent 12 V (LOGIC EFI86 5 A)</t>
+          <t>B2-M5 A/C clutch relay (k_acc) - amp A15 pin 8 sinks coil- (85); coil+ (86) fused +12 V from B2-BUS2-8</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>via SP-ACC12</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>EFI</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>ST185-CabinPower</t>
+          <t>ST185-AB-cabin</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>EFI</t>
-        </is>
-      </c>
-      <c r="W102" t="inlineStr"/>
+          <t>SP-ACC12</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>SP-ACC12 also joins ST185-CabinPower</t>
+        </is>
+      </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>glove-box branch (POWER / LOGIC boxes)</t>
+          <t>A/C amp branch (behind dash)</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>POWER box (glove box) relay R2 EFI main, pin 85 | owner proposed: longer half (drawn today as w76 on ECU-cabin, 370 mm; w76_cp on CabinPower, 400 mm)</t>
+          <t>LOGIC box (glove box) relay M15 A/C clutch, pin 86 | B15: coil 86 is fused +12 V. Pressure switch stays on amp pin 13 only.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>w_eps_rly</t>
+          <t>w76</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>K-EPS</t>
+          <t>K-EFI</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -12059,12 +12063,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>DRB102-CABIN</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
@@ -12075,7 +12079,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>EHPS relay coil (-)</t>
+          <t>EFI relay coil (-)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -12085,7 +12089,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Blue-Blue-Blue</t>
+          <t>Blue-Yellow</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -12095,7 +12099,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>370</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -12107,65 +12111,61 @@
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>282110-1</t>
+          <t>42281-1</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>0460-202-1631</t>
+          <t>3-1447221-3</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>B4 EPS pump relay (HCR150, glove box, beside the POWER box) - coil- (85) switched to ground by the MR-S pump pin B5 (R22); coil+ (86) switched 12 V - HCR 150 coil is a 2-pole plug (TE terminals 1/2, not marked 85/86), resistor-suppressed so polarity-free</t>
+          <t>B1-R2 EFI Main Relay (seated in the POWER box R2) - ACTIVE-LOW - ECU sinks coil- (85); coil+ (86) permanent 12 V (LOGIC EFI86 5 A)</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>DRB102 receptacle (RH firewall)</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>EPS</t>
+          <t>EFI</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin</t>
+          <t>ST185-CabinPower</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>EPS</t>
-        </is>
-      </c>
-      <c r="W103" t="inlineStr">
-        <is>
-          <t>ST185-EngineRoom-C w_eps_rly_e at DRB102-ENGINE 85, to MRS-B 5</t>
-        </is>
-      </c>
+          <t>EFI</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr"/>
       <c r="X103" t="inlineStr">
         <is>
-          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
+          <t>glove-box branch (POWER / LOGIC boxes)</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr"/>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>EHPS pump relay (glove box), pin 85 | owner proposed: longer half (drawn today as w_eps_rly on ECU-cabin, 530 mm; w_eps_rly_cp on CabinPower, 400 mm)</t>
+          <t>POWER box (glove box) relay R2 EFI main, pin 85 | owner proposed: longer half (drawn today as w76 on ECU-cabin, 370 mm; w76_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>w81</t>
+          <t>w_eps_rly</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>K-ETB</t>
+          <t>K-EPS</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>DRB102-CABIN</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -12191,7 +12191,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>ETB relay coil (-)</t>
+          <t>EHPS relay coil (-)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -12201,78 +12201,82 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>White-White</t>
+          <t>Blue-Blue-Blue</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>530</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-18-9</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>280919-2</t>
+          <t>282110-1</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>0460-202-1631</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>B2-M4 ETB Power Relay (seated in the LOGIC box M4) - ACTIVE-LOW - ECU sinks coil- (85); coil+ (86) switched 12 V</t>
+          <t>B4 EPS pump relay (HCR150, glove box, beside the POWER box) - coil- (85) switched to ground by the MR-S pump pin B5 (R22); coil+ (86) switched 12 V - HCR 150 coil is a 2-pole plug (TE terminals 1/2, not marked 85/86), resistor-suppressed so polarity-free</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>DRB102 receptacle (RH firewall)</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>ETB</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>ST185-CabinPower</t>
+          <t>ST185-AB-cabin</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>ETB</t>
-        </is>
-      </c>
-      <c r="W104" t="inlineStr"/>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>ST185-AB-engine w_eps_rly_e at DRB102-ENGINE 85, to MRS-B 5</t>
+        </is>
+      </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>glove-box branch (POWER / LOGIC boxes)</t>
+          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr"/>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) relay M14 ETB power, pin 85 | owner proposed: longer half (drawn today as w81 on ECU-cabin, 380 mm; w81_cp on CabinPower, 400 mm)</t>
+          <t>EHPS pump relay (glove box), pin 85 | owner proposed: longer half (drawn today as w_eps_rly on ECU-cabin, 530 mm; w_eps_rly_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>w82_ac</t>
+          <t>w81</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -12282,17 +12286,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
@@ -12303,12 +12307,12 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>ETB motor +12 V</t>
+          <t>ETB relay coil (-)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -12318,29 +12322,29 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>380</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>M22759/16-18-2</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>42281-1</t>
+          <t>280919-2</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>3-1447221-3</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -12350,7 +12354,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
@@ -12369,38 +12373,42 @@
         </is>
       </c>
       <c r="W105" t="inlineStr"/>
-      <c r="X105" t="inlineStr"/>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>glove-box branch (POWER / LOGIC boxes)</t>
+        </is>
+      </c>
       <c r="Y105" t="inlineStr"/>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w82_ac on CabinPower, 400 mm; w82 on ECU-cabin, 340 mm)</t>
+          <t>LOGIC box (glove box) relay M14 ETB power, pin 85 | owner proposed: longer half (drawn today as w81 on ECU-cabin, 380 mm; w81_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>w_fan85</t>
+          <t>w82_ac</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>K-FAN</t>
+          <t>K-ETB</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
@@ -12411,17 +12419,17 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Rad fan relay (-)</t>
+          <t>ETB motor +12 V</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Yellow-White</t>
+          <t>White-White</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -12431,12 +12439,12 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>400</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>M22759/16-18-2</t>
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
@@ -12453,51 +12461,47 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>B1-R4 Radiator fan relay (seated in the POWER box R4)</t>
+          <t>B2-M4 ETB Power Relay (seated in the LOGIC box M4) - ACTIVE-LOW - ECU sinks coil- (85); coil+ (86) switched 12 V</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>ETB</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin</t>
+          <t>ST185-CabinPower</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>ETB</t>
         </is>
       </c>
       <c r="W106" t="inlineStr"/>
-      <c r="X106" t="inlineStr">
-        <is>
-          <t>glove-box branch (POWER / LOGIC boxes)</t>
-        </is>
-      </c>
+      <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr"/>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>POWER box (glove box) relay R4 radiator fan, pin 85 | owner proposed: longer half (drawn today as w_fan85 on ECU-cabin, 410 mm; w_fan85_cp on CabinPower, 400 mm)</t>
+          <t>owner proposed: longer half (drawn today as w82_ac on CabinPower, 400 mm; w82 on ECU-cabin, 340 mm)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>w_fan285</t>
+          <t>w_fan85</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>K-FAN2</t>
+          <t>K-FAN</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -12507,12 +12511,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
@@ -12523,7 +12527,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Cond fan relay (-)</t>
+          <t>Rad fan relay (-)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -12533,7 +12537,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>White-Blue</t>
+          <t>Yellow-White</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -12543,7 +12547,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>410</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -12565,17 +12569,17 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>B1-R5 Condenser fan relay (seated in the POWER box R5)</t>
+          <t>B1-R4 Radiator fan relay (seated in the POWER box R4)</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>FAN2</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -12585,27 +12589,31 @@
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>FAN2</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="W107" t="inlineStr"/>
-      <c r="X107" t="inlineStr"/>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>glove-box branch (POWER / LOGIC boxes)</t>
+        </is>
+      </c>
       <c r="Y107" t="inlineStr"/>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_fan285_cp on CabinPower, 400 mm; w_fan285 on ECU-cabin, 480 mm)</t>
+          <t>POWER box (glove box) relay R4 radiator fan, pin 85 | owner proposed: longer half (drawn today as w_fan85 on ECU-cabin, 410 mm; w_fan85_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>w_fp85</t>
+          <t>w_fan285</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>K-FP</t>
+          <t>K-FAN2</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -12615,12 +12623,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
@@ -12631,7 +12639,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Fuel pump relay (-)</t>
+          <t>Cond fan relay (-)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -12641,7 +12649,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>White-White-Blue</t>
+          <t>White-Blue</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -12651,7 +12659,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>480</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -12663,7 +12671,7 @@
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>282110-1</t>
+          <t>42281-1</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
@@ -12673,17 +12681,17 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>B3-K1 Fuel Pump Relay, TE HCR150 (seated in the battery relay block K1) - ACTIVE-LOW - ECU sinks coil- (85); coil+ (86) switched 12 V - HCR 150 coil is a 2-pole Superseal plug (TE terminals 1/2, not marked 85/86), resistor-suppressed so polarity-free</t>
+          <t>B1-R5 Condenser fan relay (seated in the POWER box R5)</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>FP</t>
+          <t>FAN2</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -12693,46 +12701,42 @@
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>FP</t>
+          <t>FAN2</t>
         </is>
       </c>
       <c r="W108" t="inlineStr"/>
-      <c r="X108" t="inlineStr">
-        <is>
-          <t>glove-box branch (POWER / LOGIC boxes) / cabin run to the trunk relay block (Routes 1 / 11)</t>
-        </is>
-      </c>
+      <c r="X108" t="inlineStr"/>
       <c r="Y108" t="inlineStr"/>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>Battery relay block (trunk) relay K1 fuel pump, pin 85 | est length: ECU-A to the glove-box boxes (390 mm) plus the cabin run to K-FP in the trunk relay block, alongside w_k_fp_86_cp (2500 mm); row 157</t>
+          <t>owner proposed: longer half (drawn today as w_fan285_cp on CabinPower, 400 mm; w_fan285 on ECU-cabin, 480 mm)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>w_lam12_cp</t>
+          <t>w_fp85</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LOGIC</t>
+          <t>K-FP</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BUS2-1</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>DRB102-CABIN</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
@@ -12743,88 +12747,88 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC LAM 7.5 A fuse</t>
+          <t>Fuel pump relay (-)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Blue-White-White</t>
+          <t>White-White-Blue</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>M22759/16-14-2</t>
+          <t>M22759/16-18-9</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>1-968851-1</t>
+          <t>282110-1</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>0460-220-1231</t>
+          <t>3-1447221-3</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>B2 LOGIC box - custom fuse + relay box, glove box inboard (cad/fusebox rev 5, DECISIONS R75): Bus 1 (permanent) and Bus 2 (switched, k_efi 30) mini fuse strips, micro relays M1-M10</t>
+          <t>B3-K1 Fuel Pump Relay, TE HCR150 (seated in the battery relay block K1) - ACTIVE-LOW - ECU sinks coil- (85); coil+ (86) switched 12 V - HCR 150 coil is a 2-pole Superseal plug (TE terminals 1/2, not marked 85/86), resistor-suppressed so polarity-free</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>DRB102 receptacle (RH firewall)</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>LAM</t>
+          <t>FP</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>ST185-CabinPower</t>
+          <t>ST185-AB-cabin</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>LAM</t>
-        </is>
-      </c>
-      <c r="W109" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine w_lam12_be14 at DRB102-ENGINE 95, to splice SP-LAM12-B</t>
-        </is>
-      </c>
-      <c r="X109" t="inlineStr"/>
+          <t>FP</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr"/>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>glove-box branch (POWER / LOGIC boxes) / cabin run to the trunk relay block (Routes 1 / 11)</t>
+        </is>
+      </c>
       <c r="Y109" t="inlineStr"/>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>CAN-Lambda +12 V | CAN-Lambda +12 V | owner proposed: longer half (drawn today as w_lam12_cp on CabinPower, 250 mm; w_lam12_bc on ECU-cabin, 120 mm)</t>
+          <t>Battery relay block (trunk) relay K1 fuel pump, pin 85 | est length: ECU-A to the glove-box boxes (390 mm) plus the cabin run to K-FP in the trunk relay block, alongside w_k_fp_86_cp (2500 mm); row 157</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>w_fb_mrs_en</t>
+          <t>w_lam12_cp</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -12834,7 +12838,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BUS2-12</t>
+          <t>BUS2-1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -12844,7 +12848,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
@@ -12855,7 +12859,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC MRS 7.5 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC LAM 7.5 A fuse</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -12865,34 +12869,34 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Blue-White</t>
+          <t>Blue-White-White</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>250</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>M22759/16-20-2</t>
+          <t>M22759/16-14-2</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>1-968849-1</t>
+          <t>1-968851-1</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>0460-202-1631</t>
+          <t>0460-220-1231</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -12907,40 +12911,36 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>EPSEN</t>
+          <t>LAM</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin</t>
+          <t>ST185-CabinPower</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>EPSEN</t>
+          <t>LAM</t>
         </is>
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>ST185-EngineRoom-C w_hv_mrs_en_e at DRB102-ENGINE 83, to MRS-C 1</t>
-        </is>
-      </c>
-      <c r="X110" t="inlineStr">
-        <is>
-          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
-        </is>
-      </c>
+          <t>ST185-AB-engine w_lam12_be14 at DRB102-ENGINE 95, to splice SP-LAM12-B</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr"/>
       <c r="Y110" t="inlineStr"/>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) fuse MRS 7.5A Fuse fed from EPS enable relay k_eps_en pin 87 (ignition-switched). | EHPS enable +12 V | fuse fed from EPS enable relay k_eps_en pin 87 (ignition-switched); owner proposed: longer half (drawn today as w_fb_mrs_en on ECU-cabin, 530 mm; w_fb_mrs_en_cp on CabinPower, 250 mm)</t>
+          <t>CAN-Lambda +12 V | CAN-Lambda +12 V | owner proposed: longer half (drawn today as w_lam12_cp on CabinPower, 250 mm; w_lam12_bc on ECU-cabin, 120 mm)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>w_start</t>
+          <t>w_fb_mrs_en</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -12950,17 +12950,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BUS2-13</t>
+          <t>BUS2-12</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>DRB102-CABIN</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>83</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
@@ -12971,17 +12971,17 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Start request</t>
+          <t>EFI relay k_efi -&gt; LOGIC MRS 7.5 A fuse</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Blue-Yellow-Yellow</t>
+          <t>Blue-White</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>530</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>M22759/16-20-2</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -13008,7 +13008,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>0460-202-1631</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>DRB102 receptacle (RH firewall)</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>B30</t>
+          <t>EPSEN</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
@@ -13033,22 +13033,30 @@
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>B30</t>
-        </is>
-      </c>
-      <c r="W111" t="inlineStr"/>
-      <c r="X111" t="inlineStr"/>
+          <t>EPSEN</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>ST185-AB-engine w_hv_mrs_en_e at DRB102-ENGINE 83, to MRS-C 1</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
+        </is>
+      </c>
       <c r="Y111" t="inlineStr"/>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_start_cp on CabinPower, 530 mm; w_start on ECU-cabin, 1230 mm)</t>
+          <t>LOGIC box (glove box) fuse MRS 7.5A Fuse fed from EPS enable relay k_eps_en pin 87 (ignition-switched). | EHPS enable +12 V | fuse fed from EPS enable relay k_eps_en pin 87 (ignition-switched); owner proposed: longer half (drawn today as w_fb_mrs_en on ECU-cabin, 530 mm; w_fb_mrs_en_cp on CabinPower, 250 mm)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>w_cop_pwr_ac</t>
+          <t>w_start</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -13058,17 +13066,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>BUS2-3</t>
+          <t>BUS2-13</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>DRB102-CABIN</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
@@ -13079,44 +13087,44 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC COP 15 A fuse</t>
+          <t>Start request</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Blue-White-Yellow</t>
+          <t>Blue-Yellow-Yellow</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>M22759/16-14-2</t>
+          <t>M22759/16-20-4</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>1-968851-1</t>
+          <t>1-968849-1</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>0460-220-1231</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -13126,45 +13134,37 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>DRB102 receptacle (RH firewall)</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>B30</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>ST185-CabinPower</t>
+          <t>ST185-AB-cabin</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>COP</t>
-        </is>
-      </c>
-      <c r="W112" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine w_cop_pwr_e_ae at DRB102-ENGINE 1, to splice SP-COP-ENG</t>
-        </is>
-      </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
-        </is>
-      </c>
+          <t>B30</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr"/>
+      <c r="X112" t="inlineStr"/>
       <c r="Y112" t="inlineStr"/>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) fuse COP 15A | Coil +12 V feed | owner proposed: longer half (drawn today as w_cop_pwr_ac on ECU-cabin, 180 mm; w_cop_pwr_c_ac on CabinPower, 250 mm)</t>
+          <t>owner proposed: longer half (drawn today as w_start_cp on CabinPower, 530 mm; w_start on ECU-cabin, 1230 mm)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>w_inj_pwr_ac</t>
+          <t>w_cop_pwr_ac</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>BUS2-4</t>
+          <t>BUS2-3</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
@@ -13195,7 +13195,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC INJ 15 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC COP 15 A fuse</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -13205,7 +13205,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Blue-White-Blue</t>
+          <t>Blue-White-Yellow</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -13247,7 +13247,7 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>INJ</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
@@ -13257,12 +13257,12 @@
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>INJ</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_inj_pwr_e_ae at DRB102-ENGINE 2, to splice SP-INJ-ENG</t>
+          <t>ST185-AB-engine w_cop_pwr_e_ae at DRB102-ENGINE 1, to splice SP-COP-ENG</t>
         </is>
       </c>
       <c r="X113" t="inlineStr">
@@ -13273,24 +13273,24 @@
       <c r="Y113" t="inlineStr"/>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) fuse INJ 15A | Injector +12 V feed | owner proposed: longer half (drawn today as w_inj_pwr_ac on ECU-cabin, 180 mm; w_inj_pwr_c_ac on CabinPower, 250 mm)</t>
+          <t>LOGIC box (glove box) fuse COP 15A | Coil +12 V feed | owner proposed: longer half (drawn today as w_cop_pwr_ac on ECU-cabin, 180 mm; w_cop_pwr_c_ac on CabinPower, 250 mm)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>w_sw7_c</t>
+          <t>w_inj_pwr_ac</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>OPTO-8</t>
+          <t>LOGIC</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>IN2</t>
+          <t>BUS2-4</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13300,128 +13300,128 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>SP-REV</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Reverse to opto in 2</t>
+          <t>EFI relay k_efi -&gt; LOGIC INJ 15 A fuse</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue-White-Blue</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>M22759/16-16-4</t>
+          <t>M22759/16-14-2</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>screw terminal (on the board)</t>
+          <t>1-968851-1</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>solder splice SP-REV</t>
+          <t>0460-220-1231</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>Optocoupler board, 8 channel (Dan's, generic EL814) - inline at the CSB3</t>
+          <t>B2 LOGIC box - custom fuse + relay box, glove box inboard (cad/fusebox rev 5, DECISIONS R75): Bus 1 (permanent) and Bus 2 (switched, k_efi 30) mini fuse strips, micro relays M1-M10</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>via SP-REV</t>
+          <t>DRB102 receptacle (RH firewall)</t>
         </is>
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>REV</t>
+          <t>INJ</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin</t>
+          <t>ST185-CabinPower</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>SP-REV</t>
+          <t>INJ</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_sw7_e at DRB102-ENGINE 78, to REV-SW 1</t>
-        </is>
-      </c>
-      <c r="X114" t="inlineStr"/>
+          <t>ST185-AB-engine w_inj_pwr_e_ae at DRB102-ENGINE 2, to splice SP-INJ-ENG</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
+        </is>
+      </c>
       <c r="Y114" t="inlineStr"/>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as w_sw7_c on ECU-cabin, ? mm; w_sw7_c_csb on CSB3, 180 mm)</t>
+          <t>LOGIC box (glove box) fuse INJ 15A | Injector +12 V feed | owner proposed: longer half (drawn today as w_inj_pwr_ac on ECU-cabin, 180 mm; w_inj_pwr_c_ac on CabinPower, 250 mm)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>w_cam_pullup_8v</t>
+          <t>w_sw7_c</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>R-CAM-PULLUP</t>
+          <t>OPTO-8</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>IN2</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>DRB102-CABIN</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>SP-8V</t>
+          <t>SP-REV</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -13431,22 +13431,22 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>+8 V to cam pull-up</t>
+          <t>Reverse to opto in 2</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Blue-Blue-Yellow</t>
+          <t>White</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -13456,30 +13456,34 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>M22759/16-16-4</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>screw terminal (on the board)</t>
+        </is>
+      </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>solder splice SP-8V</t>
+          <t>solder splice SP-REV</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>Cam pull-up 1.8 k to +8 V</t>
+          <t>Optocoupler board, 8 channel (Dan's, generic EL814) - inline at the CSB3</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>via SP-8V</t>
+          <t>via SP-REV</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>CAM</t>
+          <t>REV</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
@@ -13489,22 +13493,26 @@
       </c>
       <c r="V115" t="inlineStr">
         <is>
-          <t>SP-8V</t>
-        </is>
-      </c>
-      <c r="W115" t="inlineStr"/>
-      <c r="X115" t="inlineStr">
-        <is>
-          <t>at ECU-A plug</t>
-        </is>
-      </c>
+          <t>SP-REV</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>ST185-AB-engine w_sw7_e at DRB102-ENGINE 78, to REV-SW 1</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr"/>
       <c r="Y115" t="inlineStr"/>
-      <c r="Z115" t="inlineStr"/>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>owner TBD: a half has no length estimate (drawn today as w_sw7_c on ECU-cabin, ? mm; w_sw7_c_csb on CSB3, 180 mm)</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>w_cam_pullup_sig</t>
+          <t>w_cam_pullup_8v</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -13514,7 +13522,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -13524,12 +13532,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>SP-CAM</t>
+          <t>SP-8V</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -13539,12 +13547,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Cam pull-up 1.8k</t>
+          <t>+8 V to cam pull-up</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -13564,7 +13572,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-20-3</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -13572,7 +13580,7 @@
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>solder splice SP-CAM</t>
+          <t>solder splice SP-8V</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -13582,7 +13590,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>via SP-CAM</t>
+          <t>via SP-8V</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
@@ -13597,7 +13605,7 @@
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>SP-CAM</t>
+          <t>SP-8V</t>
         </is>
       </c>
       <c r="W116" t="inlineStr"/>
@@ -13612,32 +13620,32 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>w43</t>
+          <t>w_cam_pullup_sig</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>R-FUELLVL</t>
+          <t>R-CAM-PULLUP</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>SP-FUEL-LVL</t>
+          <t>SP-CAM</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -13647,7 +13655,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Fuel lvl pull-up</t>
+          <t>Cam pull-up 1.8k</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -13657,7 +13665,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Blue-Yellow-Blue</t>
+          <t>Blue-Blue-Yellow</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -13680,22 +13688,22 @@
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>solder splice SP-FUEL-LVL</t>
+          <t>solder splice SP-CAM</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>470R fuel level pull-up to +5V</t>
+          <t>Cam pull-up 1.8 k to +8 V</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>via SP-FUEL-LVL</t>
+          <t>via SP-CAM</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>FLVL</t>
+          <t>CAM</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
@@ -13705,18 +13713,22 @@
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>SP-FUEL-LVL</t>
+          <t>SP-CAM</t>
         </is>
       </c>
       <c r="W117" t="inlineStr"/>
-      <c r="X117" t="inlineStr"/>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>at ECU-A plug</t>
+        </is>
+      </c>
       <c r="Y117" t="inlineStr"/>
       <c r="Z117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>w44</t>
+          <t>w43</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -13726,33 +13738,37 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>BUS-5V-2</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr"/>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>SP-FUEL-LVL</t>
+        </is>
+      </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>+5 V fuel lvl pullup</t>
+          <t>Fuel lvl pull-up</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -13772,7 +13788,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -13780,7 +13796,7 @@
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>solder splice SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -13790,7 +13806,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>DT06-8 plug (ECU splice point)</t>
+          <t>via SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="T118" t="inlineStr">
@@ -13805,7 +13821,7 @@
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>BUS-5V-2</t>
+          <t>SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="W118" t="inlineStr"/>
@@ -13816,52 +13832,48 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>w_tach_r</t>
+          <t>w44</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>R-LOCK</t>
+          <t>R-FUELLVL</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>BUS-5V-2</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>SP-TACH</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Tacho to lock-sensor 4.7k</t>
+          <t>+5 V fuel lvl pullup</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Yellow-Blue-Yellow</t>
+          <t>Blue-Yellow-Blue</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -13876,7 +13888,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-20-3</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -13884,22 +13896,22 @@
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>solder splice SP-TACH</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>Lock-sensor tap 4.7 k from tacho</t>
+          <t>470R fuel level pull-up to +5V</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>via SP-TACH</t>
+          <t>DT06-8 plug (ECU splice point)</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>TACH</t>
+          <t>FLVL</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
@@ -13909,26 +13921,18 @@
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>SP-TACH</t>
+          <t>BUS-5V-2</t>
         </is>
       </c>
       <c r="W119" t="inlineStr"/>
-      <c r="X119" t="inlineStr">
-        <is>
-          <t>A/C amp branch (behind dash)</t>
-        </is>
-      </c>
+      <c r="X119" t="inlineStr"/>
       <c r="Y119" t="inlineStr"/>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>OPEN-ITEMS History 2026-10-21 N61: first bench try is tach -&gt; 4.7 kohm -&gt; A15-9. Dan 2026-10-26: lock-sensor input needs a modified tachometer signal; apply that workaround.</t>
-        </is>
-      </c>
+      <c r="Z119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>w_lock_9</t>
+          <t>w_tach_r</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -13938,28 +13942,32 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>A18</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>SP-TACH</t>
+        </is>
+      </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Lock-sensor input (modified tacho)</t>
+          <t>Tacho to lock-sensor 4.7k</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -13992,7 +14000,7 @@
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>solder onto the factory lead</t>
+          <t>solder splice SP-TACH</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -14002,7 +14010,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>OEM A/C amplifier A18 (1993 book: A15)</t>
+          <t>via SP-TACH</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
@@ -14017,7 +14025,7 @@
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>TACH</t>
+          <t>SP-TACH</t>
         </is>
       </c>
       <c r="W120" t="inlineStr"/>
@@ -14026,41 +14034,37 @@
           <t>A/C amp branch (behind dash)</t>
         </is>
       </c>
-      <c r="Y120" t="inlineStr">
-        <is>
-          <t>A/C amplifier A18 (1993: A15) pin 9, behind the glove box; OEM colour W-L; EWD 1993 p.210-211; solder onto the factory lead</t>
-        </is>
-      </c>
+      <c r="Y120" t="inlineStr"/>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>A15 pin 9 lock-sensor (factory W-L / IH1-4). Engine-side lock sensor unused. | Factory lock sensor is A15 pins 9-14 (W-L / W-R, Mitchell ~115 ohm). Workaround: modified tacho through 4.7k to pin 9 (N61 2026-10-21). IH1-4/5 engine wires unused (Engine Wire gone).</t>
+          <t>OPEN-ITEMS History 2026-10-21 N61: first bench try is tach -&gt; 4.7 kohm -&gt; A15-9. Dan 2026-10-26: lock-sensor input needs a modified tachometer signal; apply that workaround.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>w_start_in_cp</t>
+          <t>w_lock_9</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>RB4</t>
+          <t>R-LOCK</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LOGIC</t>
+          <t>A18</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>BUS2-13 IN</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
@@ -14071,17 +14075,17 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Start sw ST1 feed</t>
+          <t>Lock-sensor input (modified tacho)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Blue-Yellow-Yellow</t>
+          <t>Yellow-Blue-Yellow</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -14091,184 +14095,180 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr">
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr">
         <is>
           <t>solder onto the factory lead</t>
         </is>
       </c>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>1-968849-1</t>
-        </is>
-      </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>OEM ST1 lead B-W at old R/B No.4 pin 1, RH kick panel</t>
+          <t>Lock-sensor tap 4.7 k from tacho</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>B2 LOGIC box - custom fuse + relay box, glove box inboard (cad/fusebox rev 5, DECISIONS R75): Bus 1 (permanent) and Bus 2 (switched, k_efi 30) mini fuse strips, micro relays M1-M10</t>
+          <t>OEM A/C amplifier A18 (1993 book: A15)</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>B30</t>
+          <t>TACH</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>ST185-CabinPower</t>
+          <t>ST185-AB-cabin</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>B30</t>
+          <t>TACH</t>
         </is>
       </c>
       <c r="W121" t="inlineStr"/>
-      <c r="X121" t="inlineStr"/>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>A/C amp branch (behind dash)</t>
+        </is>
+      </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>OEM ST1 lead B-W at old R/B No.4 pin 1, RH kick panel - start (EWD 1993 p.66); OEM colour B-W; EWD 1993 TIS EWD p.66 (Starting and Ignition, All-Trac); solder splice onto the factory lead</t>
+          <t>A/C amplifier A18 (1993: A15) pin 9, behind the glove box; OEM colour W-L; EWD 1993 p.210-211; solder onto the factory lead</t>
         </is>
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_start_in on ECU-cabin, 350 mm; w_start_in_cp on CabinPower, 530 mm)</t>
+          <t>A15 pin 9 lock-sensor (factory W-L / IH1-4). Engine-side lock sensor unused. | Factory lock sensor is A15 pins 9-14 (W-L / W-R, Mitchell ~115 ohm). Workaround: modified tacho through 4.7k to pin 9 (N61 2026-10-21). IH1-4/5 engine wires unused (Engine Wire gone).</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>cab_aps1_sh</t>
+          <t>w_start_in_cp</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>NC, floats</t>
+          <t>RB4</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>LOGIC</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
-        </is>
-      </c>
+          <t>BUS2-13 IN</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>drain</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Pedal 1 cable shield</t>
+          <t>Start sw ST1 feed</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Yellow-White-White</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr"/>
+          <t>Blue-Yellow-Yellow</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>530</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>(cable core)</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr">
-        <is>
-          <t>CAB-APS1</t>
-        </is>
-      </c>
-      <c r="O122" t="inlineStr">
-        <is>
-          <t>55A1831-20-2/4/6-9</t>
-        </is>
-      </c>
-      <c r="P122" t="inlineStr"/>
+          <t>M22759/16-20-4</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>solder onto the factory lead</t>
+        </is>
+      </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-A-APS</t>
+          <t>1-968849-1</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>cab_aps1 screen (floats at the device end)</t>
+          <t>OEM ST1 lead B-W at old R/B No.4 pin 1, RH kick panel</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
+          <t>B2 LOGIC box - custom fuse + relay box, glove box inboard (cad/fusebox rev 5, DECISIONS R75): Bus 1 (permanent) and Bus 2 (switched, k_efi 30) mini fuse strips, micro relays M1-M10</t>
         </is>
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>B30</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin</t>
+          <t>ST185-CabinPower</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-APS</t>
+          <t>B30</t>
         </is>
       </c>
       <c r="W122" t="inlineStr"/>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>at ECU-A plug</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr"/>
+      <c r="X122" t="inlineStr"/>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>OEM ST1 lead B-W at old R/B No.4 pin 1, RH kick panel - start (EWD 1993 p.66); OEM colour B-W; EWD 1993 TIS EWD p.66 (Starting and Ignition, All-Trac); solder splice onto the factory lead</t>
+        </is>
+      </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>Screen floats at this end: cut back and seal under heat-shrink | screen floats at the far end; pedal branch length estimated from OEM body dimensions + 10 % (990 mm ECU-A</t>
+          <t>owner proposed: longer half (drawn today as w_start_in on ECU-cabin, 350 mm; w_start_in_cp on CabinPower, 530 mm)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>cab_aps_sh</t>
+          <t>cab_aps1_sh</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -14303,7 +14303,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Pedal 2 cable shield</t>
+          <t>Pedal 1 cable shield</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -14329,7 +14329,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>CAB-APS2</t>
+          <t>CAB-APS1</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -14345,7 +14345,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>cab_aps2 screen (floats at the device end)</t>
+          <t>cab_aps1 screen (floats at the device end)</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
@@ -14384,7 +14384,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>cab_fspur_fr_sh_ac</t>
+          <t>cab_aps_sh</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
+          <t>SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -14419,7 +14419,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>FR wheel spd shield</t>
+          <t>Pedal 2 cable shield</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -14429,7 +14429,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>White-Blue-Yellow</t>
+          <t>Yellow-White-White</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -14445,33 +14445,33 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>CAB-FSPUR-FR-AC</t>
+          <t>CAB-APS2</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>55A1811-20-9-9CS2275</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-A-WSF</t>
+          <t>solder splice SP-SHIELD-A-APS</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>cab_fspur_fr_ac screen (floats at the device end)</t>
+          <t>cab_aps2 screen (floats at the device end)</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
+          <t>via SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>WSSF</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
@@ -14481,36 +14481,36 @@
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-WSF</t>
+          <t>SP-SHIELD-A-APS</t>
         </is>
       </c>
       <c r="W124" t="inlineStr"/>
       <c r="X124" t="inlineStr">
         <is>
-          <t>dash branch (front WS inline)</t>
+          <t>at ECU-A plug</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr"/>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>Screen floats at this end: cut back and seal under heat-shrink | tied at the A end only; the far (B) end floats, dressed back at the ECU-B plug (no A-B shield bridge)</t>
+          <t>Screen floats at this end: cut back and seal under heat-shrink | screen floats at the far end; pedal branch length estimated from OEM body dimensions + 10 % (990 mm ECU-A</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>w19</t>
+          <t>cab_fspur_fr_sh_ac</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>legs of SP-8V</t>
+          <t>NC, floats</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -14520,39 +14520,35 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>SP-8V</t>
+          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>trunk</t>
+          <t>drain</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>+8 V sensor supply</t>
+          <t>FR wheel spd shield</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Shield</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>White-Blue-White</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>White-Blue-Yellow</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -14560,34 +14556,38 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr">
-        <is>
-          <t>solder splice</t>
-        </is>
-      </c>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>CAB-FSPUR-FR-AC</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>55A1811-20-9-9CS2275</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>solder splice SP-SHIELD-A-WSF</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>ECU splice point - SP-8V: +8 V cam sensor supply (ECU A6)</t>
+          <t>cab_fspur_fr_ac screen (floats at the device end)</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>via SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>8V</t>
+          <t>WSSF</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
@@ -14597,27 +14597,31 @@
       </c>
       <c r="V125" t="inlineStr">
         <is>
-          <t>SP-8V</t>
+          <t>SP-SHIELD-A-WSF</t>
         </is>
       </c>
       <c r="W125" t="inlineStr"/>
       <c r="X125" t="inlineStr">
         <is>
-          <t>at ECU-A plug</t>
+          <t>dash branch (front WS inline)</t>
         </is>
       </c>
       <c r="Y125" t="inlineStr"/>
-      <c r="Z125" t="inlineStr"/>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>Screen floats at this end: cut back and seal under heat-shrink | tied at the A end only; the far (B) end floats, dressed back at the ECU-B plug (no A-B shield bridge)</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>w_a5_pin</t>
+          <t>w19</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>legs of SP-A5</t>
+          <t>legs of SP-8V</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -14632,12 +14636,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SP-A5</t>
+          <t>SP-8V</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -14647,22 +14651,22 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse (+ IG2 wake diode)</t>
+          <t>+8 V sensor supply</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White-Blue-White</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -14672,7 +14676,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>M22759/16-18-2</t>
+          <t>M22759/16-20-3</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -14684,12 +14688,12 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>3-1447221-3</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>ECU splice point - SP-A5: ECU main feed (SW12 + IG2 diode)</t>
+          <t>ECU splice point - SP-8V: +8 V cam sensor supply (ECU A6)</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
@@ -14699,7 +14703,7 @@
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>SW12</t>
+          <t>8V</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
@@ -14709,7 +14713,7 @@
       </c>
       <c r="V126" t="inlineStr">
         <is>
-          <t>SP-A5</t>
+          <t>SP-8V</t>
         </is>
       </c>
       <c r="W126" t="inlineStr"/>
@@ -14719,21 +14723,17 @@
         </is>
       </c>
       <c r="Y126" t="inlineStr"/>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>ECU main +12 V | ECU main +12 V</t>
-        </is>
-      </c>
+      <c r="Z126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>w_ac_psw_in</t>
+          <t>w_a5_pin</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>legs of SP-AC-PSW</t>
+          <t>legs of SP-A5</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -14743,17 +14743,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>SP-AC-PSW</t>
+          <t>SP-A5</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -14763,22 +14763,22 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>A/C pressure sw out</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse (+ IG2 wake diode)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Yellow-Blue</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -14788,7 +14788,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>M22759/16-18-2</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -14800,22 +14800,22 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t xml:space="preserve">new-wire run terminated at the switch's </t>
+          <t>3-1447221-3</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>At A/C amp - SP-AC-PSW: A/C pressure switch output</t>
+          <t>ECU splice point - SP-A5: ECU main feed (SW12 + IG2 diode)</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>OEM A5, factory Y-R lead</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>SW12</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
@@ -14825,35 +14825,31 @@
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>SP-AC-PSW</t>
+          <t>SP-A5</t>
         </is>
       </c>
       <c r="W127" t="inlineStr"/>
       <c r="X127" t="inlineStr">
         <is>
-          <t>A/C amp branch (behind dash)</t>
-        </is>
-      </c>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>A/C pressure switch A5, engine bay; exact spot TBD (no locator figure in the repo); OEM colour Y-R (factory wiring; new wire here); EWD 1990 ST185 EWD p.152 (docs/electrical/ewd-snips/1990-st185-autoac-pressure-clutch-p152.png); 1990 ST185 EWD p.152 (A5 pin 4 Y-R); new-wire run terminated at the switch's own mating plug (no factory engine-bay wire reused, Section 39, 2026-10-04); plug part number not yet chosen</t>
-        </is>
-      </c>
+          <t>at ECU-A plug</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr"/>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>Runs on in ST185-EngineRoom-C to A/C pressure switch A5 pin 4 (engine bay): new wire to the switch's own mating plug, plug part TBD. EWD 1990 p.152. | owner TBD: a half has no length estimate (drawn today as w_ac_psw_in on ECU-cabin, ? mm; w_ac_psw on EngineRoom-C, 100 mm)</t>
+          <t>ECU main +12 V | ECU main +12 V</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>w_amb_sg</t>
+          <t>w_ac_psw_in</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>legs of SP-AC-SG</t>
+          <t>legs of SP-AC-PSW</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -14863,17 +14859,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>A32</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SP-AC-SG</t>
+          <t>SP-AC-PSW</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -14883,7 +14879,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>A/C sensor common</t>
+          <t>A/C pressure sw out</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -14893,7 +14889,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Blue-Yellow</t>
+          <t>Yellow-Blue</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -14903,7 +14899,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -14920,22 +14916,22 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>solder onto the factory lead</t>
+          <t xml:space="preserve">new-wire run terminated at the switch's </t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>SP-AC-SG - cabin A/C sensor common (replaces E10; A32-15, A24-3, A21, A18-2 stay factory)</t>
+          <t>At A/C amp - SP-AC-PSW: A/C pressure switch output</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>OEM auto A/C amplifier A32 pin 15 SG</t>
+          <t>OEM A5, factory Y-R lead</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>AMB</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="U128" t="inlineStr">
@@ -14945,31 +14941,35 @@
       </c>
       <c r="V128" t="inlineStr">
         <is>
-          <t>SP-AC-SG</t>
+          <t>SP-AC-PSW</t>
         </is>
       </c>
       <c r="W128" t="inlineStr"/>
-      <c r="X128" t="inlineStr"/>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>A/C amp branch (behind dash)</t>
+        </is>
+      </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>Auto A/C amplifier A32 pin 15 SG, behind the glove box; OEM colour V-W; EWD 1993 p.211-212; solder onto the factory lead</t>
+          <t>A/C pressure switch A5, engine bay; exact spot TBD (no locator figure in the repo); OEM colour Y-R (factory wiring; new wire here); EWD 1990 ST185 EWD p.152 (docs/electrical/ewd-snips/1990-st185-autoac-pressure-clutch-p152.png); 1990 ST185 EWD p.152 (A5 pin 4 Y-R); new-wire run terminated at the switch's own mating plug (no factory engine-bay wire reused, Section 39, 2026-10-04); plug part number not yet chosen</t>
         </is>
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>Cabin landing of SP-AC-SG on the amp sensor common.</t>
+          <t>Runs on in ST185-EngineRoom-C to A/C pressure switch A5 pin 4 (engine bay): new wire to the switch's own mating plug, plug part TBD. EWD 1990 p.152. | owner TBD: a half has no length estimate (drawn today as w_ac_psw_in on ECU-cabin, ? mm; w_ac_psw on EngineRoom-C, 100 mm)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>w_trig2_pin</t>
+          <t>w_amb_sg</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>legs of SP-CAM</t>
+          <t>legs of SP-AC-SG</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -14979,17 +14979,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>A32</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>SP-CAM</t>
+          <t>SP-AC-SG</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -14999,17 +14999,17 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Cam sensor signal</t>
+          <t>A/C sensor common</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Blue-Blue-Yellow</t>
+          <t>Blue-Yellow</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -15019,12 +15019,12 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>200</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-20-4</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
@@ -15036,22 +15036,22 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>solder onto the factory lead</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>At the ECU plugs - SP-CAM: cam signal + 1.8k pull-up to +8V</t>
+          <t>SP-AC-SG - cabin A/C sensor common (replaces E10; A32-15, A24-3, A21, A18-2 stay factory)</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>OEM auto A/C amplifier A32 pin 15 SG</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>CAM</t>
+          <t>AMB</t>
         </is>
       </c>
       <c r="U129" t="inlineStr">
@@ -15061,27 +15061,31 @@
       </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>SP-CAM</t>
+          <t>SP-AC-SG</t>
         </is>
       </c>
       <c r="W129" t="inlineStr"/>
-      <c r="X129" t="inlineStr">
-        <is>
-          <t>at ECU-A plug</t>
-        </is>
-      </c>
-      <c r="Y129" t="inlineStr"/>
-      <c r="Z129" t="inlineStr"/>
+      <c r="X129" t="inlineStr"/>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>Auto A/C amplifier A32 pin 15 SG, behind the glove box; OEM colour V-W; EWD 1993 p.211-212; solder onto the factory lead</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>Cabin landing of SP-AC-SG on the amp sensor common.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>w_csbg_ac</t>
+          <t>w_trig2_pin</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>legs of SP-CSB-GND</t>
+          <t>legs of SP-CAM</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -15091,17 +15095,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>POWER-NEG-BAR</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Lug</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>SP-CSB-GND</t>
+          <t>SP-CAM</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -15111,17 +15115,17 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>CSB3 + opto ground</t>
+          <t>Cam sensor signal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Yellow-Blue-Blue</t>
+          <t>Blue-Blue-Yellow</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -15131,12 +15135,12 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>M22759/16-20-0</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
@@ -15148,22 +15152,22 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>CSB3 ground splice - CSB3 pin 2, opto board COM and stalk ground</t>
+          <t>At the ECU plugs - SP-CAM: cam signal + 1.8k pull-up to +8V</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>POWER box NEG bar M8 stud (glove box)</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>CAM</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
@@ -15173,35 +15177,27 @@
       </c>
       <c r="V130" t="inlineStr">
         <is>
-          <t>SP-CSB-GND</t>
-        </is>
-      </c>
-      <c r="W130" t="inlineStr">
-        <is>
-          <t>SP-CSB-GND also joins ST185-CSB3</t>
-        </is>
-      </c>
+          <t>SP-CAM</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr"/>
       <c r="X130" t="inlineStr">
         <is>
-          <t>glove-box POWER box to the CSB3 branch</t>
+          <t>at ECU-A plug</t>
         </is>
       </c>
       <c r="Y130" t="inlineStr"/>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>M8 ring lug on the POWER box battery-negative bar (R213: CSB3, opto board and cruise ladder never on chassis or the ECU ground) | (CSB3 loom, under centre cluster) | est length; runs with the CSB3 +12 V (w_csb12, LOGIC CSB 5A) (R217)</t>
-        </is>
-      </c>
+      <c r="Z130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>w_fl_sig_pin</t>
+          <t>w_csbg_ac</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>legs of SP-FUEL-LVL</t>
+          <t>legs of SP-CSB-GND</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -15211,17 +15207,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>POWER-NEG-BAR</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Lug</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>SP-FUEL-LVL</t>
+          <t>SP-CSB-GND</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -15231,17 +15227,17 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Fuel level signal</t>
+          <t>CSB3 + opto ground</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Blue-Yellow-Blue</t>
+          <t>Yellow-Blue-Blue</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -15251,12 +15247,12 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>900</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-20-0</t>
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
@@ -15268,22 +15264,22 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>SP-FUEL-LVL - fuel sender signal + 470R pull-up to ECU-B B24</t>
+          <t>CSB3 ground splice - CSB3 pin 2, opto board COM and stalk ground</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>POWER box NEG bar M8 stud (glove box)</t>
         </is>
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>FLVL</t>
+          <t>CSB</t>
         </is>
       </c>
       <c r="U131" t="inlineStr">
@@ -15293,23 +15289,35 @@
       </c>
       <c r="V131" t="inlineStr">
         <is>
-          <t>SP-FUEL-LVL</t>
-        </is>
-      </c>
-      <c r="W131" t="inlineStr"/>
-      <c r="X131" t="inlineStr"/>
+          <t>SP-CSB-GND</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>SP-CSB-GND also joins ST185-CSB3</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>glove-box POWER box to the CSB3 branch</t>
+        </is>
+      </c>
       <c r="Y131" t="inlineStr"/>
-      <c r="Z131" t="inlineStr"/>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>M8 ring lug on the POWER box battery-negative bar (R213: CSB3, opto board and cruise ladder never on chassis or the ECU ground) | (CSB3 loom, under centre cluster) | est length; runs with the CSB3 +12 V (w_csb12, LOGIC CSB 5A) (R217)</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>w66</t>
+          <t>w_fl_sig_pin</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>legs of SP-GND-ECU</t>
+          <t>legs of SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -15319,17 +15327,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>POWER-NEG-BAR</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Lug</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>SP-GND-ECU</t>
+          <t>SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -15339,32 +15347,32 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>ECU power ground</t>
+          <t>Fuel level signal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Yellow-Yellow-White</t>
+          <t>Blue-Yellow-Blue</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>M22759/16-10-0</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -15376,22 +15384,22 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>ECU splice point - SP-GND-ECU: ECU power ground (A25 A34 B25 B34) to the NEG bar</t>
+          <t>SP-FUEL-LVL - fuel sender signal + 470R pull-up to ECU-B B24</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>POWER box NEG bar M8 stud (glove box)</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>GND</t>
+          <t>FLVL</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
@@ -15401,31 +15409,23 @@
       </c>
       <c r="V132" t="inlineStr">
         <is>
-          <t>SP-GND-ECU</t>
+          <t>SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="W132" t="inlineStr"/>
-      <c r="X132" t="inlineStr">
-        <is>
-          <t>ECU to the glove-box POWER box</t>
-        </is>
-      </c>
+      <c r="X132" t="inlineStr"/>
       <c r="Y132" t="inlineStr"/>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>M8 ring lug on the POWER box battery-negative bar (R216): the ECU grounds only, nothing else | est length; the ONE ECU ground return (DECISIONS R216)</t>
-        </is>
-      </c>
+      <c r="Z132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>w_rev_sw_c</t>
+          <t>w66</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>legs of SP-REV</t>
+          <t>legs of SP-GND-ECU</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -15435,17 +15435,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>DRB102-CABIN</t>
+          <t>POWER-NEG-BAR</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>Lug</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>SP-REV</t>
+          <t>SP-GND-ECU</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -15455,32 +15455,32 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Reverse sw +12 V out</t>
+          <t>ECU power ground</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Yellow-Yellow-White</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>900</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>M22759/16-16-4</t>
+          <t>M22759/16-10-0</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -15492,22 +15492,22 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>0460-202-1631</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>SP-REV - reverse switch out to CSB3 opto IN2 and IG2-13 lamps</t>
+          <t>ECU splice point - SP-GND-ECU: ECU power ground (A25 A34 B25 B34) to the NEG bar</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>DRB102 receptacle (RH firewall)</t>
+          <t>POWER box NEG bar M8 stud (glove box)</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>REV</t>
+          <t>GND</t>
         </is>
       </c>
       <c r="U133" t="inlineStr">
@@ -15517,31 +15517,31 @@
       </c>
       <c r="V133" t="inlineStr">
         <is>
-          <t>SP-REV</t>
-        </is>
-      </c>
-      <c r="W133" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine w_sw7_e at DRB102-ENGINE 78, to REV-SW 1</t>
-        </is>
-      </c>
-      <c r="X133" t="inlineStr"/>
+          <t>SP-GND-ECU</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr"/>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>ECU to the glove-box POWER box</t>
+        </is>
+      </c>
       <c r="Y133" t="inlineStr"/>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>Circuit 11: switch out tapped to opto IN2; lamps stay on the factory IG2-13 run.</t>
+          <t>M8 ring lug on the POWER box battery-negative bar (R216): the ECU grounds only, nothing else | est length; the ONE ECU ground return (DECISIONS R216)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>w_drain_ecu_a</t>
+          <t>w_rev_sw_c</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-A</t>
+          <t>legs of SP-REV</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -15551,17 +15551,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>DRB102-CABIN</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-REV</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -15571,22 +15571,22 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Shield drain</t>
+          <t>Reverse sw +12 V out</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Yellow-White-Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -15596,7 +15596,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>M22759/16-16-4</t>
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
@@ -15608,22 +15608,22 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>0460-202-1631</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>6 mm behind the ECU-A plug - SP-SHIELD-A: drains to A7</t>
+          <t>SP-REV - reverse switch out to CSB3 opto IN2 and IG2-13 lamps</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>DRB102 receptacle (RH firewall)</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>SHLD</t>
+          <t>REV</t>
         </is>
       </c>
       <c r="U134" t="inlineStr">
@@ -15633,31 +15633,31 @@
       </c>
       <c r="V134" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
-        </is>
-      </c>
-      <c r="W134" t="inlineStr"/>
-      <c r="X134" t="inlineStr">
-        <is>
-          <t>at ECU-A plug</t>
-        </is>
-      </c>
+          <t>SP-REV</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>ST185-AB-engine w_sw7_e at DRB102-ENGINE 78, to REV-SW 1</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr"/>
       <c r="Y134" t="inlineStr"/>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>build (R30): the crank drain is the one crimped into A7; the other drains are soldered onto it 6 mm behind the plug</t>
+          <t>Circuit 11: switch out tapped to opto IN2; lamps stay on the factory IG2-13 run.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>w_shd_a_aps</t>
+          <t>w_drain_ecu_a</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-A-APS</t>
+          <t>legs of SP-SHIELD-A</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -15667,22 +15667,22 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-A</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>trunk</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -15724,17 +15724,17 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>solder splice</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>At the pedal branch - SP-SHIELD-A-APS: pedal drains</t>
+          <t>6 mm behind the ECU-A plug - SP-SHIELD-A: drains to A7</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>6 mm behind the ECU-A plug - SP-SHIELD-A: drains to A7</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="T135" t="inlineStr">
@@ -15749,27 +15749,31 @@
       </c>
       <c r="V135" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-APS / SP-SHIELD-A</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="W135" t="inlineStr"/>
-      <c r="X135" t="inlineStr"/>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>at ECU-A plug</t>
+        </is>
+      </c>
       <c r="Y135" t="inlineStr"/>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>branch-point join (R207): the device drain meets the loom shield trunk where its signal wires join the main loom, then runs to the ECU splice</t>
+          <t>build (R30): the crank drain is the one crimped into A7; the other drains are soldered onto it 6 mm behind the plug</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>w_shd_a_wsf</t>
+          <t>w_shd_a_aps</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-A-WSF</t>
+          <t>legs of SP-SHIELD-A-APS</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -15789,7 +15793,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
+          <t>SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -15841,7 +15845,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>At the front WS inline - SP-SHIELD-A-WSF: front wheel-speed drains</t>
+          <t>At the pedal branch - SP-SHIELD-A-APS: pedal drains</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
@@ -15861,7 +15865,7 @@
       </c>
       <c r="V136" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-WSF / SP-SHIELD-A</t>
+          <t>SP-SHIELD-A-APS / SP-SHIELD-A</t>
         </is>
       </c>
       <c r="W136" t="inlineStr"/>
@@ -15876,12 +15880,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>w_drain_ecu_b</t>
+          <t>w_shd_a_wsf</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-B</t>
+          <t>legs of SP-SHIELD-A-WSF</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -15891,27 +15895,27 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>legs of SP-SHIELD-A</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B</t>
+          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>trunk</t>
+          <t>link</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Shield drain B</t>
+          <t>Shield drain</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -15948,17 +15952,17 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>solder splice</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>6 mm behind the ECU-B plug - SP-SHIELD-B: drains to B17</t>
+          <t>At the front WS inline - SP-SHIELD-A-WSF: front wheel-speed drains</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>6 mm behind the ECU-A plug - SP-SHIELD-A: drains to A7</t>
         </is>
       </c>
       <c r="T137" t="inlineStr">
@@ -15973,23 +15977,27 @@
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B</t>
+          <t>SP-SHIELD-A-WSF / SP-SHIELD-A</t>
         </is>
       </c>
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr"/>
       <c r="Y137" t="inlineStr"/>
-      <c r="Z137" t="inlineStr"/>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>branch-point join (R207): the device drain meets the loom shield trunk where its signal wires join the main loom, then runs to the ECU splice</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>w_shd_b_wsr</t>
+          <t>w_drain_ecu_b</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-B-WSR</t>
+          <t>legs of SP-SHIELD-B</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -15999,22 +16007,22 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-B</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B-WSR &gt; SP-SHIELD-B</t>
+          <t>SP-SHIELD-B</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>trunk</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -16056,17 +16064,17 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>solder splice</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>At the rear WS inline - SP-SHIELD-B-WSR: rear wheel-speed drains</t>
+          <t>6 mm behind the ECU-B plug - SP-SHIELD-B: drains to B17</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>6 mm behind the ECU-B plug - SP-SHIELD-B: drains to B17</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="T138" t="inlineStr">
@@ -16081,27 +16089,23 @@
       </c>
       <c r="V138" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B-WSR / SP-SHIELD-B</t>
+          <t>SP-SHIELD-B</t>
         </is>
       </c>
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr"/>
       <c r="Y138" t="inlineStr"/>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>branch-point join (R207): the device drain meets the loom shield trunk where its signal wires join the main loom, then runs to the ECU splice</t>
-        </is>
-      </c>
+      <c r="Z138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>w78</t>
+          <t>w_shd_b_wsr</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>legs of SP-SW12</t>
+          <t>legs of SP-SHIELD-B-WSR</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -16111,7 +16115,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>legs of SP-A5</t>
+          <t>legs of SP-SHIELD-B</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -16121,7 +16125,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>SP-SW12 &gt; SP-A5</t>
+          <t>SP-SHIELD-B-WSR &gt; SP-SHIELD-B</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -16131,22 +16135,22 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse (+ IG2 wake diode)</t>
+          <t>Shield drain B</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Yellow-White-Blue</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -16156,7 +16160,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>M22759/16-18-2</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
@@ -16173,17 +16177,17 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>ECU splice point - SP-SW12: switched +12 V (LOGIC SW12)</t>
+          <t>At the rear WS inline - SP-SHIELD-B-WSR: rear wheel-speed drains</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>ECU splice point - SP-A5: ECU main feed (SW12 + IG2 diode)</t>
+          <t>6 mm behind the ECU-B plug - SP-SHIELD-B: drains to B17</t>
         </is>
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>SW12</t>
+          <t>SHLD</t>
         </is>
       </c>
       <c r="U139" t="inlineStr">
@@ -16193,31 +16197,27 @@
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>SP-SW12 / SP-A5</t>
+          <t>SP-SHIELD-B-WSR / SP-SHIELD-B</t>
         </is>
       </c>
       <c r="W139" t="inlineStr"/>
-      <c r="X139" t="inlineStr">
-        <is>
-          <t>at ECU-A plug</t>
-        </is>
-      </c>
+      <c r="X139" t="inlineStr"/>
       <c r="Y139" t="inlineStr"/>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>ECU main +12 V | ECU main +12 V</t>
+          <t>branch-point join (R207): the device drain meets the loom shield trunk where its signal wires join the main loom, then runs to the ECU splice</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>w_tach</t>
+          <t>w78</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>legs of SP-TACH</t>
+          <t>legs of SP-SW12</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -16227,52 +16227,52 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>legs of SP-A5</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SP-TACH</t>
+          <t>SP-SW12 &gt; SP-A5</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>trunk</t>
+          <t>link</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Engine speed (tacho)</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse (+ IG2 wake diode)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Yellow-Blue-Yellow</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-18-2</t>
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
@@ -16284,22 +16284,22 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>solder splice</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>SP-TACH - Ign 8 tacho to A15 pin 18 and 4.7k lock-sensor tap</t>
+          <t>ECU splice point - SP-SW12: switched +12 V (LOGIC SW12)</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>ECU splice point - SP-A5: ECU main feed (SW12 + IG2 diode)</t>
         </is>
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>TACH</t>
+          <t>SW12</t>
         </is>
       </c>
       <c r="U140" t="inlineStr">
@@ -16309,24 +16309,140 @@
       </c>
       <c r="V140" t="inlineStr">
         <is>
-          <t>SP-TACH</t>
+          <t>SP-SW12 / SP-A5</t>
         </is>
       </c>
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr">
         <is>
-          <t>A/C amp branch (behind dash)</t>
+          <t>at ECU-A plug</t>
         </is>
       </c>
       <c r="Y140" t="inlineStr"/>
       <c r="Z140" t="inlineStr">
         <is>
+          <t>ECU main +12 V | ECU main +12 V</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>w_tach</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>legs of SP-TACH</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>ECU-B</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>SP-TACH</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>trunk</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Engine speed (tacho)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Yellow-Blue-Yellow</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>M22759/16-20-9</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>solder splice</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>3-1447221-4</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>SP-TACH - Ign 8 tacho to A15 pin 18 and 4.7k lock-sensor tap</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>TACH</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>ST185-AB-cabin</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>SP-TACH</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr"/>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>A/C amp branch (behind dash)</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr"/>
+      <c r="Z141" t="inlineStr">
+        <is>
           <t>Ign 8 (ECU-B 10) tacho. Split at SP-TACH: pin 18 plus 4.7k to pin 9 (OPEN-ITEMS History 2026-10-21 N61).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z140"/>
+  <autoFilter ref="A1:Z141"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16727,10 +16843,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -17632,7 +17748,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -19248,7 +19364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -19529,7 +19645,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -19551,7 +19667,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -19573,7 +19689,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -19595,7 +19711,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -19617,12 +19733,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0413-214-1205</t>
+          <t>114017</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -19639,7 +19755,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -19661,7 +19777,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -19683,7 +19799,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -19705,7 +19821,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -19727,7 +19843,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -19749,7 +19865,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -19771,7 +19887,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -19793,12 +19909,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>114017</t>
+          <t>114019-ZZ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -19815,12 +19931,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>114019-ZZ</t>
+          <t>114018-ZZ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -19837,7 +19953,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -19859,12 +19975,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>114018-ZZ</t>
+          <t>114017</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -19881,12 +19997,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>114017</t>
+          <t>114018-ZZ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -19903,7 +20019,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -19925,12 +20041,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>114018-ZZ</t>
+          <t>114019-ZZ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -19947,12 +20063,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>114019-ZZ</t>
+          <t>114017</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -19969,7 +20085,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>82</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -19991,7 +20107,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -20013,7 +20129,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -20035,7 +20151,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -20057,7 +20173,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -20079,7 +20195,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -20101,7 +20217,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>91</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -20123,7 +20239,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>92</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -20145,7 +20261,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -20167,7 +20283,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>94</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -20189,12 +20305,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>97</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>114017</t>
+          <t>0413-214-1205</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -20211,7 +20327,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>98</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -20233,7 +20349,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -20255,7 +20371,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -20277,7 +20393,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>101</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -20299,7 +20415,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -20316,34 +20432,34 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DRB102-CABIN</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>0413-214-1205</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
+          <t>spare, not used</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -20365,7 +20481,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -20387,7 +20503,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -20409,7 +20525,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -20431,7 +20547,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -20453,7 +20569,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -20475,7 +20591,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -20497,7 +20613,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -20519,7 +20635,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -20536,29 +20652,29 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>IX-WS-F-S</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>114017</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>spare, not used</t>
+          <t>spare, sealing plug</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IX-WS-F-S</t>
+          <t>IX-WS-R-S</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -20577,30 +20693,8 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>IX-WS-R-S</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>114017</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D61"/>
+  <autoFilter ref="A1:D60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20690,7 +20784,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Wires: 139   Connectors / ends: 59   Splices: 20   Spare cavities: 60</t>
+          <t>Wires: 140   Connectors / ends: 59   Splices: 20   Spare cavities: 59</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
@@ -4130,7 +4130,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w35_e at DRB102-ENGINE 26, to CLNT-P 3</t>
+          <t>ST185-AB-engine w35_e at DRB102-ENGINE 26, to CLNT-P C</t>
         </is>
       </c>
       <c r="X33" t="inlineStr"/>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_5v_brail_e_c47 at DRB102-ENGINE 25, to CLNT-P 2</t>
+          <t>ST185-AB-engine w_5v_brail_e_c47 at DRB102-ENGINE 25, to CLNT-P B</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">

--- a/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wires" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Splices" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Wires" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Splices" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Key" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wires'!$A$1:$Z$141</definedName>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3876,14 +3876,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>3-1447221-3</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4312,14 +4312,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>3-1447221-3</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">

--- a/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Wires" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Splices" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Key" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wires" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Splices" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wires'!$A$1:$Z$141</definedName>

--- a/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
@@ -3866,7 +3866,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3876,14 +3876,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-16-9</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>3-1447221-3</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4312,14 +4312,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-16-9</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>3-1447221-3</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">

--- a/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
@@ -7715,7 +7715,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse (+ IG2 wake diode)</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse (+ IG2 wake diode)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC MRS 7.5 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC MRS 5 A fuse</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse (+ IG2 wake diode)</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse (+ IG2 wake diode)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -16247,7 +16247,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse (+ IG2 wake diode)</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse (+ IG2 wake diode)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">

--- a/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
@@ -3866,7 +3866,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>M22759/16-16-9</t>
+          <t>M22759/16-18-9</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>M22759/16-16-9</t>
+          <t>M22759/16-18-9</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -8017,7 +8017,7 @@
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>(firewall bulkhead, RH) | M8 ring lug on the POWER box battery-negative bar (Dan 2026-10-29: coil ground, cleanest return) | est length; runs with the coil +12 V (w_cop_pwr_ac, LOGIC COP 15 A) from the glove box to bulkhead pin 1 / 4; 14 AWG like that feed</t>
+          <t>(firewall bulkhead, RH) | M8 ring lug on the POWER box battery-negative bar (Dan 2026-10-29: coil ground, cleanest return) | est length; runs with the coil +12 V (w_cop_pwr_ac, LOGIC COP 10 A) from the glove box to bulkhead pin 1 / 4; 14 AWG like that feed</t>
         </is>
       </c>
     </row>
@@ -13195,7 +13195,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC COP 15 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -13273,7 +13273,7 @@
       <c r="Y113" t="inlineStr"/>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) fuse COP 15A | Coil +12 V feed | owner proposed: longer half (drawn today as w_cop_pwr_ac on ECU-cabin, 180 mm; w_cop_pwr_c_ac on CabinPower, 250 mm)</t>
+          <t>LOGIC box (glove box) fuse COP 10A | Coil +12 V feed | owner proposed: longer half (drawn today as w_cop_pwr_ac on ECU-cabin, 180 mm; w_cop_pwr_c_ac on CabinPower, 250 mm)</t>
         </is>
       </c>
     </row>
@@ -13311,7 +13311,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC INJ 15 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC INJ 7.5 A fuse</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -13389,7 +13389,7 @@
       <c r="Y114" t="inlineStr"/>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) fuse INJ 15A | Injector +12 V feed | owner proposed: longer half (drawn today as w_inj_pwr_ac on ECU-cabin, 180 mm; w_inj_pwr_c_ac on CabinPower, 250 mm)</t>
+          <t>LOGIC box (glove box) fuse INJ 7.5A | Injector +12 V feed | owner proposed: longer half (drawn today as w_inj_pwr_ac on ECU-cabin, 180 mm; w_inj_pwr_c_ac on CabinPower, 250 mm)</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
@@ -3866,7 +3866,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>M22759/16-16-9</t>
+          <t>M22759/16-18-9</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>M22759/16-16-9</t>
+          <t>M22759/16-18-9</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -7715,7 +7715,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse (+ IG2 wake diode)</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse (+ IG2 wake diode)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -8017,7 +8017,7 @@
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>(firewall bulkhead, RH) | M8 ring lug on the POWER box battery-negative bar (Dan 2026-10-29: coil ground, cleanest return) | est length; runs with the coil +12 V (w_cop_pwr_ac, LOGIC COP 15 A) from the glove box to bulkhead pin 1 / 4; 14 AWG like that feed</t>
+          <t>(firewall bulkhead, RH) | M8 ring lug on the POWER box battery-negative bar (Dan 2026-10-29: coil ground, cleanest return) | est length; runs with the coil +12 V (w_cop_pwr_ac, LOGIC COP 10 A) from the glove box to bulkhead pin 1 / 4; 14 AWG like that feed</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC MRS 7.5 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC MRS 5 A fuse</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -13195,7 +13195,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC COP 15 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -13273,7 +13273,7 @@
       <c r="Y113" t="inlineStr"/>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) fuse COP 15A | Coil +12 V feed | owner proposed: longer half (drawn today as w_cop_pwr_ac on ECU-cabin, 180 mm; w_cop_pwr_c_ac on CabinPower, 250 mm)</t>
+          <t>LOGIC box (glove box) fuse COP 10A | Coil +12 V feed | owner proposed: longer half (drawn today as w_cop_pwr_ac on ECU-cabin, 180 mm; w_cop_pwr_c_ac on CabinPower, 250 mm)</t>
         </is>
       </c>
     </row>
@@ -13311,7 +13311,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC INJ 15 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC INJ 7.5 A fuse</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -13389,7 +13389,7 @@
       <c r="Y114" t="inlineStr"/>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) fuse INJ 15A | Injector +12 V feed | owner proposed: longer half (drawn today as w_inj_pwr_ac on ECU-cabin, 180 mm; w_inj_pwr_c_ac on CabinPower, 250 mm)</t>
+          <t>LOGIC box (glove box) fuse INJ 7.5A | Injector +12 V feed | owner proposed: longer half (drawn today as w_inj_pwr_ac on ECU-cabin, 180 mm; w_inj_pwr_c_ac on CabinPower, 250 mm)</t>
         </is>
       </c>
     </row>
@@ -14763,7 +14763,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse (+ IG2 wake diode)</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse (+ IG2 wake diode)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -16247,7 +16247,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 7.5 A fuse (+ IG2 wake diode)</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse (+ IG2 wake diode)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">

--- a/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
@@ -656,7 +656,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -768,7 +768,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -880,7 +880,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -992,7 +992,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>M22759/16-18-6</t>
+          <t>J1128-TXL-18-BLUE</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>M22759/16-18-0</t>
+          <t>J1128-TXL-18-BLACK</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>M22759/16-18-3</t>
+          <t>J1128-TXL-18-ORANGE</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>M22759/16-18-0</t>
+          <t>J1128-TXL-18-BLACK</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>J1128-TXL-18-WHITE</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>J1128-TXL-18-WHITE</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>M22759/16-18-6</t>
+          <t>J1128-TXL-18-BLUE</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>M22759/16-18-0</t>
+          <t>J1128-TXL-18-BLACK</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>J1128-TXL-18-WHITE</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>M22759/16-18-0</t>
+          <t>J1128-TXL-18-BLACK</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>J1128-TXL-20-YELLOW</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>J1128-TXL-20-YELLOW</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>M22759/16-20-0</t>
+          <t>J1128-TXL-20-BLACK</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>J1128-TXL-20-ORANGE</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>J1128-TXL-20-ORANGE</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>J1128-TXL-20-ORANGE</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -6396,7 +6396,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>J1128-TXL-20-ORANGE</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>J1128-TXL-20-ORANGE</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>J1128-TXL-20-ORANGE</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>J1128-TXL-20-ORANGE</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>J1128-TXL-20-ORANGE</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>J1128-TXL-20-BLUE</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>J1128-TXL-20-BLUE</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>J1128-TXL-20-BLUE</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -7288,7 +7288,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>J1128-TXL-20-BLUE</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -7400,7 +7400,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>J1128-TXL-20-BLUE</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -7512,7 +7512,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>J1128-TXL-20-BLUE</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -7624,7 +7624,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>J1128-TXL-20-BLUE</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7740,7 +7740,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>M22759/16-18-2</t>
+          <t>J1128-TXL-18-RED</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>M22759/16-20-2</t>
+          <t>J1128-TXL-20-RED</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7964,7 +7964,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>M22759/16-14-0</t>
+          <t>J1128-TXL-14-BLACK</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>M22759/16-18-2</t>
+          <t>J1128-TXL-18-RED</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -8664,7 +8664,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>J1128-TXL-20-ORANGE</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>M22759/16-20-2</t>
+          <t>J1128-TXL-20-RED</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -9348,7 +9348,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>J1128-TXL-20-BLUE</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>M22759/16-14-0</t>
+          <t>J1128-TXL-14-BLACK</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>M22759/16-16-2</t>
+          <t>J1128-TXL-16-RED</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>M22759/16-16-4</t>
+          <t>J1128-TXL-16-YELLOW</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -10416,7 +10416,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>J1128-TXL-20-BLUE</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -11768,7 +11768,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>J1128-TXL-20-YELLOW</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>J1128-TXL-20-YELLOW</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -12104,7 +12104,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>J1128-TXL-18-WHITE</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -12444,7 +12444,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>M22759/16-18-2</t>
+          <t>J1128-TXL-18-RED</t>
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>M22759/16-14-2</t>
+          <t>J1128-TXL-14-RED</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -12996,7 +12996,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>M22759/16-20-2</t>
+          <t>J1128-TXL-20-RED</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -13112,7 +13112,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>J1128-TXL-20-YELLOW</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -13220,7 +13220,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>M22759/16-14-2</t>
+          <t>J1128-TXL-14-RED</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>M22759/16-14-2</t>
+          <t>J1128-TXL-14-RED</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -13456,7 +13456,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>M22759/16-16-4</t>
+          <t>J1128-TXL-16-YELLOW</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
@@ -13572,7 +13572,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>J1128-TXL-20-ORANGE</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -13680,7 +13680,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -13888,7 +13888,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>J1128-TXL-20-ORANGE</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -13992,7 +13992,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -14100,7 +14100,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -14212,7 +14212,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>J1128-TXL-20-YELLOW</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -14676,7 +14676,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>J1128-TXL-20-ORANGE</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>M22759/16-18-2</t>
+          <t>J1128-TXL-18-RED</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -15024,7 +15024,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>J1128-TXL-20-YELLOW</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
@@ -15140,7 +15140,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
@@ -15252,7 +15252,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>M22759/16-20-0</t>
+          <t>J1128-TXL-20-BLACK</t>
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
@@ -15372,7 +15372,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -15480,7 +15480,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>M22759/16-10-0</t>
+          <t>J1128-TXL-10-BLACK</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -15596,7 +15596,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>M22759/16-16-4</t>
+          <t>J1128-TXL-16-YELLOW</t>
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
@@ -16272,7 +16272,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>M22759/16-18-2</t>
+          <t>J1128-TXL-18-RED</t>
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="N141" t="inlineStr"/>

--- a/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wires" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Splices" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Wires" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Splices" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Key" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wires'!$A$1:$Z$141</definedName>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>A/C amplifier A18 (1993 book: A15), passenger side behind the glove box, on the bottom of the evaporator housing; tap point on the lead at the amplifier, distance TBD; OEM colour G-Y; EWD 1992 Celica EWD132U p.93 and p.218 (docs/electrical/ewd-snips/1992-celica-ewd132u-a17-act-p093.png, 1992-celica-ewd132u-a17-clutch-p218.png); 1990 ST185 book locator A18; 1992 EWD132U p.93 and p.218 (A17-11 = A18-11); locator 1990 ST185 EWD p.17 Instrument Panel (ewd-snips/1990-st185-locations-dash.png); Mitchell locations (docs/research/AUTO-AC-AMP-OPTIONS.html); solder splice onto the factory G-Y ACT lead at the A/C amplifier</t>
+          <t>A/C amplifier A18 (1993 book: A15), passenger side behind the glove box, on the bottom of the evaporator housing; tap point on the lead at the amplifier, distance TBD; OEM colour G-Y; EWD 1992 Celica EWD132U p.93 and p.218 (docs/electrical/ewd-snips/1992-celica-ewd132u-a17-act-p093.png, 1992-celica-ewd132u-a17-clutch-p218.png); 1990 ST185 book locator A18; 1992 EWD132U p.93 and p.218 (A17-11 = A18-11); locator 1990 ST185 EWD p.17 Instrument Panel (ewd-snips/1990-st185-locations-dash.png); Mitchell 1993 Celica component locations; solder splice onto the factory G-Y ACT lead at the A/C amplifier</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>A/C amplifier A18 (1993 book: A15), passenger side behind the glove box, on the bottom of the evaporator housing; tap point on the lead at the amplifier, distance TBD; OEM colour Y-R; EWD 1990 ST185 EWD p.152 (docs/electrical/ewd-snips/1990-st185-autoac-pressure-clutch-p152.png); 1992 EWD132U p.219 A17-13 (ewd-snips/1992-celica-ewd132u-a17-pressure-p219.png); 1990 ST185 EWD p.152; 1992 EWD132U p.219 (A17-13); locator 1990 ST185 EWD p.17 Instrument Panel (ewd-snips/1990-st185-locations-dash.png); Mitchell locations (docs/research/AUTO-AC-AMP-OPTIONS.html); solder splice onto the factory Y-R lead at the A/C amplifier</t>
+          <t>A/C amplifier A18 (1993 book: A15), passenger side behind the glove box, on the bottom of the evaporator housing; tap point on the lead at the amplifier, distance TBD; OEM colour Y-R; EWD 1990 ST185 EWD p.152 (docs/electrical/ewd-snips/1990-st185-autoac-pressure-clutch-p152.png); 1992 EWD132U p.219 A17-13 (ewd-snips/1992-celica-ewd132u-a17-pressure-p219.png); 1990 ST185 EWD p.152; 1992 EWD132U p.219 (A17-13); locator 1990 ST185 EWD p.17 Instrument Panel (ewd-snips/1990-st185-locations-dash.png); Mitchell 1993 Celica component locations; solder splice onto the factory Y-R lead at the A/C amplifier</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
@@ -17525,7 +17525,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>EWD 1992 Celica EWD132U p.93 and p.218 (docs/electrical/ewd-snips/1992-celica-ewd132u-a17-act-p093.png, 1992-celica-ewd132u-a17-clutch-p218.png); 1990 ST185 book locator A18; 1992 EWD132U p.93 and p.218 (A17-11 = A18-11); locator 1990 ST185 EWD p.17 Instrument Panel (ewd-snips/1990-st185-locations-dash.png); Mitchell locations (docs/research/AUTO-AC-AMP-OPTIONS.html)</t>
+          <t>EWD 1992 Celica EWD132U p.93 and p.218 (docs/electrical/ewd-snips/1992-celica-ewd132u-a17-act-p093.png, 1992-celica-ewd132u-a17-clutch-p218.png); 1990 ST185 book locator A18; 1992 EWD132U p.93 and p.218 (A17-11 = A18-11); locator 1990 ST185 EWD p.17 Instrument Panel (ewd-snips/1990-st185-locations-dash.png); Mitchell 1993 Celica component locations</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>820</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>310</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>310</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>310</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>310</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>680</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>310</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>310</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>310</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4402,7 +4402,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>w_amb_rtn</t>
+          <t>w_amb_sig</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4422,22 +4422,18 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>SP-AC-SG</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Ambient sensor return</t>
+          <t>Ambient temp signal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4452,7 +4448,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4469,17 +4465,17 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>solder splice SP-AC-SG</t>
+          <t>solder onto the factory lead</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>OEM ambient air temp sensor A1 pin 1 (front, 6 in pigtail)</t>
+          <t>OEM ambient air temp sensor A1 pin 2 (front, 6 in pigtail)</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>via SP-AC-SG</t>
+          <t>OEM auto A/C amplifier A32 pin 6 TAM</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4494,31 +4490,31 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>SP-AC-SG</t>
+          <t>AMB</t>
         </is>
       </c>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ambient air temp sensor A1 pin 1 (6 in pigtail, B9); OEM colour Y; EWD 1993 p.211; new-wire run terminated at the sensor's own mating plug; 6 in OEM pigtail stays</t>
+          <t>Ambient air temp sensor A1 pin 2 (6 in pigtail, B9); OEM colour Y; EWD 1993 p.211 / p.148-150; new-wire run terminated at the sensor's own mating plug; 6 in OEM pigtail stays</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>Row 164: E10 sensor-common dies under B9. Cabin splice SP-AC-SG kept. Factory Y-R is the A/C pressure-switch output (A5-4 through joiner E10 to A18-13), not sensor ground; sensor common is Y (1990 ST185 EWD p.150 / p.152).</t>
+          <t>B9 front pigtail. TAM signal to the auto A/C amp. Factory EA1/IQ1 path is gone.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>w_amb_sig</t>
+          <t>w_ac_cool_gnd</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4528,12 +4524,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>A32</t>
+          <t>POWER-NEG-BAR</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Lug</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -4544,12 +4540,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Ambient temp signal</t>
+          <t>A/C coolant-OK ground</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4559,39 +4555,39 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>860</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-YELLOW</t>
+          <t>J1128-TXL-20-BLACK</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t xml:space="preserve">new-wire run terminated at the sensor's </t>
+          <t>solder onto the factory lead</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>solder onto the factory lead</t>
+          <t>320575</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>OEM ambient air temp sensor A1 pin 2 (front, 6 in pigtail)</t>
+          <t>OEM A/C amplifier A18 (1993 book: A15)</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>OEM auto A/C amplifier A32 pin 6 TAM</t>
+          <t>POWER box NEG bar M8 stud (glove box)</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>AMB</t>
+          <t>ACCGND</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -4601,26 +4597,30 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>AMB</t>
+          <t>ACCGND</t>
         </is>
       </c>
       <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>A/C amp branch (behind dash)</t>
+        </is>
+      </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ambient air temp sensor A1 pin 2 (6 in pigtail, B9); OEM colour Y; EWD 1993 p.211 / p.148-150; new-wire run terminated at the sensor's own mating plug; 6 in OEM pigtail stays</t>
+          <t>A/C amplifier A18 (1993: A15) pin 2, behind the glove box; OEM colour L-Y; EWD 1993 p.210; solder onto the factory lead</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>B9 front pigtail. TAM signal to the auto A/C amp. Factory EA1/IQ1 path is gone.</t>
+          <t>D16: amp coolant-OK input hard-grounded. No Link ECT handshake.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>w_ac_cool_gnd</t>
+          <t>w_acc_trig</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4630,17 +4630,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>POWER-NEG-BAR</t>
+          <t>K-ACC</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lug</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -4651,27 +4651,27 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>A/C coolant-OK ground</t>
+          <t>A/C clutch relay coil (-)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>860</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-BLACK</t>
+          <t>M22759/16-18-9</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>320575</t>
+          <t>280919-2</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -4693,12 +4693,12 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>POWER box NEG bar M8 stud (glove box)</t>
+          <t>B2-M5 A/C clutch relay (k_acc) - amp A15 pin 8 sinks coil- (85); coil+ (86) fused +12 V from B2-BUS2-8</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>ACCGND</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
@@ -4708,30 +4708,26 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>ACCGND</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>A/C amp branch (behind dash)</t>
-        </is>
-      </c>
+      <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A/C amplifier A18 (1993: A15) pin 2, behind the glove box; OEM colour L-Y; EWD 1993 p.210; solder onto the factory lead</t>
+          <t>A/C amplifier A18 (1993: A15), behind the glove box; OEM colour L-Y; EWD 1993 p.210-211; solder onto the factory lead</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>D16: amp coolant-OK input hard-grounded. No Link ECT handshake.</t>
+          <t>A15 pin 8 MGC output (D16 option A). Solder onto the factory L-Y lead. | D16: amp drives k_acc coil 85. Link only sends ACT kill on Aux 4.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>w_acc_trig</t>
+          <t>w_ac_psw_sw</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4741,48 +4737,52 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>K-ACC</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>SP-AC-PSW</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>A/C clutch relay coil (-)</t>
+          <t>A/C pressure sw out</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>M22759/16-20-4</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -4794,17 +4794,17 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>280919-2</t>
+          <t>solder splice SP-AC-PSW</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>OEM A/C amplifier A18 (1993 book: A15)</t>
+          <t>OEM A/C amplifier</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>B2-M5 A/C clutch relay (k_acc) - amp A15 pin 8 sinks coil- (85); coil+ (86) fused +12 V from B2-BUS2-8</t>
+          <t>via SP-AC-PSW</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4819,26 +4819,30 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>SP-AC-PSW</t>
         </is>
       </c>
       <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>A/C amp branch (behind dash)</t>
+        </is>
+      </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A/C amplifier A18 (1993: A15), behind the glove box; OEM colour L-Y; EWD 1993 p.210-211; solder onto the factory lead</t>
+          <t>A/C amplifier A18 (1993 book: A15), passenger side behind the glove box, on the bottom of the evaporator housing; tap point on the lead at the amplifier, distance TBD; OEM colour Y-R; EWD 1990 ST185 EWD p.152 (docs/electrical/ewd-snips/1990-st185-autoac-pressure-clutch-p152.png); 1992 EWD132U p.219 A17-13 (ewd-snips/1992-celica-ewd132u-a17-pressure-p219.png); 1990 ST185 EWD p.152; 1992 EWD132U p.219 (A17-13); locator 1990 ST185 EWD p.17 Instrument Panel (ewd-snips/1990-st185-locations-dash.png); Mitchell 1993 Celica component locations; solder splice onto the factory Y-R lead at the A/C amplifier</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>A15 pin 8 MGC output (D16 option A). Solder onto the factory L-Y lead. | D16: amp drives k_acc coil 85. Link only sends ACT kill on Aux 4.</t>
+          <t>A/C amp A18 pin 13 (1993: A15), behind the glove box. Solder splice onto the factory Y-R lead. EWD 1990 p.152; locator 1990 p.17.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>w_ac_psw_sw</t>
+          <t>w_tach_18</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4848,22 +4852,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SP-AC-PSW</t>
+          <t>SP-TACH</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4873,12 +4877,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>A/C pressure sw out</t>
+          <t>Engine speed (tacho)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4888,12 +4892,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
@@ -4905,22 +4909,22 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>solder splice SP-AC-PSW</t>
+          <t>solder splice SP-TACH</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>OEM A/C amplifier</t>
+          <t>OEM A/C amplifier A18 (1993 book: A15)</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>via SP-AC-PSW</t>
+          <t>via SP-TACH</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>TACH</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
@@ -4930,7 +4934,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>SP-AC-PSW</t>
+          <t>SP-TACH</t>
         </is>
       </c>
       <c r="V42" t="inlineStr"/>
@@ -4941,44 +4945,44 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A/C amplifier A18 (1993 book: A15), passenger side behind the glove box, on the bottom of the evaporator housing; tap point on the lead at the amplifier, distance TBD; OEM colour Y-R; EWD 1990 ST185 EWD p.152 (docs/electrical/ewd-snips/1990-st185-autoac-pressure-clutch-p152.png); 1992 EWD132U p.219 A17-13 (ewd-snips/1992-celica-ewd132u-a17-pressure-p219.png); 1990 ST185 EWD p.152; 1992 EWD132U p.219 (A17-13); locator 1990 ST185 EWD p.17 Instrument Panel (ewd-snips/1990-st185-locations-dash.png); Mitchell 1993 Celica component locations; solder splice onto the factory Y-R lead at the A/C amplifier</t>
+          <t>A/C amplifier A18 (1993: A15) pin 18, behind the glove box; OEM colour B; EWD 1993 p.211; solder onto the factory lead</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>A/C amp A18 pin 13 (1993: A15), behind the glove box. Solder splice onto the factory Y-R lead. EWD 1990 p.152; locator 1990 p.17.</t>
+          <t>A15 pin 18 RPM input; 10-14 V average with the engine running (Mitchell 1993 Electrical). | D16: Ign 8 tacho to A15 pin 18.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>w_tach_18</t>
+          <t>w_amb_sg</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>A18</t>
+          <t>A32</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SP-TACH</t>
+          <t>SP-AC-SG</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4988,12 +4992,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Engine speed (tacho)</t>
+          <t>A/C sensor common</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5003,12 +5007,12 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-WHITE</t>
+          <t>J1128-TXL-20-YELLOW</t>
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
@@ -5020,22 +5024,22 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>solder splice SP-TACH</t>
+          <t>solder splice SP-AC-SG</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>OEM A/C amplifier A18 (1993 book: A15)</t>
+          <t>OEM auto A/C amplifier A32 pin 15 SG</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>via SP-TACH</t>
+          <t>via SP-AC-SG</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>TACH</t>
+          <t>AMB</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
@@ -5045,23 +5049,19 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>SP-TACH</t>
+          <t>SP-AC-SG</t>
         </is>
       </c>
       <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>A/C amp branch (behind dash)</t>
-        </is>
-      </c>
+      <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A/C amplifier A18 (1993: A15) pin 18, behind the glove box; OEM colour B; EWD 1993 p.211; solder onto the factory lead</t>
+          <t>Auto A/C amplifier A32 pin 15 SG, behind the glove box; OEM colour V-W; EWD 1993 p.211-212; solder onto the factory lead</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>A15 pin 18 RPM input; 10-14 V average with the engine running (Mitchell 1993 Electrical). | D16: Ign 8 tacho to A15 pin 18.</t>
+          <t>Cabin landing of SP-AC-SG on the amp sensor common.</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -6232,7 +6232,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>680</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>570</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>450</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>680</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>680</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -9514,7 +9514,7 @@
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>680</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -9629,7 +9629,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>450</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>310</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>640</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>640</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>530</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>530</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -10616,7 +10616,7 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>500</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -10727,7 +10727,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>640</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>640</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -11155,7 +11155,7 @@
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>500</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -11262,7 +11262,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>450</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -12011,7 +12011,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>680</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>680</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -12221,7 +12221,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>450</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -12546,7 +12546,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>680</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -12875,7 +12875,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>680</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -12986,7 +12986,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -13089,7 +13089,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -13287,7 +13287,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -13703,7 +13703,7 @@
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>840</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -13814,7 +13814,7 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>840</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -13925,7 +13925,7 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>500</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -14040,7 +14040,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>310</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>310</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -14258,7 +14258,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -14323,7 +14323,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>w_amb_sg</t>
+          <t>w_amb_rtn</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -14338,12 +14338,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>A32</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -14358,7 +14358,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>A/C sensor common</t>
+          <t>Ambient sensor return</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -14390,7 +14390,7 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>solder onto the factory lead</t>
+          <t xml:space="preserve">new-wire run terminated at the sensor's </t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>OEM auto A/C amplifier A32 pin 15 SG</t>
+          <t>OEM ambient air temp sensor A1 pin 1 (front, 6 in pigtail)</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
@@ -14422,12 +14422,12 @@
       <c r="W129" t="inlineStr"/>
       <c r="X129" t="inlineStr">
         <is>
-          <t>Auto A/C amplifier A32 pin 15 SG, behind the glove box; OEM colour V-W; EWD 1993 p.211-212; solder onto the factory lead</t>
+          <t>Ambient air temp sensor A1 pin 1 (6 in pigtail, B9); OEM colour Y; EWD 1993 p.211; new-wire run terminated at the sensor's own mating plug; 6 in OEM pigtail stays</t>
         </is>
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>Cabin landing of SP-AC-SG on the amp sensor common.</t>
+          <t>Row 164: E10 sensor-common dies under B9. Cabin splice SP-AC-SG kept. Factory Y-R is the A/C pressure-switch output (A5-4 through joiner E10 to A18-13), not sensor ground; sensor common is Y (1990 ST185 EWD p.150 / p.152).</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>310</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -14706,7 +14706,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>310</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -14809,7 +14809,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>570</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -15031,7 +15031,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -15142,7 +15142,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>450</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -15249,7 +15249,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>230</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -15356,7 +15356,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -15459,7 +15459,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>230</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -15566,7 +15566,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>820</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -18621,7 +18621,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>w_amb_sg</t>
+          <t>w_amb_rtn</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">

--- a/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wires" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Splices" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Wires" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Splices" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Key" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wires'!$A$1:$Y$141</definedName>

--- a/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
@@ -7374,17 +7374,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>DRB102-CABIN</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SP-SW12 &gt; SP-A5</t>
+          <t>SP-SW12</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>via SP-SW12 &gt; SP-A5</t>
+          <t>via SP-SW12</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7454,7 +7454,11 @@
           <t>BUS-SW12 / SP-SW12</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr"/>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>ST185-AB-engine w_rail_sp_sw12_e at DRB102-ENGINE 30, to splice SP-SW12-ENG</t>
+        </is>
+      </c>
       <c r="W65" t="inlineStr">
         <is>
           <t>glove-box branch (POWER / LOGIC boxes)</t>
@@ -7688,7 +7692,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>w_rail_sp_sw12_c</t>
+          <t>w_shc_flex</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7698,7 +7702,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -7708,12 +7712,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SP-SW12 &gt; SP-A5</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -7723,27 +7727,27 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
+          <t>Flex fuel shield</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>J1128-TXL-18-RED</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
@@ -7755,7 +7759,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>solder splice SP-SW12</t>
+          <t>solder splice SP-SHIELD-A</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -7765,12 +7769,12 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>via SP-SW12 &gt; SP-A5</t>
+          <t>via SP-SHIELD-A</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>SW12</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
@@ -7780,12 +7784,12 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>SP-SW12</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_rail_sp_sw12_e at DRB102-ENGINE 30, to splice SP-SW12-ENG</t>
+          <t>ST185-AB-engine cab_flex_sh at DRB102-ENGINE 32, to NC, floats NC</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
@@ -7794,16 +7798,12 @@
         </is>
       </c>
       <c r="X68" t="inlineStr"/>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>+12 V boost + flex | +12 V boost + flex</t>
-        </is>
-      </c>
+      <c r="Y68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>w_shc_flex</t>
+          <t>w_shc_etbs</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Flex fuel shield</t>
+          <t>Throttle shield</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>ETBS</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_flex_sh at DRB102-ENGINE 32, to NC, floats NC</t>
+          <t>ST185-AB-engine cab_etbs_sh at DRB102-ENGINE 47, to NC, floats NC</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
@@ -7914,7 +7914,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>w_shc_etbs</t>
+          <t>w_shc_etbm</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7924,22 +7924,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-SHIELD-B</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Throttle shield</t>
+          <t>ETB motor shield</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-A</t>
+          <t>solder splice SP-SHIELD-B</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-A</t>
+          <t>via SP-SHIELD-B</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>ETBS</t>
+          <t>ETBM</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
@@ -8006,26 +8006,22 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-SHIELD-B</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_etbs_sh at DRB102-ENGINE 47, to NC, floats NC</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>trunk ECU-A to bulkhead (RH firewall)</t>
-        </is>
-      </c>
+          <t>ST185-AB-engine cab_etbm_ae_sh at DRB102-ENGINE 50, to NC, floats NC</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>w_shc_etbm</t>
+          <t>w_shc_turbo</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8035,22 +8031,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -8060,7 +8056,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>ETB motor shield</t>
+          <t>Turbo speed shield</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8092,7 +8088,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-B</t>
+          <t>solder splice SP-SHIELD-A</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -8102,12 +8098,12 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-B</t>
+          <t>via SP-SHIELD-A</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>ETBM</t>
+          <t>TURBO</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
@@ -8117,22 +8113,26 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_etbm_ae_sh at DRB102-ENGINE 50, to NC, floats NC</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr"/>
+          <t>ST185-AB-engine cab_turbo_sh at DRB102-ENGINE 57, to NC, floats NC</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>trunk ECU-A to bulkhead (RH firewall)</t>
+        </is>
+      </c>
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>w_shc_turbo</t>
+          <t>w_rail_sp_8v_c</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8152,12 +8152,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-8V</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -8167,12 +8167,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Turbo speed shield</t>
+          <t>+8 V to cam sensor</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8182,12 +8182,12 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>J1128-TXL-20-ORANGE</t>
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
@@ -8199,7 +8199,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-A</t>
+          <t>solder splice SP-8V</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-A</t>
+          <t>via SP-8V</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>TURBO</t>
+          <t>8V</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-8V</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_turbo_sh at DRB102-ENGINE 57, to NC, floats NC</t>
+          <t>ST185-AB-engine w_rail_sp_8v_e at DRB102-ENGINE 63, to CAM 1</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
@@ -8243,7 +8243,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>w_rail_sp_8v_c</t>
+          <t>w_cam_sig_c</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SP-8V</t>
+          <t>SP-CAM</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>+8 V to cam sensor</t>
+          <t>Cam sensor signal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-ORANGE</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
@@ -8310,7 +8310,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>solder splice SP-8V</t>
+          <t>solder splice SP-CAM</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -8320,12 +8320,12 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>via SP-8V</t>
+          <t>via SP-CAM</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>8V</t>
+          <t>CAM</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>SP-8V</t>
+          <t>SP-CAM</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_rail_sp_8v_e at DRB102-ENGINE 63, to CAM 1</t>
+          <t>ST185-AB-engine cab_cam_c2 at DRB102-ENGINE 64, to CAM 2</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
@@ -8354,7 +8354,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>w_cam_sig_c</t>
+          <t>w_shc_cam</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -8374,12 +8374,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SP-CAM</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Cam sensor signal</t>
+          <t>Cam sensor shield</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-WHITE</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>solder splice SP-CAM</t>
+          <t>solder splice SP-SHIELD-A</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>via SP-CAM</t>
+          <t>via SP-SHIELD-A</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>SP-CAM</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_cam_c2 at DRB102-ENGINE 64, to CAM 2</t>
+          <t>ST185-AB-engine cab_cam_sh at DRB102-ENGINE 66, to NC, floats NC</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
@@ -8465,7 +8465,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>w_shc_cam</t>
+          <t>w_rail_sp_8v_vss_c</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>67</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-8V</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -8500,12 +8500,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Cam sensor shield</t>
+          <t>+8 V to gearbox speed sensor</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>J1128-TXL-20-ORANGE</t>
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
@@ -8532,7 +8532,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-A</t>
+          <t>solder splice SP-8V</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-A</t>
+          <t>via SP-8V</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>CAM</t>
+          <t>8V</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
@@ -8557,12 +8557,12 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-8V</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_cam_sh at DRB102-ENGINE 66, to NC, floats NC</t>
+          <t>ST185-AB-engine w_vss_8v at DRB102-ENGINE 67, to VSS 1</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
@@ -8571,12 +8571,16 @@
         </is>
       </c>
       <c r="X75" t="inlineStr"/>
-      <c r="Y75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>(firewall bulkhead, RH) | Dan 2026-11-01: VSS on ECU +8V (bench test 9 V: 0.008 V low / supply high, 4 pulses per turn)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>w_rail_sw12_b_c_ac</t>
+          <t>w_vss_sig_c</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8586,37 +8590,33 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>SP-SW12 &gt; SP-A5</t>
-        </is>
-      </c>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
+          <t>Gearbox speed signal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-RED</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
@@ -8643,7 +8643,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>solder splice SP-SW12</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>via SP-SW12 &gt; SP-A5</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>SW12</t>
+          <t>VSS</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
@@ -8668,30 +8668,22 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>SP-SW12</t>
+          <t>VSS</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_vss_12v at DRB102-ENGINE 67, to VSS 1</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>to ECU-B plug (beside ECU-A)</t>
-        </is>
-      </c>
+          <t>ST185-AB-engine w_vss_sig_e at DRB102-ENGINE 68, to VSS 3</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr"/>
       <c r="X76" t="inlineStr"/>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>+12 V gearbox speed | (firewall bulkhead, RH); sensor +12V | owner TBD: a half has no length estimate (drawn today as w_rail_sw12_b_c_ac on ECU-cabin, ? mm; w_rail_sw12_b_c on ECU-cabin, 520 mm)</t>
-        </is>
-      </c>
+      <c r="Y76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>w_vss_sig_c</t>
+          <t>w_shc_vss</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8701,7 +8693,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -8711,23 +8703,27 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>SP-SHIELD-B</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Gearbox speed signal</t>
+          <t>Gearbox speed shield</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8742,7 +8738,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-WHITE</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
@@ -8754,7 +8750,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>solder splice SP-SHIELD-B</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -8764,7 +8760,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>via SP-SHIELD-B</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8779,12 +8775,12 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>VSS</t>
+          <t>SP-SHIELD-B</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_vss_sig_e at DRB102-ENGINE 68, to VSS 3</t>
+          <t>ST185-AB-engine cab_vss_sh at DRB102-ENGINE 69, to NC, floats NC</t>
         </is>
       </c>
       <c r="W77" t="inlineStr"/>
@@ -8794,7 +8790,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>w_shc_vss</t>
+          <t>w12_c</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8804,37 +8800,33 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>BUS-GNDOUT-B</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>SP-SHIELD-B</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Gearbox speed shield</t>
+          <t>Knock sensor (-)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8844,12 +8836,12 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>J1128-TXL-20-BLUE</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
@@ -8861,7 +8853,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-B</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -8871,12 +8863,12 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-B</t>
+          <t>DT06-12 plug (ECU splice point)</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>VSS</t>
+          <t>KNOCK</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -8886,22 +8878,26 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B</t>
+          <t>BUS-GNDOUT-B</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_vss_sh at DRB102-ENGINE 69, to NC, floats NC</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr"/>
+          <t>ST185-AB-engine cab_knock1_c2 at DRB102-ENGINE 72, to KNOCK-1 2</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>trunk ECU to bulkhead (RH firewall)</t>
+        </is>
+      </c>
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>w12_c</t>
+          <t>w_shc_knock1</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8911,33 +8907,37 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-B</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>SP-SHIELD-B</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Knock sensor (-)</t>
+          <t>Knock sensor shield</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-BLUE</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>solder splice SP-SHIELD-B</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>DT06-12 plug (ECU splice point)</t>
+          <t>via SP-SHIELD-B</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -8989,26 +8989,22 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-B</t>
+          <t>SP-SHIELD-B</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_knock1_c2 at DRB102-ENGINE 72, to KNOCK-1 2</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>trunk ECU to bulkhead (RH firewall)</t>
-        </is>
-      </c>
+          <t>ST185-AB-engine cab_knock1_sh at DRB102-ENGINE 73, to NC, floats NC</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr"/>
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>w_shc_knock1</t>
+          <t>w_shc_crank</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9018,22 +9014,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -9043,7 +9039,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Knock sensor shield</t>
+          <t>Crank sensor shield</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -9075,7 +9071,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-B</t>
+          <t>solder splice SP-SHIELD-A</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -9085,12 +9081,12 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-B</t>
+          <t>via SP-SHIELD-A</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>KNOCK</t>
+          <t>CRANKC</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
@@ -9100,22 +9096,30 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_knock1_sh at DRB102-ENGINE 73, to NC, floats NC</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr"/>
+          <t>ST185-AB-engine cab_crank_sh at DRB102-ENGINE 76, to NC, floats NC</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>trunk ECU-A to bulkhead (RH firewall)</t>
+        </is>
+      </c>
       <c r="X80" t="inlineStr"/>
-      <c r="Y80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>build (R30): this drain is the one crimped into A7</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>w_shc_crank</t>
+          <t>wc_h_bh_bc</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9125,37 +9129,37 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>ECU-C</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-CANH</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>leg core</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Crank sensor shield</t>
+          <t>CAN H to CAN-Lambda</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9165,16 +9169,24 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>680</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>CAB-CANBH-BC</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>55A1821-20-9/5-9</t>
+        </is>
+      </c>
       <c r="O81" t="inlineStr">
         <is>
           <t>0460-202-1631</t>
@@ -9182,7 +9194,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-A</t>
+          <t>solder splice SP-CANH</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -9192,12 +9204,12 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-A</t>
+          <t>via SP-CANH</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>CRANKC</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
@@ -9207,30 +9219,26 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-CANH</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_crank_sh at DRB102-ENGINE 76, to NC, floats NC</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>trunk ECU-A to bulkhead (RH firewall)</t>
-        </is>
-      </c>
+          <t>ST185-AB-engine wc_h_lam_be at DRB102-ENGINE 79, to splice SP-CANH-LAM; SP-CANH also joins ST185-CAN</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>build (R30): this drain is the one crimped into A7</t>
+          <t>owner TBD: a half has no length estimate (drawn today as wc_h_bh on CAN, ? mm; wc_h_bh_bc on ECU-cabin, 120 mm)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>wc_h_bh_bc</t>
+          <t>wc_l_bh_bc</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9240,7 +9248,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -9250,12 +9258,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SP-CANH</t>
+          <t>SP-CANL</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -9265,12 +9273,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>CAN H to CAN-Lambda</t>
+          <t>CAN L to CAN-Lambda</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9305,7 +9313,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>solder splice SP-CANH</t>
+          <t>solder splice SP-CANL</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -9315,7 +9323,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>via SP-CANH</t>
+          <t>via SP-CANL</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -9330,26 +9338,26 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>SP-CANH</t>
+          <t>SP-CANL</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>ST185-AB-engine wc_h_lam_be at DRB102-ENGINE 79, to splice SP-CANH-LAM; SP-CANH also joins ST185-CAN</t>
+          <t>ST185-AB-engine wc_l_lam_be at DRB102-ENGINE 80, to splice SP-CANL-LAM; SP-CANL also joins ST185-CAN</t>
         </is>
       </c>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as wc_h_bh on CAN, ? mm; wc_h_bh_bc on ECU-cabin, 120 mm)</t>
+          <t>owner TBD: a half has no length estimate (drawn today as wc_l_bh on CAN, ? mm; wc_l_bh_bc on ECU-cabin, 120 mm)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>wc_l_bh_bc</t>
+          <t>cab_canbh_bc_sh</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9359,7 +9367,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -9369,12 +9377,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SP-CANL</t>
+          <t>SP-CAN-SH-BH &gt; SP-CAN-SH-CLU</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -9384,19 +9392,15 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>CAN L to CAN-Lambda</t>
+          <t>CAN-Lambda shield</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
           <t>680</t>
@@ -9424,7 +9428,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>solder splice SP-CANL</t>
+          <t>solder splice SP-CAN-SH-BH</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -9434,7 +9438,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>via SP-CANL</t>
+          <t>via SP-CAN-SH-BH &gt; SP-CAN-SH-CLU</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9449,26 +9453,26 @@
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>SP-CANL</t>
+          <t>SP-CAN-SH-BH</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>ST185-AB-engine wc_l_lam_be at DRB102-ENGINE 80, to splice SP-CANL-LAM; SP-CANL also joins ST185-CAN</t>
+          <t>ST185-AB-engine cab_lamcan_be_sh at DRB102-ENGINE 81, to NC, floats NC; SP-CAN-SH-BH also joins ST185-CAN; SP-CAN-SH-CLU also joins ST185-CAN</t>
         </is>
       </c>
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as wc_l_bh on CAN, ? mm; wc_l_bh_bc on ECU-cabin, 120 mm)</t>
+          <t>owner TBD: a half has no length estimate (drawn today as cab_can_bh_sh on CAN, ? mm; cab_canbh_bc_sh on ECU-cabin, 120 mm)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>cab_canbh_bc_sh</t>
+          <t>w_lamg_ac</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9478,68 +9482,60 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ECU-C</t>
+          <t>POWER-NEG-BAR</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>SP-CAN-SH-BH &gt; SP-CAN-SH-CLU</t>
-        </is>
-      </c>
+          <t>Lug</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>leg core</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>CAN-Lambda shield</t>
+          <t>CAN-Lambda ground</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Shield</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr"/>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>450</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>(cable core)</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>CAB-CANBH-BC</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>55A1821-20-9/5-9</t>
-        </is>
-      </c>
+          <t>J1128-TXL-14-BLACK</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
-          <t>0460-202-1631</t>
+          <t>0460-220-1231</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>solder splice SP-CAN-SH-BH</t>
+          <t>320575</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -9549,12 +9545,12 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>via SP-CAN-SH-BH &gt; SP-CAN-SH-CLU</t>
+          <t>POWER box NEG bar M8 stud (glove box)</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>LAM</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
@@ -9564,46 +9560,50 @@
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>SP-CAN-SH-BH</t>
+          <t>LAM</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_lamcan_be_sh at DRB102-ENGINE 81, to NC, floats NC; SP-CAN-SH-BH also joins ST185-CAN; SP-CAN-SH-CLU also joins ST185-CAN</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr"/>
+          <t>ST185-AB-engine w_lamg_be14 at DRB102-ENGINE 96, to splice SP-LAMG-B</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>bulkhead to the glove-box POWER box</t>
+        </is>
+      </c>
       <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as cab_can_bh_sh on CAN, ? mm; cab_canbh_bc_sh on ECU-cabin, 120 mm)</t>
+          <t>(firewall bulkhead, RH) | M8 ring lug on the POWER box battery-negative bar (R213: a CAN node never on chassis or the ECU ground) | est length; runs with the CAN-Lambda +12 V (w_lam12_cp, LOGIC LAM) from the glove box to bulkhead pin 95 / 96 (R217)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>w_lamg_ac</t>
+          <t>w_rev_feed_c</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
+          <t>IG2</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
           <t>DRB102-CABIN</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>POWER-NEG-BAR</t>
-        </is>
-      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Lug</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -9614,54 +9614,54 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>CAN-Lambda ground</t>
+          <t>Back-up sw +12 V in</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>J1128-TXL-14-BLACK</t>
+          <t>J1128-TXL-16-RED</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr">
         <is>
-          <t>0460-220-1231</t>
+          <t>crimp butt splice into the factory cowl-</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>320575</t>
+          <t>0460-202-1631</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
+          <t>OEM IG2 pin 4 (under the ECU, cowl side) - factory back-up SW feed</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
           <t>DRB102 receptacle (RH firewall)</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr">
-        <is>
-          <t>POWER box NEG bar M8 stud (glove box)</t>
-        </is>
-      </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>LAM</t>
+          <t>REV</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
@@ -9671,30 +9671,30 @@
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>LAM</t>
+          <t>REV</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_lamg_be14 at DRB102-ENGINE 96, to splice SP-LAMG-B</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>bulkhead to the glove-box POWER box</t>
-        </is>
-      </c>
-      <c r="X85" t="inlineStr"/>
+          <t>ST185-AB-engine w_rev_feed_e at DRB102-ENGINE 77, to REV-SW 2</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr"/>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>OEM IG2 pin 4 (under the ECU, cowl side) - R-L, GAUGE 15 A back-up SW feed; OEM colour R-L; EWD 1992 p.132 / 1990 p.82; crimp butt splice into the factory cowl-side lead at IG2 (cabin, under the ECU; the engine wire is removed)</t>
+        </is>
+      </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>(firewall bulkhead, RH) | M8 ring lug on the POWER box battery-negative bar (R213: a CAN node never on chassis or the ECU ground) | est length; runs with the CAN-Lambda +12 V (w_lam12_cp, LOGIC LAM) from the glove box to bulkhead pin 95 / 96 (R217)</t>
+          <t>Circuit 11: factory feed kept. New engine-harness switch in splices to the IG2-4 pigtail.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>w_rev_feed_c</t>
+          <t>w_rev_lamps</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -9714,23 +9714,27 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr"/>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>SP-REV</t>
+        </is>
+      </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Back-up sw +12 V in</t>
+          <t>Back-up lamp +12 V</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -9740,12 +9744,12 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>310</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>J1128-TXL-16-RED</t>
+          <t>J1128-TXL-16-YELLOW</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
@@ -9757,17 +9761,17 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>0460-202-1631</t>
+          <t>solder splice SP-REV</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>OEM IG2 pin 4 (under the ECU, cowl side) - factory back-up SW feed</t>
+          <t>OEM IG2 pin 13 (under the ECU, cowl side) - factory back-up lamp output</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>DRB102 receptacle (RH firewall)</t>
+          <t>via SP-REV</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9782,55 +9786,55 @@
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>REV</t>
+          <t>SP-REV</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_rev_feed_e at DRB102-ENGINE 77, to REV-SW 2</t>
+          <t>ST185-AB-engine w_sw7_e at DRB102-ENGINE 78, to REV-SW 1</t>
         </is>
       </c>
       <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr">
         <is>
-          <t>OEM IG2 pin 4 (under the ECU, cowl side) - R-L, GAUGE 15 A back-up SW feed; OEM colour R-L; EWD 1992 p.132 / 1990 p.82; crimp butt splice into the factory cowl-side lead at IG2 (cabin, under the ECU; the engine wire is removed)</t>
+          <t>OEM IG2 pin 13 (under the ECU, cowl side) - R-B, back-up lamp output; OEM colour R-B; EWD 1992 p.132; crimp butt splice into the factory cowl-side lead at IG2</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>Circuit 11: factory feed kept. New engine-harness switch in splices to the IG2-4 pigtail.</t>
+          <t>Circuit 11: new switch out splices to the IG2-13 pigtail; rear lamps stay on the factory harness.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>w_rev_lamps</t>
+          <t>w_fl_sig</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>IG2</t>
+          <t>IX-FUEL-P</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>DRB102-CABIN</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SP-REV</t>
+          <t>SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -9840,54 +9844,54 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Back-up lamp +12 V</t>
+          <t>Fuel level signal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>J1128-TXL-16-YELLOW</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr">
         <is>
-          <t>crimp butt splice into the factory cowl-</t>
+          <t>0460-202-1631</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>solder splice SP-REV</t>
+          <t>solder splice SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>OEM IG2 pin 13 (under the ECU, cowl side) - factory back-up lamp output</t>
+          <t>IX-FUEL inline to fuel sender lead (trunk end)</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>via SP-REV</t>
+          <t>via SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>REV</t>
+          <t>FLVL</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
@@ -9897,30 +9901,18 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>SP-REV</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine w_sw7_e at DRB102-ENGINE 78, to REV-SW 1</t>
-        </is>
-      </c>
+          <t>SP-FUEL-LVL</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr"/>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>OEM IG2 pin 13 (under the ECU, cowl side) - R-B, back-up lamp output; OEM colour R-B; EWD 1992 p.132; crimp butt splice into the factory cowl-side lead at IG2</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>Circuit 11: new switch out splices to the IG2-13 pigtail; rear lamps stay on the factory harness.</t>
-        </is>
-      </c>
+      <c r="X87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>w_fl_sig</t>
+          <t>w45</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9930,37 +9922,33 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>BUS-GNDOUT-B</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>SP-FUEL-LVL</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Fuel level signal</t>
+          <t>Fuel level ground</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -9975,7 +9963,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-WHITE</t>
+          <t>J1128-TXL-20-BLUE</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
@@ -9987,7 +9975,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>solder splice SP-FUEL-LVL</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
@@ -9997,12 +9985,12 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>via SP-FUEL-LVL</t>
+          <t>DT06-12 plug (ECU splice point)</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>FLVL</t>
+          <t>SGND</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
@@ -10012,7 +10000,7 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>SP-FUEL-LVL</t>
+          <t>BUS-GNDOUT-B</t>
         </is>
       </c>
       <c r="V88" t="inlineStr"/>
@@ -10023,43 +10011,43 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>w45</t>
+          <t>cab_fspur_5v</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>IX-FUEL-P</t>
+          <t>IX-WS-F-S</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-B</t>
+          <t>BUS-5V</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>core</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Fuel level ground</t>
+          <t>VRC-F +5V</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10069,19 +10057,27 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>640</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-BLUE</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>CAB-FSPUR</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>55A1831-20-2/4/6-9</t>
+        </is>
+      </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>0460-202-1631</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10091,7 +10087,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>IX-FUEL inline to fuel sender lead (trunk end)</t>
+          <t>to front VR conditioner</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -10101,7 +10097,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>SGND</t>
+          <t>5V</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
@@ -10111,18 +10107,22 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-B</t>
+          <t>BUS-5V</t>
         </is>
       </c>
       <c r="V89" t="inlineStr"/>
-      <c r="W89" t="inlineStr"/>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>dash branch (front WS inline)</t>
+        </is>
+      </c>
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>cab_fspur_5v</t>
+          <t>cab_fspur_gnd</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10132,17 +10132,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>BUS-5V</t>
+          <t>BUS-GNDOUT-A</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>VRC-F +5V</t>
+          <t>VRC-F GND</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>5V</t>
+          <t>SGND</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>BUS-5V</t>
+          <t>BUS-GNDOUT-A</t>
         </is>
       </c>
       <c r="V90" t="inlineStr"/>
@@ -10233,7 +10233,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>cab_fspur_gnd</t>
+          <t>cab_fspur_l</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10243,17 +10243,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-A</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
@@ -10264,12 +10264,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>VRC-F GND</t>
+          <t>FL conditioned out</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>530</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>DT06-12 plug (ECU splice point)</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>SGND</t>
+          <t>WSSF</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-A</t>
+          <t>WSSF</t>
         </is>
       </c>
       <c r="V91" t="inlineStr"/>
@@ -10344,7 +10344,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>cab_fspur_l</t>
+          <t>cab_fspur_r_ac</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10354,17 +10354,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
@@ -10375,12 +10375,12 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>FL conditioned out</t>
+          <t>FR conditioned out</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -10400,12 +10400,12 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>CAB-FSPUR</t>
+          <t>CAB-FSPUR-FR-AC</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>55A1811-20-9-9CS2275</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -10450,12 +10450,16 @@
         </is>
       </c>
       <c r="X92" t="inlineStr"/>
-      <c r="Y92" t="inlineStr"/>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>ECU-B plug pin B21 (Link G4X, centre dash); wheel speed | owner proposed: longer half (drawn today as cab_fspur_r_ac on ECU-cabin, 350 mm; cab_fspur_r on ECU-cabin, 530 mm)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>cab_fspur_r_ac</t>
+          <t>cab_fspur_sh</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10465,43 +10469,43 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
+        </is>
+      </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>leg core</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>FR conditioned out</t>
+          <t>WS-F screen drain</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>500</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -10511,12 +10515,12 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>CAB-FSPUR-FR-AC</t>
+          <t>CAB-FSPUR</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>55A1811-20-9-9CS2275</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -10526,7 +10530,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>solder splice SP-SHIELD-A-WSF</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -10536,7 +10540,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>via SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -10551,7 +10555,7 @@
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>WSSF</t>
+          <t>SP-SHIELD-A-WSF</t>
         </is>
       </c>
       <c r="V93" t="inlineStr"/>
@@ -10561,62 +10565,58 @@
         </is>
       </c>
       <c r="X93" t="inlineStr"/>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>ECU-B plug pin B21 (Link G4X, centre dash); wheel speed | owner proposed: longer half (drawn today as cab_fspur_r_ac on ECU-cabin, 350 mm; cab_fspur_r on ECU-cabin, 530 mm)</t>
-        </is>
-      </c>
+      <c r="Y93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>cab_fspur_sh</t>
+          <t>cab_rspur_5v</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>IX-WS-F-S</t>
+          <t>IX-WS-R-S</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>BUS-5V</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>leg core</t>
+          <t>core</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>WS-F screen drain</t>
+          <t>VRC-R +5V</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Shield</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr"/>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>640</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -10626,12 +10626,12 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>CAB-FSPUR</t>
+          <t>CAB-RSPUR</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>55A1841-20-2/4/5/6-9</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-A-WSF</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>to front VR conditioner</t>
+          <t>IX-WS-R inline to rear VRC (dash above ECU)</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
+          <t>DT06-12 plug (ECU splice point)</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>WSSF</t>
+          <t>5V</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
@@ -10666,22 +10666,18 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-WSF</t>
+          <t>BUS-5V</t>
         </is>
       </c>
       <c r="V94" t="inlineStr"/>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>dash branch (front WS inline)</t>
-        </is>
-      </c>
+      <c r="W94" t="inlineStr"/>
       <c r="X94" t="inlineStr"/>
       <c r="Y94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>cab_rspur_5v</t>
+          <t>cab_rspur_gnd</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10691,17 +10687,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>BUS-5V</t>
+          <t>BUS-GNDOUT-B</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
@@ -10712,12 +10708,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>VRC-R +5V</t>
+          <t>VRC-R GND</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -10767,7 +10763,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>5V</t>
+          <t>SGND</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
@@ -10777,7 +10773,7 @@
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>BUS-5V</t>
+          <t>BUS-GNDOUT-B</t>
         </is>
       </c>
       <c r="V95" t="inlineStr"/>
@@ -10788,7 +10784,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>cab_rspur_gnd</t>
+          <t>cab_rspur_l</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10798,17 +10794,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-B</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -10819,12 +10815,12 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>VRC-R GND</t>
+          <t>Rear left wheel spd</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -10834,7 +10830,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>530</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -10859,7 +10855,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
@@ -10869,12 +10865,12 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>DT06-12 plug (ECU splice point)</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>SGND</t>
+          <t>WSSR</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
@@ -10884,7 +10880,7 @@
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-B</t>
+          <t>WSSR</t>
         </is>
       </c>
       <c r="V96" t="inlineStr"/>
@@ -10895,7 +10891,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>cab_rspur_l</t>
+          <t>cab_rspur_r</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10905,7 +10901,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -10915,7 +10911,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -10926,12 +10922,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Rear left wheel spd</t>
+          <t>Rear right wheel spd</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11002,7 +10998,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>cab_rspur_r</t>
+          <t>cab_rspur_sh</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -11012,7 +11008,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -11022,33 +11018,33 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr"/>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>SP-SHIELD-B-WSR &gt; SP-SHIELD-B</t>
+        </is>
+      </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>leg core</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Rear right wheel spd</t>
+          <t>WS-R screen drain</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Blue</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>500</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -11073,7 +11069,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>solder splice SP-SHIELD-B-WSR</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -11083,7 +11079,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>via SP-SHIELD-B-WSR &gt; SP-SHIELD-B</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -11098,7 +11094,7 @@
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>WSSR</t>
+          <t>SP-SHIELD-B-WSR</t>
         </is>
       </c>
       <c r="V98" t="inlineStr"/>
@@ -11109,93 +11105,81 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>cab_rspur_sh</t>
+          <t>w_ig2_in</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>IX-WS-R-S</t>
+          <t>JB1-1H</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>D-IG2-WAKE</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>SP-SHIELD-B-WSR &gt; SP-SHIELD-B</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>leg core</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>WS-R screen drain</t>
+          <t>IG2 wake feed</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Shield</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr"/>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>(cable core)</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>CAB-RSPUR</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>55A1841-20-2/4/5/6-9</t>
-        </is>
-      </c>
+          <t>J1128-TXL-20-YELLOW</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>solder splice SP-SHIELD-B-WSR</t>
-        </is>
-      </c>
+          <t>solder onto the factory lead</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>IX-WS-R inline to rear VRC (dash above ECU)</t>
+          <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-B-WSR &gt; SP-SHIELD-B</t>
+          <t>IG2 wake diode (1N5822)</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>WSSR</t>
+          <t>IG2WAKE</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
@@ -11205,18 +11189,26 @@
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B-WSR</t>
+          <t>IG2WAKE</t>
         </is>
       </c>
       <c r="V99" t="inlineStr"/>
-      <c r="W99" t="inlineStr"/>
-      <c r="X99" t="inlineStr"/>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>IG2 tap branch (LH kick panel)</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O - IGN fuse out (EWD 1993 p.62); same lead as the ECU-B B28 sense tap, own splice; OEM colour B-O; EWD 1993 TIS EWD p.62 (Power Source); solder splice onto the factory lead</t>
+        </is>
+      </c>
       <c r="Y99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>w_ig2_in</t>
+          <t>w_ign</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -11231,12 +11223,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>D-IG2-WAKE</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
@@ -11247,7 +11239,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>IG2 wake feed</t>
+          <t>Ignition sw sense</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -11262,7 +11254,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -11277,7 +11269,11 @@
           <t>solder onto the factory lead</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>3-1447221-4</t>
+        </is>
+      </c>
       <c r="Q100" t="inlineStr">
         <is>
           <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O</t>
@@ -11285,12 +11281,12 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>IG2 wake diode (1N5822)</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>IG2WAKE</t>
+          <t>IGNSW</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
@@ -11300,18 +11296,14 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>IG2WAKE</t>
+          <t>IGNSW</t>
         </is>
       </c>
       <c r="V100" t="inlineStr"/>
-      <c r="W100" t="inlineStr">
-        <is>
-          <t>IG2 tap branch (LH kick panel)</t>
-        </is>
-      </c>
+      <c r="W100" t="inlineStr"/>
       <c r="X100" t="inlineStr">
         <is>
-          <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O - IGN fuse out (EWD 1993 p.62); same lead as the ECU-B B28 sense tap, own splice; OEM colour B-O; EWD 1993 TIS EWD p.62 (Power Source); solder splice onto the factory lead</t>
+          <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O - IGN fuse out (EWD 1993 p.62); OEM colour B-O; EWD 1993 TIS EWD p.62 (Power Source); solder splice onto the factory lead</t>
         </is>
       </c>
       <c r="Y100" t="inlineStr"/>
@@ -11319,85 +11311,89 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>w_ign</t>
+          <t>w_acc86</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>JB1-1H</t>
+          <t>K-ACC</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>86</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>LOGIC</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
+          <t>BUS2-8</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>SP-ACC12</t>
+        </is>
+      </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Ignition sw sense</t>
+          <t>A/C clutch relay coil+</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-YELLOW</t>
+          <t>M22759/16-18-2</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
         <is>
-          <t>solder onto the factory lead</t>
+          <t>280919-2</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>solder splice SP-ACC12</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O</t>
+          <t>B2-M5 A/C clutch relay (k_acc) - amp A15 pin 8 sinks coil- (85); coil+ (86) fused +12 V from B2-BUS2-8</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>via SP-ACC12</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>IGNSW</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="T101" t="inlineStr">
@@ -11407,62 +11403,66 @@
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>IGNSW</t>
-        </is>
-      </c>
-      <c r="V101" t="inlineStr"/>
-      <c r="W101" t="inlineStr"/>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O - IGN fuse out (EWD 1993 p.62); OEM colour B-O; EWD 1993 TIS EWD p.62 (Power Source); solder splice onto the factory lead</t>
-        </is>
-      </c>
-      <c r="Y101" t="inlineStr"/>
+          <t>SP-ACC12</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>SP-ACC12 also joins ST185-CabinPower</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>A/C amp branch (behind dash)</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr"/>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>LOGIC box (glove box) relay M15 A/C clutch, pin 86 | B15: coil 86 is fused +12 V. Pressure switch stays on amp pin 13 only.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>w_acc86</t>
+          <t>w76</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>K-ACC</t>
+          <t>K-EFI</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LOGIC</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>BUS2-8</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>SP-ACC12</t>
-        </is>
-      </c>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>A/C clutch relay coil+</t>
+          <t>EFI relay coil (-)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -11472,77 +11472,73 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>370</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>M22759/16-18-2</t>
+          <t>J1128-TXL-18-WHITE</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr">
         <is>
-          <t>280919-2</t>
+          <t>42281-1</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>solder splice SP-ACC12</t>
+          <t>3-1447221-3</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>B2-M5 A/C clutch relay (k_acc) - amp A15 pin 8 sinks coil- (85); coil+ (86) fused +12 V from B2-BUS2-8</t>
+          <t>B1-R2 EFI Main Relay (seated in the POWER box R2) - ACTIVE-LOW - ECU sinks coil- (85); coil+ (86) permanent 12 V (LOGIC EFI86 5 A)</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>via SP-ACC12</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>EFI</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin</t>
+          <t>ST185-CabinPower</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>SP-ACC12</t>
-        </is>
-      </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>SP-ACC12 also joins ST185-CabinPower</t>
-        </is>
-      </c>
+          <t>EFI</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr"/>
       <c r="W102" t="inlineStr">
         <is>
-          <t>A/C amp branch (behind dash)</t>
+          <t>glove-box branch (POWER / LOGIC boxes)</t>
         </is>
       </c>
       <c r="X102" t="inlineStr"/>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) relay M15 A/C clutch, pin 86 | B15: coil 86 is fused +12 V. Pressure switch stays on amp pin 13 only.</t>
+          <t>POWER box (glove box) relay R2 EFI main, pin 85 | owner proposed: longer half (drawn today as w76 on ECU-cabin, 370 mm; w76_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>w76</t>
+          <t>w_eps_rly</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>K-EFI</t>
+          <t>K-EPS</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -11552,12 +11548,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>DRB102-CABIN</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
@@ -11568,7 +11564,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>EFI relay coil (-)</t>
+          <t>EHPS relay coil (-)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -11583,73 +11579,77 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>450</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>J1128-TXL-18-WHITE</t>
+          <t>M22759/16-18-9</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr">
         <is>
-          <t>42281-1</t>
+          <t>282110-1</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>3-1447221-3</t>
+          <t>0460-202-1631</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>B1-R2 EFI Main Relay (seated in the POWER box R2) - ACTIVE-LOW - ECU sinks coil- (85); coil+ (86) permanent 12 V (LOGIC EFI86 5 A)</t>
+          <t>B4 EPS pump relay (HCR150, glove box, beside the POWER box) - coil- (85) switched to ground by the MR-S pump pin B5 (R22); coil+ (86) switched 12 V - HCR 150 coil is a 2-pole plug (TE terminals 1/2, not marked 85/86), resistor-suppressed so polarity-free</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>DRB102 receptacle (RH firewall)</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>EFI</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>ST185-CabinPower</t>
+          <t>ST185-AB-cabin</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>EFI</t>
-        </is>
-      </c>
-      <c r="V103" t="inlineStr"/>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>ST185-AB-engine w_eps_rly_e at DRB102-ENGINE 85, to MRS-B 5</t>
+        </is>
+      </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>glove-box branch (POWER / LOGIC boxes)</t>
+          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
         </is>
       </c>
       <c r="X103" t="inlineStr"/>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>POWER box (glove box) relay R2 EFI main, pin 85 | owner proposed: longer half (drawn today as w76 on ECU-cabin, 370 mm; w76_cp on CabinPower, 400 mm)</t>
+          <t>EHPS pump relay (glove box), pin 85 | owner proposed: longer half (drawn today as w_eps_rly on ECU-cabin, 530 mm; w_eps_rly_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>w_eps_rly</t>
+          <t>w81</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>K-EPS</t>
+          <t>K-ETB</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -11659,12 +11659,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>DRB102-CABIN</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>EHPS relay coil (-)</t>
+          <t>ETB relay coil (-)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -11685,77 +11685,73 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>380</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr">
         <is>
-          <t>282110-1</t>
+          <t>280919-2</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>0460-202-1631</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>B4 EPS pump relay (HCR150, glove box, beside the POWER box) - coil- (85) switched to ground by the MR-S pump pin B5 (R22); coil+ (86) switched 12 V - HCR 150 coil is a 2-pole plug (TE terminals 1/2, not marked 85/86), resistor-suppressed so polarity-free</t>
+          <t>B2-M4 ETB Power Relay (seated in the LOGIC box M4) - ACTIVE-LOW - ECU sinks coil- (85); coil+ (86) switched 12 V</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>DRB102 receptacle (RH firewall)</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>EPS</t>
+          <t>ETB</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin</t>
+          <t>ST185-CabinPower</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>EPS</t>
-        </is>
-      </c>
-      <c r="V104" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine w_eps_rly_e at DRB102-ENGINE 85, to MRS-B 5</t>
-        </is>
-      </c>
+          <t>ETB</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr"/>
       <c r="W104" t="inlineStr">
         <is>
-          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
+          <t>glove-box branch (POWER / LOGIC boxes)</t>
         </is>
       </c>
       <c r="X104" t="inlineStr"/>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>EHPS pump relay (glove box), pin 85 | owner proposed: longer half (drawn today as w_eps_rly on ECU-cabin, 530 mm; w_eps_rly_cp on CabinPower, 400 mm)</t>
+          <t>LOGIC box (glove box) relay M14 ETB power, pin 85 | owner proposed: longer half (drawn today as w81 on ECU-cabin, 380 mm; w81_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>w81</t>
+          <t>w82_ac</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -11765,17 +11761,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
@@ -11786,39 +11782,39 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>ETB relay coil (-)</t>
+          <t>ETB motor +12 V</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>400</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-18-RED</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr">
         <is>
-          <t>280919-2</t>
+          <t>42281-1</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>3-1447221-3</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -11828,7 +11824,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
@@ -11847,42 +11843,38 @@
         </is>
       </c>
       <c r="V105" t="inlineStr"/>
-      <c r="W105" t="inlineStr">
-        <is>
-          <t>glove-box branch (POWER / LOGIC boxes)</t>
-        </is>
-      </c>
+      <c r="W105" t="inlineStr"/>
       <c r="X105" t="inlineStr"/>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) relay M14 ETB power, pin 85 | owner proposed: longer half (drawn today as w81 on ECU-cabin, 380 mm; w81_cp on CabinPower, 400 mm)</t>
+          <t>owner proposed: longer half (drawn today as w82_ac on CabinPower, 400 mm; w82 on ECU-cabin, 340 mm)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>w82_ac</t>
+          <t>w_fan85</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>K-ETB</t>
+          <t>K-FAN</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
@@ -11893,12 +11885,12 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>ETB motor +12 V</t>
+          <t>Rad fan relay (-)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -11908,12 +11900,12 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>680</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>J1128-TXL-18-RED</t>
+          <t>M22759/16-18-9</t>
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
@@ -11930,47 +11922,51 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>B2-M4 ETB Power Relay (seated in the LOGIC box M4) - ACTIVE-LOW - ECU sinks coil- (85); coil+ (86) switched 12 V</t>
+          <t>B1-R4 Radiator fan relay (seated in the POWER box R4)</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>ETB</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>ST185-CabinPower</t>
+          <t>ST185-AB-cabin</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>ETB</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="V106" t="inlineStr"/>
-      <c r="W106" t="inlineStr"/>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>glove-box branch (POWER / LOGIC boxes)</t>
+        </is>
+      </c>
       <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w82_ac on CabinPower, 400 mm; w82 on ECU-cabin, 340 mm)</t>
+          <t>POWER box (glove box) relay R4 radiator fan, pin 85 | owner proposed: longer half (drawn today as w_fan85 on ECU-cabin, 410 mm; w_fan85_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>w_fan85</t>
+          <t>w_fan285</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>K-FAN</t>
+          <t>K-FAN2</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -11980,12 +11976,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
@@ -11996,7 +11992,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Rad fan relay (-)</t>
+          <t>Cond fan relay (-)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -12033,17 +12029,17 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>B1-R4 Radiator fan relay (seated in the POWER box R4)</t>
+          <t>B1-R5 Condenser fan relay (seated in the POWER box R5)</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>FAN2</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
@@ -12053,31 +12049,27 @@
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>FAN2</t>
         </is>
       </c>
       <c r="V107" t="inlineStr"/>
-      <c r="W107" t="inlineStr">
-        <is>
-          <t>glove-box branch (POWER / LOGIC boxes)</t>
-        </is>
-      </c>
+      <c r="W107" t="inlineStr"/>
       <c r="X107" t="inlineStr"/>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>POWER box (glove box) relay R4 radiator fan, pin 85 | owner proposed: longer half (drawn today as w_fan85 on ECU-cabin, 410 mm; w_fan85_cp on CabinPower, 400 mm)</t>
+          <t>owner proposed: longer half (drawn today as w_fan285_cp on CabinPower, 400 mm; w_fan285 on ECU-cabin, 480 mm)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>w_fan285</t>
+          <t>w_fp85</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>K-FAN2</t>
+          <t>K-FP</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -12087,12 +12079,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
@@ -12103,7 +12095,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Cond fan relay (-)</t>
+          <t>Fuel pump relay (-)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -12118,7 +12110,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -12130,7 +12122,7 @@
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
-          <t>42281-1</t>
+          <t>282110-1</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -12140,17 +12132,17 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>B1-R5 Condenser fan relay (seated in the POWER box R5)</t>
+          <t>B3-K1 Fuel Pump Relay, TE HCR150 (seated in the battery relay block K1) - ACTIVE-LOW - ECU sinks coil- (85); coil+ (86) switched 12 V - HCR 150 coil is a 2-pole Superseal plug (TE terminals 1/2, not marked 85/86), resistor-suppressed so polarity-free</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>FAN2</t>
+          <t>FP</t>
         </is>
       </c>
       <c r="T108" t="inlineStr">
@@ -12160,42 +12152,46 @@
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>FAN2</t>
+          <t>FP</t>
         </is>
       </c>
       <c r="V108" t="inlineStr"/>
-      <c r="W108" t="inlineStr"/>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>glove-box branch (POWER / LOGIC boxes) / cabin run to the trunk relay block (Routes 1 / 11)</t>
+        </is>
+      </c>
       <c r="X108" t="inlineStr"/>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_fan285_cp on CabinPower, 400 mm; w_fan285 on ECU-cabin, 480 mm)</t>
+          <t>Battery relay block (trunk) relay K1 fuel pump, pin 85 | est length: ECU-A to the glove-box boxes (390 mm) plus the cabin run to K-FP in the trunk relay block, alongside w_k_fp_86_cp (2500 mm); row 157</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>w_fp85</t>
+          <t>w_lam12_cp</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>K-FP</t>
+          <t>LOGIC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>BUS2-1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>DRB102-CABIN</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
@@ -12206,83 +12202,83 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Fuel pump relay (-)</t>
+          <t>EFI relay k_efi -&gt; LOGIC LAM 7.5 A fuse</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>250</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>J1128-TXL-14-RED</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr">
         <is>
-          <t>282110-1</t>
+          <t>1-968851-1</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>3-1447221-3</t>
+          <t>0460-220-1231</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>B3-K1 Fuel Pump Relay, TE HCR150 (seated in the battery relay block K1) - ACTIVE-LOW - ECU sinks coil- (85); coil+ (86) switched 12 V - HCR 150 coil is a 2-pole Superseal plug (TE terminals 1/2, not marked 85/86), resistor-suppressed so polarity-free</t>
+          <t>B2 LOGIC box - custom fuse + relay box, glove box inboard (cad/fusebox rev 5, DECISIONS R75): Bus 1 (permanent) and Bus 2 (switched, k_efi 30) mini fuse strips, micro relays M1-M10</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>DRB102 receptacle (RH firewall)</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>FP</t>
+          <t>LAM</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin</t>
+          <t>ST185-CabinPower</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>FP</t>
-        </is>
-      </c>
-      <c r="V109" t="inlineStr"/>
-      <c r="W109" t="inlineStr">
-        <is>
-          <t>glove-box branch (POWER / LOGIC boxes) / cabin run to the trunk relay block (Routes 1 / 11)</t>
-        </is>
-      </c>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>ST185-AB-engine w_lam12_be14 at DRB102-ENGINE 95, to splice SP-LAM12-B</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr"/>
       <c r="X109" t="inlineStr"/>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>Battery relay block (trunk) relay K1 fuel pump, pin 85 | est length: ECU-A to the glove-box boxes (390 mm) plus the cabin run to K-FP in the trunk relay block, alongside w_k_fp_86_cp (2500 mm); row 157</t>
+          <t>CAN-Lambda +12 V | CAN-Lambda +12 V | owner proposed: longer half (drawn today as w_lam12_cp on CabinPower, 250 mm; w_lam12_bc on ECU-cabin, 120 mm)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>w_lam12_cp</t>
+          <t>w_fb_mrs_en</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -12292,7 +12288,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BUS2-1</t>
+          <t>BUS2-12</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -12302,7 +12298,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>83</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
@@ -12313,7 +12309,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC LAM 7.5 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC MRS 5 A fuse</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -12323,29 +12319,29 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>450</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>J1128-TXL-14-RED</t>
+          <t>J1128-TXL-20-RED</t>
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr">
         <is>
-          <t>1-968851-1</t>
+          <t>1-968849-1</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>0460-220-1231</t>
+          <t>0460-202-1631</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -12360,36 +12356,40 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>LAM</t>
+          <t>EPSEN</t>
         </is>
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>ST185-CabinPower</t>
+          <t>ST185-AB-cabin</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>LAM</t>
+          <t>EPSEN</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_lam12_be14 at DRB102-ENGINE 95, to splice SP-LAM12-B</t>
-        </is>
-      </c>
-      <c r="W110" t="inlineStr"/>
+          <t>ST185-AB-engine w_hv_mrs_en_e at DRB102-ENGINE 83, to MRS-C 1</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
+        </is>
+      </c>
       <c r="X110" t="inlineStr"/>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>CAN-Lambda +12 V | CAN-Lambda +12 V | owner proposed: longer half (drawn today as w_lam12_cp on CabinPower, 250 mm; w_lam12_bc on ECU-cabin, 120 mm)</t>
+          <t>LOGIC box (glove box) fuse MRS 7.5A Fuse fed from EPS enable relay k_eps_en pin 87 (ignition-switched). | EHPS enable +12 V | fuse fed from EPS enable relay k_eps_en pin 87 (ignition-switched); owner proposed: longer half (drawn today as w_fb_mrs_en on ECU-cabin, 530 mm; w_fb_mrs_en_cp on CabinPower, 250 mm)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>w_fb_mrs_en</t>
+          <t>w_start</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -12399,17 +12399,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BUS2-12</t>
+          <t>BUS2-13</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>DRB102-CABIN</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
@@ -12420,12 +12420,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC MRS 5 A fuse</t>
+          <t>Start request</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -12435,12 +12435,12 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>680</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-RED</t>
+          <t>J1128-TXL-20-YELLOW</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
@@ -12452,7 +12452,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>0460-202-1631</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -12462,12 +12462,12 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>DRB102 receptacle (RH firewall)</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>EPSEN</t>
+          <t>B30</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
@@ -12477,30 +12477,22 @@
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>EPSEN</t>
-        </is>
-      </c>
-      <c r="V111" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine w_hv_mrs_en_e at DRB102-ENGINE 83, to MRS-C 1</t>
-        </is>
-      </c>
-      <c r="W111" t="inlineStr">
-        <is>
-          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
-        </is>
-      </c>
+          <t>B30</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr"/>
+      <c r="W111" t="inlineStr"/>
       <c r="X111" t="inlineStr"/>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) fuse MRS 7.5A Fuse fed from EPS enable relay k_eps_en pin 87 (ignition-switched). | EHPS enable +12 V | fuse fed from EPS enable relay k_eps_en pin 87 (ignition-switched); owner proposed: longer half (drawn today as w_fb_mrs_en on ECU-cabin, 530 mm; w_fb_mrs_en_cp on CabinPower, 250 mm)</t>
+          <t>owner proposed: longer half (drawn today as w_start_cp on CabinPower, 530 mm; w_start on ECU-cabin, 1230 mm)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>w_start</t>
+          <t>w_cop_pwr_ac</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -12510,17 +12502,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>BUS2-13</t>
+          <t>BUS2-3</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>DRB102-CABIN</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
@@ -12531,39 +12523,39 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Start request</t>
+          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>180</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-YELLOW</t>
+          <t>J1128-TXL-14-RED</t>
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
-          <t>1-968849-1</t>
+          <t>1-968851-1</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>0460-220-1231</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
@@ -12573,37 +12565,45 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>DRB102 receptacle (RH firewall)</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>B30</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin</t>
+          <t>ST185-CabinPower</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>B30</t>
-        </is>
-      </c>
-      <c r="V112" t="inlineStr"/>
-      <c r="W112" t="inlineStr"/>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>ST185-AB-engine w_cop_pwr_e_ae at DRB102-ENGINE 1, to splice SP-COP-ENG</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
+        </is>
+      </c>
       <c r="X112" t="inlineStr"/>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_start_cp on CabinPower, 530 mm; w_start on ECU-cabin, 1230 mm)</t>
+          <t>LOGIC box (glove box) fuse COP 10A | Coil +12 V feed | owner proposed: longer half (drawn today as w_cop_pwr_ac on ECU-cabin, 180 mm; w_cop_pwr_c_ac on CabinPower, 250 mm)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>w_cop_pwr_ac</t>
+          <t>w_inj_pwr_ac</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>BUS2-3</t>
+          <t>BUS2-4</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -12623,7 +12623,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC INJ 7.5 A fuse</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>INJ</t>
         </is>
       </c>
       <c r="T113" t="inlineStr">
@@ -12691,12 +12691,12 @@
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>INJ</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_cop_pwr_e_ae at DRB102-ENGINE 1, to splice SP-COP-ENG</t>
+          <t>ST185-AB-engine w_inj_pwr_e_ae at DRB102-ENGINE 2, to splice SP-INJ-ENG</t>
         </is>
       </c>
       <c r="W113" t="inlineStr">
@@ -12707,24 +12707,24 @@
       <c r="X113" t="inlineStr"/>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) fuse COP 10A | Coil +12 V feed | owner proposed: longer half (drawn today as w_cop_pwr_ac on ECU-cabin, 180 mm; w_cop_pwr_c_ac on CabinPower, 250 mm)</t>
+          <t>LOGIC box (glove box) fuse INJ 7.5A | Injector +12 V feed | owner proposed: longer half (drawn today as w_inj_pwr_ac on ECU-cabin, 180 mm; w_inj_pwr_c_ac on CabinPower, 250 mm)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>w_inj_pwr_ac</t>
+          <t>w_sw7_c</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>LOGIC</t>
+          <t>OPTO-8</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>BUS2-4</t>
+          <t>IN2</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -12734,123 +12734,123 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr"/>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>SP-REV</t>
+        </is>
+      </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC INJ 7.5 A fuse</t>
+          <t>Reverse to opto in 2</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>680</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>J1128-TXL-14-RED</t>
+          <t>J1128-TXL-16-YELLOW</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr">
         <is>
-          <t>1-968851-1</t>
+          <t>screw terminal (on the board)</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>0460-220-1231</t>
+          <t>solder splice SP-REV</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>B2 LOGIC box - custom fuse + relay box, glove box inboard (cad/fusebox rev 5, DECISIONS R75): Bus 1 (permanent) and Bus 2 (switched, k_efi 30) mini fuse strips, micro relays M1-M10</t>
+          <t>Optocoupler board, 8 channel (Dan's, generic EL814) - inline at the CSB3</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>DRB102 receptacle (RH firewall)</t>
+          <t>via SP-REV</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>INJ</t>
+          <t>REV</t>
         </is>
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>ST185-CabinPower</t>
+          <t>ST185-AB-cabin</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>INJ</t>
+          <t>SP-REV</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_inj_pwr_e_ae at DRB102-ENGINE 2, to splice SP-INJ-ENG</t>
-        </is>
-      </c>
-      <c r="W114" t="inlineStr">
-        <is>
-          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
-        </is>
-      </c>
+          <t>ST185-AB-engine w_sw7_e at DRB102-ENGINE 78, to REV-SW 1</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr"/>
       <c r="X114" t="inlineStr"/>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) fuse INJ 7.5A | Injector +12 V feed | owner proposed: longer half (drawn today as w_inj_pwr_ac on ECU-cabin, 180 mm; w_inj_pwr_c_ac on CabinPower, 250 mm)</t>
+          <t>owner TBD: a half has no length estimate (drawn today as w_sw7_c on ECU-cabin, ? mm; w_sw7_c_csb on CSB3, 180 mm)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>w_sw7_c</t>
+          <t>w_cam_pullup_8v</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>OPTO-8</t>
+          <t>R-CAM-PULLUP</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>IN2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>DRB102-CABIN</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>SP-REV</t>
+          <t>SP-8V</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -12860,54 +12860,50 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Reverse to opto in 2</t>
+          <t>+8 V to cam pull-up</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>J1128-TXL-16-YELLOW</t>
+          <t>J1128-TXL-20-ORANGE</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr">
-        <is>
-          <t>screw terminal (on the board)</t>
-        </is>
-      </c>
+      <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>solder splice SP-REV</t>
+          <t>solder splice SP-8V</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>Optocoupler board, 8 channel (Dan's, generic EL814) - inline at the CSB3</t>
+          <t>Cam pull-up 1.8 k to +8 V</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>via SP-REV</t>
+          <t>via SP-8V</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>REV</t>
+          <t>CAM</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
@@ -12917,26 +12913,22 @@
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>SP-REV</t>
-        </is>
-      </c>
-      <c r="V115" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine w_sw7_e at DRB102-ENGINE 78, to REV-SW 1</t>
-        </is>
-      </c>
-      <c r="W115" t="inlineStr"/>
+          <t>SP-8V</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr"/>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>at ECU-A plug</t>
+        </is>
+      </c>
       <c r="X115" t="inlineStr"/>
-      <c r="Y115" t="inlineStr">
-        <is>
-          <t>owner TBD: a half has no length estimate (drawn today as w_sw7_c on ECU-cabin, ? mm; w_sw7_c_csb on CSB3, 180 mm)</t>
-        </is>
-      </c>
+      <c r="Y115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>w_cam_pullup_8v</t>
+          <t>w_cam_pullup_sig</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -12946,7 +12938,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -12956,12 +12948,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>SP-8V</t>
+          <t>SP-CAM</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -12971,12 +12963,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>+8 V to cam pull-up</t>
+          <t>Cam pull-up 1.8k</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -12991,7 +12983,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-ORANGE</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
@@ -12999,7 +12991,7 @@
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>solder splice SP-8V</t>
+          <t>solder splice SP-CAM</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
@@ -13009,7 +13001,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>via SP-8V</t>
+          <t>via SP-CAM</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
@@ -13024,7 +13016,7 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>SP-8V</t>
+          <t>SP-CAM</t>
         </is>
       </c>
       <c r="V116" t="inlineStr"/>
@@ -13039,32 +13031,32 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>w_cam_pullup_sig</t>
+          <t>w43</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>R-CAM-PULLUP</t>
+          <t>R-FUELLVL</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>SP-CAM</t>
+          <t>SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -13074,7 +13066,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Cam pull-up 1.8k</t>
+          <t>Fuel lvl pull-up</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -13102,22 +13094,22 @@
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>solder splice SP-CAM</t>
+          <t>solder splice SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>Cam pull-up 1.8 k to +8 V</t>
+          <t>470R fuel level pull-up to +5V</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>via SP-CAM</t>
+          <t>via SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>CAM</t>
+          <t>FLVL</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
@@ -13127,22 +13119,18 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>SP-CAM</t>
+          <t>SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="V117" t="inlineStr"/>
-      <c r="W117" t="inlineStr">
-        <is>
-          <t>at ECU-A plug</t>
-        </is>
-      </c>
+      <c r="W117" t="inlineStr"/>
       <c r="X117" t="inlineStr"/>
       <c r="Y117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>w43</t>
+          <t>w44</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -13152,37 +13140,33 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>BUS-5V-2</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>SP-FUEL-LVL</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Fuel lvl pull-up</t>
+          <t>+5 V fuel lvl pullup</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -13197,7 +13181,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-WHITE</t>
+          <t>J1128-TXL-20-ORANGE</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
@@ -13205,7 +13189,7 @@
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>solder splice SP-FUEL-LVL</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
@@ -13215,7 +13199,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>via SP-FUEL-LVL</t>
+          <t>DT06-8 plug (ECU splice point)</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
@@ -13230,7 +13214,7 @@
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>SP-FUEL-LVL</t>
+          <t>BUS-5V-2</t>
         </is>
       </c>
       <c r="V118" t="inlineStr"/>
@@ -13241,43 +13225,47 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>w44</t>
+          <t>w_tach_r</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>R-FUELLVL</t>
+          <t>R-LOCK</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>BUS-5V-2</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>SP-TACH</t>
+        </is>
+      </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>+5 V fuel lvl pullup</t>
+          <t>Tacho to lock-sensor 4.7k</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -13292,7 +13280,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-ORANGE</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
@@ -13300,22 +13288,22 @@
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>solder splice SP-TACH</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>470R fuel level pull-up to +5V</t>
+          <t>Lock-sensor tap 4.7 k from tacho</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>DT06-8 plug (ECU splice point)</t>
+          <t>via SP-TACH</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>FLVL</t>
+          <t>TACH</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
@@ -13325,18 +13313,26 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>BUS-5V-2</t>
+          <t>SP-TACH</t>
         </is>
       </c>
       <c r="V119" t="inlineStr"/>
-      <c r="W119" t="inlineStr"/>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>A/C amp branch (behind dash)</t>
+        </is>
+      </c>
       <c r="X119" t="inlineStr"/>
-      <c r="Y119" t="inlineStr"/>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>OPEN-ITEMS History 2026-10-21 N61: first bench try is tach -&gt; 4.7 kohm -&gt; A15-9. Dan 2026-10-26: lock-sensor input needs a modified tachometer signal; apply that workaround.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>w_tach_r</t>
+          <t>w_lock_9</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -13346,32 +13342,28 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>A18</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>SP-TACH</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Tacho to lock-sensor 4.7k</t>
+          <t>Lock-sensor input (modified tacho)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -13399,7 +13391,7 @@
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>solder splice SP-TACH</t>
+          <t>solder onto the factory lead</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -13409,7 +13401,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>via SP-TACH</t>
+          <t>OEM A/C amplifier A18 (1993 book: A15)</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -13424,7 +13416,7 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>SP-TACH</t>
+          <t>TACH</t>
         </is>
       </c>
       <c r="V120" t="inlineStr"/>
@@ -13433,37 +13425,41 @@
           <t>A/C amp branch (behind dash)</t>
         </is>
       </c>
-      <c r="X120" t="inlineStr"/>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>A/C amplifier A18 (1993: A15) pin 9, behind the glove box; OEM colour W-L; EWD 1993 p.210-211; solder onto the factory lead</t>
+        </is>
+      </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>OPEN-ITEMS History 2026-10-21 N61: first bench try is tach -&gt; 4.7 kohm -&gt; A15-9. Dan 2026-10-26: lock-sensor input needs a modified tachometer signal; apply that workaround.</t>
+          <t>A15 pin 9 lock-sensor (factory W-L / IH1-4). Engine-side lock sensor unused. | Factory lock sensor is A15 pins 9-14 (W-L / W-R, Mitchell ~115 ohm). Workaround: modified tacho through 4.7k to pin 9 (N61 2026-10-21). IH1-4/5 engine wires unused (Engine Wire gone).</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>w_lock_9</t>
+          <t>w_start_in_cp</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>R-LOCK</t>
+          <t>RB4</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>A18</t>
+          <t>LOGIC</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>BUS2-13 IN</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
@@ -13474,12 +13470,12 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Lock-sensor input (modified tacho)</t>
+          <t>Start sw ST1 feed</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -13489,175 +13485,179 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>530</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-WHITE</t>
+          <t>J1128-TXL-20-YELLOW</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>solder onto the factory lead</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>solder onto the factory lead</t>
+          <t>1-968849-1</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>Lock-sensor tap 4.7 k from tacho</t>
+          <t>OEM ST1 lead B-W at old R/B No.4 pin 1, RH kick panel</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>OEM A/C amplifier A18 (1993 book: A15)</t>
+          <t>B2 LOGIC box - custom fuse + relay box, glove box inboard (cad/fusebox rev 5, DECISIONS R75): Bus 1 (permanent) and Bus 2 (switched, k_efi 30) mini fuse strips, micro relays M1-M10</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>TACH</t>
+          <t>B30</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin</t>
+          <t>ST185-CabinPower</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>TACH</t>
+          <t>B30</t>
         </is>
       </c>
       <c r="V121" t="inlineStr"/>
-      <c r="W121" t="inlineStr">
-        <is>
-          <t>A/C amp branch (behind dash)</t>
-        </is>
-      </c>
+      <c r="W121" t="inlineStr"/>
       <c r="X121" t="inlineStr">
         <is>
-          <t>A/C amplifier A18 (1993: A15) pin 9, behind the glove box; OEM colour W-L; EWD 1993 p.210-211; solder onto the factory lead</t>
+          <t>OEM ST1 lead B-W at old R/B No.4 pin 1, RH kick panel - start (EWD 1993 p.66); OEM colour B-W; EWD 1993 TIS EWD p.66 (Starting and Ignition, All-Trac); solder splice onto the factory lead</t>
         </is>
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>A15 pin 9 lock-sensor (factory W-L / IH1-4). Engine-side lock sensor unused. | Factory lock sensor is A15 pins 9-14 (W-L / W-R, Mitchell ~115 ohm). Workaround: modified tacho through 4.7k to pin 9 (N61 2026-10-21). IH1-4/5 engine wires unused (Engine Wire gone).</t>
+          <t>owner proposed: longer half (drawn today as w_start_in on ECU-cabin, 350 mm; w_start_in_cp on CabinPower, 530 mm)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>w_start_in_cp</t>
+          <t>cab_aps1_sh</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>RB4</t>
+          <t>NC, floats</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LOGIC</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>BUS2-13 IN</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
+        </is>
+      </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>drain</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Start sw ST1 feed</t>
+          <t>Pedal 1 cable shield</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>840</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-YELLOW</t>
-        </is>
-      </c>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr">
-        <is>
-          <t>solder onto the factory lead</t>
-        </is>
-      </c>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>CAB-APS1</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>55A1831-20-2/4/6-9</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>1-968849-1</t>
+          <t>solder splice SP-SHIELD-A-APS</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>OEM ST1 lead B-W at old R/B No.4 pin 1, RH kick panel</t>
+          <t>cab_aps1 screen (floats at the device end)</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>B2 LOGIC box - custom fuse + relay box, glove box inboard (cad/fusebox rev 5, DECISIONS R75): Bus 1 (permanent) and Bus 2 (switched, k_efi 30) mini fuse strips, micro relays M1-M10</t>
+          <t>via SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>B30</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>ST185-CabinPower</t>
+          <t>ST185-AB-cabin</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>B30</t>
+          <t>SP-SHIELD-A-APS</t>
         </is>
       </c>
       <c r="V122" t="inlineStr"/>
-      <c r="W122" t="inlineStr"/>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>OEM ST1 lead B-W at old R/B No.4 pin 1, RH kick panel - start (EWD 1993 p.66); OEM colour B-W; EWD 1993 TIS EWD p.66 (Starting and Ignition, All-Trac); solder splice onto the factory lead</t>
-        </is>
-      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>at ECU-A plug</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr"/>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_start_in on ECU-cabin, 350 mm; w_start_in_cp on CabinPower, 530 mm)</t>
+          <t>Screen floats at this end: cut back and seal under heat-shrink | screen floats at the far end; pedal branch length estimated from OEM body dimensions + 10 % (990 mm ECU-A</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>cab_aps1_sh</t>
+          <t>cab_aps_sh</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -13692,7 +13692,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Pedal 1 cable shield</t>
+          <t>Pedal 2 cable shield</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>CAB-APS1</t>
+          <t>CAB-APS2</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -13729,7 +13729,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>cab_aps1 screen (floats at the device end)</t>
+          <t>cab_aps2 screen (floats at the device end)</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -13768,7 +13768,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>cab_aps_sh</t>
+          <t>cab_fspur_fr_sh_ac</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
+          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -13803,7 +13803,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Pedal 2 cable shield</t>
+          <t>FR wheel spd shield</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -13814,7 +13814,7 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>500</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -13824,33 +13824,33 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>CAB-APS2</t>
+          <t>CAB-FSPUR-FR-AC</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>55A1811-20-9-9CS2275</t>
         </is>
       </c>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-A-APS</t>
+          <t>solder splice SP-SHIELD-A-WSF</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>cab_aps2 screen (floats at the device end)</t>
+          <t>cab_fspur_fr_ac screen (floats at the device end)</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
+          <t>via SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>WSSF</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
@@ -13860,36 +13860,36 @@
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-APS</t>
+          <t>SP-SHIELD-A-WSF</t>
         </is>
       </c>
       <c r="V124" t="inlineStr"/>
       <c r="W124" t="inlineStr">
         <is>
-          <t>at ECU-A plug</t>
+          <t>dash branch (front WS inline)</t>
         </is>
       </c>
       <c r="X124" t="inlineStr"/>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>Screen floats at this end: cut back and seal under heat-shrink | screen floats at the far end; pedal branch length estimated from OEM body dimensions + 10 % (990 mm ECU-A</t>
+          <t>Screen floats at this end: cut back and seal under heat-shrink | tied at the A end only; the far (B) end floats, dressed back at the ECU-B plug (no A-B shield bridge)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>cab_fspur_fr_sh_ac</t>
+          <t>w19</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>NC, floats</t>
+          <t>legs of SP-8V</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -13899,69 +13899,69 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
+          <t>SP-8V</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>drain</t>
+          <t>trunk</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>FR wheel spd shield</t>
+          <t>+8 V sensor supply</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Shield</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr"/>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>310</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>(cable core)</t>
-        </is>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>CAB-FSPUR-FR-AC</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t>55A1811-20-9-9CS2275</t>
-        </is>
-      </c>
-      <c r="O125" t="inlineStr"/>
+          <t>J1128-TXL-20-ORANGE</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>solder splice</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-A-WSF</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>cab_fspur_fr_ac screen (floats at the device end)</t>
+          <t>ECU splice point - SP-8V: +8 V supply, cam sensor + gearbox speed sensor only (ECU A6)</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>WSSF</t>
+          <t>8V</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
@@ -13971,31 +13971,27 @@
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-WSF</t>
+          <t>SP-8V</t>
         </is>
       </c>
       <c r="V125" t="inlineStr"/>
       <c r="W125" t="inlineStr">
         <is>
-          <t>dash branch (front WS inline)</t>
+          <t>at ECU-A plug</t>
         </is>
       </c>
       <c r="X125" t="inlineStr"/>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>Screen floats at this end: cut back and seal under heat-shrink | tied at the A end only; the far (B) end floats, dressed back at the ECU-B plug (no A-B shield bridge)</t>
-        </is>
-      </c>
+      <c r="Y125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>w19</t>
+          <t>w_a5_pin</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>legs of SP-8V</t>
+          <t>legs of SP-A5</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -14010,12 +14006,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SP-8V</t>
+          <t>SP-A5</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -14025,17 +14021,17 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>+8 V sensor supply</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse (+ IG2 wake diode)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -14045,7 +14041,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-ORANGE</t>
+          <t>J1128-TXL-18-RED</t>
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
@@ -14057,12 +14053,12 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>3-1447221-3</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>ECU splice point - SP-8V: +8 V cam sensor supply (ECU A6)</t>
+          <t>ECU splice point - SP-A5: ECU main feed (SW12 + IG2 diode)</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -14072,7 +14068,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>8V</t>
+          <t>SW12</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
@@ -14082,7 +14078,7 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>SP-8V</t>
+          <t>SP-A5</t>
         </is>
       </c>
       <c r="V126" t="inlineStr"/>
@@ -14092,17 +14088,21 @@
         </is>
       </c>
       <c r="X126" t="inlineStr"/>
-      <c r="Y126" t="inlineStr"/>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>ECU main +12 V | ECU main +12 V</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>w_a5_pin</t>
+          <t>w_ac_psw_in</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>legs of SP-A5</t>
+          <t>legs of SP-AC-PSW</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -14112,17 +14112,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>SP-A5</t>
+          <t>SP-AC-PSW</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -14132,27 +14132,27 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse (+ IG2 wake diode)</t>
+          <t>A/C pressure sw out</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>J1128-TXL-18-RED</t>
+          <t>M22759/16-20-4</t>
         </is>
       </c>
       <c r="M127" t="inlineStr"/>
@@ -14164,22 +14164,22 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>3-1447221-3</t>
+          <t xml:space="preserve">new-wire run terminated at the switch's </t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>ECU splice point - SP-A5: ECU main feed (SW12 + IG2 diode)</t>
+          <t>At A/C amp - SP-AC-PSW: A/C pressure switch output</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>OEM A5, factory Y-R lead</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>SW12</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
@@ -14189,31 +14189,35 @@
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>SP-A5</t>
+          <t>SP-AC-PSW</t>
         </is>
       </c>
       <c r="V127" t="inlineStr"/>
       <c r="W127" t="inlineStr">
         <is>
-          <t>at ECU-A plug</t>
-        </is>
-      </c>
-      <c r="X127" t="inlineStr"/>
+          <t>A/C amp branch (behind dash)</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>A/C pressure switch A5, engine bay; exact spot TBD (no locator figure in the repo); OEM colour Y-R (factory wiring; new wire here); EWD 1990 ST185 EWD p.152 (docs/electrical/ewd-snips/1990-st185-autoac-pressure-clutch-p152.png); 1990 ST185 EWD p.152 (A5 pin 4 Y-R); new-wire run terminated at the switch's own mating plug (no factory engine-bay wire reused, Section 39, 2026-10-04); plug part number not yet chosen</t>
+        </is>
+      </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>ECU main +12 V | ECU main +12 V</t>
+          <t>Runs on in ST185-EngineRoom-C to A/C pressure switch A5 pin 4 (engine bay): new wire to the switch's own mating plug, plug part TBD. EWD 1990 p.152. | owner TBD: a half has no length estimate (drawn today as w_ac_psw_in on ECU-cabin, ? mm; w_ac_psw on EngineRoom-C, 100 mm)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>w_ac_psw_in</t>
+          <t>w_amb_rtn</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>legs of SP-AC-PSW</t>
+          <t>legs of SP-AC-SG</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -14223,17 +14227,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SP-AC-PSW</t>
+          <t>SP-AC-SG</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -14243,7 +14247,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>A/C pressure sw out</t>
+          <t>Ambient sensor return</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -14258,12 +14262,12 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>J1128-TXL-20-YELLOW</t>
         </is>
       </c>
       <c r="M128" t="inlineStr"/>
@@ -14275,22 +14279,22 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t xml:space="preserve">new-wire run terminated at the switch's </t>
+          <t xml:space="preserve">new-wire run terminated at the sensor's </t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>At A/C amp - SP-AC-PSW: A/C pressure switch output</t>
+          <t>SP-AC-SG - cabin A/C sensor common (replaces E10; A32-15, A24-3, A21, A18-2 stay factory)</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>OEM A5, factory Y-R lead</t>
+          <t>OEM ambient air temp sensor A1 pin 1 (front, 6 in pigtail)</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>AMB</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
@@ -14300,35 +14304,31 @@
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>SP-AC-PSW</t>
+          <t>SP-AC-SG</t>
         </is>
       </c>
       <c r="V128" t="inlineStr"/>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>A/C amp branch (behind dash)</t>
-        </is>
-      </c>
+      <c r="W128" t="inlineStr"/>
       <c r="X128" t="inlineStr">
         <is>
-          <t>A/C pressure switch A5, engine bay; exact spot TBD (no locator figure in the repo); OEM colour Y-R (factory wiring; new wire here); EWD 1990 ST185 EWD p.152 (docs/electrical/ewd-snips/1990-st185-autoac-pressure-clutch-p152.png); 1990 ST185 EWD p.152 (A5 pin 4 Y-R); new-wire run terminated at the switch's own mating plug (no factory engine-bay wire reused, Section 39, 2026-10-04); plug part number not yet chosen</t>
+          <t>Ambient air temp sensor A1 pin 1 (6 in pigtail, B9); OEM colour Y; EWD 1993 p.211; new-wire run terminated at the sensor's own mating plug; 6 in OEM pigtail stays</t>
         </is>
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>Runs on in ST185-EngineRoom-C to A/C pressure switch A5 pin 4 (engine bay): new wire to the switch's own mating plug, plug part TBD. EWD 1990 p.152. | owner TBD: a half has no length estimate (drawn today as w_ac_psw_in on ECU-cabin, ? mm; w_ac_psw on EngineRoom-C, 100 mm)</t>
+          <t>Row 164: E10 sensor-common dies under B9. Cabin splice SP-AC-SG kept. Factory Y-R is the A/C pressure-switch output (A5-4 through joiner E10 to A18-13), not sensor ground; sensor common is Y (1990 ST185 EWD p.150 / p.152).</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>w_amb_rtn</t>
+          <t>w_trig2_pin</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>legs of SP-AC-SG</t>
+          <t>legs of SP-CAM</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -14338,17 +14338,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>SP-AC-SG</t>
+          <t>SP-CAM</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -14358,12 +14358,12 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Ambient sensor return</t>
+          <t>Cam sensor signal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14373,12 +14373,12 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>310</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-YELLOW</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="M129" t="inlineStr"/>
@@ -14390,22 +14390,22 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t xml:space="preserve">new-wire run terminated at the sensor's </t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>SP-AC-SG - cabin A/C sensor common (replaces E10; A32-15, A24-3, A21, A18-2 stay factory)</t>
+          <t>At the ECU plugs - SP-CAM: cam signal + 1.8k pull-up to +8V</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>OEM ambient air temp sensor A1 pin 1 (front, 6 in pigtail)</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>AMB</t>
+          <t>CAM</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
@@ -14415,31 +14415,27 @@
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>SP-AC-SG</t>
+          <t>SP-CAM</t>
         </is>
       </c>
       <c r="V129" t="inlineStr"/>
-      <c r="W129" t="inlineStr"/>
-      <c r="X129" t="inlineStr">
-        <is>
-          <t>Ambient air temp sensor A1 pin 1 (6 in pigtail, B9); OEM colour Y; EWD 1993 p.211; new-wire run terminated at the sensor's own mating plug; 6 in OEM pigtail stays</t>
-        </is>
-      </c>
-      <c r="Y129" t="inlineStr">
-        <is>
-          <t>Row 164: E10 sensor-common dies under B9. Cabin splice SP-AC-SG kept. Factory Y-R is the A/C pressure-switch output (A5-4 through joiner E10 to A18-13), not sensor ground; sensor common is Y (1990 ST185 EWD p.150 / p.152).</t>
-        </is>
-      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>at ECU-A plug</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr"/>
+      <c r="Y129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>w_trig2_pin</t>
+          <t>w_csbg_ac</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>legs of SP-CAM</t>
+          <t>legs of SP-CSB-GND</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -14449,17 +14445,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>POWER-NEG-BAR</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Lug</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>SP-CAM</t>
+          <t>SP-CSB-GND</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -14469,12 +14465,12 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Cam sensor signal</t>
+          <t>CSB3 + opto ground</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14484,12 +14480,12 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-WHITE</t>
+          <t>J1128-TXL-20-BLACK</t>
         </is>
       </c>
       <c r="M130" t="inlineStr"/>
@@ -14501,22 +14497,22 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>At the ECU plugs - SP-CAM: cam signal + 1.8k pull-up to +8V</t>
+          <t>CSB3 ground splice - CSB3 pin 2, opto board COM and stalk ground</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>POWER box NEG bar M8 stud (glove box)</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>CAM</t>
+          <t>CSB</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
@@ -14526,27 +14522,35 @@
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>SP-CAM</t>
-        </is>
-      </c>
-      <c r="V130" t="inlineStr"/>
+          <t>SP-CSB-GND</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>SP-CSB-GND also joins ST185-CSB3</t>
+        </is>
+      </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>at ECU-A plug</t>
+          <t>glove-box POWER box to the CSB3 branch</t>
         </is>
       </c>
       <c r="X130" t="inlineStr"/>
-      <c r="Y130" t="inlineStr"/>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>M8 ring lug on the POWER box battery-negative bar (R213: CSB3, opto board and cruise ladder never on chassis or the ECU ground) | (CSB3 loom, under centre cluster) | est length; runs with the CSB3 +12 V (w_csb12, LOGIC CSB 5A) (R217)</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>w_csbg_ac</t>
+          <t>w_fl_sig_pin</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>legs of SP-CSB-GND</t>
+          <t>legs of SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -14556,17 +14560,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>POWER-NEG-BAR</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Lug</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>SP-CSB-GND</t>
+          <t>SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -14576,12 +14580,12 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>CSB3 + opto ground</t>
+          <t>Fuel level signal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -14591,12 +14595,12 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>310</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-BLACK</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="M131" t="inlineStr"/>
@@ -14608,22 +14612,22 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>CSB3 ground splice - CSB3 pin 2, opto board COM and stalk ground</t>
+          <t>SP-FUEL-LVL - fuel sender signal + 470R pull-up to ECU-B B24</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>POWER box NEG bar M8 stud (glove box)</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>FLVL</t>
         </is>
       </c>
       <c r="T131" t="inlineStr">
@@ -14633,35 +14637,23 @@
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>SP-CSB-GND</t>
-        </is>
-      </c>
-      <c r="V131" t="inlineStr">
-        <is>
-          <t>SP-CSB-GND also joins ST185-CSB3</t>
-        </is>
-      </c>
-      <c r="W131" t="inlineStr">
-        <is>
-          <t>glove-box POWER box to the CSB3 branch</t>
-        </is>
-      </c>
+          <t>SP-FUEL-LVL</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr"/>
+      <c r="W131" t="inlineStr"/>
       <c r="X131" t="inlineStr"/>
-      <c r="Y131" t="inlineStr">
-        <is>
-          <t>M8 ring lug on the POWER box battery-negative bar (R213: CSB3, opto board and cruise ladder never on chassis or the ECU ground) | (CSB3 loom, under centre cluster) | est length; runs with the CSB3 +12 V (w_csb12, LOGIC CSB 5A) (R217)</t>
-        </is>
-      </c>
+      <c r="Y131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>w_fl_sig_pin</t>
+          <t>w66</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>legs of SP-FUEL-LVL</t>
+          <t>legs of SP-GND-ECU</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -14671,17 +14663,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>POWER-NEG-BAR</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Lug</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>SP-FUEL-LVL</t>
+          <t>SP-GND-ECU</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -14691,27 +14683,27 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Fuel level signal</t>
+          <t>ECU power ground</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>570</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-WHITE</t>
+          <t>J1128-TXL-10-BLACK</t>
         </is>
       </c>
       <c r="M132" t="inlineStr"/>
@@ -14723,22 +14715,22 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>SP-FUEL-LVL - fuel sender signal + 470R pull-up to ECU-B B24</t>
+          <t>ECU splice point - SP-GND-ECU: ECU power ground (A25 A34 B25 B34) to the NEG bar</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>POWER box NEG bar M8 stud (glove box)</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>FLVL</t>
+          <t>GND</t>
         </is>
       </c>
       <c r="T132" t="inlineStr">
@@ -14748,23 +14740,31 @@
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>SP-FUEL-LVL</t>
+          <t>SP-GND-ECU</t>
         </is>
       </c>
       <c r="V132" t="inlineStr"/>
-      <c r="W132" t="inlineStr"/>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>ECU to the glove-box POWER box</t>
+        </is>
+      </c>
       <c r="X132" t="inlineStr"/>
-      <c r="Y132" t="inlineStr"/>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>M8 ring lug on the POWER box battery-negative bar (R216): the ECU grounds only, nothing else | est length; the ONE ECU ground return (DECISIONS R216)</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>w66</t>
+          <t>w_rev_sw_c</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>legs of SP-GND-ECU</t>
+          <t>legs of SP-REV</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -14774,17 +14774,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>POWER-NEG-BAR</t>
+          <t>DRB102-CABIN</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Lug</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>SP-GND-ECU</t>
+          <t>SP-REV</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -14794,27 +14794,27 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>ECU power ground</t>
+          <t>Reverse sw +12 V out</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>J1128-TXL-10-BLACK</t>
+          <t>J1128-TXL-16-YELLOW</t>
         </is>
       </c>
       <c r="M133" t="inlineStr"/>
@@ -14826,22 +14826,22 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>0460-202-1631</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>ECU splice point - SP-GND-ECU: ECU power ground (A25 A34 B25 B34) to the NEG bar</t>
+          <t>SP-REV - reverse switch out to CSB3 opto IN2 and IG2-13 lamps</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>POWER box NEG bar M8 stud (glove box)</t>
+          <t>DRB102 receptacle (RH firewall)</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>GND</t>
+          <t>REV</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
@@ -14851,31 +14851,31 @@
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>SP-GND-ECU</t>
-        </is>
-      </c>
-      <c r="V133" t="inlineStr"/>
-      <c r="W133" t="inlineStr">
-        <is>
-          <t>ECU to the glove-box POWER box</t>
-        </is>
-      </c>
+          <t>SP-REV</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>ST185-AB-engine w_sw7_e at DRB102-ENGINE 78, to REV-SW 1</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr"/>
       <c r="X133" t="inlineStr"/>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>M8 ring lug on the POWER box battery-negative bar (R216): the ECU grounds only, nothing else | est length; the ONE ECU ground return (DECISIONS R216)</t>
+          <t>Circuit 11: switch out tapped to opto IN2; lamps stay on the factory IG2-13 run.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>w_rev_sw_c</t>
+          <t>w_drain_ecu_a</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>legs of SP-REV</t>
+          <t>legs of SP-SHIELD-A</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -14885,17 +14885,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>DRB102-CABIN</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>SP-REV</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -14905,27 +14905,27 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Reverse sw +12 V out</t>
+          <t>Shield drain</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>J1128-TXL-16-YELLOW</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M134" t="inlineStr"/>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>0460-202-1631</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>SP-REV - reverse switch out to CSB3 opto IN2 and IG2-13 lamps</t>
+          <t>6 mm behind the ECU-A plug - SP-SHIELD-A: drains to A7</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>DRB102 receptacle (RH firewall)</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>REV</t>
+          <t>SHLD</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
@@ -14962,56 +14962,56 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>SP-REV</t>
-        </is>
-      </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine w_sw7_e at DRB102-ENGINE 78, to REV-SW 1</t>
-        </is>
-      </c>
-      <c r="W134" t="inlineStr"/>
+          <t>SP-SHIELD-A</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr"/>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>at ECU-A plug</t>
+        </is>
+      </c>
       <c r="X134" t="inlineStr"/>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>Circuit 11: switch out tapped to opto IN2; lamps stay on the factory IG2-13 run.</t>
+          <t>build (R30): the crank drain is the one crimped into A7; the other drains are soldered onto it 6 mm behind the plug</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>w_drain_ecu_a</t>
+          <t>w_shd_a_aps</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
+          <t>legs of SP-SHIELD-A-APS</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
           <t>legs of SP-SHIELD-A</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>ECU-A</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>trunk</t>
+          <t>link</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -15031,7 +15031,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>450</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -15048,19 +15048,19 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>solder splice</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
+          <t>At the pedal branch - SP-SHIELD-A-APS: pedal drains</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
           <t>6 mm behind the ECU-A plug - SP-SHIELD-A: drains to A7</t>
         </is>
       </c>
-      <c r="R135" t="inlineStr">
-        <is>
-          <t>Link G4X plug A (centre dash)</t>
-        </is>
-      </c>
       <c r="S135" t="inlineStr">
         <is>
           <t>SHLD</t>
@@ -15073,31 +15073,27 @@
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-SHIELD-A-APS / SP-SHIELD-A</t>
         </is>
       </c>
       <c r="V135" t="inlineStr"/>
-      <c r="W135" t="inlineStr">
-        <is>
-          <t>at ECU-A plug</t>
-        </is>
-      </c>
+      <c r="W135" t="inlineStr"/>
       <c r="X135" t="inlineStr"/>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>build (R30): the crank drain is the one crimped into A7; the other drains are soldered onto it 6 mm behind the plug</t>
+          <t>branch-point join (R207): the device drain meets the loom shield trunk where its signal wires join the main loom, then runs to the ECU splice</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>w_shd_a_aps</t>
+          <t>w_shd_a_wsf</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-A-APS</t>
+          <t>legs of SP-SHIELD-A-WSF</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -15117,7 +15113,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
+          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -15142,7 +15138,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>230</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -15164,7 +15160,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>At the pedal branch - SP-SHIELD-A-APS: pedal drains</t>
+          <t>At the front WS inline - SP-SHIELD-A-WSF: front wheel-speed drains</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -15184,7 +15180,7 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-APS / SP-SHIELD-A</t>
+          <t>SP-SHIELD-A-WSF / SP-SHIELD-A</t>
         </is>
       </c>
       <c r="V136" t="inlineStr"/>
@@ -15199,12 +15195,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>w_shd_a_wsf</t>
+          <t>w_drain_ecu_b</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-A-WSF</t>
+          <t>legs of SP-SHIELD-B</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -15214,27 +15210,27 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-A</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
+          <t>SP-SHIELD-B</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>trunk</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Shield drain</t>
+          <t>Shield drain B</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -15249,7 +15245,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -15266,17 +15262,17 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>solder splice</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>At the front WS inline - SP-SHIELD-A-WSF: front wheel-speed drains</t>
+          <t>6 mm behind the ECU-B plug - SP-SHIELD-B: drains to B17</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>6 mm behind the ECU-A plug - SP-SHIELD-A: drains to A7</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
@@ -15291,52 +15287,48 @@
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-WSF / SP-SHIELD-A</t>
+          <t>SP-SHIELD-B</t>
         </is>
       </c>
       <c r="V137" t="inlineStr"/>
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr"/>
-      <c r="Y137" t="inlineStr">
-        <is>
-          <t>branch-point join (R207): the device drain meets the loom shield trunk where its signal wires join the main loom, then runs to the ECU splice</t>
-        </is>
-      </c>
+      <c r="Y137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>w_drain_ecu_b</t>
+          <t>w_shd_b_wsr</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
+          <t>legs of SP-SHIELD-B-WSR</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
           <t>legs of SP-SHIELD-B</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>ECU-B</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B</t>
+          <t>SP-SHIELD-B-WSR &gt; SP-SHIELD-B</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>trunk</t>
+          <t>link</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -15356,7 +15348,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>230</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -15373,19 +15365,19 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>solder splice</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
+          <t>At the rear WS inline - SP-SHIELD-B-WSR: rear wheel-speed drains</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
           <t>6 mm behind the ECU-B plug - SP-SHIELD-B: drains to B17</t>
         </is>
       </c>
-      <c r="R138" t="inlineStr">
-        <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
-        </is>
-      </c>
       <c r="S138" t="inlineStr">
         <is>
           <t>SHLD</t>
@@ -15398,23 +15390,27 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B</t>
+          <t>SP-SHIELD-B-WSR / SP-SHIELD-B</t>
         </is>
       </c>
       <c r="V138" t="inlineStr"/>
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr"/>
-      <c r="Y138" t="inlineStr"/>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>branch-point join (R207): the device drain meets the loom shield trunk where its signal wires join the main loom, then runs to the ECU splice</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>w_shd_b_wsr</t>
+          <t>w78</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-B-WSR</t>
+          <t>legs of SP-SW12</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -15424,7 +15420,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-B</t>
+          <t>legs of SP-A5</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -15434,7 +15430,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B-WSR &gt; SP-SHIELD-B</t>
+          <t>SP-SW12 &gt; SP-A5</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -15444,27 +15440,27 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Shield drain B</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse (+ IG2 wake diode)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>J1128-TXL-18-RED</t>
         </is>
       </c>
       <c r="M139" t="inlineStr"/>
@@ -15481,17 +15477,17 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>At the rear WS inline - SP-SHIELD-B-WSR: rear wheel-speed drains</t>
+          <t>ECU splice point - SP-SW12: switched +12 V (LOGIC SW12)</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>6 mm behind the ECU-B plug - SP-SHIELD-B: drains to B17</t>
+          <t>ECU splice point - SP-A5: ECU main feed (SW12 + IG2 diode)</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>SHLD</t>
+          <t>SW12</t>
         </is>
       </c>
       <c r="T139" t="inlineStr">
@@ -15501,22 +15497,26 @@
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B-WSR / SP-SHIELD-B</t>
+          <t>SP-SW12 / SP-A5</t>
         </is>
       </c>
       <c r="V139" t="inlineStr"/>
-      <c r="W139" t="inlineStr"/>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>at ECU-A plug</t>
+        </is>
+      </c>
       <c r="X139" t="inlineStr"/>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>branch-point join (R207): the device drain meets the loom shield trunk where its signal wires join the main loom, then runs to the ECU splice</t>
+          <t>ECU main +12 V | ECU main +12 V</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>w78</t>
+          <t>w_rail_sp_sw12_c</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -15531,27 +15531,27 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>legs of SP-A5</t>
+          <t>DRB102-CABIN</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SP-SW12 &gt; SP-A5</t>
+          <t>SP-SW12</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>trunk</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse (+ IG2 wake diode)</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -15566,7 +15566,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -15583,7 +15583,7 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>solder splice</t>
+          <t>0460-202-1631</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
@@ -15593,7 +15593,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>ECU splice point - SP-A5: ECU main feed (SW12 + IG2 diode)</t>
+          <t>DRB102 receptacle (RH firewall)</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
@@ -15608,19 +15608,23 @@
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>SP-SW12 / SP-A5</t>
-        </is>
-      </c>
-      <c r="V140" t="inlineStr"/>
+          <t>SP-SW12</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>ST185-AB-engine w_rail_sp_sw12_e at DRB102-ENGINE 30, to splice SP-SW12-ENG</t>
+        </is>
+      </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>at ECU-A plug</t>
+          <t>trunk ECU-A to bulkhead (RH firewall)</t>
         </is>
       </c>
       <c r="X140" t="inlineStr"/>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>ECU main +12 V | ECU main +12 V</t>
+          <t>+12 V boost + flex | +12 V boost + flex</t>
         </is>
       </c>
     </row>
@@ -17063,7 +17067,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ECU splice point - SP-8V: +8 V cam sensor supply (ECU A6)</t>
+          <t>ECU splice point - SP-8V: +8 V supply, cam sensor + gearbox speed sensor only (ECU A6)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -17073,7 +17077,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -17631,7 +17635,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -18032,7 +18036,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ECU splice point - SP-8V: +8 V cam sensor supply (ECU A6)</t>
+          <t>ECU splice point - SP-8V: +8 V supply, cam sensor + gearbox speed sensor only (ECU A6)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -18041,14 +18045,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>1.56</v>
+        <v>2.08</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>w_cam_pullup_8v (20 AWG), w19 (20 AWG), w_rail_sp_8v_c (20 AWG)</t>
+          <t>w_cam_pullup_8v (20 AWG), w19 (20 AWG), w_rail_sp_8v_c (20 AWG), w_rail_sp_8v_vss_c (20 AWG)</t>
         </is>
       </c>
     </row>
@@ -18060,7 +18064,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>w78</t>
+          <t>w_rail_sp_sw12_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -18074,14 +18078,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>2.99</v>
+        <v>2.47</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>w_fb_sw12 (18 AWG), w78 (18 AWG), w_rail_sp_sw12_c (18 AWG), w_rail_sw12_b_c_ac (20 AWG)</t>
+          <t>w_fb_sw12 (18 AWG), w78 (18 AWG), w_rail_sp_sw12_c (18 AWG)</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Wires" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Splices" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Key" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wires" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connectors" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Splices" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spare Cavities" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wires'!$A$1:$Y$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wires'!$A$1:$Y$140</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Connectors'!$A$1:$I$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Splices'!$A$1:$G$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spare Cavities'!$A$1:$D$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spare Cavities'!$A$1:$D$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y141"/>
+  <dimension ref="A1:Y140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8683,7 +8683,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>w_shc_vss</t>
+          <t>w12_c</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8693,37 +8693,33 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>BUS-GNDOUT-B</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>SP-SHIELD-B</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Gearbox speed shield</t>
+          <t>Knock sensor (-)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8733,12 +8729,12 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>J1128-TXL-20-BLUE</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
@@ -8750,7 +8746,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-B</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -8760,12 +8756,12 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-B</t>
+          <t>DT06-12 plug (ECU splice point)</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>VSS</t>
+          <t>KNOCK</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -8775,22 +8771,26 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B</t>
+          <t>BUS-GNDOUT-B</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_vss_sh at DRB102-ENGINE 69, to NC, floats NC</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr"/>
+          <t>ST185-AB-engine cab_knock1_c2 at DRB102-ENGINE 72, to KNOCK-1 2</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>trunk ECU to bulkhead (RH firewall)</t>
+        </is>
+      </c>
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>w12_c</t>
+          <t>w_shc_knock1</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8800,33 +8800,37 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-B</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>SP-SHIELD-B</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Knock sensor (-)</t>
+          <t>Knock sensor shield</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8836,12 +8840,12 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-BLUE</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
@@ -8853,7 +8857,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>solder splice SP-SHIELD-B</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -8863,7 +8867,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>DT06-12 plug (ECU splice point)</t>
+          <t>via SP-SHIELD-B</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8878,26 +8882,22 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-B</t>
+          <t>SP-SHIELD-B</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_knock1_c2 at DRB102-ENGINE 72, to KNOCK-1 2</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>trunk ECU to bulkhead (RH firewall)</t>
-        </is>
-      </c>
+          <t>ST185-AB-engine cab_knock1_sh at DRB102-ENGINE 73, to NC, floats NC</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>w_shc_knock1</t>
+          <t>w_shc_crank</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8907,22 +8907,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Knock sensor shield</t>
+          <t>Crank sensor shield</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8964,7 +8964,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-B</t>
+          <t>solder splice SP-SHIELD-A</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-B</t>
+          <t>via SP-SHIELD-A</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>KNOCK</t>
+          <t>CRANKC</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -8989,22 +8989,30 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_knock1_sh at DRB102-ENGINE 73, to NC, floats NC</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr"/>
+          <t>ST185-AB-engine cab_crank_sh at DRB102-ENGINE 76, to NC, floats NC</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>trunk ECU-A to bulkhead (RH firewall)</t>
+        </is>
+      </c>
       <c r="X79" t="inlineStr"/>
-      <c r="Y79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>build (R30): this drain is the one crimped into A7</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>w_shc_crank</t>
+          <t>wc_h_bh_bc</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9014,37 +9022,37 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>ECU-C</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-CANH</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>leg core</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Crank sensor shield</t>
+          <t>CAN H to CAN-Lambda</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9054,16 +9062,24 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>680</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>CAB-CANBH-BC</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>55A1821-20-9/5-9</t>
+        </is>
+      </c>
       <c r="O80" t="inlineStr">
         <is>
           <t>0460-202-1631</t>
@@ -9071,7 +9087,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-A</t>
+          <t>solder splice SP-CANH</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -9081,12 +9097,12 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-A</t>
+          <t>via SP-CANH</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>CRANKC</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
@@ -9096,30 +9112,26 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-CANH</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_crank_sh at DRB102-ENGINE 76, to NC, floats NC</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>trunk ECU-A to bulkhead (RH firewall)</t>
-        </is>
-      </c>
+          <t>ST185-AB-engine wc_h_lam_be at DRB102-ENGINE 79, to splice SP-CANH-LAM; SP-CANH also joins ST185-CAN</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr"/>
       <c r="X80" t="inlineStr"/>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>build (R30): this drain is the one crimped into A7</t>
+          <t>owner TBD: a half has no length estimate (drawn today as wc_h_bh on CAN, ? mm; wc_h_bh_bc on ECU-cabin, 120 mm)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>wc_h_bh_bc</t>
+          <t>wc_l_bh_bc</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9129,7 +9141,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -9139,12 +9151,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SP-CANH</t>
+          <t>SP-CANL</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -9154,12 +9166,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>CAN H to CAN-Lambda</t>
+          <t>CAN L to CAN-Lambda</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9194,7 +9206,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>solder splice SP-CANH</t>
+          <t>solder splice SP-CANL</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -9204,7 +9216,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>via SP-CANH</t>
+          <t>via SP-CANL</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9219,26 +9231,26 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>SP-CANH</t>
+          <t>SP-CANL</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>ST185-AB-engine wc_h_lam_be at DRB102-ENGINE 79, to splice SP-CANH-LAM; SP-CANH also joins ST185-CAN</t>
+          <t>ST185-AB-engine wc_l_lam_be at DRB102-ENGINE 80, to splice SP-CANL-LAM; SP-CANL also joins ST185-CAN</t>
         </is>
       </c>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as wc_h_bh on CAN, ? mm; wc_h_bh_bc on ECU-cabin, 120 mm)</t>
+          <t>owner TBD: a half has no length estimate (drawn today as wc_l_bh on CAN, ? mm; wc_l_bh_bc on ECU-cabin, 120 mm)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>wc_l_bh_bc</t>
+          <t>cab_canbh_bc_sh</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9248,7 +9260,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -9258,12 +9270,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SP-CANL</t>
+          <t>SP-CAN-SH-BH &gt; SP-CAN-SH-CLU</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -9273,19 +9285,15 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>CAN L to CAN-Lambda</t>
+          <t>CAN-Lambda shield</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
           <t>680</t>
@@ -9313,7 +9321,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>solder splice SP-CANL</t>
+          <t>solder splice SP-CAN-SH-BH</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -9323,7 +9331,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>via SP-CANL</t>
+          <t>via SP-CAN-SH-BH &gt; SP-CAN-SH-CLU</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -9338,26 +9346,26 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>SP-CANL</t>
+          <t>SP-CAN-SH-BH</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>ST185-AB-engine wc_l_lam_be at DRB102-ENGINE 80, to splice SP-CANL-LAM; SP-CANL also joins ST185-CAN</t>
+          <t>ST185-AB-engine cab_lamcan_be_sh at DRB102-ENGINE 81, to NC, floats NC; SP-CAN-SH-BH also joins ST185-CAN; SP-CAN-SH-CLU also joins ST185-CAN</t>
         </is>
       </c>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as wc_l_bh on CAN, ? mm; wc_l_bh_bc on ECU-cabin, 120 mm)</t>
+          <t>owner TBD: a half has no length estimate (drawn today as cab_can_bh_sh on CAN, ? mm; cab_canbh_bc_sh on ECU-cabin, 120 mm)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>cab_canbh_bc_sh</t>
+          <t>w_lamg_ac</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9367,68 +9375,60 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ECU-C</t>
+          <t>POWER-NEG-BAR</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>SP-CAN-SH-BH &gt; SP-CAN-SH-CLU</t>
-        </is>
-      </c>
+          <t>Lug</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>leg core</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>CAN-Lambda shield</t>
+          <t>CAN-Lambda ground</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Shield</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr"/>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>450</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>(cable core)</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>CAB-CANBH-BC</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>55A1821-20-9/5-9</t>
-        </is>
-      </c>
+          <t>J1128-TXL-14-BLACK</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr">
         <is>
-          <t>0460-202-1631</t>
+          <t>0460-220-1231</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>solder splice SP-CAN-SH-BH</t>
+          <t>320575</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>via SP-CAN-SH-BH &gt; SP-CAN-SH-CLU</t>
+          <t>POWER box NEG bar M8 stud (glove box)</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>LAM</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
@@ -9453,46 +9453,50 @@
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>SP-CAN-SH-BH</t>
+          <t>LAM</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>ST185-AB-engine cab_lamcan_be_sh at DRB102-ENGINE 81, to NC, floats NC; SP-CAN-SH-BH also joins ST185-CAN; SP-CAN-SH-CLU also joins ST185-CAN</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr"/>
+          <t>ST185-AB-engine w_lamg_be14 at DRB102-ENGINE 96, to splice SP-LAMG-B</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>bulkhead to the glove-box POWER box</t>
+        </is>
+      </c>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as cab_can_bh_sh on CAN, ? mm; cab_canbh_bc_sh on ECU-cabin, 120 mm)</t>
+          <t>(firewall bulkhead, RH) | M8 ring lug on the POWER box battery-negative bar (R213: a CAN node never on chassis or the ECU ground) | est length; runs with the CAN-Lambda +12 V (w_lam12_cp, LOGIC LAM) from the glove box to bulkhead pin 95 / 96 (R217)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>w_lamg_ac</t>
+          <t>w_rev_feed_c</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
+          <t>IG2</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
           <t>DRB102-CABIN</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>POWER-NEG-BAR</t>
-        </is>
-      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Lug</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -9503,54 +9507,54 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>CAN-Lambda ground</t>
+          <t>Back-up sw +12 V in</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>J1128-TXL-14-BLACK</t>
+          <t>J1128-TXL-16-RED</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
-          <t>0460-220-1231</t>
+          <t>crimp butt splice into the factory cowl-</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>320575</t>
+          <t>0460-202-1631</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
+          <t>OEM IG2 pin 4 (under the ECU, cowl side) - factory back-up SW feed</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
           <t>DRB102 receptacle (RH firewall)</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>POWER box NEG bar M8 stud (glove box)</t>
-        </is>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>LAM</t>
+          <t>REV</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
@@ -9560,30 +9564,30 @@
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>LAM</t>
+          <t>REV</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_lamg_be14 at DRB102-ENGINE 96, to splice SP-LAMG-B</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>bulkhead to the glove-box POWER box</t>
-        </is>
-      </c>
-      <c r="X84" t="inlineStr"/>
+          <t>ST185-AB-engine w_rev_feed_e at DRB102-ENGINE 77, to REV-SW 2</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>OEM IG2 pin 4 (under the ECU, cowl side) - R-L, GAUGE 15 A back-up SW feed; OEM colour R-L; EWD 1992 p.132 / 1990 p.82; crimp butt splice into the factory cowl-side lead at IG2 (cabin, under the ECU; the engine wire is removed)</t>
+        </is>
+      </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>(firewall bulkhead, RH) | M8 ring lug on the POWER box battery-negative bar (R213: a CAN node never on chassis or the ECU ground) | est length; runs with the CAN-Lambda +12 V (w_lam12_cp, LOGIC LAM) from the glove box to bulkhead pin 95 / 96 (R217)</t>
+          <t>Circuit 11: factory feed kept. New engine-harness switch in splices to the IG2-4 pigtail.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>w_rev_feed_c</t>
+          <t>w_rev_lamps</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9593,7 +9597,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -9603,23 +9607,27 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr"/>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>SP-REV</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Back-up sw +12 V in</t>
+          <t>Back-up lamp +12 V</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -9629,12 +9637,12 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>310</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>J1128-TXL-16-RED</t>
+          <t>J1128-TXL-16-YELLOW</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
@@ -9646,17 +9654,17 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>0460-202-1631</t>
+          <t>solder splice SP-REV</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>OEM IG2 pin 4 (under the ECU, cowl side) - factory back-up SW feed</t>
+          <t>OEM IG2 pin 13 (under the ECU, cowl side) - factory back-up lamp output</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>DRB102 receptacle (RH firewall)</t>
+          <t>via SP-REV</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9671,55 +9679,55 @@
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>REV</t>
+          <t>SP-REV</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_rev_feed_e at DRB102-ENGINE 77, to REV-SW 2</t>
+          <t>ST185-AB-engine w_sw7_e at DRB102-ENGINE 78, to REV-SW 1</t>
         </is>
       </c>
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr">
         <is>
-          <t>OEM IG2 pin 4 (under the ECU, cowl side) - R-L, GAUGE 15 A back-up SW feed; OEM colour R-L; EWD 1992 p.132 / 1990 p.82; crimp butt splice into the factory cowl-side lead at IG2 (cabin, under the ECU; the engine wire is removed)</t>
+          <t>OEM IG2 pin 13 (under the ECU, cowl side) - R-B, back-up lamp output; OEM colour R-B; EWD 1992 p.132; crimp butt splice into the factory cowl-side lead at IG2</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>Circuit 11: factory feed kept. New engine-harness switch in splices to the IG2-4 pigtail.</t>
+          <t>Circuit 11: new switch out splices to the IG2-13 pigtail; rear lamps stay on the factory harness.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>w_rev_lamps</t>
+          <t>w_fl_sig</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>IG2</t>
+          <t>IX-FUEL-P</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>DRB102-CABIN</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SP-REV</t>
+          <t>SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -9729,54 +9737,54 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Back-up lamp +12 V</t>
+          <t>Fuel level signal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>J1128-TXL-16-YELLOW</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr">
         <is>
-          <t>crimp butt splice into the factory cowl-</t>
+          <t>0460-202-1631</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>solder splice SP-REV</t>
+          <t>solder splice SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>OEM IG2 pin 13 (under the ECU, cowl side) - factory back-up lamp output</t>
+          <t>IX-FUEL inline to fuel sender lead (trunk end)</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>via SP-REV</t>
+          <t>via SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>REV</t>
+          <t>FLVL</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
@@ -9786,30 +9794,18 @@
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>SP-REV</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine w_sw7_e at DRB102-ENGINE 78, to REV-SW 1</t>
-        </is>
-      </c>
+          <t>SP-FUEL-LVL</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr"/>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>OEM IG2 pin 13 (under the ECU, cowl side) - R-B, back-up lamp output; OEM colour R-B; EWD 1992 p.132; crimp butt splice into the factory cowl-side lead at IG2</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>Circuit 11: new switch out splices to the IG2-13 pigtail; rear lamps stay on the factory harness.</t>
-        </is>
-      </c>
+      <c r="X86" t="inlineStr"/>
+      <c r="Y86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>w_fl_sig</t>
+          <t>w45</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9819,37 +9815,33 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>BUS-GNDOUT-B</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>SP-FUEL-LVL</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Fuel level signal</t>
+          <t>Fuel level ground</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -9864,7 +9856,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-WHITE</t>
+          <t>J1128-TXL-20-BLUE</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
@@ -9876,7 +9868,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>solder splice SP-FUEL-LVL</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -9886,12 +9878,12 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>via SP-FUEL-LVL</t>
+          <t>DT06-12 plug (ECU splice point)</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>FLVL</t>
+          <t>SGND</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
@@ -9901,7 +9893,7 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>SP-FUEL-LVL</t>
+          <t>BUS-GNDOUT-B</t>
         </is>
       </c>
       <c r="V87" t="inlineStr"/>
@@ -9912,43 +9904,43 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>w45</t>
+          <t>cab_fspur_5v</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>IX-FUEL-P</t>
+          <t>IX-WS-F-S</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-B</t>
+          <t>BUS-5V</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>core</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Fuel level ground</t>
+          <t>VRC-F +5V</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -9958,19 +9950,27 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>640</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-BLUE</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>CAB-FSPUR</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>55A1831-20-2/4/6-9</t>
+        </is>
+      </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>0460-202-1631</t>
+          <t>0462-201-1631</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>IX-FUEL inline to fuel sender lead (trunk end)</t>
+          <t>to front VR conditioner</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>SGND</t>
+          <t>5V</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
@@ -10000,18 +10000,22 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-B</t>
+          <t>BUS-5V</t>
         </is>
       </c>
       <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>dash branch (front WS inline)</t>
+        </is>
+      </c>
       <c r="X88" t="inlineStr"/>
       <c r="Y88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>cab_fspur_5v</t>
+          <t>cab_fspur_gnd</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10021,17 +10025,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>BUS-5V</t>
+          <t>BUS-GNDOUT-A</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
@@ -10042,12 +10046,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>VRC-F +5V</t>
+          <t>VRC-F GND</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10097,7 +10101,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>5V</t>
+          <t>SGND</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
@@ -10107,7 +10111,7 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>BUS-5V</t>
+          <t>BUS-GNDOUT-A</t>
         </is>
       </c>
       <c r="V89" t="inlineStr"/>
@@ -10122,7 +10126,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>cab_fspur_gnd</t>
+          <t>cab_fspur_l</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10132,17 +10136,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-A</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -10153,12 +10157,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>VRC-F GND</t>
+          <t>FL conditioned out</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10168,7 +10172,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>530</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -10193,7 +10197,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -10203,12 +10207,12 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>DT06-12 plug (ECU splice point)</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>SGND</t>
+          <t>WSSF</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
@@ -10218,7 +10222,7 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-A</t>
+          <t>WSSF</t>
         </is>
       </c>
       <c r="V90" t="inlineStr"/>
@@ -10233,7 +10237,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>cab_fspur_l</t>
+          <t>cab_fspur_r_ac</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10243,17 +10247,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
@@ -10264,12 +10268,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>FL conditioned out</t>
+          <t>FR conditioned out</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10289,12 +10293,12 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>CAB-FSPUR</t>
+          <t>CAB-FSPUR-FR-AC</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>55A1811-20-9-9CS2275</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -10314,7 +10318,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -10339,12 +10343,16 @@
         </is>
       </c>
       <c r="X91" t="inlineStr"/>
-      <c r="Y91" t="inlineStr"/>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>ECU-B plug pin B21 (Link G4X, centre dash); wheel speed | owner proposed: longer half (drawn today as cab_fspur_r_ac on ECU-cabin, 350 mm; cab_fspur_r on ECU-cabin, 530 mm)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>cab_fspur_r_ac</t>
+          <t>cab_fspur_sh</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10354,43 +10362,43 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>leg core</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>FR conditioned out</t>
+          <t>WS-F screen drain</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>500</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -10400,12 +10408,12 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>CAB-FSPUR-FR-AC</t>
+          <t>CAB-FSPUR</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>55A1811-20-9-9CS2275</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -10415,7 +10423,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>solder splice SP-SHIELD-A-WSF</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
@@ -10425,7 +10433,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>via SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -10440,7 +10448,7 @@
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>WSSF</t>
+          <t>SP-SHIELD-A-WSF</t>
         </is>
       </c>
       <c r="V92" t="inlineStr"/>
@@ -10450,62 +10458,58 @@
         </is>
       </c>
       <c r="X92" t="inlineStr"/>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>ECU-B plug pin B21 (Link G4X, centre dash); wheel speed | owner proposed: longer half (drawn today as cab_fspur_r_ac on ECU-cabin, 350 mm; cab_fspur_r on ECU-cabin, 530 mm)</t>
-        </is>
-      </c>
+      <c r="Y92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>cab_fspur_sh</t>
+          <t>cab_rspur_5v</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>IX-WS-F-S</t>
+          <t>IX-WS-R-S</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>BUS-5V</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>leg core</t>
+          <t>core</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>WS-F screen drain</t>
+          <t>VRC-R +5V</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Shield</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr"/>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>640</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -10515,12 +10519,12 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>CAB-FSPUR</t>
+          <t>CAB-RSPUR</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>55A1841-20-2/4/5/6-9</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -10530,22 +10534,22 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-A-WSF</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>to front VR conditioner</t>
+          <t>IX-WS-R inline to rear VRC (dash above ECU)</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
+          <t>DT06-12 plug (ECU splice point)</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>WSSF</t>
+          <t>5V</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
@@ -10555,22 +10559,18 @@
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-WSF</t>
+          <t>BUS-5V</t>
         </is>
       </c>
       <c r="V93" t="inlineStr"/>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>dash branch (front WS inline)</t>
-        </is>
-      </c>
+      <c r="W93" t="inlineStr"/>
       <c r="X93" t="inlineStr"/>
       <c r="Y93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>cab_rspur_5v</t>
+          <t>cab_rspur_gnd</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10580,17 +10580,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>BUS-5V</t>
+          <t>BUS-GNDOUT-B</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
@@ -10601,12 +10601,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>VRC-R +5V</t>
+          <t>VRC-R GND</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>5V</t>
+          <t>SGND</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>BUS-5V</t>
+          <t>BUS-GNDOUT-B</t>
         </is>
       </c>
       <c r="V94" t="inlineStr"/>
@@ -10677,7 +10677,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>cab_rspur_gnd</t>
+          <t>cab_rspur_l</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10687,17 +10687,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-B</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
@@ -10708,12 +10708,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>VRC-R GND</t>
+          <t>Rear left wheel spd</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>530</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -10758,12 +10758,12 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>DT06-12 plug (ECU splice point)</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>SGND</t>
+          <t>WSSR</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
@@ -10773,7 +10773,7 @@
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>BUS-GNDOUT-B</t>
+          <t>WSSR</t>
         </is>
       </c>
       <c r="V95" t="inlineStr"/>
@@ -10784,7 +10784,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>cab_rspur_l</t>
+          <t>cab_rspur_r</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Rear left wheel spd</t>
+          <t>Rear right wheel spd</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -10891,7 +10891,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>cab_rspur_r</t>
+          <t>cab_rspur_sh</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -10911,33 +10911,33 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr"/>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>SP-SHIELD-B-WSR &gt; SP-SHIELD-B</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>leg core</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Rear right wheel spd</t>
+          <t>WS-R screen drain</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Blue</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>500</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -10962,7 +10962,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>solder splice SP-SHIELD-B-WSR</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
@@ -10972,7 +10972,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>via SP-SHIELD-B-WSR &gt; SP-SHIELD-B</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -10987,7 +10987,7 @@
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>WSSR</t>
+          <t>SP-SHIELD-B-WSR</t>
         </is>
       </c>
       <c r="V97" t="inlineStr"/>
@@ -10998,93 +10998,81 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>cab_rspur_sh</t>
+          <t>w_ig2_in</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>IX-WS-R-S</t>
+          <t>JB1-1H</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>D-IG2-WAKE</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>SP-SHIELD-B-WSR &gt; SP-SHIELD-B</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>leg core</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>WS-R screen drain</t>
+          <t>IG2 wake feed</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Shield</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr"/>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>(cable core)</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>CAB-RSPUR</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>55A1841-20-2/4/5/6-9</t>
-        </is>
-      </c>
+          <t>J1128-TXL-20-YELLOW</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr">
         <is>
-          <t>0462-201-1631</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>solder splice SP-SHIELD-B-WSR</t>
-        </is>
-      </c>
+          <t>solder onto the factory lead</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>IX-WS-R inline to rear VRC (dash above ECU)</t>
+          <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-B-WSR &gt; SP-SHIELD-B</t>
+          <t>IG2 wake diode (1N5822)</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>WSSR</t>
+          <t>IG2WAKE</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
@@ -11094,18 +11082,26 @@
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B-WSR</t>
+          <t>IG2WAKE</t>
         </is>
       </c>
       <c r="V98" t="inlineStr"/>
-      <c r="W98" t="inlineStr"/>
-      <c r="X98" t="inlineStr"/>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>IG2 tap branch (LH kick panel)</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O - IGN fuse out (EWD 1993 p.62); same lead as the ECU-B B28 sense tap, own splice; OEM colour B-O; EWD 1993 TIS EWD p.62 (Power Source); solder splice onto the factory lead</t>
+        </is>
+      </c>
       <c r="Y98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>w_ig2_in</t>
+          <t>w_ign</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -11120,12 +11116,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>D-IG2-WAKE</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
@@ -11136,7 +11132,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>IG2 wake feed</t>
+          <t>Ignition sw sense</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -11151,7 +11147,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -11166,7 +11162,11 @@
           <t>solder onto the factory lead</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>3-1447221-4</t>
+        </is>
+      </c>
       <c r="Q99" t="inlineStr">
         <is>
           <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O</t>
@@ -11174,12 +11174,12 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>IG2 wake diode (1N5822)</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>IG2WAKE</t>
+          <t>IGNSW</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
@@ -11189,18 +11189,14 @@
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>IG2WAKE</t>
+          <t>IGNSW</t>
         </is>
       </c>
       <c r="V99" t="inlineStr"/>
-      <c r="W99" t="inlineStr">
-        <is>
-          <t>IG2 tap branch (LH kick panel)</t>
-        </is>
-      </c>
+      <c r="W99" t="inlineStr"/>
       <c r="X99" t="inlineStr">
         <is>
-          <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O - IGN fuse out (EWD 1993 p.62); same lead as the ECU-B B28 sense tap, own splice; OEM colour B-O; EWD 1993 TIS EWD p.62 (Power Source); solder splice onto the factory lead</t>
+          <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O - IGN fuse out (EWD 1993 p.62); OEM colour B-O; EWD 1993 TIS EWD p.62 (Power Source); solder splice onto the factory lead</t>
         </is>
       </c>
       <c r="Y99" t="inlineStr"/>
@@ -11208,85 +11204,89 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>w_ign</t>
+          <t>w_acc86</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>JB1-1H</t>
+          <t>K-ACC</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>86</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>LOGIC</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr"/>
+          <t>BUS2-8</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>SP-ACC12</t>
+        </is>
+      </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Ignition sw sense</t>
+          <t>A/C clutch relay coil+</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-YELLOW</t>
+          <t>M22759/16-18-2</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr">
         <is>
-          <t>solder onto the factory lead</t>
+          <t>280919-2</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>solder splice SP-ACC12</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O</t>
+          <t>B2-M5 A/C clutch relay (k_acc) - amp A15 pin 8 sinks coil- (85); coil+ (86) fused +12 V from B2-BUS2-8</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>via SP-ACC12</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>IGNSW</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
@@ -11296,62 +11296,66 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>IGNSW</t>
-        </is>
-      </c>
-      <c r="V100" t="inlineStr"/>
-      <c r="W100" t="inlineStr"/>
-      <c r="X100" t="inlineStr">
-        <is>
-          <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O - IGN fuse out (EWD 1993 p.62); OEM colour B-O; EWD 1993 TIS EWD p.62 (Power Source); solder splice onto the factory lead</t>
-        </is>
-      </c>
-      <c r="Y100" t="inlineStr"/>
+          <t>SP-ACC12</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>SP-ACC12 also joins ST185-CabinPower</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>A/C amp branch (behind dash)</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr"/>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>LOGIC box (glove box) relay M15 A/C clutch, pin 86 | B15: coil 86 is fused +12 V. Pressure switch stays on amp pin 13 only.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>w_acc86</t>
+          <t>w76</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>K-ACC</t>
+          <t>K-EFI</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LOGIC</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>BUS2-8</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>SP-ACC12</t>
-        </is>
-      </c>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>A/C clutch relay coil+</t>
+          <t>EFI relay coil (-)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -11361,77 +11365,73 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>370</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>M22759/16-18-2</t>
+          <t>J1128-TXL-18-WHITE</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
         <is>
-          <t>280919-2</t>
+          <t>42281-1</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>solder splice SP-ACC12</t>
+          <t>3-1447221-3</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>B2-M5 A/C clutch relay (k_acc) - amp A15 pin 8 sinks coil- (85); coil+ (86) fused +12 V from B2-BUS2-8</t>
+          <t>B1-R2 EFI Main Relay (seated in the POWER box R2) - ACTIVE-LOW - ECU sinks coil- (85); coil+ (86) permanent 12 V (LOGIC EFI86 5 A)</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>via SP-ACC12</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>EFI</t>
         </is>
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin</t>
+          <t>ST185-CabinPower</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>SP-ACC12</t>
-        </is>
-      </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>SP-ACC12 also joins ST185-CabinPower</t>
-        </is>
-      </c>
+          <t>EFI</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr"/>
       <c r="W101" t="inlineStr">
         <is>
-          <t>A/C amp branch (behind dash)</t>
+          <t>glove-box branch (POWER / LOGIC boxes)</t>
         </is>
       </c>
       <c r="X101" t="inlineStr"/>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) relay M15 A/C clutch, pin 86 | B15: coil 86 is fused +12 V. Pressure switch stays on amp pin 13 only.</t>
+          <t>POWER box (glove box) relay R2 EFI main, pin 85 | owner proposed: longer half (drawn today as w76 on ECU-cabin, 370 mm; w76_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>w76</t>
+          <t>w_eps_rly</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>K-EFI</t>
+          <t>K-EPS</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>DRB102-CABIN</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
@@ -11457,7 +11457,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>EFI relay coil (-)</t>
+          <t>EHPS relay coil (-)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -11472,73 +11472,77 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>450</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>J1128-TXL-18-WHITE</t>
+          <t>M22759/16-18-9</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr">
         <is>
-          <t>42281-1</t>
+          <t>282110-1</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>3-1447221-3</t>
+          <t>0460-202-1631</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>B1-R2 EFI Main Relay (seated in the POWER box R2) - ACTIVE-LOW - ECU sinks coil- (85); coil+ (86) permanent 12 V (LOGIC EFI86 5 A)</t>
+          <t>B4 EPS pump relay (HCR150, glove box, beside the POWER box) - coil- (85) switched to ground by the MR-S pump pin B5 (R22); coil+ (86) switched 12 V - HCR 150 coil is a 2-pole plug (TE terminals 1/2, not marked 85/86), resistor-suppressed so polarity-free</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>DRB102 receptacle (RH firewall)</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>EFI</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>ST185-CabinPower</t>
+          <t>ST185-AB-cabin</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>EFI</t>
-        </is>
-      </c>
-      <c r="V102" t="inlineStr"/>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>ST185-AB-engine w_eps_rly_e at DRB102-ENGINE 85, to MRS-B 5</t>
+        </is>
+      </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>glove-box branch (POWER / LOGIC boxes)</t>
+          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
         </is>
       </c>
       <c r="X102" t="inlineStr"/>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>POWER box (glove box) relay R2 EFI main, pin 85 | owner proposed: longer half (drawn today as w76 on ECU-cabin, 370 mm; w76_cp on CabinPower, 400 mm)</t>
+          <t>EHPS pump relay (glove box), pin 85 | owner proposed: longer half (drawn today as w_eps_rly on ECU-cabin, 530 mm; w_eps_rly_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>w_eps_rly</t>
+          <t>w81</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>K-EPS</t>
+          <t>K-ETB</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -11548,12 +11552,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>DRB102-CABIN</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
@@ -11564,7 +11568,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>EHPS relay coil (-)</t>
+          <t>ETB relay coil (-)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -11574,77 +11578,73 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>380</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr">
         <is>
-          <t>282110-1</t>
+          <t>280919-2</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>0460-202-1631</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>B4 EPS pump relay (HCR150, glove box, beside the POWER box) - coil- (85) switched to ground by the MR-S pump pin B5 (R22); coil+ (86) switched 12 V - HCR 150 coil is a 2-pole plug (TE terminals 1/2, not marked 85/86), resistor-suppressed so polarity-free</t>
+          <t>B2-M4 ETB Power Relay (seated in the LOGIC box M4) - ACTIVE-LOW - ECU sinks coil- (85); coil+ (86) switched 12 V</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>DRB102 receptacle (RH firewall)</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>EPS</t>
+          <t>ETB</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin</t>
+          <t>ST185-CabinPower</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>EPS</t>
-        </is>
-      </c>
-      <c r="V103" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine w_eps_rly_e at DRB102-ENGINE 85, to MRS-B 5</t>
-        </is>
-      </c>
+          <t>ETB</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr"/>
       <c r="W103" t="inlineStr">
         <is>
-          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
+          <t>glove-box branch (POWER / LOGIC boxes)</t>
         </is>
       </c>
       <c r="X103" t="inlineStr"/>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>EHPS pump relay (glove box), pin 85 | owner proposed: longer half (drawn today as w_eps_rly on ECU-cabin, 530 mm; w_eps_rly_cp on CabinPower, 400 mm)</t>
+          <t>LOGIC box (glove box) relay M14 ETB power, pin 85 | owner proposed: longer half (drawn today as w81 on ECU-cabin, 380 mm; w81_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>w81</t>
+          <t>w82_ac</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -11654,17 +11654,17 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -11675,39 +11675,39 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>ETB relay coil (-)</t>
+          <t>ETB motor +12 V</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>400</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>J1128-TXL-18-RED</t>
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr">
         <is>
-          <t>280919-2</t>
+          <t>42281-1</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>3-1447221-3</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -11736,42 +11736,38 @@
         </is>
       </c>
       <c r="V104" t="inlineStr"/>
-      <c r="W104" t="inlineStr">
-        <is>
-          <t>glove-box branch (POWER / LOGIC boxes)</t>
-        </is>
-      </c>
+      <c r="W104" t="inlineStr"/>
       <c r="X104" t="inlineStr"/>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) relay M14 ETB power, pin 85 | owner proposed: longer half (drawn today as w81 on ECU-cabin, 380 mm; w81_cp on CabinPower, 400 mm)</t>
+          <t>owner proposed: longer half (drawn today as w82_ac on CabinPower, 400 mm; w82 on ECU-cabin, 340 mm)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>w82_ac</t>
+          <t>w_fan85</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>K-ETB</t>
+          <t>K-FAN</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
@@ -11782,12 +11778,12 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>ETB motor +12 V</t>
+          <t>Rad fan relay (-)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -11797,12 +11793,12 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>680</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>J1128-TXL-18-RED</t>
+          <t>M22759/16-18-9</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
@@ -11819,47 +11815,51 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>B2-M4 ETB Power Relay (seated in the LOGIC box M4) - ACTIVE-LOW - ECU sinks coil- (85); coil+ (86) switched 12 V</t>
+          <t>B1-R4 Radiator fan relay (seated in the POWER box R4)</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>ETB</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>ST185-CabinPower</t>
+          <t>ST185-AB-cabin</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>ETB</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="V105" t="inlineStr"/>
-      <c r="W105" t="inlineStr"/>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>glove-box branch (POWER / LOGIC boxes)</t>
+        </is>
+      </c>
       <c r="X105" t="inlineStr"/>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w82_ac on CabinPower, 400 mm; w82 on ECU-cabin, 340 mm)</t>
+          <t>POWER box (glove box) relay R4 radiator fan, pin 85 | owner proposed: longer half (drawn today as w_fan85 on ECU-cabin, 410 mm; w_fan85_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>w_fan85</t>
+          <t>w_fan285</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>K-FAN</t>
+          <t>K-FAN2</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
@@ -11885,7 +11885,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Rad fan relay (-)</t>
+          <t>Cond fan relay (-)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -11922,17 +11922,17 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>B1-R4 Radiator fan relay (seated in the POWER box R4)</t>
+          <t>B1-R5 Condenser fan relay (seated in the POWER box R5)</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>FAN2</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
@@ -11942,31 +11942,27 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>FAN2</t>
         </is>
       </c>
       <c r="V106" t="inlineStr"/>
-      <c r="W106" t="inlineStr">
-        <is>
-          <t>glove-box branch (POWER / LOGIC boxes)</t>
-        </is>
-      </c>
+      <c r="W106" t="inlineStr"/>
       <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>POWER box (glove box) relay R4 radiator fan, pin 85 | owner proposed: longer half (drawn today as w_fan85 on ECU-cabin, 410 mm; w_fan85_cp on CabinPower, 400 mm)</t>
+          <t>owner proposed: longer half (drawn today as w_fan285_cp on CabinPower, 400 mm; w_fan285 on ECU-cabin, 480 mm)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>w_fan285</t>
+          <t>w_fp85</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>K-FAN2</t>
+          <t>K-FP</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -11976,12 +11972,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
@@ -11992,7 +11988,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Cond fan relay (-)</t>
+          <t>Fuel pump relay (-)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -12007,7 +12003,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -12019,7 +12015,7 @@
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
-          <t>42281-1</t>
+          <t>282110-1</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -12029,17 +12025,17 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>B1-R5 Condenser fan relay (seated in the POWER box R5)</t>
+          <t>B3-K1 Fuel Pump Relay, TE HCR150 (seated in the battery relay block K1) - ACTIVE-LOW - ECU sinks coil- (85); coil+ (86) switched 12 V - HCR 150 coil is a 2-pole Superseal plug (TE terminals 1/2, not marked 85/86), resistor-suppressed so polarity-free</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>FAN2</t>
+          <t>FP</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
@@ -12049,42 +12045,46 @@
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>FAN2</t>
+          <t>FP</t>
         </is>
       </c>
       <c r="V107" t="inlineStr"/>
-      <c r="W107" t="inlineStr"/>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>glove-box branch (POWER / LOGIC boxes) / cabin run to the trunk relay block (Routes 1 / 11)</t>
+        </is>
+      </c>
       <c r="X107" t="inlineStr"/>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_fan285_cp on CabinPower, 400 mm; w_fan285 on ECU-cabin, 480 mm)</t>
+          <t>Battery relay block (trunk) relay K1 fuel pump, pin 85 | est length: ECU-A to the glove-box boxes (390 mm) plus the cabin run to K-FP in the trunk relay block, alongside w_k_fp_86_cp (2500 mm); row 157</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>w_fp85</t>
+          <t>w_lam12_cp</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>K-FP</t>
+          <t>LOGIC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>BUS2-1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>DRB102-CABIN</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
@@ -12095,83 +12095,83 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Fuel pump relay (-)</t>
+          <t>EFI relay k_efi -&gt; LOGIC LAM 7.5 A fuse</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>250</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>J1128-TXL-14-RED</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
-          <t>282110-1</t>
+          <t>1-968851-1</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>3-1447221-3</t>
+          <t>0460-220-1231</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>B3-K1 Fuel Pump Relay, TE HCR150 (seated in the battery relay block K1) - ACTIVE-LOW - ECU sinks coil- (85); coil+ (86) switched 12 V - HCR 150 coil is a 2-pole Superseal plug (TE terminals 1/2, not marked 85/86), resistor-suppressed so polarity-free</t>
+          <t>B2 LOGIC box - custom fuse + relay box, glove box inboard (cad/fusebox rev 5, DECISIONS R75): Bus 1 (permanent) and Bus 2 (switched, k_efi 30) mini fuse strips, micro relays M1-M10</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>DRB102 receptacle (RH firewall)</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>FP</t>
+          <t>LAM</t>
         </is>
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin</t>
+          <t>ST185-CabinPower</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>FP</t>
-        </is>
-      </c>
-      <c r="V108" t="inlineStr"/>
-      <c r="W108" t="inlineStr">
-        <is>
-          <t>glove-box branch (POWER / LOGIC boxes) / cabin run to the trunk relay block (Routes 1 / 11)</t>
-        </is>
-      </c>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>ST185-AB-engine w_lam12_be14 at DRB102-ENGINE 95, to splice SP-LAM12-B</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr"/>
       <c r="X108" t="inlineStr"/>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>Battery relay block (trunk) relay K1 fuel pump, pin 85 | est length: ECU-A to the glove-box boxes (390 mm) plus the cabin run to K-FP in the trunk relay block, alongside w_k_fp_86_cp (2500 mm); row 157</t>
+          <t>CAN-Lambda +12 V | CAN-Lambda +12 V | owner proposed: longer half (drawn today as w_lam12_cp on CabinPower, 250 mm; w_lam12_bc on ECU-cabin, 120 mm)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>w_lam12_cp</t>
+          <t>w_fb_mrs_en</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -12181,7 +12181,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BUS2-1</t>
+          <t>BUS2-12</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>83</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
@@ -12202,7 +12202,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC LAM 7.5 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC MRS 5 A fuse</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -12212,29 +12212,29 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>450</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>J1128-TXL-14-RED</t>
+          <t>J1128-TXL-20-RED</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr">
         <is>
-          <t>1-968851-1</t>
+          <t>1-968849-1</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>0460-220-1231</t>
+          <t>0460-202-1631</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
@@ -12249,36 +12249,40 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>LAM</t>
+          <t>EPSEN</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>ST185-CabinPower</t>
+          <t>ST185-AB-cabin</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>LAM</t>
+          <t>EPSEN</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_lam12_be14 at DRB102-ENGINE 95, to splice SP-LAM12-B</t>
-        </is>
-      </c>
-      <c r="W109" t="inlineStr"/>
+          <t>ST185-AB-engine w_hv_mrs_en_e at DRB102-ENGINE 83, to MRS-C 1</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
+        </is>
+      </c>
       <c r="X109" t="inlineStr"/>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>CAN-Lambda +12 V | CAN-Lambda +12 V | owner proposed: longer half (drawn today as w_lam12_cp on CabinPower, 250 mm; w_lam12_bc on ECU-cabin, 120 mm)</t>
+          <t>LOGIC box (glove box) fuse MRS 7.5A Fuse fed from EPS enable relay k_eps_en pin 87 (ignition-switched). | EHPS enable +12 V | fuse fed from EPS enable relay k_eps_en pin 87 (ignition-switched); owner proposed: longer half (drawn today as w_fb_mrs_en on ECU-cabin, 530 mm; w_fb_mrs_en_cp on CabinPower, 250 mm)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>w_fb_mrs_en</t>
+          <t>w_start</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -12288,17 +12292,17 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BUS2-12</t>
+          <t>BUS2-13</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>DRB102-CABIN</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
@@ -12309,12 +12313,12 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC MRS 5 A fuse</t>
+          <t>Start request</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -12324,12 +12328,12 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>680</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-RED</t>
+          <t>J1128-TXL-20-YELLOW</t>
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
@@ -12341,7 +12345,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>0460-202-1631</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -12351,12 +12355,12 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>DRB102 receptacle (RH firewall)</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>EPSEN</t>
+          <t>B30</t>
         </is>
       </c>
       <c r="T110" t="inlineStr">
@@ -12366,30 +12370,22 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>EPSEN</t>
-        </is>
-      </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine w_hv_mrs_en_e at DRB102-ENGINE 83, to MRS-C 1</t>
-        </is>
-      </c>
-      <c r="W110" t="inlineStr">
-        <is>
-          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
-        </is>
-      </c>
+          <t>B30</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr"/>
+      <c r="W110" t="inlineStr"/>
       <c r="X110" t="inlineStr"/>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) fuse MRS 7.5A Fuse fed from EPS enable relay k_eps_en pin 87 (ignition-switched). | EHPS enable +12 V | fuse fed from EPS enable relay k_eps_en pin 87 (ignition-switched); owner proposed: longer half (drawn today as w_fb_mrs_en on ECU-cabin, 530 mm; w_fb_mrs_en_cp on CabinPower, 250 mm)</t>
+          <t>owner proposed: longer half (drawn today as w_start_cp on CabinPower, 530 mm; w_start on ECU-cabin, 1230 mm)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>w_start</t>
+          <t>w_cop_pwr_ac</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -12399,17 +12395,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BUS2-13</t>
+          <t>BUS2-3</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>DRB102-CABIN</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
@@ -12420,39 +12416,39 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Start request</t>
+          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>180</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-YELLOW</t>
+          <t>J1128-TXL-14-RED</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr">
         <is>
-          <t>1-968849-1</t>
+          <t>1-968851-1</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>0460-220-1231</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -12462,37 +12458,45 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>DRB102 receptacle (RH firewall)</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>B30</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin</t>
+          <t>ST185-CabinPower</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>B30</t>
-        </is>
-      </c>
-      <c r="V111" t="inlineStr"/>
-      <c r="W111" t="inlineStr"/>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>ST185-AB-engine w_cop_pwr_e_ae at DRB102-ENGINE 1, to splice SP-COP-ENG</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
+        </is>
+      </c>
       <c r="X111" t="inlineStr"/>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_start_cp on CabinPower, 530 mm; w_start on ECU-cabin, 1230 mm)</t>
+          <t>LOGIC box (glove box) fuse COP 10A | Coil +12 V feed | owner proposed: longer half (drawn today as w_cop_pwr_ac on ECU-cabin, 180 mm; w_cop_pwr_c_ac on CabinPower, 250 mm)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>w_cop_pwr_ac</t>
+          <t>w_inj_pwr_ac</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -12502,7 +12506,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>BUS2-3</t>
+          <t>BUS2-4</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -12512,7 +12516,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
@@ -12523,7 +12527,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC COP 10 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC INJ 7.5 A fuse</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -12570,7 +12574,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>INJ</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
@@ -12580,12 +12584,12 @@
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>INJ</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_cop_pwr_e_ae at DRB102-ENGINE 1, to splice SP-COP-ENG</t>
+          <t>ST185-AB-engine w_inj_pwr_e_ae at DRB102-ENGINE 2, to splice SP-INJ-ENG</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
@@ -12596,24 +12600,24 @@
       <c r="X112" t="inlineStr"/>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) fuse COP 10A | Coil +12 V feed | owner proposed: longer half (drawn today as w_cop_pwr_ac on ECU-cabin, 180 mm; w_cop_pwr_c_ac on CabinPower, 250 mm)</t>
+          <t>LOGIC box (glove box) fuse INJ 7.5A | Injector +12 V feed | owner proposed: longer half (drawn today as w_inj_pwr_ac on ECU-cabin, 180 mm; w_inj_pwr_c_ac on CabinPower, 250 mm)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>w_inj_pwr_ac</t>
+          <t>w_sw7_c</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>LOGIC</t>
+          <t>OPTO-8</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>BUS2-4</t>
+          <t>IN2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -12623,123 +12627,123 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr"/>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>SP-REV</t>
+        </is>
+      </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC INJ 7.5 A fuse</t>
+          <t>Reverse to opto in 2</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>680</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>J1128-TXL-14-RED</t>
+          <t>J1128-TXL-16-YELLOW</t>
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr">
         <is>
-          <t>1-968851-1</t>
+          <t>screw terminal (on the board)</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>0460-220-1231</t>
+          <t>solder splice SP-REV</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>B2 LOGIC box - custom fuse + relay box, glove box inboard (cad/fusebox rev 5, DECISIONS R75): Bus 1 (permanent) and Bus 2 (switched, k_efi 30) mini fuse strips, micro relays M1-M10</t>
+          <t>Optocoupler board, 8 channel (Dan's, generic EL814) - inline at the CSB3</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>DRB102 receptacle (RH firewall)</t>
+          <t>via SP-REV</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>INJ</t>
+          <t>REV</t>
         </is>
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>ST185-CabinPower</t>
+          <t>ST185-AB-cabin</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>INJ</t>
+          <t>SP-REV</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>ST185-AB-engine w_inj_pwr_e_ae at DRB102-ENGINE 2, to splice SP-INJ-ENG</t>
-        </is>
-      </c>
-      <c r="W113" t="inlineStr">
-        <is>
-          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
-        </is>
-      </c>
+          <t>ST185-AB-engine w_sw7_e at DRB102-ENGINE 78, to REV-SW 1</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr"/>
       <c r="X113" t="inlineStr"/>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) fuse INJ 7.5A | Injector +12 V feed | owner proposed: longer half (drawn today as w_inj_pwr_ac on ECU-cabin, 180 mm; w_inj_pwr_c_ac on CabinPower, 250 mm)</t>
+          <t>owner TBD: a half has no length estimate (drawn today as w_sw7_c on ECU-cabin, ? mm; w_sw7_c_csb on CSB3, 180 mm)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>w_sw7_c</t>
+          <t>w_cam_pullup_8v</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>OPTO-8</t>
+          <t>R-CAM-PULLUP</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>IN2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>DRB102-CABIN</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>SP-REV</t>
+          <t>SP-8V</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -12749,54 +12753,50 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Reverse to opto in 2</t>
+          <t>+8 V to cam pull-up</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>J1128-TXL-16-YELLOW</t>
+          <t>J1128-TXL-20-ORANGE</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr">
-        <is>
-          <t>screw terminal (on the board)</t>
-        </is>
-      </c>
+      <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>solder splice SP-REV</t>
+          <t>solder splice SP-8V</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>Optocoupler board, 8 channel (Dan's, generic EL814) - inline at the CSB3</t>
+          <t>Cam pull-up 1.8 k to +8 V</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>via SP-REV</t>
+          <t>via SP-8V</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>REV</t>
+          <t>CAM</t>
         </is>
       </c>
       <c r="T114" t="inlineStr">
@@ -12806,26 +12806,22 @@
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>SP-REV</t>
-        </is>
-      </c>
-      <c r="V114" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine w_sw7_e at DRB102-ENGINE 78, to REV-SW 1</t>
-        </is>
-      </c>
-      <c r="W114" t="inlineStr"/>
+          <t>SP-8V</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr"/>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>at ECU-A plug</t>
+        </is>
+      </c>
       <c r="X114" t="inlineStr"/>
-      <c r="Y114" t="inlineStr">
-        <is>
-          <t>owner TBD: a half has no length estimate (drawn today as w_sw7_c on ECU-cabin, ? mm; w_sw7_c_csb on CSB3, 180 mm)</t>
-        </is>
-      </c>
+      <c r="Y114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>w_cam_pullup_8v</t>
+          <t>w_cam_pullup_sig</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -12835,7 +12831,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -12845,12 +12841,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>SP-8V</t>
+          <t>SP-CAM</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -12860,12 +12856,12 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>+8 V to cam pull-up</t>
+          <t>Cam pull-up 1.8k</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -12880,7 +12876,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-ORANGE</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
@@ -12888,7 +12884,7 @@
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>solder splice SP-8V</t>
+          <t>solder splice SP-CAM</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
@@ -12898,7 +12894,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>via SP-8V</t>
+          <t>via SP-CAM</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
@@ -12913,7 +12909,7 @@
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>SP-8V</t>
+          <t>SP-CAM</t>
         </is>
       </c>
       <c r="V115" t="inlineStr"/>
@@ -12928,32 +12924,32 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>w_cam_pullup_sig</t>
+          <t>w43</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>R-CAM-PULLUP</t>
+          <t>R-FUELLVL</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>SP-CAM</t>
+          <t>SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -12963,7 +12959,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Cam pull-up 1.8k</t>
+          <t>Fuel lvl pull-up</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -12991,22 +12987,22 @@
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>solder splice SP-CAM</t>
+          <t>solder splice SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>Cam pull-up 1.8 k to +8 V</t>
+          <t>470R fuel level pull-up to +5V</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>via SP-CAM</t>
+          <t>via SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>CAM</t>
+          <t>FLVL</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
@@ -13016,22 +13012,18 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>SP-CAM</t>
+          <t>SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="V116" t="inlineStr"/>
-      <c r="W116" t="inlineStr">
-        <is>
-          <t>at ECU-A plug</t>
-        </is>
-      </c>
+      <c r="W116" t="inlineStr"/>
       <c r="X116" t="inlineStr"/>
       <c r="Y116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>w43</t>
+          <t>w44</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -13041,37 +13033,33 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>BUS-5V-2</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>SP-FUEL-LVL</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Fuel lvl pull-up</t>
+          <t>+5 V fuel lvl pullup</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -13086,7 +13074,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-WHITE</t>
+          <t>J1128-TXL-20-ORANGE</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
@@ -13094,7 +13082,7 @@
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>solder splice SP-FUEL-LVL</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
@@ -13104,7 +13092,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>via SP-FUEL-LVL</t>
+          <t>DT06-8 plug (ECU splice point)</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
@@ -13119,7 +13107,7 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>SP-FUEL-LVL</t>
+          <t>BUS-5V-2</t>
         </is>
       </c>
       <c r="V117" t="inlineStr"/>
@@ -13130,43 +13118,47 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>w44</t>
+          <t>w_tach_r</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>R-FUELLVL</t>
+          <t>R-LOCK</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>BUS-5V-2</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>SP-TACH</t>
+        </is>
+      </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>leg</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>+5 V fuel lvl pullup</t>
+          <t>Tacho to lock-sensor 4.7k</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -13181,7 +13173,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-ORANGE</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
@@ -13189,22 +13181,22 @@
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>solder splice SP-TACH</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>470R fuel level pull-up to +5V</t>
+          <t>Lock-sensor tap 4.7 k from tacho</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>DT06-8 plug (ECU splice point)</t>
+          <t>via SP-TACH</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>FLVL</t>
+          <t>TACH</t>
         </is>
       </c>
       <c r="T118" t="inlineStr">
@@ -13214,18 +13206,26 @@
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>BUS-5V-2</t>
+          <t>SP-TACH</t>
         </is>
       </c>
       <c r="V118" t="inlineStr"/>
-      <c r="W118" t="inlineStr"/>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>A/C amp branch (behind dash)</t>
+        </is>
+      </c>
       <c r="X118" t="inlineStr"/>
-      <c r="Y118" t="inlineStr"/>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>OPEN-ITEMS History 2026-10-21 N61: first bench try is tach -&gt; 4.7 kohm -&gt; A15-9. Dan 2026-10-26: lock-sensor input needs a modified tachometer signal; apply that workaround.</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>w_tach_r</t>
+          <t>w_lock_9</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -13235,32 +13235,28 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>A18</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>SP-TACH</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Tacho to lock-sensor 4.7k</t>
+          <t>Lock-sensor input (modified tacho)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -13288,7 +13284,7 @@
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>solder splice SP-TACH</t>
+          <t>solder onto the factory lead</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
@@ -13298,7 +13294,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>via SP-TACH</t>
+          <t>OEM A/C amplifier A18 (1993 book: A15)</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
@@ -13313,7 +13309,7 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>SP-TACH</t>
+          <t>TACH</t>
         </is>
       </c>
       <c r="V119" t="inlineStr"/>
@@ -13322,37 +13318,41 @@
           <t>A/C amp branch (behind dash)</t>
         </is>
       </c>
-      <c r="X119" t="inlineStr"/>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>A/C amplifier A18 (1993: A15) pin 9, behind the glove box; OEM colour W-L; EWD 1993 p.210-211; solder onto the factory lead</t>
+        </is>
+      </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>OPEN-ITEMS History 2026-10-21 N61: first bench try is tach -&gt; 4.7 kohm -&gt; A15-9. Dan 2026-10-26: lock-sensor input needs a modified tachometer signal; apply that workaround.</t>
+          <t>A15 pin 9 lock-sensor (factory W-L / IH1-4). Engine-side lock sensor unused. | Factory lock sensor is A15 pins 9-14 (W-L / W-R, Mitchell ~115 ohm). Workaround: modified tacho through 4.7k to pin 9 (N61 2026-10-21). IH1-4/5 engine wires unused (Engine Wire gone).</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>w_lock_9</t>
+          <t>w_start_in_cp</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>R-LOCK</t>
+          <t>RB4</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>A18</t>
+          <t>LOGIC</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>BUS2-13 IN</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
@@ -13363,12 +13363,12 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Lock-sensor input (modified tacho)</t>
+          <t>Start sw ST1 feed</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -13378,175 +13378,179 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>530</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-WHITE</t>
+          <t>J1128-TXL-20-YELLOW</t>
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>solder onto the factory lead</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>solder onto the factory lead</t>
+          <t>1-968849-1</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>Lock-sensor tap 4.7 k from tacho</t>
+          <t>OEM ST1 lead B-W at old R/B No.4 pin 1, RH kick panel</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>OEM A/C amplifier A18 (1993 book: A15)</t>
+          <t>B2 LOGIC box - custom fuse + relay box, glove box inboard (cad/fusebox rev 5, DECISIONS R75): Bus 1 (permanent) and Bus 2 (switched, k_efi 30) mini fuse strips, micro relays M1-M10</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>TACH</t>
+          <t>B30</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>ST185-AB-cabin</t>
+          <t>ST185-CabinPower</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>TACH</t>
+          <t>B30</t>
         </is>
       </c>
       <c r="V120" t="inlineStr"/>
-      <c r="W120" t="inlineStr">
-        <is>
-          <t>A/C amp branch (behind dash)</t>
-        </is>
-      </c>
+      <c r="W120" t="inlineStr"/>
       <c r="X120" t="inlineStr">
         <is>
-          <t>A/C amplifier A18 (1993: A15) pin 9, behind the glove box; OEM colour W-L; EWD 1993 p.210-211; solder onto the factory lead</t>
+          <t>OEM ST1 lead B-W at old R/B No.4 pin 1, RH kick panel - start (EWD 1993 p.66); OEM colour B-W; EWD 1993 TIS EWD p.66 (Starting and Ignition, All-Trac); solder splice onto the factory lead</t>
         </is>
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>A15 pin 9 lock-sensor (factory W-L / IH1-4). Engine-side lock sensor unused. | Factory lock sensor is A15 pins 9-14 (W-L / W-R, Mitchell ~115 ohm). Workaround: modified tacho through 4.7k to pin 9 (N61 2026-10-21). IH1-4/5 engine wires unused (Engine Wire gone).</t>
+          <t>owner proposed: longer half (drawn today as w_start_in on ECU-cabin, 350 mm; w_start_in_cp on CabinPower, 530 mm)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>w_start_in_cp</t>
+          <t>cab_aps1_sh</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>RB4</t>
+          <t>NC, floats</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LOGIC</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>BUS2-13 IN</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
+        </is>
+      </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>drain</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Start sw ST1 feed</t>
+          <t>Pedal 1 cable shield</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>840</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-YELLOW</t>
-        </is>
-      </c>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr">
-        <is>
-          <t>solder onto the factory lead</t>
-        </is>
-      </c>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>CAB-APS1</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>55A1831-20-2/4/6-9</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>1-968849-1</t>
+          <t>solder splice SP-SHIELD-A-APS</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>OEM ST1 lead B-W at old R/B No.4 pin 1, RH kick panel</t>
+          <t>cab_aps1 screen (floats at the device end)</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>B2 LOGIC box - custom fuse + relay box, glove box inboard (cad/fusebox rev 5, DECISIONS R75): Bus 1 (permanent) and Bus 2 (switched, k_efi 30) mini fuse strips, micro relays M1-M10</t>
+          <t>via SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>B30</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>ST185-CabinPower</t>
+          <t>ST185-AB-cabin</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>B30</t>
+          <t>SP-SHIELD-A-APS</t>
         </is>
       </c>
       <c r="V121" t="inlineStr"/>
-      <c r="W121" t="inlineStr"/>
-      <c r="X121" t="inlineStr">
-        <is>
-          <t>OEM ST1 lead B-W at old R/B No.4 pin 1, RH kick panel - start (EWD 1993 p.66); OEM colour B-W; EWD 1993 TIS EWD p.66 (Starting and Ignition, All-Trac); solder splice onto the factory lead</t>
-        </is>
-      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>at ECU-A plug</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr"/>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_start_in on ECU-cabin, 350 mm; w_start_in_cp on CabinPower, 530 mm)</t>
+          <t>Screen floats at this end: cut back and seal under heat-shrink | screen floats at the far end; pedal branch length estimated from OEM body dimensions + 10 % (990 mm ECU-A</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>cab_aps1_sh</t>
+          <t>cab_aps_sh</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -13581,7 +13585,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Pedal 1 cable shield</t>
+          <t>Pedal 2 cable shield</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -13602,7 +13606,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>CAB-APS1</t>
+          <t>CAB-APS2</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -13618,7 +13622,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>cab_aps1 screen (floats at the device end)</t>
+          <t>cab_aps2 screen (floats at the device end)</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -13657,7 +13661,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>cab_aps_sh</t>
+          <t>cab_fspur_fr_sh_ac</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -13682,7 +13686,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
+          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -13692,7 +13696,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Pedal 2 cable shield</t>
+          <t>FR wheel spd shield</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -13703,7 +13707,7 @@
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>500</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -13713,33 +13717,33 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>CAB-APS2</t>
+          <t>CAB-FSPUR-FR-AC</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>55A1811-20-9-9CS2275</t>
         </is>
       </c>
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-A-APS</t>
+          <t>solder splice SP-SHIELD-A-WSF</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>cab_aps2 screen (floats at the device end)</t>
+          <t>cab_fspur_fr_ac screen (floats at the device end)</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
+          <t>via SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>WSSF</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
@@ -13749,36 +13753,36 @@
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-APS</t>
+          <t>SP-SHIELD-A-WSF</t>
         </is>
       </c>
       <c r="V123" t="inlineStr"/>
       <c r="W123" t="inlineStr">
         <is>
-          <t>at ECU-A plug</t>
+          <t>dash branch (front WS inline)</t>
         </is>
       </c>
       <c r="X123" t="inlineStr"/>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>Screen floats at this end: cut back and seal under heat-shrink | screen floats at the far end; pedal branch length estimated from OEM body dimensions + 10 % (990 mm ECU-A</t>
+          <t>Screen floats at this end: cut back and seal under heat-shrink | tied at the A end only; the far (B) end floats, dressed back at the ECU-B plug (no A-B shield bridge)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>cab_fspur_fr_sh_ac</t>
+          <t>w19</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>NC, floats</t>
+          <t>legs of SP-8V</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -13788,69 +13792,69 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
+          <t>SP-8V</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>drain</t>
+          <t>trunk</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>FR wheel spd shield</t>
+          <t>+8 V sensor supply</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Shield</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr"/>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>310</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>(cable core)</t>
-        </is>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>CAB-FSPUR-FR-AC</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>55A1811-20-9-9CS2275</t>
-        </is>
-      </c>
-      <c r="O124" t="inlineStr"/>
+          <t>J1128-TXL-20-ORANGE</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>solder splice</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-A-WSF</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>cab_fspur_fr_ac screen (floats at the device end)</t>
+          <t>ECU splice point - SP-8V: +8 V supply, cam sensor + gearbox speed sensor only (ECU A6)</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>WSSF</t>
+          <t>8V</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
@@ -13860,31 +13864,27 @@
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-WSF</t>
+          <t>SP-8V</t>
         </is>
       </c>
       <c r="V124" t="inlineStr"/>
       <c r="W124" t="inlineStr">
         <is>
-          <t>dash branch (front WS inline)</t>
+          <t>at ECU-A plug</t>
         </is>
       </c>
       <c r="X124" t="inlineStr"/>
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>Screen floats at this end: cut back and seal under heat-shrink | tied at the A end only; the far (B) end floats, dressed back at the ECU-B plug (no A-B shield bridge)</t>
-        </is>
-      </c>
+      <c r="Y124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>w19</t>
+          <t>w_a5_pin</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>legs of SP-8V</t>
+          <t>legs of SP-A5</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -13899,12 +13899,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>SP-8V</t>
+          <t>SP-A5</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -13914,17 +13914,17 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>+8 V sensor supply</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse (+ IG2 wake diode)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -13934,7 +13934,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-ORANGE</t>
+          <t>J1128-TXL-18-RED</t>
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
@@ -13946,12 +13946,12 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>3-1447221-3</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>ECU splice point - SP-8V: +8 V supply, cam sensor + gearbox speed sensor only (ECU A6)</t>
+          <t>ECU splice point - SP-A5: ECU main feed (SW12 + IG2 diode)</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -13961,7 +13961,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>8V</t>
+          <t>SW12</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>SP-8V</t>
+          <t>SP-A5</t>
         </is>
       </c>
       <c r="V125" t="inlineStr"/>
@@ -13981,17 +13981,21 @@
         </is>
       </c>
       <c r="X125" t="inlineStr"/>
-      <c r="Y125" t="inlineStr"/>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>ECU main +12 V | ECU main +12 V</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>w_a5_pin</t>
+          <t>w_ac_psw_in</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>legs of SP-A5</t>
+          <t>legs of SP-AC-PSW</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -14001,17 +14005,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SP-A5</t>
+          <t>SP-AC-PSW</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -14021,27 +14025,27 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse (+ IG2 wake diode)</t>
+          <t>A/C pressure sw out</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>J1128-TXL-18-RED</t>
+          <t>M22759/16-20-4</t>
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
@@ -14053,22 +14057,22 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>3-1447221-3</t>
+          <t xml:space="preserve">new-wire run terminated at the switch's </t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>ECU splice point - SP-A5: ECU main feed (SW12 + IG2 diode)</t>
+          <t>At A/C amp - SP-AC-PSW: A/C pressure switch output</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>OEM A5, factory Y-R lead</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>SW12</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
@@ -14078,31 +14082,35 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>SP-A5</t>
+          <t>SP-AC-PSW</t>
         </is>
       </c>
       <c r="V126" t="inlineStr"/>
       <c r="W126" t="inlineStr">
         <is>
-          <t>at ECU-A plug</t>
-        </is>
-      </c>
-      <c r="X126" t="inlineStr"/>
+          <t>A/C amp branch (behind dash)</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>A/C pressure switch A5, engine bay; exact spot TBD (no locator figure in the repo); OEM colour Y-R (factory wiring; new wire here); EWD 1990 ST185 EWD p.152 (docs/electrical/ewd-snips/1990-st185-autoac-pressure-clutch-p152.png); 1990 ST185 EWD p.152 (A5 pin 4 Y-R); new-wire run terminated at the switch's own mating plug (no factory engine-bay wire reused, Section 39, 2026-10-04); plug part number not yet chosen</t>
+        </is>
+      </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>ECU main +12 V | ECU main +12 V</t>
+          <t>Runs on in ST185-EngineRoom-C to A/C pressure switch A5 pin 4 (engine bay): new wire to the switch's own mating plug, plug part TBD. EWD 1990 p.152. | owner TBD: a half has no length estimate (drawn today as w_ac_psw_in on ECU-cabin, ? mm; w_ac_psw on EngineRoom-C, 100 mm)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>w_ac_psw_in</t>
+          <t>w_amb_rtn</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>legs of SP-AC-PSW</t>
+          <t>legs of SP-AC-SG</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -14112,17 +14120,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>SP-AC-PSW</t>
+          <t>SP-AC-SG</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -14132,7 +14140,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>A/C pressure sw out</t>
+          <t>Ambient sensor return</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -14147,12 +14155,12 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>J1128-TXL-20-YELLOW</t>
         </is>
       </c>
       <c r="M127" t="inlineStr"/>
@@ -14164,22 +14172,22 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t xml:space="preserve">new-wire run terminated at the switch's </t>
+          <t xml:space="preserve">new-wire run terminated at the sensor's </t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>At A/C amp - SP-AC-PSW: A/C pressure switch output</t>
+          <t>SP-AC-SG - cabin A/C sensor common (replaces E10; A32-15, A24-3, A21, A18-2 stay factory)</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>OEM A5, factory Y-R lead</t>
+          <t>OEM ambient air temp sensor A1 pin 1 (front, 6 in pigtail)</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>AMB</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
@@ -14189,35 +14197,31 @@
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>SP-AC-PSW</t>
+          <t>SP-AC-SG</t>
         </is>
       </c>
       <c r="V127" t="inlineStr"/>
-      <c r="W127" t="inlineStr">
-        <is>
-          <t>A/C amp branch (behind dash)</t>
-        </is>
-      </c>
+      <c r="W127" t="inlineStr"/>
       <c r="X127" t="inlineStr">
         <is>
-          <t>A/C pressure switch A5, engine bay; exact spot TBD (no locator figure in the repo); OEM colour Y-R (factory wiring; new wire here); EWD 1990 ST185 EWD p.152 (docs/electrical/ewd-snips/1990-st185-autoac-pressure-clutch-p152.png); 1990 ST185 EWD p.152 (A5 pin 4 Y-R); new-wire run terminated at the switch's own mating plug (no factory engine-bay wire reused, Section 39, 2026-10-04); plug part number not yet chosen</t>
+          <t>Ambient air temp sensor A1 pin 1 (6 in pigtail, B9); OEM colour Y; EWD 1993 p.211; new-wire run terminated at the sensor's own mating plug; 6 in OEM pigtail stays</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>Runs on in ST185-EngineRoom-C to A/C pressure switch A5 pin 4 (engine bay): new wire to the switch's own mating plug, plug part TBD. EWD 1990 p.152. | owner TBD: a half has no length estimate (drawn today as w_ac_psw_in on ECU-cabin, ? mm; w_ac_psw on EngineRoom-C, 100 mm)</t>
+          <t>Row 164: E10 sensor-common dies under B9. Cabin splice SP-AC-SG kept. Factory Y-R is the A/C pressure-switch output (A5-4 through joiner E10 to A18-13), not sensor ground; sensor common is Y (1990 ST185 EWD p.150 / p.152).</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>w_amb_rtn</t>
+          <t>w_trig2_pin</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>legs of SP-AC-SG</t>
+          <t>legs of SP-CAM</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -14227,17 +14231,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SP-AC-SG</t>
+          <t>SP-CAM</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -14247,12 +14251,12 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Ambient sensor return</t>
+          <t>Cam sensor signal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14262,12 +14266,12 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>310</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-YELLOW</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="M128" t="inlineStr"/>
@@ -14279,22 +14283,22 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t xml:space="preserve">new-wire run terminated at the sensor's </t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>SP-AC-SG - cabin A/C sensor common (replaces E10; A32-15, A24-3, A21, A18-2 stay factory)</t>
+          <t>At the ECU plugs - SP-CAM: cam signal + 1.8k pull-up to +8V</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>OEM ambient air temp sensor A1 pin 1 (front, 6 in pigtail)</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>AMB</t>
+          <t>CAM</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
@@ -14304,31 +14308,27 @@
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>SP-AC-SG</t>
+          <t>SP-CAM</t>
         </is>
       </c>
       <c r="V128" t="inlineStr"/>
-      <c r="W128" t="inlineStr"/>
-      <c r="X128" t="inlineStr">
-        <is>
-          <t>Ambient air temp sensor A1 pin 1 (6 in pigtail, B9); OEM colour Y; EWD 1993 p.211; new-wire run terminated at the sensor's own mating plug; 6 in OEM pigtail stays</t>
-        </is>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>Row 164: E10 sensor-common dies under B9. Cabin splice SP-AC-SG kept. Factory Y-R is the A/C pressure-switch output (A5-4 through joiner E10 to A18-13), not sensor ground; sensor common is Y (1990 ST185 EWD p.150 / p.152).</t>
-        </is>
-      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>at ECU-A plug</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr"/>
+      <c r="Y128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>w_trig2_pin</t>
+          <t>w_csbg_ac</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>legs of SP-CAM</t>
+          <t>legs of SP-CSB-GND</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -14338,17 +14338,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>POWER-NEG-BAR</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Lug</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>SP-CAM</t>
+          <t>SP-CSB-GND</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -14358,12 +14358,12 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Cam sensor signal</t>
+          <t>CSB3 + opto ground</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14373,12 +14373,12 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-WHITE</t>
+          <t>J1128-TXL-20-BLACK</t>
         </is>
       </c>
       <c r="M129" t="inlineStr"/>
@@ -14390,22 +14390,22 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>At the ECU plugs - SP-CAM: cam signal + 1.8k pull-up to +8V</t>
+          <t>CSB3 ground splice - CSB3 pin 2, opto board COM and stalk ground</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>POWER box NEG bar M8 stud (glove box)</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>CAM</t>
+          <t>CSB</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
@@ -14415,27 +14415,35 @@
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>SP-CAM</t>
-        </is>
-      </c>
-      <c r="V129" t="inlineStr"/>
+          <t>SP-CSB-GND</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>SP-CSB-GND also joins ST185-CSB3</t>
+        </is>
+      </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>at ECU-A plug</t>
+          <t>glove-box POWER box to the CSB3 branch</t>
         </is>
       </c>
       <c r="X129" t="inlineStr"/>
-      <c r="Y129" t="inlineStr"/>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>M8 ring lug on the POWER box battery-negative bar (R213: CSB3, opto board and cruise ladder never on chassis or the ECU ground) | (CSB3 loom, under centre cluster) | est length; runs with the CSB3 +12 V (w_csb12, LOGIC CSB 5A) (R217)</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>w_csbg_ac</t>
+          <t>w_fl_sig_pin</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>legs of SP-CSB-GND</t>
+          <t>legs of SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -14445,17 +14453,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>POWER-NEG-BAR</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Lug</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>SP-CSB-GND</t>
+          <t>SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -14465,12 +14473,12 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>CSB3 + opto ground</t>
+          <t>Fuel level signal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14480,12 +14488,12 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>310</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-BLACK</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="M130" t="inlineStr"/>
@@ -14497,22 +14505,22 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>CSB3 ground splice - CSB3 pin 2, opto board COM and stalk ground</t>
+          <t>SP-FUEL-LVL - fuel sender signal + 470R pull-up to ECU-B B24</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>POWER box NEG bar M8 stud (glove box)</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>FLVL</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
@@ -14522,35 +14530,23 @@
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>SP-CSB-GND</t>
-        </is>
-      </c>
-      <c r="V130" t="inlineStr">
-        <is>
-          <t>SP-CSB-GND also joins ST185-CSB3</t>
-        </is>
-      </c>
-      <c r="W130" t="inlineStr">
-        <is>
-          <t>glove-box POWER box to the CSB3 branch</t>
-        </is>
-      </c>
+          <t>SP-FUEL-LVL</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr"/>
+      <c r="W130" t="inlineStr"/>
       <c r="X130" t="inlineStr"/>
-      <c r="Y130" t="inlineStr">
-        <is>
-          <t>M8 ring lug on the POWER box battery-negative bar (R213: CSB3, opto board and cruise ladder never on chassis or the ECU ground) | (CSB3 loom, under centre cluster) | est length; runs with the CSB3 +12 V (w_csb12, LOGIC CSB 5A) (R217)</t>
-        </is>
-      </c>
+      <c r="Y130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>w_fl_sig_pin</t>
+          <t>w66</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>legs of SP-FUEL-LVL</t>
+          <t>legs of SP-GND-ECU</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -14560,17 +14556,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>POWER-NEG-BAR</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Lug</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>SP-FUEL-LVL</t>
+          <t>SP-GND-ECU</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -14580,27 +14576,27 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Fuel level signal</t>
+          <t>ECU power ground</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>570</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-WHITE</t>
+          <t>J1128-TXL-10-BLACK</t>
         </is>
       </c>
       <c r="M131" t="inlineStr"/>
@@ -14612,22 +14608,22 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>SP-FUEL-LVL - fuel sender signal + 470R pull-up to ECU-B B24</t>
+          <t>ECU splice point - SP-GND-ECU: ECU power ground (A25 A34 B25 B34) to the NEG bar</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>POWER box NEG bar M8 stud (glove box)</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>FLVL</t>
+          <t>GND</t>
         </is>
       </c>
       <c r="T131" t="inlineStr">
@@ -14637,23 +14633,31 @@
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>SP-FUEL-LVL</t>
+          <t>SP-GND-ECU</t>
         </is>
       </c>
       <c r="V131" t="inlineStr"/>
-      <c r="W131" t="inlineStr"/>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>ECU to the glove-box POWER box</t>
+        </is>
+      </c>
       <c r="X131" t="inlineStr"/>
-      <c r="Y131" t="inlineStr"/>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>M8 ring lug on the POWER box battery-negative bar (R216): the ECU grounds only, nothing else | est length; the ONE ECU ground return (DECISIONS R216)</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>w66</t>
+          <t>w_rev_sw_c</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>legs of SP-GND-ECU</t>
+          <t>legs of SP-REV</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -14663,17 +14667,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>POWER-NEG-BAR</t>
+          <t>DRB102-CABIN</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Lug</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>SP-GND-ECU</t>
+          <t>SP-REV</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -14683,27 +14687,27 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>ECU power ground</t>
+          <t>Reverse sw +12 V out</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>J1128-TXL-10-BLACK</t>
+          <t>J1128-TXL-16-YELLOW</t>
         </is>
       </c>
       <c r="M132" t="inlineStr"/>
@@ -14715,22 +14719,22 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>0460-202-1631</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>ECU splice point - SP-GND-ECU: ECU power ground (A25 A34 B25 B34) to the NEG bar</t>
+          <t>SP-REV - reverse switch out to CSB3 opto IN2 and IG2-13 lamps</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>POWER box NEG bar M8 stud (glove box)</t>
+          <t>DRB102 receptacle (RH firewall)</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>GND</t>
+          <t>REV</t>
         </is>
       </c>
       <c r="T132" t="inlineStr">
@@ -14740,31 +14744,31 @@
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>SP-GND-ECU</t>
-        </is>
-      </c>
-      <c r="V132" t="inlineStr"/>
-      <c r="W132" t="inlineStr">
-        <is>
-          <t>ECU to the glove-box POWER box</t>
-        </is>
-      </c>
+          <t>SP-REV</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>ST185-AB-engine w_sw7_e at DRB102-ENGINE 78, to REV-SW 1</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr"/>
       <c r="X132" t="inlineStr"/>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>M8 ring lug on the POWER box battery-negative bar (R216): the ECU grounds only, nothing else | est length; the ONE ECU ground return (DECISIONS R216)</t>
+          <t>Circuit 11: switch out tapped to opto IN2; lamps stay on the factory IG2-13 run.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>w_rev_sw_c</t>
+          <t>w_drain_ecu_a</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>legs of SP-REV</t>
+          <t>legs of SP-SHIELD-A</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -14774,17 +14778,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>DRB102-CABIN</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>SP-REV</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -14794,27 +14798,27 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Reverse sw +12 V out</t>
+          <t>Shield drain</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>J1128-TXL-16-YELLOW</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M133" t="inlineStr"/>
@@ -14826,22 +14830,22 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>0460-202-1631</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>SP-REV - reverse switch out to CSB3 opto IN2 and IG2-13 lamps</t>
+          <t>6 mm behind the ECU-A plug - SP-SHIELD-A: drains to A7</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>DRB102 receptacle (RH firewall)</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>REV</t>
+          <t>SHLD</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
@@ -14851,56 +14855,56 @@
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>SP-REV</t>
-        </is>
-      </c>
-      <c r="V133" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine w_sw7_e at DRB102-ENGINE 78, to REV-SW 1</t>
-        </is>
-      </c>
-      <c r="W133" t="inlineStr"/>
+          <t>SP-SHIELD-A</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr"/>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>at ECU-A plug</t>
+        </is>
+      </c>
       <c r="X133" t="inlineStr"/>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>Circuit 11: switch out tapped to opto IN2; lamps stay on the factory IG2-13 run.</t>
+          <t>build (R30): the crank drain is the one crimped into A7; the other drains are soldered onto it 6 mm behind the plug</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>w_drain_ecu_a</t>
+          <t>w_shd_a_aps</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
+          <t>legs of SP-SHIELD-A-APS</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
           <t>legs of SP-SHIELD-A</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
+      <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>ECU-A</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>trunk</t>
+          <t>link</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -14920,7 +14924,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>450</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -14937,19 +14941,19 @@
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>solder splice</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
+          <t>At the pedal branch - SP-SHIELD-A-APS: pedal drains</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
           <t>6 mm behind the ECU-A plug - SP-SHIELD-A: drains to A7</t>
         </is>
       </c>
-      <c r="R134" t="inlineStr">
-        <is>
-          <t>Link G4X plug A (centre dash)</t>
-        </is>
-      </c>
       <c r="S134" t="inlineStr">
         <is>
           <t>SHLD</t>
@@ -14962,31 +14966,27 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-SHIELD-A-APS / SP-SHIELD-A</t>
         </is>
       </c>
       <c r="V134" t="inlineStr"/>
-      <c r="W134" t="inlineStr">
-        <is>
-          <t>at ECU-A plug</t>
-        </is>
-      </c>
+      <c r="W134" t="inlineStr"/>
       <c r="X134" t="inlineStr"/>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>build (R30): the crank drain is the one crimped into A7; the other drains are soldered onto it 6 mm behind the plug</t>
+          <t>branch-point join (R207): the device drain meets the loom shield trunk where its signal wires join the main loom, then runs to the ECU splice</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>w_shd_a_aps</t>
+          <t>w_shd_a_wsf</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-A-APS</t>
+          <t>legs of SP-SHIELD-A-WSF</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -15006,7 +15006,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
+          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -15031,7 +15031,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>230</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -15053,7 +15053,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>At the pedal branch - SP-SHIELD-A-APS: pedal drains</t>
+          <t>At the front WS inline - SP-SHIELD-A-WSF: front wheel-speed drains</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -15073,7 +15073,7 @@
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-APS / SP-SHIELD-A</t>
+          <t>SP-SHIELD-A-WSF / SP-SHIELD-A</t>
         </is>
       </c>
       <c r="V135" t="inlineStr"/>
@@ -15088,12 +15088,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>w_shd_a_wsf</t>
+          <t>w_drain_ecu_b</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-A-WSF</t>
+          <t>legs of SP-SHIELD-B</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -15103,27 +15103,27 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-A</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
+          <t>SP-SHIELD-B</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>trunk</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Shield drain</t>
+          <t>Shield drain B</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -15155,17 +15155,17 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>solder splice</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>At the front WS inline - SP-SHIELD-A-WSF: front wheel-speed drains</t>
+          <t>6 mm behind the ECU-B plug - SP-SHIELD-B: drains to B17</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>6 mm behind the ECU-A plug - SP-SHIELD-A: drains to A7</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
@@ -15180,52 +15180,48 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-WSF / SP-SHIELD-A</t>
+          <t>SP-SHIELD-B</t>
         </is>
       </c>
       <c r="V136" t="inlineStr"/>
       <c r="W136" t="inlineStr"/>
       <c r="X136" t="inlineStr"/>
-      <c r="Y136" t="inlineStr">
-        <is>
-          <t>branch-point join (R207): the device drain meets the loom shield trunk where its signal wires join the main loom, then runs to the ECU splice</t>
-        </is>
-      </c>
+      <c r="Y136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>w_drain_ecu_b</t>
+          <t>w_shd_b_wsr</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
+          <t>legs of SP-SHIELD-B-WSR</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
           <t>legs of SP-SHIELD-B</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>ECU-B</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B</t>
+          <t>SP-SHIELD-B-WSR &gt; SP-SHIELD-B</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>trunk</t>
+          <t>link</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -15245,7 +15241,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>230</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -15262,19 +15258,19 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>solder splice</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
+          <t>At the rear WS inline - SP-SHIELD-B-WSR: rear wheel-speed drains</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
           <t>6 mm behind the ECU-B plug - SP-SHIELD-B: drains to B17</t>
         </is>
       </c>
-      <c r="R137" t="inlineStr">
-        <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
-        </is>
-      </c>
       <c r="S137" t="inlineStr">
         <is>
           <t>SHLD</t>
@@ -15287,23 +15283,27 @@
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B</t>
+          <t>SP-SHIELD-B-WSR / SP-SHIELD-B</t>
         </is>
       </c>
       <c r="V137" t="inlineStr"/>
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr"/>
-      <c r="Y137" t="inlineStr"/>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>branch-point join (R207): the device drain meets the loom shield trunk where its signal wires join the main loom, then runs to the ECU splice</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>w_shd_b_wsr</t>
+          <t>w78</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-B-WSR</t>
+          <t>legs of SP-SW12</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -15313,7 +15313,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-B</t>
+          <t>legs of SP-A5</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -15323,7 +15323,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B-WSR &gt; SP-SHIELD-B</t>
+          <t>SP-SW12 &gt; SP-A5</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -15333,27 +15333,27 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Shield drain B</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse (+ IG2 wake diode)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>J1128-TXL-18-RED</t>
         </is>
       </c>
       <c r="M138" t="inlineStr"/>
@@ -15370,17 +15370,17 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>At the rear WS inline - SP-SHIELD-B-WSR: rear wheel-speed drains</t>
+          <t>ECU splice point - SP-SW12: switched +12 V (LOGIC SW12)</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>6 mm behind the ECU-B plug - SP-SHIELD-B: drains to B17</t>
+          <t>ECU splice point - SP-A5: ECU main feed (SW12 + IG2 diode)</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>SHLD</t>
+          <t>SW12</t>
         </is>
       </c>
       <c r="T138" t="inlineStr">
@@ -15390,22 +15390,26 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B-WSR / SP-SHIELD-B</t>
+          <t>SP-SW12 / SP-A5</t>
         </is>
       </c>
       <c r="V138" t="inlineStr"/>
-      <c r="W138" t="inlineStr"/>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>at ECU-A plug</t>
+        </is>
+      </c>
       <c r="X138" t="inlineStr"/>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>branch-point join (R207): the device drain meets the loom shield trunk where its signal wires join the main loom, then runs to the ECU splice</t>
+          <t>ECU main +12 V | ECU main +12 V</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>w78</t>
+          <t>w_rail_sp_sw12_c</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -15420,27 +15424,27 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>legs of SP-A5</t>
+          <t>DRB102-CABIN</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>SP-SW12 &gt; SP-A5</t>
+          <t>SP-SW12</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>trunk</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse (+ IG2 wake diode)</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -15455,7 +15459,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -15472,7 +15476,7 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>solder splice</t>
+          <t>0460-202-1631</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
@@ -15482,7 +15486,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>ECU splice point - SP-A5: ECU main feed (SW12 + IG2 diode)</t>
+          <t>DRB102 receptacle (RH firewall)</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
@@ -15497,31 +15501,35 @@
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>SP-SW12 / SP-A5</t>
-        </is>
-      </c>
-      <c r="V139" t="inlineStr"/>
+          <t>SP-SW12</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>ST185-AB-engine w_rail_sp_sw12_e at DRB102-ENGINE 30, to splice SP-SW12-ENG</t>
+        </is>
+      </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>at ECU-A plug</t>
+          <t>trunk ECU-A to bulkhead (RH firewall)</t>
         </is>
       </c>
       <c r="X139" t="inlineStr"/>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>ECU main +12 V | ECU main +12 V</t>
+          <t>+12 V boost + flex | +12 V boost + flex</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>w_rail_sp_sw12_c</t>
+          <t>w_tach</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>legs of SP-SW12</t>
+          <t>legs of SP-TACH</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -15531,17 +15539,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>DRB102-CABIN</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SP-SW12</t>
+          <t>SP-TACH</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -15551,27 +15559,27 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
+          <t>Engine speed (tacho)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>820</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>J1128-TXL-18-RED</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="M140" t="inlineStr"/>
@@ -15583,22 +15591,22 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>0460-202-1631</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>ECU splice point - SP-SW12: switched +12 V (LOGIC SW12)</t>
+          <t>SP-TACH - Ign 8 tacho to A15 pin 18 and 4.7k lock-sensor tap</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>DRB102 receptacle (RH firewall)</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>SW12</t>
+          <t>TACH</t>
         </is>
       </c>
       <c r="T140" t="inlineStr">
@@ -15608,139 +15616,24 @@
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>SP-SW12</t>
-        </is>
-      </c>
-      <c r="V140" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine w_rail_sp_sw12_e at DRB102-ENGINE 30, to splice SP-SW12-ENG</t>
-        </is>
-      </c>
+          <t>SP-TACH</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr"/>
       <c r="W140" t="inlineStr">
         <is>
-          <t>trunk ECU-A to bulkhead (RH firewall)</t>
+          <t>A/C amp branch (behind dash)</t>
         </is>
       </c>
       <c r="X140" t="inlineStr"/>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>+12 V boost + flex | +12 V boost + flex</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>w_tach</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>legs of SP-TACH</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>ECU-B</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>SP-TACH</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>trunk</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Engine speed (tacho)</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>820</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>J1128-TXL-20-WHITE</t>
-        </is>
-      </c>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr">
-        <is>
-          <t>solder splice</t>
-        </is>
-      </c>
-      <c r="P141" t="inlineStr">
-        <is>
-          <t>3-1447221-4</t>
-        </is>
-      </c>
-      <c r="Q141" t="inlineStr">
-        <is>
-          <t>SP-TACH - Ign 8 tacho to A15 pin 18 and 4.7k lock-sensor tap</t>
-        </is>
-      </c>
-      <c r="R141" t="inlineStr">
-        <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
-        </is>
-      </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>TACH</t>
-        </is>
-      </c>
-      <c r="T141" t="inlineStr">
-        <is>
-          <t>ST185-AB-cabin</t>
-        </is>
-      </c>
-      <c r="U141" t="inlineStr">
-        <is>
-          <t>SP-TACH</t>
-        </is>
-      </c>
-      <c r="V141" t="inlineStr"/>
-      <c r="W141" t="inlineStr">
-        <is>
-          <t>A/C amp branch (behind dash)</t>
-        </is>
-      </c>
-      <c r="X141" t="inlineStr"/>
-      <c r="Y141" t="inlineStr">
-        <is>
           <t>Ign 8 (ECU-B 10) tacho. Split at SP-TACH: pin 18 plus 4.7k to pin 9 (OPEN-ITEMS History 2026-10-21 N61).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y141"/>
+  <autoFilter ref="A1:Y140"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16141,10 +16034,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -17573,7 +17466,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -18408,14 +18301,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>w_shc_knock1 (20 AWG), w_shc_etbm (20 AWG), w_shc_vss (20 AWG), w_drain_ecu_b (20 AWG), w_shd_b_wsr (20 AWG)</t>
+          <t>w_shc_knock1 (20 AWG), w_shc_etbm (20 AWG), w_drain_ecu_b (20 AWG), w_shd_b_wsr (20 AWG)</t>
         </is>
       </c>
     </row>
@@ -18662,7 +18555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -19383,7 +19276,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>69</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -19405,7 +19298,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>82</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -19427,7 +19320,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -19449,7 +19342,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -19471,7 +19364,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -19493,7 +19386,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -19515,7 +19408,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -19537,7 +19430,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>91</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -19559,7 +19452,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -19581,7 +19474,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -19603,12 +19496,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>94</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0413-214-1205</t>
+          <t>114017</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -19625,7 +19518,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>97</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -19647,7 +19540,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>98</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -19669,7 +19562,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -19691,7 +19584,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -19713,7 +19606,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -19730,34 +19623,34 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>DRB102-CABIN</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>102</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>0413-214-1205</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>spare, not used</t>
+          <t>spare, sealing plug</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -19779,7 +19672,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -19801,7 +19694,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -19823,7 +19716,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -19845,7 +19738,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -19867,7 +19760,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -19889,7 +19782,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -19911,7 +19804,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -19933,7 +19826,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -19950,49 +19843,71 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>IX-WS-F-S</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>114017</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
+          <t>spare, not used</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>IX-WS-F-S</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>114017</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>IX-WS-R-S</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>114017</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>spare, sealing plug</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D60"/>
+  <autoFilter ref="A1:D61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20082,7 +19997,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Wires: 140   Connectors / ends: 59   Splices: 20   Spare cavities: 59</t>
+          <t>Wires: 139   Connectors / ends: 59   Splices: 20   Spare cavities: 60</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
@@ -4762,7 +4762,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>A/C pressure sw out</t>
+          <t>A/C pressure switch signal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Back-up sw +12 V in</t>
+          <t>+12 V to reverse switch</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -14025,7 +14025,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>A/C pressure sw out</t>
+          <t>A/C pressure switch signal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -14687,7 +14687,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Reverse sw +12 V out</t>
+          <t>Switched +12 V from reverse switch</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -14724,7 +14724,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>SP-REV - reverse switch out to CSB3 opto IN2 and IG2-13 lamps</t>
+          <t>SP-REV - reverse switch signal to CSB3 opto IN2 and IG2-13 lamps</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -17332,7 +17332,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SP-REV - reverse switch out to CSB3 opto IN2 and IG2-13 lamps</t>
+          <t>SP-REV - reverse switch signal to CSB3 opto IN2 and IG2-13 lamps</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -18259,7 +18259,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SP-REV - reverse switch out to CSB3 opto IN2 and IG2-13 lamps</t>
+          <t>SP-REV - reverse switch signal to CSB3 opto IN2 and IG2-13 lamps</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">

--- a/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
@@ -1048,7 +1048,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>core</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1073,11 +1073,19 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-WHITE</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>CAB-CRANK-C</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>55A1821-20-6/9-9</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>3-1447221-4</t>
@@ -1124,7 +1132,11 @@
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>same Spec 55 cable both sides of the firewall (B14, row 171)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2122,7 +2134,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>core</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2132,7 +2144,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2147,11 +2159,19 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-WHITE</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>CAB-ETBS-C</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>55A1841-20-2/4/5/6-9</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
           <t>3-1447221-4</t>
@@ -2198,7 +2218,11 @@
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>same Spec 55 cable both sides of the firewall (B14, row 171); yellow core unused in the cabin: cut back and sealed under heat shrink at both ends</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2546,7 +2570,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>core</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2556,7 +2580,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2571,11 +2595,19 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-WHITE</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>CAB-TURBO-C</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>55A1831-20-2/4/6-9</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
           <t>3-1447221-4</t>
@@ -2622,7 +2654,11 @@
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>same Spec 55 cable both sides of the firewall (B14, row 171)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2653,7 +2689,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>core</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2663,7 +2699,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2678,11 +2714,19 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-WHITE</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>CAB-FLEX-C</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>55A1831-20-2/4/6-9</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
           <t>3-1447221-4</t>
@@ -2729,7 +2773,11 @@
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>same Spec 55 cable both sides of the firewall (B14, row 171); red and yellow cores unused in the cabin: cut back and sealed under heat shrink at both ends</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2863,7 +2911,7 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>core</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2873,7 +2921,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2888,11 +2936,19 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-WHITE</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>CAB-ETBS-C</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>55A1841-20-2/4/5/6-9</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
           <t>3-1447221-4</t>
@@ -2939,7 +2995,11 @@
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>same Spec 55 cable both sides of the firewall (B14, row 171); yellow core unused in the cabin: cut back and sealed under heat shrink at both ends</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3283,7 +3343,7 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>core</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3293,7 +3353,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3308,11 +3368,19 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-WHITE</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>CAB-KNOCK1-C</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>55A1821-20-6/9-9</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
           <t>3-1447221-4</t>
@@ -3355,7 +3423,11 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>same Spec 55 cable both sides of the firewall (B14, row 171)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3695,7 +3767,7 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>core</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3705,7 +3777,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3720,11 +3792,19 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>J1128-TXL-18-WHITE</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>CAB-ETBM-C</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>55A1821-18-2/0-9</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
           <t>3-1447221-3</t>
@@ -3767,7 +3847,11 @@
       </c>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>same Spec 55 cable both sides of the firewall (B14, row 171)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4111,7 +4195,7 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>core</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4121,7 +4205,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4136,11 +4220,19 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>J1128-TXL-18-WHITE</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>CAB-ETBM-C</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>55A1821-18-2/0-9</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr">
         <is>
           <t>3-1447221-3</t>
@@ -4183,7 +4275,11 @@
       </c>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>same Spec 55 cable both sides of the firewall (B14, row 171)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4433,7 +4529,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Ambient temp signal</t>
+          <t>Signal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -5099,7 +5195,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>+5 V pedal sensor 2</t>
+          <t>+5 V (sensor 2)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5214,7 +5310,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Pedal 2 ground</t>
+          <t>Gnd (sensor 2)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5329,7 +5425,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Pedal 2 signal sub</t>
+          <t>Signal 2 (sub)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5444,7 +5540,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>+5 V pedal sensor 1</t>
+          <t>+5 V (sensor 1)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5559,7 +5655,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Pedal 1 ground</t>
+          <t>Gnd (sensor 1)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5674,7 +5770,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Pedal 1 signal main</t>
+          <t>Signal 1 (main)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5784,7 +5880,7 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>core</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5794,7 +5890,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5804,16 +5900,24 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-ORANGE</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>CAB-ETBS-C</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>55A1841-20-2/4/5/6-9</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr">
         <is>
           <t>0462-201-16141</t>
@@ -5860,7 +5964,11 @@
         </is>
       </c>
       <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>same Spec 55 cable both sides of the firewall (B14, row 171); yellow core unused in the cabin: cut back and sealed under heat shrink at both ends</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5998,7 +6106,7 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>core</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6008,7 +6116,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6018,16 +6126,24 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-ORANGE</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>CAB-TURBO-C</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>55A1831-20-2/4/6-9</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr">
         <is>
           <t>0462-201-16141</t>
@@ -6074,7 +6190,11 @@
         </is>
       </c>
       <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>same Spec 55 cable both sides of the firewall (B14, row 171)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6641,7 +6761,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Gnd IAT/TPS/coolant</t>
+          <t>Gnd to intake temp, throttle sensor, coolant temp</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6743,7 +6863,7 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>core</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6763,16 +6883,24 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-BLUE</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>CAB-CRANK-C</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>55A1821-20-6/9-9</t>
+        </is>
+      </c>
       <c r="O59" t="inlineStr">
         <is>
           <t>0462-201-16141</t>
@@ -6819,7 +6947,11 @@
         </is>
       </c>
       <c r="X59" t="inlineStr"/>
-      <c r="Y59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>same Spec 55 cable both sides of the firewall (B14, row 171)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6850,7 +6982,7 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>core</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6860,7 +6992,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6870,16 +7002,24 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-BLUE</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>CAB-CAM-C</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>55A1831-20-2/4/6-9</t>
+        </is>
+      </c>
       <c r="O60" t="inlineStr">
         <is>
           <t>0462-201-16141</t>
@@ -6926,7 +7066,11 @@
         </is>
       </c>
       <c r="X60" t="inlineStr"/>
-      <c r="Y60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>same Spec 55 cable both sides of the firewall (B14, row 171)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6957,7 +7101,7 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>core</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6967,7 +7111,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6977,16 +7121,24 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-BLUE</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>CAB-TURBO-C</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>55A1831-20-2/4/6-9</t>
+        </is>
+      </c>
       <c r="O61" t="inlineStr">
         <is>
           <t>0462-201-16141</t>
@@ -7033,7 +7185,11 @@
         </is>
       </c>
       <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>same Spec 55 cable both sides of the firewall (B14, row 171)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7069,7 +7225,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Gnd flex + MAP</t>
+          <t>Gnd to flex fuel, MAP sensor</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7176,7 +7332,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Gnd oil/clnt/temps</t>
+          <t>Gnd to oil pressure, coolant pressure, oil temp, charge temp</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7283,7 +7439,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Gnd fuel press + VSS</t>
+          <t>Gnd to fuel pressure, gearbox speed</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7722,7 +7878,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>leg core</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7732,14 +7888,10 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
           <t>630</t>
@@ -7747,11 +7899,19 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>CAB-FLEX-C</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>55A1831-20-2/4/6-9</t>
+        </is>
+      </c>
       <c r="O68" t="inlineStr">
         <is>
           <t>0460-202-1631</t>
@@ -7798,7 +7958,11 @@
         </is>
       </c>
       <c r="X68" t="inlineStr"/>
-      <c r="Y68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>cable screen: firewall pin to the shield splice</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7833,7 +7997,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>leg core</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7843,14 +8007,10 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>630</t>
@@ -7858,11 +8018,19 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>CAB-ETBS-C</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>55A1841-20-2/4/5/6-9</t>
+        </is>
+      </c>
       <c r="O69" t="inlineStr">
         <is>
           <t>0460-202-1631</t>
@@ -7909,7 +8077,11 @@
         </is>
       </c>
       <c r="X69" t="inlineStr"/>
-      <c r="Y69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>cable screen: firewall pin to the shield splice</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7944,7 +8116,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>leg core</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7954,14 +8126,10 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>630</t>
@@ -7969,11 +8137,19 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>CAB-ETBM-C</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>55A1821-18-2/0-9</t>
+        </is>
+      </c>
       <c r="O70" t="inlineStr">
         <is>
           <t>0460-202-1631</t>
@@ -8016,7 +8192,11 @@
       </c>
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr"/>
-      <c r="Y70" t="inlineStr"/>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>cable screen: firewall pin to the shield splice</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8051,7 +8231,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>leg core</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8061,14 +8241,10 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>630</t>
@@ -8076,11 +8252,19 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>CAB-TURBO-C</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>55A1831-20-2/4/6-9</t>
+        </is>
+      </c>
       <c r="O71" t="inlineStr">
         <is>
           <t>0460-202-1631</t>
@@ -8127,7 +8311,11 @@
         </is>
       </c>
       <c r="X71" t="inlineStr"/>
-      <c r="Y71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>cable screen: firewall pin to the shield splice</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8162,7 +8350,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>leg core</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8172,7 +8360,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8182,16 +8370,24 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-ORANGE</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>CAB-CAM-C</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>55A1831-20-2/4/6-9</t>
+        </is>
+      </c>
       <c r="O72" t="inlineStr">
         <is>
           <t>0460-202-1631</t>
@@ -8238,7 +8434,11 @@
         </is>
       </c>
       <c r="X72" t="inlineStr"/>
-      <c r="Y72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>same Spec 55 cable both sides of the firewall (B14, row 171)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8273,7 +8473,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>leg core</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8283,7 +8483,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8293,16 +8493,24 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-WHITE</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>CAB-CAM-C</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>55A1831-20-2/4/6-9</t>
+        </is>
+      </c>
       <c r="O73" t="inlineStr">
         <is>
           <t>0460-202-1631</t>
@@ -8349,7 +8557,11 @@
         </is>
       </c>
       <c r="X73" t="inlineStr"/>
-      <c r="Y73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>same Spec 55 cable both sides of the firewall (B14, row 171)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8384,7 +8596,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>leg core</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8394,14 +8606,10 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>630</t>
@@ -8409,11 +8617,19 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>CAB-CAM-C</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>55A1831-20-2/4/6-9</t>
+        </is>
+      </c>
       <c r="O74" t="inlineStr">
         <is>
           <t>0460-202-1631</t>
@@ -8460,7 +8676,11 @@
         </is>
       </c>
       <c r="X74" t="inlineStr"/>
-      <c r="Y74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>cable screen: firewall pin to the shield splice</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8709,7 +8929,7 @@
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>wire</t>
+          <t>core</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -8719,7 +8939,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8729,16 +8949,24 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>630</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-BLUE</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>CAB-KNOCK1-C</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>55A1821-20-6/9-9</t>
+        </is>
+      </c>
       <c r="O77" t="inlineStr">
         <is>
           <t>0460-202-1631</t>
@@ -8785,7 +9013,11 @@
         </is>
       </c>
       <c r="X77" t="inlineStr"/>
-      <c r="Y77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>same Spec 55 cable both sides of the firewall (B14, row 171)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8820,7 +9052,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>leg core</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -8830,14 +9062,10 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
           <t>630</t>
@@ -8845,11 +9073,19 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>CAB-KNOCK1-C</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>55A1821-20-6/9-9</t>
+        </is>
+      </c>
       <c r="O78" t="inlineStr">
         <is>
           <t>0460-202-1631</t>
@@ -8892,7 +9128,11 @@
       </c>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
-      <c r="Y78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>cable screen: firewall pin to the shield splice</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8927,7 +9167,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>leg</t>
+          <t>leg core</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -8937,14 +9177,10 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
           <t>630</t>
@@ -8952,11 +9188,19 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>CAB-CRANK-C</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>55A1821-20-6/9-9</t>
+        </is>
+      </c>
       <c r="O79" t="inlineStr">
         <is>
           <t>0460-202-1631</t>
@@ -9005,7 +9249,7 @@
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>build (R30): this drain is the one crimped into A7</t>
+          <t>build (R30): this drain is the one crimped into A7; cable screen: firewall pin to the shield splice</t>
         </is>
       </c>
     </row>
@@ -9622,7 +9866,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Back-up lamp +12 V</t>
+          <t>+12 V to reverse lamps</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -12959,7 +13203,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Fuel lvl pull-up</t>
+          <t>Fuel level pull-up</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -13054,7 +13298,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>+5 V fuel lvl pullup</t>
+          <t>+5 V to fuel level pull-up</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -13256,7 +13500,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Lock-sensor input (modified tacho)</t>
+          <t>Lock sensor signal (modified tacho)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -14025,7 +14269,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>A/C pressure switch signal</t>
+          <t>Signal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -14140,7 +14384,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Ambient sensor return</t>
+          <t>Gnd</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -14358,7 +14602,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>CSB3 + opto ground</t>
+          <t>Gnd to CSB3, opto board</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -18106,11 +18350,11 @@
         <v>8</v>
       </c>
       <c r="F8" t="n">
-        <v>4.15</v>
+        <v>1.56</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>w_drain_ecu_a (20 AWG), w_shd_a_aps (20 AWG), w_shd_a_wsf (20 AWG), w_shc_crank (20 AWG), w_shc_cam (20 AWG), w_shc_turbo (20 AWG), w_shc_flex (20 AWG), w_shc_etbs (20 AWG)</t>
+          <t>w_drain_ecu_a (20 AWG), w_shd_a_aps (20 AWG), w_shd_a_wsf (20 AWG), w_shc_crank (screen AWG), w_shc_cam (screen AWG), w_shc_turbo (screen AWG), w_shc_flex (screen AWG), w_shc_etbs (screen AWG)</t>
         </is>
       </c>
     </row>
@@ -18304,11 +18548,11 @@
         <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>w_shc_knock1 (20 AWG), w_shc_etbm (20 AWG), w_drain_ecu_b (20 AWG), w_shd_b_wsr (20 AWG)</t>
+          <t>w_shc_knock1 (screen AWG), w_shc_etbm (screen AWG), w_drain_ecu_b (20 AWG), w_shd_b_wsr (20 AWG)</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
+++ b/docs/harness/wirelists/ST185-AB-cabin-wirelist.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wires'!$A$1:$Y$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wires'!$A$1:$Y$141</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Connectors'!$A$1:$I$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Splices'!$A$1:$G$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spare Cavities'!$A$1:$D$61</definedName>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y140"/>
+  <dimension ref="A1:Y141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4367,7 +4367,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>ST185-AntiTheft</t>
+          <t>ST185-AB-cabin</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4380,7 +4380,7 @@
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_at_immob2_bc on ECU-cabin, 120 mm; w_at_immob2 on AntiTheft, 1210 mm)</t>
+          <t>owner proposed: longer half (drawn today as w_at_immob2_bc on ECU-cabin, 120 mm; w_at_immob2 on AntiTheft, 1210 mm); harness ownership (Dan 2026-11-01): was AntiTheft via AB-cabin</t>
         </is>
       </c>
     </row>
@@ -9361,7 +9361,7 @@
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>ST185-AB-engine wc_h_lam_be at DRB102-ENGINE 79, to splice SP-CANH-LAM; SP-CANH also joins ST185-CAN</t>
+          <t>ST185-AB-engine wc_h_lam_be at DRB102-ENGINE 79, to splice SP-CANH-LAM; SP-CANH also joins ST185-CAN, ST185-CSB3</t>
         </is>
       </c>
       <c r="W80" t="inlineStr"/>
@@ -9480,7 +9480,7 @@
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>ST185-AB-engine wc_l_lam_be at DRB102-ENGINE 80, to splice SP-CANL-LAM; SP-CANL also joins ST185-CAN</t>
+          <t>ST185-AB-engine wc_l_lam_be at DRB102-ENGINE 80, to splice SP-CANL-LAM; SP-CANL also joins ST185-CAN, ST185-CSB3</t>
         </is>
       </c>
       <c r="W81" t="inlineStr"/>
@@ -11646,7 +11646,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>ST185-CabinPower</t>
+          <t>ST185-AB-cabin</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -11663,7 +11663,7 @@
       <c r="X101" t="inlineStr"/>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>POWER box (glove box) relay R2 EFI main, pin 85 | owner proposed: longer half (drawn today as w76 on ECU-cabin, 370 mm; w76_cp on CabinPower, 400 mm)</t>
+          <t>POWER box (glove box) relay R2 EFI main, pin 85 | owner proposed: longer half (drawn today as w76 on ECU-cabin, 370 mm; w76_cp on CabinPower, 400 mm); harness ownership (Dan 2026-11-01): was CabinPower via AB-cabin</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>ST185-CabinPower</t>
+          <t>ST185-AB-cabin</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
@@ -11881,7 +11881,7 @@
       <c r="X103" t="inlineStr"/>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) relay M14 ETB power, pin 85 | owner proposed: longer half (drawn today as w81 on ECU-cabin, 380 mm; w81_cp on CabinPower, 400 mm)</t>
+          <t>LOGIC box (glove box) relay M14 ETB power, pin 85 | owner proposed: longer half (drawn today as w81 on ECU-cabin, 380 mm; w81_cp on CabinPower, 400 mm); harness ownership (Dan 2026-11-01): was CabinPower via AB-cabin</t>
         </is>
       </c>
     </row>
@@ -11971,7 +11971,7 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>ST185-CabinPower</t>
+          <t>ST185-AB-cabin</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -11984,7 +11984,7 @@
       <c r="X104" t="inlineStr"/>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w82_ac on CabinPower, 400 mm; w82 on ECU-cabin, 340 mm)</t>
+          <t>owner proposed: longer half (drawn today as w82_ac on CabinPower, 400 mm; w82 on ECU-cabin, 340 mm); harness ownership (Dan 2026-11-01): was CabinPower via AB-cabin</t>
         </is>
       </c>
     </row>
@@ -12391,7 +12391,7 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>ST185-CabinPower</t>
+          <t>ST185-AB-cabin</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -12408,7 +12408,7 @@
       <c r="X108" t="inlineStr"/>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>CAN-Lambda +12 V | CAN-Lambda +12 V | owner proposed: longer half (drawn today as w_lam12_cp on CabinPower, 250 mm; w_lam12_bc on ECU-cabin, 120 mm)</t>
+          <t>CAN-Lambda +12 V | CAN-Lambda +12 V | owner proposed: longer half (drawn today as w_lam12_cp on CabinPower, 250 mm; w_lam12_bc on ECU-cabin, 120 mm); harness ownership (Dan 2026-11-01): was CabinPower via AB-cabin</t>
         </is>
       </c>
     </row>
@@ -12712,7 +12712,7 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>ST185-CabinPower</t>
+          <t>ST185-AB-cabin</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
@@ -12733,7 +12733,7 @@
       <c r="X111" t="inlineStr"/>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) fuse COP 10A | Coil +12 V feed | owner proposed: longer half (drawn today as w_cop_pwr_ac on ECU-cabin, 180 mm; w_cop_pwr_c_ac on CabinPower, 250 mm)</t>
+          <t>LOGIC box (glove box) fuse COP 10A | Coil +12 V feed | owner proposed: longer half (drawn today as w_cop_pwr_ac on ECU-cabin, 180 mm; w_cop_pwr_c_ac on CabinPower, 250 mm); harness ownership (Dan 2026-11-01): was CabinPower via AB-cabin</t>
         </is>
       </c>
     </row>
@@ -12823,7 +12823,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>ST185-CabinPower</t>
+          <t>ST185-AB-cabin</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -12844,7 +12844,7 @@
       <c r="X112" t="inlineStr"/>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) fuse INJ 7.5A | Injector +12 V feed | owner proposed: longer half (drawn today as w_inj_pwr_ac on ECU-cabin, 180 mm; w_inj_pwr_c_ac on CabinPower, 250 mm)</t>
+          <t>LOGIC box (glove box) fuse INJ 7.5A | Injector +12 V feed | owner proposed: longer half (drawn today as w_inj_pwr_ac on ECU-cabin, 180 mm; w_inj_pwr_c_ac on CabinPower, 250 mm); harness ownership (Dan 2026-11-01): was CabinPower via AB-cabin</t>
         </is>
       </c>
     </row>
@@ -13683,89 +13683,85 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>cab_aps1_sh</t>
+          <t>w_strl_c</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>NC, floats</t>
+          <t>RB4</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>DRB102-CABIN</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>drain</t>
+          <t>wire</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Pedal 1 cable shield</t>
+          <t>Starter solenoid S</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Shield</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr"/>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>(cable core)</t>
-        </is>
-      </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>CAB-APS1</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>55A1831-20-2/4/6-9</t>
-        </is>
-      </c>
-      <c r="O121" t="inlineStr"/>
+          <t>J1128-TXL-12-RED</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>crimp butt splice into the factory lead</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-A-APS</t>
+          <t>0460-220-1231</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>cab_aps1 screen (floats at the device end)</t>
+          <t>OEM R/B No.4 starter relay pin 4 (RH kick), starter out</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
+          <t>DRB102 receptacle (RH firewall)</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
@@ -13775,26 +13771,30 @@
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-APS</t>
-        </is>
-      </c>
-      <c r="V121" t="inlineStr"/>
-      <c r="W121" t="inlineStr">
-        <is>
-          <t>at ECU-A plug</t>
-        </is>
-      </c>
-      <c r="X121" t="inlineStr"/>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>ST185-AB-engine w_strl_e at DRB102-ENGINE 3, to STARTER-TRIGGER 1</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr"/>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>R/B No.4 starter relay pin 4, RH kick; OEM colour B; EWD 1993 p.66; crimp butt splice into the factory lead at R/B No.4 pin 4</t>
+        </is>
+      </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>Screen floats at this end: cut back and seal under heat-shrink | screen floats at the far end; pedal branch length estimated from OEM body dimensions + 10 % (990 mm ECU-A</t>
+          <t>OEM starter relay output (was EB1-2). New wire to the starter S terminal. | (firewall bulkhead, RH) | Starter S crosses the firewall on its own DRB102 size-12 cavity (Dan 2026-10-27); 12 AWG: the DRB size-12 contact takes 12-14 AWG, solenoid S draw is brief, OEM lead is lighter; harness ownership (Dan 2026-11-01): was CabinPower</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>cab_aps_sh</t>
+          <t>cab_aps1_sh</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -13829,7 +13829,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Pedal 2 cable shield</t>
+          <t>Pedal 1 cable shield</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -13850,7 +13850,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>CAB-APS2</t>
+          <t>CAB-APS1</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>cab_aps2 screen (floats at the device end)</t>
+          <t>cab_aps1 screen (floats at the device end)</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -13905,7 +13905,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>cab_fspur_fr_sh_ac</t>
+          <t>cab_aps_sh</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -13930,7 +13930,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
+          <t>SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>FR wheel spd shield</t>
+          <t>Pedal 2 cable shield</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -13951,7 +13951,7 @@
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>840</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -13961,33 +13961,33 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>CAB-FSPUR-FR-AC</t>
+          <t>CAB-APS2</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>55A1811-20-9-9CS2275</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>solder splice SP-SHIELD-A-WSF</t>
+          <t>solder splice SP-SHIELD-A-APS</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>cab_fspur_fr_ac screen (floats at the device end)</t>
+          <t>cab_aps2 screen (floats at the device end)</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>via SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
+          <t>via SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>WSSF</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
@@ -13997,36 +13997,36 @@
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-WSF</t>
+          <t>SP-SHIELD-A-APS</t>
         </is>
       </c>
       <c r="V123" t="inlineStr"/>
       <c r="W123" t="inlineStr">
         <is>
-          <t>dash branch (front WS inline)</t>
+          <t>at ECU-A plug</t>
         </is>
       </c>
       <c r="X123" t="inlineStr"/>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>Screen floats at this end: cut back and seal under heat-shrink | tied at the A end only; the far (B) end floats, dressed back at the ECU-B plug (no A-B shield bridge)</t>
+          <t>Screen floats at this end: cut back and seal under heat-shrink | screen floats at the far end; pedal branch length estimated from OEM body dimensions + 10 % (990 mm ECU-A</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>w19</t>
+          <t>cab_fspur_fr_sh_ac</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>legs of SP-8V</t>
+          <t>NC, floats</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -14036,69 +14036,69 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SP-8V</t>
+          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>trunk</t>
+          <t>drain</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>+8 V sensor supply</t>
+          <t>FR wheel spd shield</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Orange</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>500</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-ORANGE</t>
-        </is>
-      </c>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr">
-        <is>
-          <t>solder splice</t>
-        </is>
-      </c>
+          <t>(cable core)</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>CAB-FSPUR-FR-AC</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>55A1811-20-9-9CS2275</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>solder splice SP-SHIELD-A-WSF</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>ECU splice point - SP-8V: +8 V supply, cam sensor + gearbox speed sensor only (ECU A6)</t>
+          <t>cab_fspur_fr_ac screen (floats at the device end)</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>via SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>8V</t>
+          <t>WSSF</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
@@ -14108,27 +14108,31 @@
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>SP-8V</t>
+          <t>SP-SHIELD-A-WSF</t>
         </is>
       </c>
       <c r="V124" t="inlineStr"/>
       <c r="W124" t="inlineStr">
         <is>
-          <t>at ECU-A plug</t>
+          <t>dash branch (front WS inline)</t>
         </is>
       </c>
       <c r="X124" t="inlineStr"/>
-      <c r="Y124" t="inlineStr"/>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>Screen floats at this end: cut back and seal under heat-shrink | tied at the A end only; the far (B) end floats, dressed back at the ECU-B plug (no A-B shield bridge)</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>w_a5_pin</t>
+          <t>w19</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>legs of SP-A5</t>
+          <t>legs of SP-8V</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -14143,12 +14147,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>SP-A5</t>
+          <t>SP-8V</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -14158,17 +14162,17 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse (+ IG2 wake diode)</t>
+          <t>+8 V sensor supply</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -14178,7 +14182,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>J1128-TXL-18-RED</t>
+          <t>J1128-TXL-20-ORANGE</t>
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
@@ -14190,12 +14194,12 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>3-1447221-3</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>ECU splice point - SP-A5: ECU main feed (SW12 + IG2 diode)</t>
+          <t>ECU splice point - SP-8V: +8 V supply, cam sensor + gearbox speed sensor only (ECU A6)</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -14205,7 +14209,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>SW12</t>
+          <t>8V</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
@@ -14215,7 +14219,7 @@
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>SP-A5</t>
+          <t>SP-8V</t>
         </is>
       </c>
       <c r="V125" t="inlineStr"/>
@@ -14225,21 +14229,17 @@
         </is>
       </c>
       <c r="X125" t="inlineStr"/>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>ECU main +12 V | ECU main +12 V</t>
-        </is>
-      </c>
+      <c r="Y125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>w_ac_psw_in</t>
+          <t>w_a5_pin</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>legs of SP-AC-PSW</t>
+          <t>legs of SP-A5</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -14249,17 +14249,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SP-AC-PSW</t>
+          <t>SP-A5</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -14269,27 +14269,27 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Signal</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse (+ IG2 wake diode)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>310</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>J1128-TXL-18-RED</t>
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
@@ -14301,22 +14301,22 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t xml:space="preserve">new-wire run terminated at the switch's </t>
+          <t>3-1447221-3</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>At A/C amp - SP-AC-PSW: A/C pressure switch output</t>
+          <t>ECU splice point - SP-A5: ECU main feed (SW12 + IG2 diode)</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>OEM A5, factory Y-R lead</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>SW12</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
@@ -14326,35 +14326,31 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>SP-AC-PSW</t>
+          <t>SP-A5</t>
         </is>
       </c>
       <c r="V126" t="inlineStr"/>
       <c r="W126" t="inlineStr">
         <is>
-          <t>A/C amp branch (behind dash)</t>
-        </is>
-      </c>
-      <c r="X126" t="inlineStr">
-        <is>
-          <t>A/C pressure switch A5, engine bay; exact spot TBD (no locator figure in the repo); OEM colour Y-R (factory wiring; new wire here); EWD 1990 ST185 EWD p.152 (docs/electrical/ewd-snips/1990-st185-autoac-pressure-clutch-p152.png); 1990 ST185 EWD p.152 (A5 pin 4 Y-R); new-wire run terminated at the switch's own mating plug (no factory engine-bay wire reused, Section 39, 2026-10-04); plug part number not yet chosen</t>
-        </is>
-      </c>
+          <t>at ECU-A plug</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr"/>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>Runs on in ST185-EngineRoom-C to A/C pressure switch A5 pin 4 (engine bay): new wire to the switch's own mating plug, plug part TBD. EWD 1990 p.152. | owner TBD: a half has no length estimate (drawn today as w_ac_psw_in on ECU-cabin, ? mm; w_ac_psw on EngineRoom-C, 100 mm)</t>
+          <t>ECU main +12 V | ECU main +12 V</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>w_amb_rtn</t>
+          <t>w_ac_psw_in</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>legs of SP-AC-SG</t>
+          <t>legs of SP-AC-PSW</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -14364,17 +14360,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>SP-AC-SG</t>
+          <t>SP-AC-PSW</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -14384,7 +14380,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Gnd</t>
+          <t>Signal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -14399,12 +14395,12 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-YELLOW</t>
+          <t>M22759/16-20-4</t>
         </is>
       </c>
       <c r="M127" t="inlineStr"/>
@@ -14416,22 +14412,22 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t xml:space="preserve">new-wire run terminated at the sensor's </t>
+          <t xml:space="preserve">new-wire run terminated at the switch's </t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>SP-AC-SG - cabin A/C sensor common (replaces E10; A32-15, A24-3, A21, A18-2 stay factory)</t>
+          <t>At A/C amp - SP-AC-PSW: A/C pressure switch output</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>OEM ambient air temp sensor A1 pin 1 (front, 6 in pigtail)</t>
+          <t>OEM A5, factory Y-R lead</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>AMB</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
@@ -14441,31 +14437,35 @@
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>SP-AC-SG</t>
+          <t>SP-AC-PSW</t>
         </is>
       </c>
       <c r="V127" t="inlineStr"/>
-      <c r="W127" t="inlineStr"/>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>A/C amp branch (behind dash)</t>
+        </is>
+      </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>Ambient air temp sensor A1 pin 1 (6 in pigtail, B9); OEM colour Y; EWD 1993 p.211; new-wire run terminated at the sensor's own mating plug; 6 in OEM pigtail stays</t>
+          <t>A/C pressure switch A5, engine bay; exact spot TBD (no locator figure in the repo); OEM colour Y-R (factory wiring; new wire here); EWD 1990 ST185 EWD p.152 (docs/electrical/ewd-snips/1990-st185-autoac-pressure-clutch-p152.png); 1990 ST185 EWD p.152 (A5 pin 4 Y-R); new-wire run terminated at the switch's own mating plug (no factory engine-bay wire reused, Section 39, 2026-10-04); plug part number not yet chosen</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>Row 164: E10 sensor-common dies under B9. Cabin splice SP-AC-SG kept. Factory Y-R is the A/C pressure-switch output (A5-4 through joiner E10 to A18-13), not sensor ground; sensor common is Y (1990 ST185 EWD p.150 / p.152).</t>
+          <t>Runs on in ST185-EngineRoom-C to A/C pressure switch A5 pin 4 (engine bay): new wire to the switch's own mating plug, plug part TBD. EWD 1990 p.152. | owner TBD: a half has no length estimate (drawn today as w_ac_psw_in on ECU-cabin, ? mm; w_ac_psw on EngineRoom-C, 100 mm)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>w_trig2_pin</t>
+          <t>w_amb_rtn</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>legs of SP-CAM</t>
+          <t>legs of SP-AC-SG</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -14475,17 +14475,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SP-CAM</t>
+          <t>SP-AC-SG</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -14495,12 +14495,12 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Cam sensor signal</t>
+          <t>Gnd</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14510,12 +14510,12 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-WHITE</t>
+          <t>J1128-TXL-20-YELLOW</t>
         </is>
       </c>
       <c r="M128" t="inlineStr"/>
@@ -14527,22 +14527,22 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t xml:space="preserve">new-wire run terminated at the sensor's </t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>At the ECU plugs - SP-CAM: cam signal + 1.8k pull-up to +8V</t>
+          <t>SP-AC-SG - cabin A/C sensor common (replaces E10; A32-15, A24-3, A21, A18-2 stay factory)</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>OEM ambient air temp sensor A1 pin 1 (front, 6 in pigtail)</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>CAM</t>
+          <t>AMB</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
@@ -14552,27 +14552,31 @@
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>SP-CAM</t>
+          <t>SP-AC-SG</t>
         </is>
       </c>
       <c r="V128" t="inlineStr"/>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>at ECU-A plug</t>
-        </is>
-      </c>
-      <c r="X128" t="inlineStr"/>
-      <c r="Y128" t="inlineStr"/>
+      <c r="W128" t="inlineStr"/>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>Ambient air temp sensor A1 pin 1 (6 in pigtail, B9); OEM colour Y; EWD 1993 p.211; new-wire run terminated at the sensor's own mating plug; 6 in OEM pigtail stays</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>Row 164: E10 sensor-common dies under B9. Cabin splice SP-AC-SG kept. Factory Y-R is the A/C pressure-switch output (A5-4 through joiner E10 to A18-13), not sensor ground; sensor common is Y (1990 ST185 EWD p.150 / p.152).</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>w_csbg_ac</t>
+          <t>w_trig2_pin</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>legs of SP-CSB-GND</t>
+          <t>legs of SP-CAM</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -14582,17 +14586,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>POWER-NEG-BAR</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Lug</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>SP-CSB-GND</t>
+          <t>SP-CAM</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -14602,12 +14606,12 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Gnd to CSB3, opto board</t>
+          <t>Cam sensor signal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14617,12 +14621,12 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>310</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-BLACK</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="M129" t="inlineStr"/>
@@ -14634,22 +14638,22 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>CSB3 ground splice - CSB3 pin 2, opto board COM and stalk ground</t>
+          <t>At the ECU plugs - SP-CAM: cam signal + 1.8k pull-up to +8V</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>POWER box NEG bar M8 stud (glove box)</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>CAM</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
@@ -14659,35 +14663,27 @@
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>SP-CSB-GND</t>
-        </is>
-      </c>
-      <c r="V129" t="inlineStr">
-        <is>
-          <t>SP-CSB-GND also joins ST185-CSB3</t>
-        </is>
-      </c>
+          <t>SP-CAM</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr"/>
       <c r="W129" t="inlineStr">
         <is>
-          <t>glove-box POWER box to the CSB3 branch</t>
+          <t>at ECU-A plug</t>
         </is>
       </c>
       <c r="X129" t="inlineStr"/>
-      <c r="Y129" t="inlineStr">
-        <is>
-          <t>M8 ring lug on the POWER box battery-negative bar (R213: CSB3, opto board and cruise ladder never on chassis or the ECU ground) | (CSB3 loom, under centre cluster) | est length; runs with the CSB3 +12 V (w_csb12, LOGIC CSB 5A) (R217)</t>
-        </is>
-      </c>
+      <c r="Y129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>w_fl_sig_pin</t>
+          <t>w_csbg_ac</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>legs of SP-FUEL-LVL</t>
+          <t>legs of SP-CSB-GND</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -14697,17 +14693,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>POWER-NEG-BAR</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Lug</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>SP-FUEL-LVL</t>
+          <t>SP-CSB-GND</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -14717,12 +14713,12 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Fuel level signal</t>
+          <t>Gnd to CSB3, opto board</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14732,12 +14728,12 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-WHITE</t>
+          <t>J1128-TXL-20-BLACK</t>
         </is>
       </c>
       <c r="M130" t="inlineStr"/>
@@ -14749,22 +14745,22 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>SP-FUEL-LVL - fuel sender signal + 470R pull-up to ECU-B B24</t>
+          <t>CSB3 ground splice - CSB3 pin 2, opto board COM and stalk ground</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>POWER box NEG bar M8 stud (glove box)</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>FLVL</t>
+          <t>CSB</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
@@ -14774,23 +14770,35 @@
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>SP-FUEL-LVL</t>
-        </is>
-      </c>
-      <c r="V130" t="inlineStr"/>
-      <c r="W130" t="inlineStr"/>
+          <t>SP-CSB-GND</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>SP-CSB-GND also joins ST185-CSB3</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>glove-box POWER box to the CSB3 branch</t>
+        </is>
+      </c>
       <c r="X130" t="inlineStr"/>
-      <c r="Y130" t="inlineStr"/>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>M8 ring lug on the POWER box battery-negative bar (R213: CSB3, opto board and cruise ladder never on chassis or the ECU ground) | (CSB3 loom, under centre cluster) | est length; runs with the CSB3 +12 V (w_csb12, LOGIC CSB 5A) (R217)</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>w66</t>
+          <t>w_fl_sig_pin</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>legs of SP-GND-ECU</t>
+          <t>legs of SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -14800,17 +14808,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>POWER-NEG-BAR</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Lug</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>SP-GND-ECU</t>
+          <t>SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -14820,27 +14828,27 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>ECU power ground</t>
+          <t>Fuel level signal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>White</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>310</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>J1128-TXL-10-BLACK</t>
+          <t>J1128-TXL-20-WHITE</t>
         </is>
       </c>
       <c r="M131" t="inlineStr"/>
@@ -14852,22 +14860,22 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>ECU splice point - SP-GND-ECU: ECU power ground (A25 A34 B25 B34) to the NEG bar</t>
+          <t>SP-FUEL-LVL - fuel sender signal + 470R pull-up to ECU-B B24</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>POWER box NEG bar M8 stud (glove box)</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>GND</t>
+          <t>FLVL</t>
         </is>
       </c>
       <c r="T131" t="inlineStr">
@@ -14877,31 +14885,23 @@
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>SP-GND-ECU</t>
+          <t>SP-FUEL-LVL</t>
         </is>
       </c>
       <c r="V131" t="inlineStr"/>
-      <c r="W131" t="inlineStr">
-        <is>
-          <t>ECU to the glove-box POWER box</t>
-        </is>
-      </c>
+      <c r="W131" t="inlineStr"/>
       <c r="X131" t="inlineStr"/>
-      <c r="Y131" t="inlineStr">
-        <is>
-          <t>M8 ring lug on the POWER box battery-negative bar (R216): the ECU grounds only, nothing else | est length; the ONE ECU ground return (DECISIONS R216)</t>
-        </is>
-      </c>
+      <c r="Y131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>w_rev_sw_c</t>
+          <t>w66</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>legs of SP-REV</t>
+          <t>legs of SP-GND-ECU</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -14911,17 +14911,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>DRB102-CABIN</t>
+          <t>POWER-NEG-BAR</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>Lug</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>SP-REV</t>
+          <t>SP-GND-ECU</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -14931,27 +14931,27 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Switched +12 V from reverse switch</t>
+          <t>ECU power ground</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>570</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>J1128-TXL-16-YELLOW</t>
+          <t>J1128-TXL-10-BLACK</t>
         </is>
       </c>
       <c r="M132" t="inlineStr"/>
@@ -14963,22 +14963,22 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>0460-202-1631</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>SP-REV - reverse switch signal to CSB3 opto IN2 and IG2-13 lamps</t>
+          <t>ECU splice point - SP-GND-ECU: ECU power ground (A25 A34 B25 B34) to the NEG bar</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>DRB102 receptacle (RH firewall)</t>
+          <t>POWER box NEG bar M8 stud (glove box)</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>REV</t>
+          <t>GND</t>
         </is>
       </c>
       <c r="T132" t="inlineStr">
@@ -14988,31 +14988,31 @@
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>SP-REV</t>
-        </is>
-      </c>
-      <c r="V132" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine w_sw7_e at DRB102-ENGINE 78, to REV-SW 1</t>
-        </is>
-      </c>
-      <c r="W132" t="inlineStr"/>
+          <t>SP-GND-ECU</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr"/>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>ECU to the glove-box POWER box</t>
+        </is>
+      </c>
       <c r="X132" t="inlineStr"/>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>Circuit 11: switch out tapped to opto IN2; lamps stay on the factory IG2-13 run.</t>
+          <t>M8 ring lug on the POWER box battery-negative bar (R216): the ECU grounds only, nothing else | est length; the ONE ECU ground return (DECISIONS R216)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>w_drain_ecu_a</t>
+          <t>w_rev_sw_c</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-A</t>
+          <t>legs of SP-REV</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -15022,17 +15022,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>DRB102-CABIN</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
+          <t>SP-REV</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -15042,27 +15042,27 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Shield drain</t>
+          <t>Switched +12 V from reverse switch</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>J1128-TXL-16-YELLOW</t>
         </is>
       </c>
       <c r="M133" t="inlineStr"/>
@@ -15074,22 +15074,22 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>0460-202-1631</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>6 mm behind the ECU-A plug - SP-SHIELD-A: drains to A7</t>
+          <t>SP-REV - reverse switch signal to CSB3 opto IN2 and IG2-13 lamps</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>Link G4X plug A (centre dash)</t>
+          <t>DRB102 receptacle (RH firewall)</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>SHLD</t>
+          <t>REV</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
@@ -15099,31 +15099,31 @@
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A</t>
-        </is>
-      </c>
-      <c r="V133" t="inlineStr"/>
-      <c r="W133" t="inlineStr">
-        <is>
-          <t>at ECU-A plug</t>
-        </is>
-      </c>
+          <t>SP-REV</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>ST185-AB-engine w_sw7_e at DRB102-ENGINE 78, to REV-SW 1</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr"/>
       <c r="X133" t="inlineStr"/>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>build (R30): the crank drain is the one crimped into A7; the other drains are soldered onto it 6 mm behind the plug</t>
+          <t>Circuit 11: switch out tapped to opto IN2; lamps stay on the factory IG2-13 run.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>w_shd_a_aps</t>
+          <t>w_drain_ecu_a</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-A-APS</t>
+          <t>legs of SP-SHIELD-A</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -15133,22 +15133,22 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-A</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>trunk</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -15168,7 +15168,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -15185,17 +15185,17 @@
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>solder splice</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>At the pedal branch - SP-SHIELD-A-APS: pedal drains</t>
+          <t>6 mm behind the ECU-A plug - SP-SHIELD-A: drains to A7</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>6 mm behind the ECU-A plug - SP-SHIELD-A: drains to A7</t>
+          <t>Link G4X plug A (centre dash)</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
@@ -15210,27 +15210,31 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-APS / SP-SHIELD-A</t>
+          <t>SP-SHIELD-A</t>
         </is>
       </c>
       <c r="V134" t="inlineStr"/>
-      <c r="W134" t="inlineStr"/>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>at ECU-A plug</t>
+        </is>
+      </c>
       <c r="X134" t="inlineStr"/>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>branch-point join (R207): the device drain meets the loom shield trunk where its signal wires join the main loom, then runs to the ECU splice</t>
+          <t>build (R30): the crank drain is the one crimped into A7; the other drains are soldered onto it 6 mm behind the plug</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>w_shd_a_wsf</t>
+          <t>w_shd_a_aps</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-A-WSF</t>
+          <t>legs of SP-SHIELD-A-APS</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -15250,7 +15254,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
+          <t>SP-SHIELD-A-APS &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -15275,7 +15279,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>450</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -15297,7 +15301,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>At the front WS inline - SP-SHIELD-A-WSF: front wheel-speed drains</t>
+          <t>At the pedal branch - SP-SHIELD-A-APS: pedal drains</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -15317,7 +15321,7 @@
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>SP-SHIELD-A-WSF / SP-SHIELD-A</t>
+          <t>SP-SHIELD-A-APS / SP-SHIELD-A</t>
         </is>
       </c>
       <c r="V135" t="inlineStr"/>
@@ -15332,12 +15336,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>w_drain_ecu_b</t>
+          <t>w_shd_a_wsf</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-B</t>
+          <t>legs of SP-SHIELD-A-WSF</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -15347,27 +15351,27 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>legs of SP-SHIELD-A</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B</t>
+          <t>SP-SHIELD-A-WSF &gt; SP-SHIELD-A</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>trunk</t>
+          <t>link</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Shield drain B</t>
+          <t>Shield drain</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -15382,7 +15386,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>230</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -15399,17 +15403,17 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>solder splice</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>6 mm behind the ECU-B plug - SP-SHIELD-B: drains to B17</t>
+          <t>At the front WS inline - SP-SHIELD-A-WSF: front wheel-speed drains</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>6 mm behind the ECU-A plug - SP-SHIELD-A: drains to A7</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
@@ -15424,23 +15428,27 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B</t>
+          <t>SP-SHIELD-A-WSF / SP-SHIELD-A</t>
         </is>
       </c>
       <c r="V136" t="inlineStr"/>
       <c r="W136" t="inlineStr"/>
       <c r="X136" t="inlineStr"/>
-      <c r="Y136" t="inlineStr"/>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>branch-point join (R207): the device drain meets the loom shield trunk where its signal wires join the main loom, then runs to the ECU splice</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>w_shd_b_wsr</t>
+          <t>w_drain_ecu_b</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-B-WSR</t>
+          <t>legs of SP-SHIELD-B</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -15450,22 +15458,22 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>legs of SP-SHIELD-B</t>
+          <t>ECU-B</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B-WSR &gt; SP-SHIELD-B</t>
+          <t>SP-SHIELD-B</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>trunk</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -15485,7 +15493,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -15502,17 +15510,17 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>solder splice</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>At the rear WS inline - SP-SHIELD-B-WSR: rear wheel-speed drains</t>
+          <t>6 mm behind the ECU-B plug - SP-SHIELD-B: drains to B17</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>6 mm behind the ECU-B plug - SP-SHIELD-B: drains to B17</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
@@ -15527,27 +15535,23 @@
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>SP-SHIELD-B-WSR / SP-SHIELD-B</t>
+          <t>SP-SHIELD-B</t>
         </is>
       </c>
       <c r="V137" t="inlineStr"/>
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr"/>
-      <c r="Y137" t="inlineStr">
-        <is>
-          <t>branch-point join (R207): the device drain meets the loom shield trunk where its signal wires join the main loom, then runs to the ECU splice</t>
-        </is>
-      </c>
+      <c r="Y137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>w78</t>
+          <t>w_shd_b_wsr</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>legs of SP-SW12</t>
+          <t>legs of SP-SHIELD-B-WSR</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -15557,7 +15561,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>legs of SP-A5</t>
+          <t>legs of SP-SHIELD-B</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -15567,7 +15571,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>SP-SW12 &gt; SP-A5</t>
+          <t>SP-SHIELD-B-WSR &gt; SP-SHIELD-B</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -15577,27 +15581,27 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse (+ IG2 wake diode)</t>
+          <t>Shield drain B</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>230</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>J1128-TXL-18-RED</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="M138" t="inlineStr"/>
@@ -15614,17 +15618,17 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>ECU splice point - SP-SW12: switched +12 V (LOGIC SW12)</t>
+          <t>At the rear WS inline - SP-SHIELD-B-WSR: rear wheel-speed drains</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>ECU splice point - SP-A5: ECU main feed (SW12 + IG2 diode)</t>
+          <t>6 mm behind the ECU-B plug - SP-SHIELD-B: drains to B17</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>SW12</t>
+          <t>SHLD</t>
         </is>
       </c>
       <c r="T138" t="inlineStr">
@@ -15634,26 +15638,22 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>SP-SW12 / SP-A5</t>
+          <t>SP-SHIELD-B-WSR / SP-SHIELD-B</t>
         </is>
       </c>
       <c r="V138" t="inlineStr"/>
-      <c r="W138" t="inlineStr">
-        <is>
-          <t>at ECU-A plug</t>
-        </is>
-      </c>
+      <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr"/>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>ECU main +12 V | ECU main +12 V</t>
+          <t>branch-point join (R207): the device drain meets the loom shield trunk where its signal wires join the main loom, then runs to the ECU splice</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>w_rail_sp_sw12_c</t>
+          <t>w78</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -15668,27 +15668,27 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>DRB102-CABIN</t>
+          <t>legs of SP-A5</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>SP-SW12</t>
+          <t>SP-SW12 &gt; SP-A5</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>trunk</t>
+          <t>link</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse (+ IG2 wake diode)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -15703,7 +15703,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>200</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -15720,7 +15720,7 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>0460-202-1631</t>
+          <t>solder splice</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
@@ -15730,7 +15730,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>DRB102 receptacle (RH firewall)</t>
+          <t>ECU splice point - SP-A5: ECU main feed (SW12 + IG2 diode)</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
@@ -15745,35 +15745,31 @@
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>SP-SW12</t>
-        </is>
-      </c>
-      <c r="V139" t="inlineStr">
-        <is>
-          <t>ST185-AB-engine w_rail_sp_sw12_e at DRB102-ENGINE 30, to splice SP-SW12-ENG</t>
-        </is>
-      </c>
+          <t>SP-SW12 / SP-A5</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr"/>
       <c r="W139" t="inlineStr">
         <is>
-          <t>trunk ECU-A to bulkhead (RH firewall)</t>
+          <t>at ECU-A plug</t>
         </is>
       </c>
       <c r="X139" t="inlineStr"/>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>+12 V boost + flex | +12 V boost + flex</t>
+          <t>ECU main +12 V | ECU main +12 V</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>w_tach</t>
+          <t>w_rail_sp_sw12_c</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>legs of SP-TACH</t>
+          <t>legs of SP-SW12</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -15783,17 +15779,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ECU-B</t>
+          <t>DRB102-CABIN</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SP-TACH</t>
+          <t>SP-SW12</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -15803,27 +15799,27 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Engine speed (tacho)</t>
+          <t>EFI relay k_efi -&gt; LOGIC SW12 5 A fuse</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>J1128-TXL-20-WHITE</t>
+          <t>J1128-TXL-18-RED</t>
         </is>
       </c>
       <c r="M140" t="inlineStr"/>
@@ -15835,22 +15831,22 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>0460-202-1631</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>SP-TACH - Ign 8 tacho to A15 pin 18 and 4.7k lock-sensor tap</t>
+          <t>ECU splice point - SP-SW12: switched +12 V (LOGIC SW12)</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>DRB102 receptacle (RH firewall)</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>TACH</t>
+          <t>SW12</t>
         </is>
       </c>
       <c r="T140" t="inlineStr">
@@ -15860,24 +15856,139 @@
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>SP-TACH</t>
-        </is>
-      </c>
-      <c r="V140" t="inlineStr"/>
+          <t>SP-SW12</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>ST185-AB-engine w_rail_sp_sw12_e at DRB102-ENGINE 30, to splice SP-SW12-ENG</t>
+        </is>
+      </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>A/C amp branch (behind dash)</t>
+          <t>trunk ECU-A to bulkhead (RH firewall)</t>
         </is>
       </c>
       <c r="X140" t="inlineStr"/>
       <c r="Y140" t="inlineStr">
         <is>
+          <t>+12 V boost + flex | +12 V boost + flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>w_tach</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>legs of SP-TACH</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>ECU-B</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>SP-TACH</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>trunk</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Engine speed (tacho)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>J1128-TXL-20-WHITE</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>solder splice</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>3-1447221-4</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>SP-TACH - Ign 8 tacho to A15 pin 18 and 4.7k lock-sensor tap</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>TACH</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>ST185-AB-cabin</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>SP-TACH</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr"/>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>A/C amp branch (behind dash)</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr"/>
+      <c r="Y141" t="inlineStr">
+        <is>
           <t>Ign 8 (ECU-B 10) tacho. Split at SP-TACH: pin 18 plus 4.7k to pin 9 (OPEN-ITEMS History 2026-10-21 N61).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y140"/>
+  <autoFilter ref="A1:Y141"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16278,7 +16389,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H9" t="n">
         <v>37</v>
@@ -17144,11 +17255,11 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>solder onto the factory lead</t>
+          <t>crimp butt splice into the factory lead, solder onto the factory lead</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -20241,7 +20352,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Wires: 139   Connectors / ends: 59   Splices: 20   Spare cavities: 60</t>
+          <t>Wires: 140   Connectors / ends: 59   Splices: 20   Spare cavities: 60</t>
         </is>
       </c>
     </row>
